--- a/database/event/2956/event_2956_evp_summary.xlsx
+++ b/database/event/2956/event_2956_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7913</v>
+        <v>8.051</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4416</v>
+        <v>3.5563</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7262</v>
+        <v>2.7636</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7913</v>
+        <v>8.051</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3173</v>
+        <v>4.577</v>
       </c>
       <c r="G2" t="n">
         <v>3.474</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8091</v>
+        <v>5.8537</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8979</v>
+        <v>4.7446</v>
       </c>
       <c r="J2" t="n">
         <v>3.474</v>
@@ -529,7 +529,7 @@
         <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3719</v>
+        <v>8.2186</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.853</v>
+        <v>7.1675</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0271</v>
+        <v>3.166</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3471</v>
+        <v>2.4116</v>
       </c>
       <c r="E3" t="n">
-        <v>6.853</v>
+        <v>7.1675</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1468</v>
+        <v>4.4613</v>
       </c>
       <c r="G3" t="n">
         <v>2.7062</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1468</v>
+        <v>5.3882</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3611</v>
+        <v>4.3673</v>
       </c>
       <c r="J3" t="n">
         <v>2.7062</v>
@@ -575,7 +575,7 @@
         <v>199</v>
       </c>
       <c r="M3" t="n">
-        <v>6.067299999999999</v>
+        <v>7.0735</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0702</v>
+        <v>5.6167</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2396</v>
+        <v>2.481</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6269</v>
+        <v>1.7938</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0702</v>
+        <v>5.6167</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5247</v>
+        <v>2.8723</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5455</v>
+        <v>2.7444</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5247</v>
+        <v>2.8723</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0464</v>
+        <v>2.3281</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5455</v>
+        <v>2.7444</v>
       </c>
       <c r="K4" t="n">
         <v>118</v>
@@ -621,7 +621,7 @@
         <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>4.591900000000001</v>
+        <v>5.0725</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -630,323 +630,323 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0322</v>
+        <v>5.6124</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2228</v>
+        <v>2.4791</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6115</v>
+        <v>1.7921</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0322</v>
+        <v>5.6124</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6323</v>
+        <v>3.0669</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3999</v>
+        <v>2.5455</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6323</v>
+        <v>3.0669</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6399</v>
+        <v>2.4858</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3999</v>
+        <v>2.5455</v>
       </c>
       <c r="K5" t="n">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="L5" t="n">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0398</v>
+        <v>5.0313</v>
       </c>
       <c r="N5" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8161</v>
+        <v>5.5862</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1274</v>
+        <v>2.4675</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5242</v>
+        <v>1.7816</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8161</v>
+        <v>5.5862</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0717</v>
+        <v>2.1863</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7444</v>
+        <v>3.3999</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0717</v>
+        <v>2.1863</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6792</v>
+        <v>2.2047</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7444</v>
+        <v>3.3999</v>
       </c>
       <c r="K6" t="n">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="L6" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4236</v>
+        <v>5.6046</v>
       </c>
       <c r="N6" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3744</v>
+        <v>4.8506</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9323</v>
+        <v>2.1426</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3458</v>
+        <v>1.4886</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3744</v>
+        <v>4.8506</v>
       </c>
       <c r="F7" t="n">
-        <v>2.798</v>
+        <v>1.941</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5763</v>
+        <v>2.9096</v>
       </c>
       <c r="H7" t="n">
-        <v>2.798</v>
+        <v>1.941</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8111</v>
+        <v>1.5733</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5763</v>
+        <v>2.9096</v>
       </c>
       <c r="K7" t="n">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="L7" t="n">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3874</v>
+        <v>4.4829</v>
       </c>
       <c r="N7" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3449</v>
+        <v>4.7128</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9192</v>
+        <v>2.0817</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3339</v>
+        <v>1.4337</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3449</v>
+        <v>4.7128</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4353</v>
+        <v>3.1365</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9096</v>
+        <v>1.5763</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4353</v>
+        <v>3.1365</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1634</v>
+        <v>3.1629</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9096</v>
+        <v>1.5763</v>
       </c>
       <c r="K8" t="n">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="L8" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>4.073</v>
+        <v>4.7392</v>
       </c>
       <c r="N8" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8795</v>
+        <v>4.4467</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7136</v>
+        <v>1.9642</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1459</v>
+        <v>1.3277</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8795</v>
+        <v>4.4467</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0325</v>
+        <v>3.1052</v>
       </c>
       <c r="G9" t="n">
-        <v>1.847</v>
+        <v>1.3415</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0325</v>
+        <v>3.1052</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6474</v>
+        <v>3.1052</v>
       </c>
       <c r="J9" t="n">
-        <v>1.847</v>
+        <v>1.3415</v>
       </c>
       <c r="K9" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="L9" t="n">
-        <v>199</v>
+        <v>89</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4944</v>
+        <v>4.4467</v>
       </c>
       <c r="N9" t="n">
-        <v>323</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4438</v>
+        <v>3.9259</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5212</v>
+        <v>1.7341</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9699</v>
+        <v>1.1202</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4438</v>
+        <v>3.9259</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1789</v>
+        <v>2.0789</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2648</v>
+        <v>1.847</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1789</v>
+        <v>2.0789</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1844</v>
+        <v>1.685</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2648</v>
+        <v>1.847</v>
       </c>
       <c r="K10" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L10" t="n">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4492</v>
+        <v>3.532</v>
       </c>
       <c r="N10" t="n">
-        <v>249</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3638</v>
+        <v>3.7924</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4859</v>
+        <v>1.6752</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9375</v>
+        <v>1.067</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3638</v>
+        <v>3.7924</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0223</v>
+        <v>3.7924</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3415</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0223</v>
+        <v>3.7924</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0223</v>
+        <v>3.7924</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3415</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L11" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3638</v>
+        <v>3.7924</v>
       </c>
       <c r="N11" t="n">
-        <v>232</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2033</v>
+        <v>3.5396</v>
       </c>
       <c r="C12" t="n">
-        <v>1.415</v>
+        <v>1.5635</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8727</v>
+        <v>0.9663</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2033</v>
+        <v>3.5396</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8418</v>
+        <v>2.1781</v>
       </c>
       <c r="G12" t="n">
         <v>1.3615</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8418</v>
+        <v>2.1781</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4928</v>
+        <v>1.7654</v>
       </c>
       <c r="J12" t="n">
         <v>1.3615</v>
@@ -989,7 +989,7 @@
         <v>169</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8543</v>
+        <v>3.1269</v>
       </c>
       <c r="N12" t="n">
         <v>287</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7175</v>
+        <v>3.5167</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2004</v>
+        <v>1.5534</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6764</v>
+        <v>0.9571</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7175</v>
+        <v>3.5167</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3379</v>
+        <v>1.2519</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3796</v>
+        <v>2.2648</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3379</v>
+        <v>1.2519</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3441</v>
+        <v>1.2624</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3796</v>
+        <v>2.2648</v>
       </c>
       <c r="K13" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="L13" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7237</v>
+        <v>3.5272</v>
       </c>
       <c r="N13" t="n">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5489</v>
+        <v>3.1338</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1259</v>
+        <v>1.3843</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6083</v>
+        <v>0.8046</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5489</v>
+        <v>3.1338</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5489</v>
+        <v>1.7542</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.3796</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5489</v>
+        <v>1.7542</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5489</v>
+        <v>1.769</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.3796</v>
       </c>
       <c r="K14" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5489</v>
+        <v>3.1486</v>
       </c>
       <c r="N14" t="n">
-        <v>143</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3249</v>
+        <v>3.0282</v>
       </c>
       <c r="C15" t="n">
-        <v>1.027</v>
+        <v>1.3376</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5178</v>
+        <v>0.7625</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3249</v>
+        <v>3.0282</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7135</v>
+        <v>3.0282</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3886</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7135</v>
+        <v>3.0282</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1993</v>
+        <v>3.0282</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3886</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="L15" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8107</v>
+        <v>3.0282</v>
       </c>
       <c r="N15" t="n">
-        <v>323</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1705</v>
+        <v>2.9074</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9587</v>
+        <v>1.2843</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4555</v>
+        <v>0.7144</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1705</v>
+        <v>2.9074</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1705</v>
+        <v>1.6559</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.2514</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1705</v>
+        <v>1.6559</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1705</v>
+        <v>1.6699</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.2514</v>
       </c>
       <c r="K16" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1705</v>
+        <v>2.9213</v>
       </c>
       <c r="N16" t="n">
-        <v>137</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9619</v>
+        <v>2.8985</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8666</v>
+        <v>1.2803</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3712</v>
+        <v>0.7109</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9619</v>
+        <v>2.8985</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9619</v>
+        <v>2.8985</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9619</v>
+        <v>2.8985</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9619</v>
+        <v>2.8985</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9619</v>
+        <v>2.8985</v>
       </c>
       <c r="N17" t="n">
         <v>151</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8955</v>
+        <v>2.8859</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8373</v>
+        <v>1.2748</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3444</v>
+        <v>0.7058</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8955</v>
+        <v>2.8859</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8955</v>
+        <v>3.2745</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.3886</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8955</v>
+        <v>3.2745</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9043</v>
+        <v>2.654</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.3886</v>
       </c>
       <c r="K18" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9043</v>
+        <v>2.2654</v>
       </c>
       <c r="N18" t="n">
-        <v>144</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8444</v>
+        <v>2.5555</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8147</v>
+        <v>1.1288</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3237</v>
+        <v>0.5742</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8444</v>
+        <v>2.5555</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8444</v>
+        <v>2.5555</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8444</v>
+        <v>2.5555</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8444</v>
+        <v>2.5555</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8444</v>
+        <v>2.5555</v>
       </c>
       <c r="N19" t="n">
         <v>148</v>
@@ -1320,231 +1320,231 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7849</v>
+        <v>2.143</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7884</v>
+        <v>0.9466</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2997</v>
+        <v>0.4099</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7849</v>
+        <v>2.143</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5335</v>
+        <v>2.143</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2514</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5335</v>
+        <v>2.143</v>
       </c>
       <c r="I20" t="n">
-        <v>0.536</v>
+        <v>2.161</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2514</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="L20" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7874</v>
+        <v>2.161</v>
       </c>
       <c r="N20" t="n">
-        <v>249</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.777</v>
+        <v>1.8598</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7849</v>
+        <v>0.8215</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2965</v>
+        <v>0.297</v>
       </c>
       <c r="E21" t="n">
-        <v>1.777</v>
+        <v>1.8598</v>
       </c>
       <c r="F21" t="n">
-        <v>1.777</v>
+        <v>1.8598</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.777</v>
+        <v>1.8598</v>
       </c>
       <c r="I21" t="n">
-        <v>1.777</v>
+        <v>1.8754</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.777</v>
+        <v>1.8754</v>
       </c>
       <c r="N21" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4328</v>
+        <v>1.8265</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6329</v>
+        <v>0.8068</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1575</v>
+        <v>0.2838</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4328</v>
+        <v>1.8265</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4328</v>
+        <v>1.9459</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.1194</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4328</v>
+        <v>1.9459</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4328</v>
+        <v>1.9459</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.1194</v>
       </c>
       <c r="K22" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4328</v>
+        <v>1.8265</v>
       </c>
       <c r="N22" t="n">
-        <v>148</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2925</v>
+        <v>1.7815</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5709</v>
+        <v>0.7869</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1008</v>
+        <v>0.2658</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2925</v>
+        <v>1.7815</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2925</v>
+        <v>1.7815</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2925</v>
+        <v>1.7815</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2985</v>
+        <v>1.7815</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2985</v>
+        <v>1.7815</v>
       </c>
       <c r="N23" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2669</v>
+        <v>1.7639</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5596</v>
+        <v>0.7791</v>
       </c>
       <c r="D24" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.2588</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2669</v>
+        <v>1.7639</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3863</v>
+        <v>1.7639</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1194</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3863</v>
+        <v>1.7639</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3863</v>
+        <v>1.7639</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1194</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L24" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2669</v>
+        <v>1.7639</v>
       </c>
       <c r="N24" t="n">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2164</v>
+        <v>1.6226</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5373</v>
+        <v>0.7167</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2025</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2164</v>
+        <v>1.6226</v>
       </c>
       <c r="F25" t="n">
-        <v>1.29</v>
+        <v>1.6962</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0736</v>
       </c>
       <c r="H25" t="n">
-        <v>1.29</v>
+        <v>1.6962</v>
       </c>
       <c r="I25" t="n">
-        <v>1.296</v>
+        <v>1.7105</v>
       </c>
       <c r="J25" t="n">
         <v>-0.0736</v>
@@ -1587,7 +1587,7 @@
         <v>135</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2224</v>
+        <v>1.6369</v>
       </c>
       <c r="N25" t="n">
         <v>249</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8698</v>
+        <v>1.4994</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3842</v>
+        <v>0.6623</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1535</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8698</v>
+        <v>1.4994</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8698</v>
+        <v>1.4994</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8698</v>
+        <v>1.4994</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8739</v>
+        <v>1.512</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8739</v>
+        <v>1.512</v>
       </c>
       <c r="N26" t="n">
         <v>144</v>
@@ -1642,323 +1642,323 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8181</v>
+        <v>1.2921</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3614</v>
+        <v>0.5707</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.0709</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8181</v>
+        <v>1.2921</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8181</v>
+        <v>1.6138</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.3217</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8181</v>
+        <v>1.6138</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8181</v>
+        <v>1.6274</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.3217</v>
       </c>
       <c r="K27" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8181</v>
+        <v>1.3057</v>
       </c>
       <c r="N27" t="n">
-        <v>137</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7655</v>
+        <v>1.1286</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3381</v>
+        <v>0.4985</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1121</v>
+        <v>0.0057</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7655</v>
+        <v>1.1286</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1581</v>
+        <v>1.1286</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6074000000000001</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1581</v>
+        <v>1.1286</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1589</v>
+        <v>1.1286</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6074000000000001</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="L28" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7663000000000001</v>
+        <v>1.1286</v>
       </c>
       <c r="N28" t="n">
-        <v>284</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.1221</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3048</v>
+        <v>0.4957</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1426</v>
+        <v>0.0031</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.1221</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9655</v>
+        <v>1.1221</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2755</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9655</v>
+        <v>1.1221</v>
       </c>
       <c r="I29" t="n">
-        <v>0.97</v>
+        <v>1.1221</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2755</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="L29" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6944999999999999</v>
+        <v>1.1221</v>
       </c>
       <c r="N29" t="n">
-        <v>249</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.9969</v>
       </c>
       <c r="C30" t="n">
-        <v>0.275</v>
+        <v>0.4403</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1699</v>
+        <v>-0.0467</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.9969</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6225000000000001</v>
+        <v>1.4683</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4714</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6225000000000001</v>
+        <v>1.4683</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6225000000000001</v>
+        <v>1.4807</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4714</v>
       </c>
       <c r="K30" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6225000000000001</v>
+        <v>1.0093</v>
       </c>
       <c r="N30" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6072</v>
+        <v>0.9054</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2682</v>
+        <v>0.3999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1761</v>
+        <v>-0.0832</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6072</v>
+        <v>0.9054</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0786</v>
+        <v>0.298</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4714</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0786</v>
+        <v>0.298</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0836</v>
+        <v>0.3005</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4714</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6121999999999999</v>
+        <v>0.9079</v>
       </c>
       <c r="N31" t="n">
-        <v>166</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5778</v>
+        <v>0.803</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2552</v>
+        <v>0.3547</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1879</v>
+        <v>-0.124</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5778</v>
+        <v>0.803</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8995</v>
+        <v>1.0785</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.3217</v>
+        <v>-0.2755</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8995</v>
+        <v>1.0785</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9036999999999999</v>
+        <v>1.0876</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3217</v>
+        <v>-0.2755</v>
       </c>
       <c r="K32" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L32" t="n">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="M32" t="n">
-        <v>0.582</v>
+        <v>0.8120999999999998</v>
       </c>
       <c r="N32" t="n">
-        <v>166</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3718</v>
+        <v>0.7887</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1642</v>
+        <v>0.3484</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2712</v>
+        <v>-0.1297</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3718</v>
+        <v>0.7887</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5014</v>
+        <v>0.7887</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1296</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5014</v>
+        <v>0.7887</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4064</v>
+        <v>0.7887</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1296</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="L33" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2768</v>
+        <v>0.7887</v>
       </c>
       <c r="N33" t="n">
-        <v>287</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3128</v>
+        <v>0.5421</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1382</v>
+        <v>0.2395</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.295</v>
+        <v>-0.2279</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3128</v>
+        <v>0.5421</v>
       </c>
       <c r="F34" t="n">
-        <v>0.994</v>
+        <v>1.2233</v>
       </c>
       <c r="G34" t="n">
         <v>-0.6812</v>
       </c>
       <c r="H34" t="n">
-        <v>0.994</v>
+        <v>1.2233</v>
       </c>
       <c r="I34" t="n">
-        <v>0.994</v>
+        <v>1.2233</v>
       </c>
       <c r="J34" t="n">
         <v>-0.6812</v>
@@ -2001,7 +2001,7 @@
         <v>89</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3128</v>
+        <v>0.5421</v>
       </c>
       <c r="N34" t="n">
         <v>232</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2768</v>
+        <v>0.5377</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1223</v>
+        <v>0.2375</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3095</v>
+        <v>-0.2297</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2768</v>
+        <v>0.5377</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2768</v>
+        <v>0.6673</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.1296</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2768</v>
+        <v>0.6673</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2768</v>
+        <v>0.5409</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.1296</v>
       </c>
       <c r="K35" t="n">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2768</v>
+        <v>0.4113000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>137</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.256</v>
+        <v>0.3403</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1131</v>
+        <v>0.1503</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3179</v>
+        <v>-0.3083</v>
       </c>
       <c r="E36" t="n">
-        <v>0.256</v>
+        <v>0.3403</v>
       </c>
       <c r="F36" t="n">
-        <v>0.256</v>
+        <v>0.3403</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.256</v>
+        <v>0.3403</v>
       </c>
       <c r="I36" t="n">
-        <v>0.256</v>
+        <v>0.3403</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.256</v>
+        <v>0.3403</v>
       </c>
       <c r="N36" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2326</v>
+        <v>0.3196</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1027</v>
+        <v>0.1412</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3274</v>
+        <v>-0.3166</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2326</v>
+        <v>0.3196</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2326</v>
+        <v>0.3196</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2326</v>
+        <v>0.3196</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2326</v>
+        <v>0.3196</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2326</v>
+        <v>0.3196</v>
       </c>
       <c r="N37" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1957</v>
+        <v>0.2931</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0864</v>
+        <v>0.1295</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3423</v>
+        <v>-0.3271</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1957</v>
+        <v>0.2931</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1957</v>
+        <v>0.2931</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1957</v>
+        <v>0.2931</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1957</v>
+        <v>0.2931</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1957</v>
+        <v>0.2931</v>
       </c>
       <c r="N38" t="n">
         <v>143</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1029</v>
+        <v>0.1861</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0455</v>
+        <v>0.0822</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3798</v>
+        <v>-0.3698</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1029</v>
+        <v>0.1861</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1029</v>
+        <v>0.1861</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1029</v>
+        <v>0.1861</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1029</v>
+        <v>0.1861</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1029</v>
+        <v>0.1861</v>
       </c>
       <c r="N39" t="n">
         <v>137</v>
@@ -2250,7 +2250,7 @@
         <v>-0.0057</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4266</v>
+        <v>-0.4491</v>
       </c>
       <c r="E40" t="n">
         <v>-0.013</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0216</v>
+        <v>-0.0215</v>
       </c>
       <c r="C41" t="n">
         <v>-0.0095</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4301</v>
+        <v>-0.4525</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0216</v>
+        <v>-0.0215</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0216</v>
+        <v>-0.0215</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0216</v>
+        <v>-0.0215</v>
       </c>
       <c r="I41" t="n">
         <v>-0.0217</v>
@@ -2332,308 +2332,308 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tsogoo</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1383</v>
+        <v>-0.1074</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0611</v>
+        <v>-0.0474</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4772</v>
+        <v>-0.4867</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1383</v>
+        <v>-0.1074</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1383</v>
+        <v>0.3452</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.4526</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1383</v>
+        <v>0.3452</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1383</v>
+        <v>0.3481</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.4526</v>
       </c>
       <c r="K42" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1383</v>
+        <v>-0.1045</v>
       </c>
       <c r="N42" t="n">
-        <v>118</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>zonic</t>
+          <t>Tsogoo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.3956</v>
+        <v>-0.1383</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1747</v>
+        <v>-0.0611</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5812</v>
+        <v>-0.499</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.3956</v>
+        <v>-0.1383</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.3956</v>
+        <v>-0.1383</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.3956</v>
+        <v>-0.1383</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3956</v>
+        <v>-0.1383</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.3956</v>
+        <v>-0.1383</v>
       </c>
       <c r="N43" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.532</v>
+        <v>-0.2566</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.235</v>
+        <v>-0.1133</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6363</v>
+        <v>-0.5461</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.532</v>
+        <v>-0.2566</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.532</v>
+        <v>-0.2566</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.532</v>
+        <v>-0.2566</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.532</v>
+        <v>-0.2566</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.532</v>
+        <v>-0.2566</v>
       </c>
       <c r="N44" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>zonic</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.6132</v>
+        <v>-0.3956</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2709</v>
+        <v>-0.1747</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6691</v>
+        <v>-0.6015</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.6132</v>
+        <v>-0.3956</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.6132</v>
+        <v>-0.3956</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.6132</v>
+        <v>-0.3956</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6132</v>
+        <v>-0.3956</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>151</v>
+        <v>27</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.6132</v>
+        <v>-0.3956</v>
       </c>
       <c r="N45" t="n">
-        <v>151</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Zilkenberg</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.631</v>
+        <v>-0.4369</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2787</v>
+        <v>-0.193</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6763</v>
+        <v>-0.618</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.631</v>
+        <v>-0.4369</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.631</v>
+        <v>0.1323</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.5692</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.631</v>
+        <v>0.1323</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.631</v>
+        <v>0.1323</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.5692</v>
       </c>
       <c r="K46" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.631</v>
+        <v>-0.4369000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>118</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.6955</v>
+        <v>-0.4862</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3072</v>
+        <v>-0.2148</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.7023</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6955</v>
+        <v>-0.4862</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6955</v>
+        <v>-0.4862</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6955</v>
+        <v>-0.4862</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6987</v>
+        <v>-0.4862</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6987</v>
+        <v>-0.4862</v>
       </c>
       <c r="N47" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6967</v>
+        <v>-0.532</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3077</v>
+        <v>-0.235</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7028</v>
+        <v>-0.6559</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6967</v>
+        <v>-0.532</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.6967</v>
+        <v>-0.532</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6967</v>
+        <v>-0.532</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6967</v>
+        <v>-0.532</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.6967</v>
+        <v>-0.532</v>
       </c>
       <c r="N48" t="n">
         <v>143</v>
@@ -2654,369 +2654,369 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Zilkenberg</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.631</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.3128</v>
+        <v>-0.2787</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7075</v>
+        <v>-0.6953</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.631</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2556</v>
+        <v>-0.631</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.4526</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2556</v>
+        <v>-0.631</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2568</v>
+        <v>-0.631</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.4526</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L49" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.7094</v>
+        <v>-0.631</v>
       </c>
       <c r="N49" t="n">
-        <v>166</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machinegun</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7341</v>
+        <v>-0.6567</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.3243</v>
+        <v>-0.2901</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7179</v>
+        <v>-0.7055</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.7341</v>
+        <v>-0.6567</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.7341</v>
+        <v>-0.6567</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.7341</v>
+        <v>-0.6567</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7341</v>
+        <v>-0.6622</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.7341</v>
+        <v>-0.6622</v>
       </c>
       <c r="N50" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fitch</t>
+          <t>Machinegun</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7554</v>
+        <v>-0.7341</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.3337</v>
+        <v>-0.3243</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7265</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.7554</v>
+        <v>-0.7341</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3201</v>
+        <v>-0.7341</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.4353</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3201</v>
+        <v>-0.7341</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3201</v>
+        <v>-0.7341</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.4353</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="L51" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.7554000000000001</v>
+        <v>-0.7341</v>
       </c>
       <c r="N51" t="n">
-        <v>232</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>fitch</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.8923</v>
+        <v>-0.7554</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3941</v>
+        <v>-0.3337</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7449</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.8923</v>
+        <v>-0.7554</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.4011</v>
+        <v>-0.3201</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4912</v>
+        <v>-0.4353</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.4011</v>
+        <v>-0.3201</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.403</v>
+        <v>-0.3201</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.4912</v>
+        <v>-0.4353</v>
       </c>
       <c r="K52" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.8942000000000001</v>
+        <v>-0.7554000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>166</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9664</v>
+        <v>-0.7653</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4269</v>
+        <v>-0.338</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8118</v>
+        <v>-0.7488</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.9664</v>
+        <v>-0.7653</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.9664</v>
+        <v>-0.2741</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.4912</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.9664</v>
+        <v>-0.2741</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9664</v>
+        <v>-0.2764</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.4912</v>
       </c>
       <c r="K53" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.9664</v>
+        <v>-0.7676000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.9867</v>
+        <v>-0.9664</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4358</v>
+        <v>-0.4269</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.82</v>
+        <v>-0.8289</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.9867</v>
+        <v>-0.9664</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.9867</v>
+        <v>-0.9664</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9867</v>
+        <v>-0.9664</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.9867</v>
+        <v>-0.9664</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.9867</v>
+        <v>-0.9664</v>
       </c>
       <c r="N54" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.9932</v>
+        <v>-0.9867</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4387</v>
+        <v>-0.4358</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8226</v>
+        <v>-0.837</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.9932</v>
+        <v>-0.9867</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.424</v>
+        <v>-0.9867</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.5692</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.424</v>
+        <v>-0.9867</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.424</v>
+        <v>-0.9867</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.5692</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L55" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.9932000000000001</v>
+        <v>-0.9867</v>
       </c>
       <c r="N55" t="n">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.4101</v>
+        <v>-1.0788</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.6229</v>
+        <v>-0.4765</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.991</v>
+        <v>-0.8737</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.4101</v>
+        <v>-1.0788</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.0328</v>
+        <v>-0.0788</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6227</v>
+        <v>-1</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.0328</v>
+        <v>-0.0788</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.0423</v>
+        <v>-0.0795</v>
       </c>
       <c r="J56" t="n">
-        <v>0.6227</v>
+        <v>-1</v>
       </c>
       <c r="K56" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="L56" t="n">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.4196</v>
+        <v>-1.0795</v>
       </c>
       <c r="N56" t="n">
-        <v>284</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.421</v>
+        <v>-1.3638</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.6277</v>
+        <v>-0.6024</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9954</v>
+        <v>-0.9872</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.421</v>
+        <v>-1.3638</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.421</v>
+        <v>-1.3638</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.421</v>
+        <v>-1.3638</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.421</v>
+        <v>-1.3638</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.421</v>
+        <v>-1.3638</v>
       </c>
       <c r="N57" t="n">
         <v>143</v>
@@ -3068,47 +3068,47 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.5412</v>
+        <v>-1.4026</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.6808</v>
+        <v>-0.6196</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.044</v>
+        <v>-1.0027</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.5412</v>
+        <v>-1.4026</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5412</v>
+        <v>-2.0253</v>
       </c>
       <c r="G58" t="n">
-        <v>-1</v>
+        <v>0.6227</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5412</v>
+        <v>-2.0253</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5437</v>
+        <v>-2.0423</v>
       </c>
       <c r="J58" t="n">
-        <v>-1</v>
+        <v>0.6227</v>
       </c>
       <c r="K58" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="L58" t="n">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.5437</v>
+        <v>-1.4196</v>
       </c>
       <c r="N58" t="n">
-        <v>166</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59">
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.5899</v>
+        <v>-1.5838</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.7023</v>
+        <v>-0.6996</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.0636</v>
+        <v>-1.0749</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.5899</v>
+        <v>-1.5838</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.6443</v>
+        <v>-1.6382</v>
       </c>
       <c r="G59" t="n">
         <v>0.0544</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.6443</v>
+        <v>-1.6382</v>
       </c>
       <c r="I59" t="n">
         <v>-1.652</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.3068</v>
+        <v>-2.0653</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.019</v>
+        <v>-0.9123</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.3533</v>
+        <v>-1.2667</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.3068</v>
+        <v>-2.0653</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.7983</v>
+        <v>-1.5568</v>
       </c>
       <c r="G60" t="n">
         <v>-0.5085</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.7983</v>
+        <v>-1.5568</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.4576</v>
+        <v>-1.2618</v>
       </c>
       <c r="J60" t="n">
         <v>-0.5085</v>
@@ -3197,7 +3197,7 @@
         <v>199</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.9661</v>
+        <v>-1.7703</v>
       </c>
       <c r="N60" t="n">
         <v>323</v>
@@ -3216,7 +3216,7 @@
         <v>-1.1216</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4471</v>
+        <v>-1.4555</v>
       </c>
       <c r="E61" t="n">
         <v>-2.5392</v>
@@ -3262,7 +3262,7 @@
         <v>-1.2028</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.5214</v>
+        <v>-1.5288</v>
       </c>
       <c r="E62" t="n">
         <v>-2.723</v>

--- a/database/event/2956/event_2956_evp_summary.xlsx
+++ b/database/event/2956/event_2956_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.051</v>
+        <v>7.4663</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5563</v>
+        <v>3.298</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7636</v>
+        <v>2.7326</v>
       </c>
       <c r="E2" t="n">
-        <v>8.051</v>
+        <v>7.4663</v>
       </c>
       <c r="F2" t="n">
-        <v>4.577</v>
+        <v>4.195</v>
       </c>
       <c r="G2" t="n">
-        <v>3.474</v>
+        <v>3.2713</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8537</v>
+        <v>9.2941</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7446</v>
+        <v>4.8325</v>
       </c>
       <c r="J2" t="n">
-        <v>3.474</v>
+        <v>3.2713</v>
       </c>
       <c r="K2" t="n">
         <v>124</v>
@@ -529,7 +529,7 @@
         <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2186</v>
+        <v>8.1038</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1675</v>
+        <v>6.2423</v>
       </c>
       <c r="C3" t="n">
-        <v>3.166</v>
+        <v>2.7573</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4116</v>
+        <v>2.1801</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1675</v>
+        <v>6.2423</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4613</v>
+        <v>3.7628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7062</v>
+        <v>2.4795</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3882</v>
+        <v>7.7714</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3673</v>
+        <v>4.0408</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7062</v>
+        <v>2.4795</v>
       </c>
       <c r="K3" t="n">
         <v>124</v>
@@ -575,7 +575,7 @@
         <v>199</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0735</v>
+        <v>6.5203</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6167</v>
+        <v>5.4437</v>
       </c>
       <c r="C4" t="n">
-        <v>2.481</v>
+        <v>2.4046</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7938</v>
+        <v>1.8195</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6167</v>
+        <v>5.4437</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8723</v>
+        <v>2.804</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7444</v>
+        <v>2.6397</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8723</v>
+        <v>4.3933</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3281</v>
+        <v>2.2843</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7444</v>
+        <v>2.6397</v>
       </c>
       <c r="K4" t="n">
         <v>118</v>
@@ -621,7 +621,7 @@
         <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0725</v>
+        <v>4.923999999999999</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6124</v>
+        <v>5.3571</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4791</v>
+        <v>2.3663</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7921</v>
+        <v>1.7804</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6124</v>
+        <v>5.3571</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0669</v>
+        <v>2.9703</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5455</v>
+        <v>2.3868</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0669</v>
+        <v>4.9791</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4858</v>
+        <v>2.5889</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5455</v>
+        <v>2.3868</v>
       </c>
       <c r="K5" t="n">
         <v>118</v>
@@ -667,7 +667,7 @@
         <v>169</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0313</v>
+        <v>4.9757</v>
       </c>
       <c r="N5" t="n">
         <v>287</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5862</v>
+        <v>4.9195</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4675</v>
+        <v>2.173</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7816</v>
+        <v>1.5829</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5862</v>
+        <v>4.9195</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1863</v>
+        <v>2.4083</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3999</v>
+        <v>2.5112</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1863</v>
+        <v>2.9992</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2047</v>
+        <v>1.5594</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3999</v>
+        <v>2.5112</v>
       </c>
       <c r="K6" t="n">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="L6" t="n">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="M6" t="n">
-        <v>5.6046</v>
+        <v>4.0706</v>
       </c>
       <c r="N6" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8506</v>
+        <v>4.6593</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1426</v>
+        <v>2.0581</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4886</v>
+        <v>1.4654</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8506</v>
+        <v>4.6593</v>
       </c>
       <c r="F7" t="n">
-        <v>1.941</v>
+        <v>2.0683</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9096</v>
+        <v>2.591</v>
       </c>
       <c r="H7" t="n">
-        <v>1.941</v>
+        <v>2.0683</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5733</v>
+        <v>2.1534</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9096</v>
+        <v>2.591</v>
       </c>
       <c r="K7" t="n">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="L7" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4829</v>
+        <v>4.744400000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7128</v>
+        <v>4.4908</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0817</v>
+        <v>1.9837</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4337</v>
+        <v>1.3894</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7128</v>
+        <v>4.4908</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1365</v>
+        <v>2.9542</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5763</v>
+        <v>1.5366</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1365</v>
+        <v>3.1272</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1629</v>
+        <v>3.2558</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5763</v>
+        <v>1.5366</v>
       </c>
       <c r="K8" t="n">
         <v>162</v>
@@ -805,7 +805,7 @@
         <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7392</v>
+        <v>4.7924</v>
       </c>
       <c r="N8" t="n">
         <v>284</v>
@@ -814,185 +814,185 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4467</v>
+        <v>4.4851</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9642</v>
+        <v>1.9812</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3277</v>
+        <v>1.3868</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4467</v>
+        <v>4.4851</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1052</v>
+        <v>2.5956</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3415</v>
+        <v>1.8895</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1052</v>
+        <v>3.659</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1052</v>
+        <v>1.9025</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3415</v>
+        <v>1.8895</v>
       </c>
       <c r="K9" t="n">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4467</v>
+        <v>3.792</v>
       </c>
       <c r="N9" t="n">
-        <v>232</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9259</v>
+        <v>4.1048</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7341</v>
+        <v>1.8132</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1202</v>
+        <v>1.2151</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9259</v>
+        <v>4.1048</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0789</v>
+        <v>2.6774</v>
       </c>
       <c r="G10" t="n">
-        <v>1.847</v>
+        <v>1.4274</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0789</v>
+        <v>3.9473</v>
       </c>
       <c r="I10" t="n">
-        <v>1.685</v>
+        <v>2.0524</v>
       </c>
       <c r="J10" t="n">
-        <v>1.847</v>
+        <v>1.4274</v>
       </c>
       <c r="K10" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L10" t="n">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="M10" t="n">
-        <v>3.532</v>
+        <v>3.4798</v>
       </c>
       <c r="N10" t="n">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7924</v>
+        <v>4.0971</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6752</v>
+        <v>1.8098</v>
       </c>
       <c r="D11" t="n">
-        <v>1.067</v>
+        <v>1.2116</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7924</v>
+        <v>4.0971</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7924</v>
+        <v>2.9053</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.1918</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7924</v>
+        <v>3.0198</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7924</v>
+        <v>3.0198</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.1918</v>
       </c>
       <c r="K11" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7924</v>
+        <v>4.2116</v>
       </c>
       <c r="N11" t="n">
-        <v>137</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5396</v>
+        <v>3.2678</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5635</v>
+        <v>1.4434</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9663</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5396</v>
+        <v>3.2678</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1781</v>
+        <v>3.2678</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3615</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1781</v>
+        <v>3.8158</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7654</v>
+        <v>3.8158</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3615</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="L12" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1269</v>
+        <v>3.8158</v>
       </c>
       <c r="N12" t="n">
-        <v>287</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5167</v>
+        <v>3.2278</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5534</v>
+        <v>1.4258</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9571</v>
+        <v>0.8192</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5167</v>
+        <v>3.2278</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2519</v>
+        <v>1.4125</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2648</v>
+        <v>1.8153</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2519</v>
+        <v>1.4125</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2624</v>
+        <v>1.4706</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2648</v>
+        <v>1.8153</v>
       </c>
       <c r="K13" t="n">
         <v>114</v>
@@ -1035,7 +1035,7 @@
         <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5272</v>
+        <v>3.2859</v>
       </c>
       <c r="N13" t="n">
         <v>249</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1338</v>
+        <v>2.945</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3843</v>
+        <v>1.3009</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8046</v>
+        <v>0.6915</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1338</v>
+        <v>2.945</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7542</v>
+        <v>1.9789</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3796</v>
+        <v>0.9661</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7542</v>
+        <v>1.9789</v>
       </c>
       <c r="I14" t="n">
-        <v>1.769</v>
+        <v>2.0603</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3796</v>
+        <v>0.9661</v>
       </c>
       <c r="K14" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="L14" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1486</v>
+        <v>3.0264</v>
       </c>
       <c r="N14" t="n">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0282</v>
+        <v>2.9321</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3376</v>
+        <v>1.2952</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7625</v>
+        <v>0.6857</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0282</v>
+        <v>2.9321</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0282</v>
+        <v>2.9321</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0282</v>
+        <v>3.0787</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0282</v>
+        <v>3.0787</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0282</v>
+        <v>3.0787</v>
       </c>
       <c r="N15" t="n">
         <v>143</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9074</v>
+        <v>2.9098</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2843</v>
+        <v>1.2853</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7144</v>
+        <v>0.6756</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9074</v>
+        <v>2.9098</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6559</v>
+        <v>1.712</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2514</v>
+        <v>1.1978</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6559</v>
+        <v>1.712</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6699</v>
+        <v>1.7824</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2514</v>
+        <v>1.1978</v>
       </c>
       <c r="K16" t="n">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="L16" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9213</v>
+        <v>2.9802</v>
       </c>
       <c r="N16" t="n">
-        <v>249</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8985</v>
+        <v>2.8899</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2803</v>
+        <v>1.2765</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7109</v>
+        <v>0.6666</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8985</v>
+        <v>2.8899</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8985</v>
+        <v>2.8899</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8985</v>
+        <v>2.986</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8985</v>
+        <v>2.986</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8985</v>
+        <v>2.986</v>
       </c>
       <c r="N17" t="n">
         <v>151</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8859</v>
+        <v>2.781</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2748</v>
+        <v>1.2284</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7058</v>
+        <v>0.6175</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8859</v>
+        <v>2.781</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2745</v>
+        <v>2.781</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3886</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2745</v>
+        <v>2.781</v>
       </c>
       <c r="I18" t="n">
-        <v>2.654</v>
+        <v>2.781</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3886</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="L18" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2654</v>
+        <v>2.781</v>
       </c>
       <c r="N18" t="n">
-        <v>323</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5555</v>
+        <v>2.4462</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1288</v>
+        <v>1.0805</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5742</v>
+        <v>0.4663</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5555</v>
+        <v>2.4462</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5555</v>
+        <v>3.0573</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6111</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5555</v>
+        <v>5.2858</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5555</v>
+        <v>2.7484</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6111</v>
       </c>
       <c r="K19" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5555</v>
+        <v>2.1373</v>
       </c>
       <c r="N19" t="n">
-        <v>148</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.143</v>
+        <v>2.2531</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9466</v>
+        <v>0.9952</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4099</v>
+        <v>0.3791</v>
       </c>
       <c r="E20" t="n">
-        <v>2.143</v>
+        <v>2.2531</v>
       </c>
       <c r="F20" t="n">
-        <v>2.143</v>
+        <v>2.2531</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.143</v>
+        <v>2.2531</v>
       </c>
       <c r="I20" t="n">
-        <v>2.161</v>
+        <v>2.3458</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.161</v>
+        <v>2.3458</v>
       </c>
       <c r="N20" t="n">
         <v>144</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8598</v>
+        <v>2.2165</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8215</v>
+        <v>0.9791</v>
       </c>
       <c r="D21" t="n">
-        <v>0.297</v>
+        <v>0.3626</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8598</v>
+        <v>2.2165</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8598</v>
+        <v>2.2757</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.0592</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8598</v>
+        <v>2.2757</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8754</v>
+        <v>2.2757</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.0592</v>
       </c>
       <c r="K21" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8754</v>
+        <v>2.2165</v>
       </c>
       <c r="N21" t="n">
-        <v>144</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8265</v>
+        <v>2.1722</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8068</v>
+        <v>0.9595</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2838</v>
+        <v>0.3426</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8265</v>
+        <v>2.1722</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9459</v>
+        <v>2.1722</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1194</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9459</v>
+        <v>2.1722</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9459</v>
+        <v>2.1722</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1194</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L22" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8265</v>
+        <v>2.1722</v>
       </c>
       <c r="N22" t="n">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7815</v>
+        <v>1.963</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7869</v>
+        <v>0.8671</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2658</v>
+        <v>0.2482</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7815</v>
+        <v>1.963</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7815</v>
+        <v>1.963</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7815</v>
+        <v>1.963</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7815</v>
+        <v>2.0437</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7815</v>
+        <v>2.0437</v>
       </c>
       <c r="N23" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7639</v>
+        <v>1.9571</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7791</v>
+        <v>0.8645</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2588</v>
+        <v>0.2455</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7639</v>
+        <v>1.9571</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7639</v>
+        <v>1.9571</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7639</v>
+        <v>1.9571</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7639</v>
+        <v>1.9571</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7639</v>
+        <v>1.9571</v>
       </c>
       <c r="N24" t="n">
         <v>148</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6226</v>
+        <v>1.8778</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7167</v>
+        <v>0.8295</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2025</v>
+        <v>0.2097</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6226</v>
+        <v>1.8778</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6962</v>
+        <v>1.7915</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0736</v>
+        <v>0.0863</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6962</v>
+        <v>1.7915</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7105</v>
+        <v>1.8652</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0736</v>
+        <v>0.0863</v>
       </c>
       <c r="K25" t="n">
         <v>114</v>
@@ -1587,7 +1587,7 @@
         <v>135</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6369</v>
+        <v>1.9515</v>
       </c>
       <c r="N25" t="n">
         <v>249</v>
@@ -1596,461 +1596,461 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4994</v>
+        <v>1.7727</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6623</v>
+        <v>0.783</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1535</v>
+        <v>0.1623</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4994</v>
+        <v>1.7727</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4994</v>
+        <v>1.9627</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4994</v>
+        <v>1.9627</v>
       </c>
       <c r="I26" t="n">
-        <v>1.512</v>
+        <v>1.0205</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="K26" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M26" t="n">
-        <v>1.512</v>
+        <v>0.8305</v>
       </c>
       <c r="N26" t="n">
-        <v>144</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2921</v>
+        <v>1.6973</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5707</v>
+        <v>0.7497</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0709</v>
+        <v>0.1282</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2921</v>
+        <v>1.6973</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6138</v>
+        <v>1.6973</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3217</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6138</v>
+        <v>1.6973</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6274</v>
+        <v>1.6973</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3217</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L27" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3057</v>
+        <v>1.6973</v>
       </c>
       <c r="N27" t="n">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1286</v>
+        <v>1.6921</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4985</v>
+        <v>0.7474</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0057</v>
+        <v>0.1259</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1286</v>
+        <v>1.6921</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1286</v>
+        <v>1.6921</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1286</v>
+        <v>1.6921</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1286</v>
+        <v>1.7617</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1286</v>
+        <v>1.7617</v>
       </c>
       <c r="N28" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1221</v>
+        <v>1.6444</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4957</v>
+        <v>0.7264</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0031</v>
+        <v>0.1044</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1221</v>
+        <v>1.6444</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1221</v>
+        <v>1.7415</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1221</v>
+        <v>1.7415</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1221</v>
+        <v>1.8131</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1221</v>
+        <v>1.716</v>
       </c>
       <c r="N29" t="n">
-        <v>137</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9969</v>
+        <v>1.3924</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4403</v>
+        <v>0.615</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0467</v>
+        <v>-0.0094</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9969</v>
+        <v>1.3924</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4683</v>
+        <v>1.2145</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4714</v>
+        <v>0.1779</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4683</v>
+        <v>1.2145</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4807</v>
+        <v>1.2645</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4714</v>
+        <v>0.1779</v>
       </c>
       <c r="K30" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0093</v>
+        <v>1.4424</v>
       </c>
       <c r="N30" t="n">
-        <v>166</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9054</v>
+        <v>1.3329</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3999</v>
+        <v>0.5888</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0832</v>
+        <v>-0.0363</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9054</v>
+        <v>1.3329</v>
       </c>
       <c r="F31" t="n">
-        <v>0.298</v>
+        <v>1.6422</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6074000000000001</v>
+        <v>-0.3093</v>
       </c>
       <c r="H31" t="n">
-        <v>0.298</v>
+        <v>1.6422</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3005</v>
+        <v>1.7097</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6074000000000001</v>
+        <v>-0.3093</v>
       </c>
       <c r="K31" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="L31" t="n">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9079</v>
+        <v>1.4004</v>
       </c>
       <c r="N31" t="n">
-        <v>284</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.803</v>
+        <v>1.1718</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3547</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.124</v>
+        <v>-0.109</v>
       </c>
       <c r="E32" t="n">
-        <v>0.803</v>
+        <v>1.1718</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0785</v>
+        <v>1.1718</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2755</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0785</v>
+        <v>1.1718</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0876</v>
+        <v>1.1718</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2755</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="L32" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8120999999999998</v>
+        <v>1.1718</v>
       </c>
       <c r="N32" t="n">
-        <v>249</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7887</v>
+        <v>1.1449</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3484</v>
+        <v>0.5057</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1297</v>
+        <v>-0.1211</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7887</v>
+        <v>1.1449</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7887</v>
+        <v>1.1449</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7887</v>
+        <v>1.1449</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7887</v>
+        <v>1.1449</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7887</v>
+        <v>1.1449</v>
       </c>
       <c r="N33" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5421</v>
+        <v>1.1047</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2395</v>
+        <v>0.488</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2279</v>
+        <v>-0.1393</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5421</v>
+        <v>1.1047</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2233</v>
+        <v>0.3547</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6812</v>
+        <v>0.75</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2233</v>
+        <v>0.3547</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2233</v>
+        <v>0.3693</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6812</v>
+        <v>0.75</v>
       </c>
       <c r="K34" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="L34" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5421</v>
+        <v>1.1193</v>
       </c>
       <c r="N34" t="n">
-        <v>232</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5377</v>
+        <v>1.0261</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2375</v>
+        <v>0.4532</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2297</v>
+        <v>-0.1748</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5377</v>
+        <v>1.0261</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6673</v>
+        <v>1.4232</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1296</v>
+        <v>-0.3971</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6673</v>
+        <v>1.4232</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5409</v>
+        <v>1.4232</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1296</v>
+        <v>-0.3971</v>
       </c>
       <c r="K35" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="L35" t="n">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4113000000000001</v>
+        <v>1.0261</v>
       </c>
       <c r="N35" t="n">
-        <v>287</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3403</v>
+        <v>0.7403</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1503</v>
+        <v>0.327</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3083</v>
+        <v>-0.3038</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3403</v>
+        <v>0.7403</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3403</v>
+        <v>0.7403</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3403</v>
+        <v>0.7403</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3403</v>
+        <v>0.7403</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3403</v>
+        <v>0.7403</v>
       </c>
       <c r="N36" t="n">
         <v>137</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3196</v>
+        <v>0.702</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1412</v>
+        <v>0.3101</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3166</v>
+        <v>-0.3211</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3196</v>
+        <v>0.702</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3196</v>
+        <v>0.702</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3196</v>
+        <v>0.702</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3196</v>
+        <v>0.702</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3196</v>
+        <v>0.702</v>
       </c>
       <c r="N37" t="n">
         <v>151</v>
@@ -2148,185 +2148,185 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2931</v>
+        <v>0.6031</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1295</v>
+        <v>0.2664</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3271</v>
+        <v>-0.3657</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2931</v>
+        <v>0.6031</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2931</v>
+        <v>0.6031</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2931</v>
+        <v>0.6031</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2931</v>
+        <v>0.6031</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2931</v>
+        <v>0.6031</v>
       </c>
       <c r="N38" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1861</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0822</v>
+        <v>0.2442</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3698</v>
+        <v>-0.3884</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1861</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1861</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1861</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1861</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1861</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>Tsogoo</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.013</v>
+        <v>0.4698</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0057</v>
+        <v>0.2075</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4491</v>
+        <v>-0.4259</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.013</v>
+        <v>0.4698</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.013</v>
+        <v>0.4698</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.013</v>
+        <v>0.4698</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.013</v>
+        <v>0.4698</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.013</v>
+        <v>0.4698</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.0215</v>
+        <v>0.391</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0095</v>
+        <v>0.1727</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4525</v>
+        <v>-0.4615</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0215</v>
+        <v>0.391</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0215</v>
+        <v>0.391</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0215</v>
+        <v>0.391</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0217</v>
+        <v>0.391</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0217</v>
+        <v>0.391</v>
       </c>
       <c r="N41" t="n">
-        <v>117</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42">
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1074</v>
+        <v>0.2994</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0474</v>
+        <v>0.1323</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4867</v>
+        <v>-0.5029</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1074</v>
+        <v>0.2994</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3452</v>
+        <v>0.5213</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.4526</v>
+        <v>-0.2219</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3452</v>
+        <v>0.5213</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3481</v>
+        <v>0.5427</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4526</v>
+        <v>-0.2219</v>
       </c>
       <c r="K42" t="n">
         <v>120</v>
@@ -2369,7 +2369,7 @@
         <v>46</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1045</v>
+        <v>0.3208</v>
       </c>
       <c r="N42" t="n">
         <v>166</v>
@@ -2378,216 +2378,216 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tsogoo</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1383</v>
+        <v>0.2802</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0611</v>
+        <v>0.1238</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.499</v>
+        <v>-0.5115</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1383</v>
+        <v>0.2802</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1383</v>
+        <v>0.2802</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1383</v>
+        <v>0.2802</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1383</v>
+        <v>0.2917</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1383</v>
+        <v>0.2917</v>
       </c>
       <c r="N43" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.2566</v>
+        <v>0.2701</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1133</v>
+        <v>0.1193</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5461</v>
+        <v>-0.5161</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.2566</v>
+        <v>0.2701</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.2566</v>
+        <v>0.5901</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.2566</v>
+        <v>0.5901</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2566</v>
+        <v>0.5901</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="K44" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.2566</v>
+        <v>0.2701</v>
       </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>zonic</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.3956</v>
+        <v>0.0786</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1747</v>
+        <v>0.0347</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6015</v>
+        <v>-0.6025</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.3956</v>
+        <v>0.0786</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.3956</v>
+        <v>0.0786</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.3956</v>
+        <v>0.0786</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3956</v>
+        <v>0.0786</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.3956</v>
+        <v>0.0786</v>
       </c>
       <c r="N45" t="n">
-        <v>27</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4369</v>
+        <v>0.0083</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.193</v>
+        <v>0.0037</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.618</v>
+        <v>-0.6343</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4369</v>
+        <v>0.0083</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1323</v>
+        <v>0.0083</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.5692</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1323</v>
+        <v>0.0083</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1323</v>
+        <v>0.0083</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.5692</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L46" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.4369000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="N46" t="n">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.4862</v>
+        <v>0.002</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2148</v>
+        <v>0.0009</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6371</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.4862</v>
+        <v>0.002</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.4862</v>
+        <v>0.002</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.4862</v>
+        <v>0.002</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.4862</v>
+        <v>0.002</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.4862</v>
+        <v>0.002</v>
       </c>
       <c r="N47" t="n">
         <v>143</v>
@@ -2608,47 +2608,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>fitch</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.532</v>
+        <v>-0.2016</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.235</v>
+        <v>-0.0891</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6559</v>
+        <v>-0.729</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.532</v>
+        <v>-0.2016</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.532</v>
+        <v>0.0648</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.2664</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.532</v>
+        <v>0.0648</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.532</v>
+        <v>0.0648</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.2664</v>
       </c>
       <c r="K48" t="n">
         <v>143</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.532</v>
+        <v>-0.2016</v>
       </c>
       <c r="N48" t="n">
-        <v>143</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.631</v>
+        <v>-0.2371</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.2787</v>
+        <v>-0.1047</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6953</v>
+        <v>-0.7451</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.631</v>
+        <v>-0.2371</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.631</v>
+        <v>-0.2371</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.631</v>
+        <v>-0.2371</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.631</v>
+        <v>-0.2371</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.631</v>
+        <v>-0.2371</v>
       </c>
       <c r="N49" t="n">
         <v>118</v>
@@ -2700,323 +2700,323 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Machinegun</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.6567</v>
+        <v>-0.2432</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2901</v>
+        <v>-0.1074</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7055</v>
+        <v>-0.7478</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.6567</v>
+        <v>-0.2432</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.6567</v>
+        <v>-0.2432</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6567</v>
+        <v>-0.2432</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6622</v>
+        <v>-0.2432</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.6622</v>
+        <v>-0.2432</v>
       </c>
       <c r="N50" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machinegun</t>
+          <t>zonic</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7341</v>
+        <v>-0.2478</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.3243</v>
+        <v>-0.1095</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.7499</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.7341</v>
+        <v>-0.2478</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.7341</v>
+        <v>-0.2478</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.7341</v>
+        <v>-0.2478</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7341</v>
+        <v>-0.2478</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.7341</v>
+        <v>-0.2478</v>
       </c>
       <c r="N51" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fitch</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.7554</v>
+        <v>-0.2574</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3337</v>
+        <v>-0.1137</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7449</v>
+        <v>-0.7542</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.7554</v>
+        <v>-0.2574</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3201</v>
+        <v>0.061</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4353</v>
+        <v>-0.3184</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3201</v>
+        <v>0.061</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3201</v>
+        <v>0.0635</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.4353</v>
+        <v>-0.3184</v>
       </c>
       <c r="K52" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="L52" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.7554000000000001</v>
+        <v>-0.2549</v>
       </c>
       <c r="N52" t="n">
-        <v>232</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.7653</v>
+        <v>-0.3298</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.338</v>
+        <v>-0.1457</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7488</v>
+        <v>-0.7869</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.7653</v>
+        <v>-0.3298</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2741</v>
+        <v>-0.3298</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.4912</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2741</v>
+        <v>-0.3298</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2764</v>
+        <v>-0.3298</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.4912</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="L53" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.7676000000000001</v>
+        <v>-0.3298</v>
       </c>
       <c r="N53" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.9664</v>
+        <v>-0.4398</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4269</v>
+        <v>-0.1943</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8289</v>
+        <v>-0.8366</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.9664</v>
+        <v>-0.4398</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.9664</v>
+        <v>-0.4398</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9664</v>
+        <v>-0.4398</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.9664</v>
+        <v>-0.4579</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.9664</v>
+        <v>-0.4579</v>
       </c>
       <c r="N54" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.9867</v>
+        <v>-0.4892</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4358</v>
+        <v>-0.2161</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.837</v>
+        <v>-0.8589</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.9867</v>
+        <v>-0.4892</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.9867</v>
+        <v>0.2772</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.7664</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.9867</v>
+        <v>0.2772</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9867</v>
+        <v>0.2886</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.7664</v>
       </c>
       <c r="K55" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.9867</v>
+        <v>-0.4777999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.0788</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4765</v>
+        <v>-0.2861</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.8737</v>
+        <v>-0.9304</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.0788</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0788</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0788</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0795</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="L56" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.0795</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.3638</v>
+        <v>-0.7662</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.6024</v>
+        <v>-0.3384</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9872</v>
+        <v>-0.9839</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3638</v>
+        <v>-0.7662</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.3638</v>
+        <v>-0.7662</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.3638</v>
+        <v>-0.7662</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.3638</v>
+        <v>-0.7662</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.3638</v>
+        <v>-0.7662</v>
       </c>
       <c r="N57" t="n">
         <v>143</v>
@@ -3068,170 +3068,170 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.4026</v>
+        <v>-0.8101</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.6196</v>
+        <v>-0.3578</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.0027</v>
+        <v>-1.0037</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.4026</v>
+        <v>-0.8101</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.0253</v>
+        <v>-1.1758</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6227</v>
+        <v>0.3657</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.0253</v>
+        <v>-1.1758</v>
       </c>
       <c r="I58" t="n">
-        <v>-2.0423</v>
+        <v>-1.2242</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6227</v>
+        <v>0.3657</v>
       </c>
       <c r="K58" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="L58" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.4196</v>
+        <v>-0.8584999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.5838</v>
+        <v>-1.1655</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.6996</v>
+        <v>-0.5148</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.0749</v>
+        <v>-1.1642</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.5838</v>
+        <v>-1.1655</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.6382</v>
+        <v>-1.3621</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0544</v>
+        <v>0.1966</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.6382</v>
+        <v>-1.3621</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.652</v>
+        <v>-1.4181</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0544</v>
+        <v>0.1966</v>
       </c>
       <c r="K59" t="n">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="L59" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.5976</v>
+        <v>-1.2215</v>
       </c>
       <c r="N59" t="n">
-        <v>249</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>ncl</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.0653</v>
+        <v>-1.7229</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.9123</v>
+        <v>-0.761</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.2667</v>
+        <v>-1.4158</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.0653</v>
+        <v>-1.7229</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.5568</v>
+        <v>-1.7229</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.5085</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.5568</v>
+        <v>-1.7229</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.2618</v>
+        <v>-1.7229</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.5085</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L60" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.7703</v>
+        <v>-1.7229</v>
       </c>
       <c r="N60" t="n">
-        <v>323</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ncl</t>
+          <t>maaRaa</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-2.5392</v>
+        <v>-1.8596</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.1216</v>
+        <v>-0.8214</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4555</v>
+        <v>-1.4775</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.5392</v>
+        <v>-1.8596</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.5392</v>
+        <v>-1.8596</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.5392</v>
+        <v>-1.8596</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.5392</v>
+        <v>-1.8596</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.5392</v>
+        <v>-1.8596</v>
       </c>
       <c r="N61" t="n">
         <v>118</v>
@@ -3252,47 +3252,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>maaRaa</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-2.723</v>
+        <v>-2.3483</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.2028</v>
+        <v>-1.0373</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.5288</v>
+        <v>-1.6982</v>
       </c>
       <c r="E62" t="n">
-        <v>-2.723</v>
+        <v>-2.3483</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.723</v>
+        <v>-1.7265</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.6218</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.723</v>
+        <v>-1.7265</v>
       </c>
       <c r="I62" t="n">
-        <v>-2.723</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.6218</v>
       </c>
       <c r="K62" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M62" t="n">
-        <v>-2.723</v>
+        <v>-1.5195</v>
       </c>
       <c r="N62" t="n">
-        <v>118</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3395,10 +3395,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2284</v>
+        <v>1.1474</v>
       </c>
       <c r="J2" t="n">
-        <v>31.9384</v>
+        <v>29.8324</v>
       </c>
     </row>
     <row r="3">
@@ -3435,10 +3435,10 @@
         <v>1.47</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1477</v>
+        <v>1.0965</v>
       </c>
       <c r="J3" t="n">
-        <v>29.8402</v>
+        <v>28.509</v>
       </c>
     </row>
     <row r="4">
@@ -3475,10 +3475,10 @@
         <v>1.27</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7013</v>
+        <v>0.7177</v>
       </c>
       <c r="J4" t="n">
-        <v>18.2338</v>
+        <v>18.6602</v>
       </c>
     </row>
     <row r="5">
@@ -3515,10 +3515,10 @@
         <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3889</v>
+        <v>0.4568</v>
       </c>
       <c r="J5" t="n">
-        <v>10.1114</v>
+        <v>11.8768</v>
       </c>
     </row>
     <row r="6">
@@ -3555,10 +3555,10 @@
         <v>0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8956</v>
+        <v>-0.8575</v>
       </c>
       <c r="J6" t="n">
-        <v>-23.2856</v>
+        <v>-22.295</v>
       </c>
     </row>
     <row r="7">
@@ -3595,10 +3595,10 @@
         <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2654</v>
+        <v>0.2725</v>
       </c>
       <c r="J7" t="n">
-        <v>6.9004</v>
+        <v>7.085</v>
       </c>
     </row>
     <row r="8">
@@ -3635,10 +3635,10 @@
         <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2063</v>
+        <v>-0.1523</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.3638</v>
+        <v>-3.9598</v>
       </c>
     </row>
     <row r="9">
@@ -3675,10 +3675,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2276</v>
+        <v>-0.1623</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.9176</v>
+        <v>-4.2198</v>
       </c>
     </row>
     <row r="10">
@@ -3715,10 +3715,10 @@
         <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2896</v>
+        <v>-0.1919</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.5296</v>
+        <v>-4.9894</v>
       </c>
     </row>
     <row r="11">
@@ -3755,10 +3755,10 @@
         <v>0.64</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5693</v>
+        <v>-0.3753</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.8018</v>
+        <v>-9.7578</v>
       </c>
     </row>
     <row r="12">
@@ -3795,10 +3795,10 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="n">
-        <v>0.26</v>
+        <v>0.2002</v>
       </c>
       <c r="J12" t="n">
-        <v>5.98</v>
+        <v>4.6046</v>
       </c>
     </row>
     <row r="13">
@@ -3875,10 +3875,10 @@
         <v>0.72</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4343</v>
+        <v>-0.2896</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.988899999999999</v>
+        <v>-6.6608</v>
       </c>
     </row>
     <row r="15">
@@ -3915,10 +3915,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5221</v>
+        <v>-0.3463</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.0083</v>
+        <v>-7.9649</v>
       </c>
     </row>
     <row r="16">
@@ -3955,10 +3955,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6433</v>
+        <v>-0.4307</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.7959</v>
+        <v>-9.9061</v>
       </c>
     </row>
     <row r="17">
@@ -3995,10 +3995,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>0.88</v>
+        <v>0.7974</v>
       </c>
       <c r="J17" t="n">
-        <v>20.24</v>
+        <v>18.3402</v>
       </c>
     </row>
     <row r="18">
@@ -4035,10 +4035,10 @@
         <v>1.64</v>
       </c>
       <c r="I18" t="n">
-        <v>0.848</v>
+        <v>0.7659</v>
       </c>
       <c r="J18" t="n">
-        <v>19.504</v>
+        <v>17.6157</v>
       </c>
     </row>
     <row r="19">
@@ -4075,10 +4075,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.221</v>
+        <v>0.2289</v>
       </c>
       <c r="J19" t="n">
-        <v>5.083</v>
+        <v>5.2647</v>
       </c>
     </row>
     <row r="20">
@@ -4115,10 +4115,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1585</v>
+        <v>0.1758</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6455</v>
+        <v>4.0434</v>
       </c>
     </row>
     <row r="21">
@@ -4155,10 +4155,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6838</v>
+        <v>-0.4585</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.7274</v>
+        <v>-10.5455</v>
       </c>
     </row>
     <row r="22">
@@ -4195,10 +4195,10 @@
         <v>1.53</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2937</v>
+        <v>1.186</v>
       </c>
       <c r="J22" t="n">
-        <v>33.6362</v>
+        <v>30.836</v>
       </c>
     </row>
     <row r="23">
@@ -4235,10 +4235,10 @@
         <v>1.39</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0066</v>
+        <v>0.9947</v>
       </c>
       <c r="J23" t="n">
-        <v>26.1716</v>
+        <v>25.8622</v>
       </c>
     </row>
     <row r="24">
@@ -4275,10 +4275,10 @@
         <v>1.22</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6085</v>
+        <v>0.6118</v>
       </c>
       <c r="J24" t="n">
-        <v>15.821</v>
+        <v>15.9068</v>
       </c>
     </row>
     <row r="25">
@@ -4315,10 +4315,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5232</v>
+        <v>-0.4545</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.6032</v>
+        <v>-11.817</v>
       </c>
     </row>
     <row r="26">
@@ -4355,10 +4355,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5756</v>
+        <v>-0.51</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.9656</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="27">
@@ -4395,10 +4395,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1979</v>
+        <v>0.1914</v>
       </c>
       <c r="J27" t="n">
-        <v>5.1454</v>
+        <v>4.9764</v>
       </c>
     </row>
     <row r="28">
@@ -4435,10 +4435,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0497</v>
+        <v>-0.0532</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.2922</v>
+        <v>-1.3832</v>
       </c>
     </row>
     <row r="29">
@@ -4475,10 +4475,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0497</v>
+        <v>-0.0532</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.2922</v>
+        <v>-1.3832</v>
       </c>
     </row>
     <row r="30">
@@ -4515,10 +4515,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.369</v>
+        <v>-0.2361</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.593999999999999</v>
+        <v>-6.1386</v>
       </c>
     </row>
     <row r="31">
@@ -4555,10 +4555,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4978</v>
+        <v>-0.3234</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.9428</v>
+        <v>-8.4084</v>
       </c>
     </row>
     <row r="32">
@@ -4595,10 +4595,10 @@
         <v>0.93</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0285</v>
+        <v>-0.055</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.627</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="33">
@@ -4635,10 +4635,10 @@
         <v>0.78</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2803</v>
+        <v>-0.2239</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.1666</v>
+        <v>-4.9258</v>
       </c>
     </row>
     <row r="34">
@@ -4675,10 +4675,10 @@
         <v>0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.33</v>
+        <v>-0.2534</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.26</v>
+        <v>-5.5748</v>
       </c>
     </row>
     <row r="35">
@@ -4715,10 +4715,10 @@
         <v>0.66</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4943</v>
+        <v>-0.3358</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.8746</v>
+        <v>-7.3876</v>
       </c>
     </row>
     <row r="36">
@@ -4755,10 +4755,10 @@
         <v>0.46</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7669</v>
+        <v>-0.5226</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.8718</v>
+        <v>-11.4972</v>
       </c>
     </row>
     <row r="37">
@@ -4795,10 +4795,10 @@
         <v>1.99</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1549</v>
+        <v>1.044</v>
       </c>
       <c r="J37" t="n">
-        <v>25.4078</v>
+        <v>22.968</v>
       </c>
     </row>
     <row r="38">
@@ -4835,10 +4835,10 @@
         <v>1.63</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.722</v>
       </c>
       <c r="J38" t="n">
-        <v>17.3756</v>
+        <v>15.884</v>
       </c>
     </row>
     <row r="39">
@@ -4875,10 +4875,10 @@
         <v>1.32</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3952</v>
+        <v>0.401</v>
       </c>
       <c r="J39" t="n">
-        <v>8.6944</v>
+        <v>8.821999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -4915,10 +4915,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0592</v>
+        <v>0.098</v>
       </c>
       <c r="J40" t="n">
-        <v>1.3024</v>
+        <v>2.156</v>
       </c>
     </row>
     <row r="41">
@@ -4955,10 +4955,10 @@
         <v>1.07</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0427</v>
+        <v>0.0829</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9394</v>
+        <v>1.8238</v>
       </c>
     </row>
     <row r="42">
@@ -4995,10 +4995,10 @@
         <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5482</v>
+        <v>0.5051</v>
       </c>
       <c r="J42" t="n">
-        <v>14.2532</v>
+        <v>13.1326</v>
       </c>
     </row>
     <row r="43">
@@ -5035,10 +5035,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2137</v>
+        <v>0.1906</v>
       </c>
       <c r="J43" t="n">
-        <v>5.5562</v>
+        <v>4.9556</v>
       </c>
     </row>
     <row r="44">
@@ -5075,10 +5075,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1329</v>
+        <v>0.1247</v>
       </c>
       <c r="J44" t="n">
-        <v>3.4554</v>
+        <v>3.2422</v>
       </c>
     </row>
     <row r="45">
@@ -5115,10 +5115,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0316</v>
+        <v>0.0493</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8216</v>
+        <v>1.2818</v>
       </c>
     </row>
     <row r="46">
@@ -5155,10 +5155,10 @@
         <v>0.88</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4674</v>
+        <v>-0.4133</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.1524</v>
+        <v>-10.7458</v>
       </c>
     </row>
     <row r="47">
@@ -5195,10 +5195,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4938</v>
+        <v>0.5855</v>
       </c>
       <c r="J47" t="n">
-        <v>12.8388</v>
+        <v>15.223</v>
       </c>
     </row>
     <row r="48">
@@ -5235,10 +5235,10 @@
         <v>1.15</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2944</v>
+        <v>0.3344</v>
       </c>
       <c r="J48" t="n">
-        <v>7.6544</v>
+        <v>8.6944</v>
       </c>
     </row>
     <row r="49">
@@ -5275,10 +5275,10 @@
         <v>1.13</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2625</v>
+        <v>0.2962</v>
       </c>
       <c r="J49" t="n">
-        <v>6.825</v>
+        <v>7.7012</v>
       </c>
     </row>
     <row r="50">
@@ -5315,10 +5315,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2723</v>
+        <v>-0.1606</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.0798</v>
+        <v>-4.1756</v>
       </c>
     </row>
     <row r="51">
@@ -5355,10 +5355,10 @@
         <v>0.75</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4614</v>
+        <v>-0.2928</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.9964</v>
+        <v>-7.6128</v>
       </c>
     </row>
     <row r="52">
@@ -5395,10 +5395,10 @@
         <v>1.25</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6904</v>
+        <v>0.541</v>
       </c>
       <c r="J52" t="n">
-        <v>16.5696</v>
+        <v>12.984</v>
       </c>
     </row>
     <row r="53">
@@ -5435,10 +5435,10 @@
         <v>1.23</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6401</v>
+        <v>0.5129</v>
       </c>
       <c r="J53" t="n">
-        <v>15.3624</v>
+        <v>12.3096</v>
       </c>
     </row>
     <row r="54">
@@ -5475,10 +5475,10 @@
         <v>1.21</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5877</v>
+        <v>0.4846</v>
       </c>
       <c r="J54" t="n">
-        <v>14.1048</v>
+        <v>11.6304</v>
       </c>
     </row>
     <row r="55">
@@ -5515,10 +5515,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4702</v>
+        <v>0.4274</v>
       </c>
       <c r="J55" t="n">
-        <v>11.2848</v>
+        <v>10.2576</v>
       </c>
     </row>
     <row r="56">
@@ -5555,10 +5555,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2118</v>
+        <v>-0.1366</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.0832</v>
+        <v>-3.2784</v>
       </c>
     </row>
     <row r="57">
@@ -5595,10 +5595,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3802</v>
+        <v>0.3887</v>
       </c>
       <c r="J57" t="n">
-        <v>9.1248</v>
+        <v>9.328799999999999</v>
       </c>
     </row>
     <row r="58">
@@ -5635,10 +5635,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3041</v>
+        <v>0.3264</v>
       </c>
       <c r="J58" t="n">
-        <v>7.2984</v>
+        <v>7.8336</v>
       </c>
     </row>
     <row r="59">
@@ -5675,10 +5675,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3496</v>
+        <v>-0.2203</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.3904</v>
+        <v>-5.2872</v>
       </c>
     </row>
     <row r="60">
@@ -5715,10 +5715,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3496</v>
+        <v>-0.2203</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.3904</v>
+        <v>-5.2872</v>
       </c>
     </row>
     <row r="61">
@@ -5755,10 +5755,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.8152</v>
+        <v>-7.6368</v>
       </c>
     </row>
     <row r="62">
@@ -5795,10 +5795,10 @@
         <v>1.7</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5372</v>
+        <v>1.0804</v>
       </c>
       <c r="J62" t="n">
-        <v>33.8184</v>
+        <v>23.7688</v>
       </c>
     </row>
     <row r="63">
@@ -5835,10 +5835,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8912</v>
+        <v>0.6896</v>
       </c>
       <c r="J63" t="n">
-        <v>19.6064</v>
+        <v>15.1712</v>
       </c>
     </row>
     <row r="64">
@@ -5875,10 +5875,10 @@
         <v>1.34</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7817</v>
+        <v>0.64</v>
       </c>
       <c r="J64" t="n">
-        <v>17.1974</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="65">
@@ -5915,10 +5915,10 @@
         <v>1.2</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4371</v>
+        <v>0.4507</v>
       </c>
       <c r="J65" t="n">
-        <v>9.616199999999999</v>
+        <v>9.9154</v>
       </c>
     </row>
     <row r="66">
@@ -5955,10 +5955,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.18</v>
+        <v>0.269</v>
       </c>
       <c r="J66" t="n">
-        <v>3.96</v>
+        <v>5.918</v>
       </c>
     </row>
     <row r="67">
@@ -5995,10 +5995,10 @@
         <v>1.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.412</v>
+        <v>0.4112</v>
       </c>
       <c r="J67" t="n">
-        <v>9.064</v>
+        <v>9.0464</v>
       </c>
     </row>
     <row r="68">
@@ -6035,10 +6035,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.032</v>
+        <v>-0.0517</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.704</v>
+        <v>-1.1374</v>
       </c>
     </row>
     <row r="69">
@@ -6075,10 +6075,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3121</v>
+        <v>-0.2161</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.8662</v>
+        <v>-4.7542</v>
       </c>
     </row>
     <row r="70">
@@ -6115,10 +6115,10 @@
         <v>0.59</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6227</v>
+        <v>-0.4152</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.6994</v>
+        <v>-9.134399999999999</v>
       </c>
     </row>
     <row r="71">
@@ -6155,10 +6155,10 @@
         <v>0.53</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.699</v>
+        <v>-0.4708</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.378</v>
+        <v>-10.3576</v>
       </c>
     </row>
     <row r="72">
@@ -6195,10 +6195,10 @@
         <v>1.07</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2336</v>
+        <v>0.2312</v>
       </c>
       <c r="J72" t="n">
-        <v>5.84</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="73">
@@ -6235,10 +6235,10 @@
         <v>0.98</v>
       </c>
       <c r="I73" t="n">
-        <v>0.014</v>
+        <v>-0.0178</v>
       </c>
       <c r="J73" t="n">
-        <v>0.35</v>
+        <v>-0.445</v>
       </c>
     </row>
     <row r="74">
@@ -6275,10 +6275,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1822</v>
+        <v>-0.141</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.555</v>
+        <v>-3.525</v>
       </c>
     </row>
     <row r="75">
@@ -6315,10 +6315,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3027</v>
+        <v>-0.201</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.5675</v>
+        <v>-5.025</v>
       </c>
     </row>
     <row r="76">
@@ -6355,10 +6355,10 @@
         <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.5037</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.585</v>
+        <v>-12.5925</v>
       </c>
     </row>
     <row r="77">
@@ -6395,10 +6395,10 @@
         <v>1.63</v>
       </c>
       <c r="I77" t="n">
-        <v>1.4389</v>
+        <v>1.0123</v>
       </c>
       <c r="J77" t="n">
-        <v>35.9725</v>
+        <v>25.3075</v>
       </c>
     </row>
     <row r="78">
@@ -6435,10 +6435,10 @@
         <v>1.52</v>
       </c>
       <c r="I78" t="n">
-        <v>1.2262</v>
+        <v>0.8763</v>
       </c>
       <c r="J78" t="n">
-        <v>30.655</v>
+        <v>21.9075</v>
       </c>
     </row>
     <row r="79">
@@ -6475,10 +6475,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5204</v>
+        <v>0.488</v>
       </c>
       <c r="J79" t="n">
-        <v>13.01</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="80">
@@ -6515,10 +6515,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1663</v>
       </c>
       <c r="J80" t="n">
-        <v>2.175</v>
+        <v>4.1575</v>
       </c>
     </row>
     <row r="81">
@@ -6555,10 +6555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3818</v>
+        <v>-0.3006</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.545</v>
+        <v>-7.515</v>
       </c>
     </row>
     <row r="82">
@@ -6595,10 +6595,10 @@
         <v>2.17</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3305</v>
+        <v>0.8779</v>
       </c>
       <c r="J82" t="n">
-        <v>31.932</v>
+        <v>21.0696</v>
       </c>
     </row>
     <row r="83">
@@ -6635,10 +6635,10 @@
         <v>1.6</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7655</v>
+        <v>0.5476</v>
       </c>
       <c r="J83" t="n">
-        <v>18.372</v>
+        <v>13.1424</v>
       </c>
     </row>
     <row r="84">
@@ -6675,10 +6675,10 @@
         <v>1.38</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4893</v>
+        <v>0.4135</v>
       </c>
       <c r="J84" t="n">
-        <v>11.7432</v>
+        <v>9.923999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -6715,10 +6715,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1796</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.3104</v>
+        <v>-2.076</v>
       </c>
     </row>
     <row r="86">
@@ -6755,10 +6755,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4411</v>
+        <v>-0.2748</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.5864</v>
+        <v>-6.5952</v>
       </c>
     </row>
     <row r="87">
@@ -6795,10 +6795,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6258</v>
+        <v>0.4835</v>
       </c>
       <c r="J87" t="n">
-        <v>15.0192</v>
+        <v>11.604</v>
       </c>
     </row>
     <row r="88">
@@ -6835,10 +6835,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0857</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.9368</v>
+        <v>-2.0568</v>
       </c>
     </row>
     <row r="89">
@@ -6875,10 +6875,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.273</v>
+        <v>-0.2052</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.552</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="90">
@@ -6915,10 +6915,10 @@
         <v>0.51</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.4869</v>
       </c>
       <c r="J90" t="n">
-        <v>-17.2872</v>
+        <v>-11.6856</v>
       </c>
     </row>
     <row r="91">
@@ -6955,10 +6955,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8643</v>
+        <v>-0.5969</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.7432</v>
+        <v>-14.3256</v>
       </c>
     </row>
     <row r="92">
@@ -6995,10 +6995,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3942</v>
+        <v>0.3972</v>
       </c>
       <c r="J92" t="n">
-        <v>10.6434</v>
+        <v>10.7244</v>
       </c>
     </row>
     <row r="93">
@@ -7035,10 +7035,10 @@
         <v>0.85</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2466</v>
+        <v>-0.1716</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.6582</v>
+        <v>-4.6332</v>
       </c>
     </row>
     <row r="94">
@@ -7075,10 +7075,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3038</v>
+        <v>-0.2012</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.2026</v>
+        <v>-5.4324</v>
       </c>
     </row>
     <row r="95">
@@ -7115,10 +7115,10 @@
         <v>0.72</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4583</v>
+        <v>-0.2987</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.3741</v>
+        <v>-8.0649</v>
       </c>
     </row>
     <row r="96">
@@ -7155,10 +7155,10 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4865</v>
+        <v>-0.3178</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.1355</v>
+        <v>-8.5806</v>
       </c>
     </row>
     <row r="97">
@@ -7195,10 +7195,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0739</v>
+        <v>0.7752</v>
       </c>
       <c r="J97" t="n">
-        <v>28.9953</v>
+        <v>20.9304</v>
       </c>
     </row>
     <row r="98">
@@ -7235,10 +7235,10 @@
         <v>1.34</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>23.7195</v>
+        <v>17.7336</v>
       </c>
     </row>
     <row r="99">
@@ -7275,10 +7275,10 @@
         <v>1.31</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8096</v>
+        <v>0.6166</v>
       </c>
       <c r="J99" t="n">
-        <v>21.8592</v>
+        <v>16.6482</v>
       </c>
     </row>
     <row r="100">
@@ -7315,10 +7315,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1853</v>
+        <v>-0.1061</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.0031</v>
+        <v>-2.8647</v>
       </c>
     </row>
     <row r="101">
@@ -7355,10 +7355,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2271</v>
+        <v>-0.1472</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.1317</v>
+        <v>-3.9744</v>
       </c>
     </row>
     <row r="102">
@@ -7395,10 +7395,10 @@
         <v>1.09</v>
       </c>
       <c r="I102" t="n">
-        <v>0.209</v>
+        <v>0.1721</v>
       </c>
       <c r="J102" t="n">
-        <v>7.315</v>
+        <v>6.0235</v>
       </c>
     </row>
     <row r="103">
@@ -7435,10 +7435,10 @@
         <v>1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1126</v>
+        <v>0.0882</v>
       </c>
       <c r="J103" t="n">
-        <v>3.941</v>
+        <v>3.087</v>
       </c>
     </row>
     <row r="104">
@@ -7475,10 +7475,10 @@
         <v>0.99</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.043</v>
+        <v>-0.0208</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.505</v>
+        <v>-0.728</v>
       </c>
     </row>
     <row r="105">
@@ -7515,10 +7515,10 @@
         <v>0.97</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0941</v>
+        <v>-0.0504</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.2935</v>
+        <v>-1.764</v>
       </c>
     </row>
     <row r="106">
@@ -7555,10 +7555,10 @@
         <v>0.93</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1758</v>
+        <v>-0.1005</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.153</v>
+        <v>-3.5175</v>
       </c>
     </row>
     <row r="107">
@@ -7595,10 +7595,10 @@
         <v>1.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.4557</v>
       </c>
       <c r="J107" t="n">
-        <v>21.7875</v>
+        <v>15.9495</v>
       </c>
     </row>
     <row r="108">
@@ -7635,10 +7635,10 @@
         <v>1.07</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1336</v>
+        <v>0.1223</v>
       </c>
       <c r="J108" t="n">
-        <v>4.676</v>
+        <v>4.2805</v>
       </c>
     </row>
     <row r="109">
@@ -7675,10 +7675,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0235</v>
+        <v>0.04</v>
       </c>
       <c r="J109" t="n">
-        <v>0.8225</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="110">
@@ -7715,10 +7715,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0271</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.5025</v>
+        <v>-0.9485</v>
       </c>
     </row>
     <row r="111">
@@ -7755,10 +7755,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.28</v>
+        <v>-0.1641</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.800000000000001</v>
+        <v>-5.7435</v>
       </c>
     </row>
     <row r="112">
@@ -7795,10 +7795,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1388</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>30.7476</v>
+        <v>22.1157</v>
       </c>
     </row>
     <row r="113">
@@ -7835,10 +7835,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8811</v>
+        <v>0.664</v>
       </c>
       <c r="J113" t="n">
-        <v>23.7897</v>
+        <v>17.928</v>
       </c>
     </row>
     <row r="114">
@@ -7875,10 +7875,10 @@
         <v>1.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4852</v>
+        <v>0.4629</v>
       </c>
       <c r="J114" t="n">
-        <v>13.1004</v>
+        <v>12.4983</v>
       </c>
     </row>
     <row r="115">
@@ -7915,10 +7915,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3258</v>
+        <v>0.3735</v>
       </c>
       <c r="J115" t="n">
-        <v>8.7966</v>
+        <v>10.0845</v>
       </c>
     </row>
     <row r="116">
@@ -7955,10 +7955,10 @@
         <v>1.07</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1278</v>
+        <v>0.2038</v>
       </c>
       <c r="J116" t="n">
-        <v>3.4506</v>
+        <v>5.5026</v>
       </c>
     </row>
     <row r="117">
@@ -7995,10 +7995,10 @@
         <v>1.22</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4353</v>
+        <v>0.4317</v>
       </c>
       <c r="J117" t="n">
-        <v>11.7531</v>
+        <v>11.6559</v>
       </c>
     </row>
     <row r="118">
@@ -8035,10 +8035,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0508</v>
       </c>
       <c r="J118" t="n">
-        <v>1.9818</v>
+        <v>1.3716</v>
       </c>
     </row>
     <row r="119">
@@ -8075,10 +8075,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0469</v>
+        <v>-0.0448</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.2663</v>
+        <v>-1.2096</v>
       </c>
     </row>
     <row r="120">
@@ -8115,10 +8115,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3959</v>
+        <v>-0.251</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.6893</v>
+        <v>-6.777</v>
       </c>
     </row>
     <row r="121">
@@ -8155,10 +8155,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5204</v>
+        <v>-0.338</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.0508</v>
+        <v>-9.125999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -8195,10 +8195,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2311</v>
+        <v>0.8722</v>
       </c>
       <c r="J122" t="n">
-        <v>33.2397</v>
+        <v>23.5494</v>
       </c>
     </row>
     <row r="123">
@@ -8235,10 +8235,10 @@
         <v>1.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9601</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>25.9227</v>
+        <v>18.9567</v>
       </c>
     </row>
     <row r="124">
@@ -8275,10 +8275,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3325</v>
+        <v>0.3662</v>
       </c>
       <c r="J124" t="n">
-        <v>8.977499999999999</v>
+        <v>9.8874</v>
       </c>
     </row>
     <row r="125">
@@ -8315,10 +8315,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="J125" t="n">
-        <v>2.4651</v>
+        <v>4.2309</v>
       </c>
     </row>
     <row r="126">
@@ -8355,10 +8355,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5774</v>
+        <v>-0.5115</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.5898</v>
+        <v>-13.8105</v>
       </c>
     </row>
     <row r="127">
@@ -8395,10 +8395,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2837</v>
+        <v>0.3044</v>
       </c>
       <c r="J127" t="n">
-        <v>7.6599</v>
+        <v>8.2188</v>
       </c>
     </row>
     <row r="128">
@@ -8435,10 +8435,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1192</v>
+        <v>0.105</v>
       </c>
       <c r="J128" t="n">
-        <v>3.2184</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="129">
@@ -8475,10 +8475,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1213</v>
+        <v>-0.0829</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.2751</v>
+        <v>-2.2383</v>
       </c>
     </row>
     <row r="130">
@@ -8515,10 +8515,10 @@
         <v>0.84</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3069</v>
+        <v>-0.1913</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.286300000000001</v>
+        <v>-5.1651</v>
       </c>
     </row>
     <row r="131">
@@ -8555,10 +8555,10 @@
         <v>0.77</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4119</v>
+        <v>-0.2616</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.1213</v>
+        <v>-7.0632</v>
       </c>
     </row>
     <row r="132">
@@ -8595,10 +8595,10 @@
         <v>2.39</v>
       </c>
       <c r="I132" t="n">
-        <v>2.1659</v>
+        <v>1.7594</v>
       </c>
       <c r="J132" t="n">
-        <v>38.9862</v>
+        <v>31.6692</v>
       </c>
     </row>
     <row r="133">
@@ -8635,10 +8635,10 @@
         <v>1.96</v>
       </c>
       <c r="I133" t="n">
-        <v>1.7908</v>
+        <v>1.3079</v>
       </c>
       <c r="J133" t="n">
-        <v>32.2344</v>
+        <v>23.5422</v>
       </c>
     </row>
     <row r="134">
@@ -8675,10 +8675,10 @@
         <v>1.54</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0351</v>
+        <v>0.8481</v>
       </c>
       <c r="J134" t="n">
-        <v>18.6318</v>
+        <v>15.2658</v>
       </c>
     </row>
     <row r="135">
@@ -8715,10 +8715,10 @@
         <v>1.49</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9381</v>
+        <v>0.7885</v>
       </c>
       <c r="J135" t="n">
-        <v>16.8858</v>
+        <v>14.193</v>
       </c>
     </row>
     <row r="136">
@@ -8755,10 +8755,10 @@
         <v>1.18</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2933</v>
+        <v>0.3788</v>
       </c>
       <c r="J136" t="n">
-        <v>5.2794</v>
+        <v>6.8184</v>
       </c>
     </row>
     <row r="137">
@@ -8795,10 +8795,10 @@
         <v>0.48</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.5893</v>
+        <v>-0.4543</v>
       </c>
       <c r="J137" t="n">
-        <v>-10.6074</v>
+        <v>-8.1774</v>
       </c>
     </row>
     <row r="138">
@@ -8835,10 +8835,10 @@
         <v>0.47</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.6077</v>
+        <v>-0.4637</v>
       </c>
       <c r="J138" t="n">
-        <v>-10.9386</v>
+        <v>-8.3466</v>
       </c>
     </row>
     <row r="139">
@@ -8875,10 +8875,10 @@
         <v>0.46</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.4728</v>
       </c>
       <c r="J139" t="n">
-        <v>-11.295</v>
+        <v>-8.510400000000001</v>
       </c>
     </row>
     <row r="140">
@@ -8915,10 +8915,10 @@
         <v>0.43</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6986</v>
+        <v>-0.4988</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.5748</v>
+        <v>-8.978400000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8955,10 +8955,10 @@
         <v>0.41</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7341</v>
+        <v>-0.5175</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.2138</v>
+        <v>-9.315</v>
       </c>
     </row>
     <row r="142">
@@ -8995,10 +8995,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7231</v>
+        <v>0.5452</v>
       </c>
       <c r="J142" t="n">
-        <v>20.2468</v>
+        <v>15.2656</v>
       </c>
     </row>
     <row r="143">
@@ -9035,10 +9035,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3108</v>
+        <v>0.2999</v>
       </c>
       <c r="J143" t="n">
-        <v>8.702400000000001</v>
+        <v>8.3972</v>
       </c>
     </row>
     <row r="144">
@@ -9075,10 +9075,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2324</v>
+        <v>0.2432</v>
       </c>
       <c r="J144" t="n">
-        <v>6.5072</v>
+        <v>6.8096</v>
       </c>
     </row>
     <row r="145">
@@ -9115,10 +9115,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1681</v>
+        <v>-0.1113</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.7068</v>
+        <v>-3.1164</v>
       </c>
     </row>
     <row r="146">
@@ -9155,10 +9155,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1681</v>
+        <v>-0.1113</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.7068</v>
+        <v>-3.1164</v>
       </c>
     </row>
     <row r="147">
@@ -9195,10 +9195,10 @@
         <v>1.23</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4124</v>
+        <v>0.4204</v>
       </c>
       <c r="J147" t="n">
-        <v>11.5472</v>
+        <v>11.7712</v>
       </c>
     </row>
     <row r="148">
@@ -9235,10 +9235,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.246</v>
+        <v>0.2769</v>
       </c>
       <c r="J148" t="n">
-        <v>6.888</v>
+        <v>7.7532</v>
       </c>
     </row>
     <row r="149">
@@ -9275,10 +9275,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1363</v>
+        <v>0.1544</v>
       </c>
       <c r="J149" t="n">
-        <v>3.8164</v>
+        <v>4.3232</v>
       </c>
     </row>
     <row r="150">
@@ -9315,10 +9315,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1363</v>
+        <v>0.1544</v>
       </c>
       <c r="J150" t="n">
-        <v>3.8164</v>
+        <v>4.3232</v>
       </c>
     </row>
     <row r="151">
@@ -9355,10 +9355,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.488</v>
+        <v>-0.3121</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.664</v>
+        <v>-8.738799999999999</v>
       </c>
     </row>
     <row r="152">
@@ -9395,10 +9395,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7696</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>23.088</v>
+        <v>28.716</v>
       </c>
     </row>
     <row r="153">
@@ -9435,10 +9435,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3056</v>
+        <v>0.3502</v>
       </c>
       <c r="J153" t="n">
-        <v>9.167999999999999</v>
+        <v>10.506</v>
       </c>
     </row>
     <row r="154">
@@ -9475,10 +9475,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.09</v>
+        <v>-0.0408</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.7</v>
+        <v>-1.224</v>
       </c>
     </row>
     <row r="155">
@@ -9515,10 +9515,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3948</v>
+        <v>-0.2449</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.844</v>
+        <v>-7.347</v>
       </c>
     </row>
     <row r="156">
@@ -9555,10 +9555,10 @@
         <v>0.8</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3948</v>
+        <v>-0.2449</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.844</v>
+        <v>-7.347</v>
       </c>
     </row>
     <row r="157">
@@ -9595,10 +9595,10 @@
         <v>1.38</v>
       </c>
       <c r="I157" t="n">
-        <v>1.02</v>
+        <v>0.9979</v>
       </c>
       <c r="J157" t="n">
-        <v>30.6</v>
+        <v>29.937</v>
       </c>
     </row>
     <row r="158">
@@ -9635,10 +9635,10 @@
         <v>1.2</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>18.009</v>
+        <v>17.403</v>
       </c>
     </row>
     <row r="159">
@@ -9675,10 +9675,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1629</v>
+        <v>0.2058</v>
       </c>
       <c r="J159" t="n">
-        <v>4.887</v>
+        <v>6.174</v>
       </c>
     </row>
     <row r="160">
@@ -9715,10 +9715,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2611</v>
+        <v>-0.1935</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.833</v>
+        <v>-5.805</v>
       </c>
     </row>
     <row r="161">
@@ -9755,10 +9755,10 @@
         <v>0.95</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2948</v>
+        <v>-0.2269</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.843999999999999</v>
+        <v>-6.807</v>
       </c>
     </row>
     <row r="162">
@@ -9795,10 +9795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.063</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>-1.575</v>
+        <v>-1.7375</v>
       </c>
     </row>
     <row r="163">
@@ -9835,10 +9835,10 @@
         <v>0.89</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1554</v>
+        <v>-0.128</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.885</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="164">
@@ -9875,10 +9875,10 @@
         <v>0.85</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2284</v>
+        <v>-0.1703</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.71</v>
+        <v>-4.2575</v>
       </c>
     </row>
     <row r="165">
@@ -9915,10 +9915,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3773</v>
+        <v>-0.248</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.432499999999999</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="166">
@@ -9955,10 +9955,10 @@
         <v>0.72</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4525</v>
+        <v>-0.2962</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.3125</v>
+        <v>-7.405</v>
       </c>
     </row>
     <row r="167">
@@ -9995,10 +9995,10 @@
         <v>1.56</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2993</v>
+        <v>1.1972</v>
       </c>
       <c r="J167" t="n">
-        <v>32.4825</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="168">
@@ -10035,10 +10035,10 @@
         <v>1.42</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0139</v>
+        <v>1.0176</v>
       </c>
       <c r="J168" t="n">
-        <v>25.3475</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="169">
@@ -10075,10 +10075,10 @@
         <v>1.37</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9038</v>
+        <v>0.9271</v>
       </c>
       <c r="J169" t="n">
-        <v>22.595</v>
+        <v>23.1775</v>
       </c>
     </row>
     <row r="170">
@@ -10115,10 +10115,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1132</v>
+        <v>0.1943</v>
       </c>
       <c r="J170" t="n">
-        <v>2.83</v>
+        <v>4.8575</v>
       </c>
     </row>
     <row r="171">
@@ -10155,10 +10155,10 @@
         <v>1.01</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0146</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.345</v>
+        <v>-0.365</v>
       </c>
     </row>
     <row r="172">
@@ -10195,10 +10195,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2736</v>
+        <v>0.2891</v>
       </c>
       <c r="J172" t="n">
-        <v>5.7456</v>
+        <v>6.0711</v>
       </c>
     </row>
     <row r="173">
@@ -10235,10 +10235,10 @@
         <v>0.73</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3165</v>
+        <v>-0.2579</v>
       </c>
       <c r="J173" t="n">
-        <v>-6.6465</v>
+        <v>-5.4159</v>
       </c>
     </row>
     <row r="174">
@@ -10275,10 +10275,10 @@
         <v>0.58</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.578</v>
+        <v>-0.3974</v>
       </c>
       <c r="J174" t="n">
-        <v>-12.138</v>
+        <v>-8.3454</v>
       </c>
     </row>
     <row r="175">
@@ -10315,10 +10315,10 @@
         <v>0.49</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7067</v>
+        <v>-0.4815</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.8407</v>
+        <v>-10.1115</v>
       </c>
     </row>
     <row r="176">
@@ -10355,10 +10355,10 @@
         <v>0.35</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8868</v>
+        <v>-0.614</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.6228</v>
+        <v>-12.894</v>
       </c>
     </row>
     <row r="177">
@@ -10395,10 +10395,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5747</v>
+        <v>1.384</v>
       </c>
       <c r="J177" t="n">
-        <v>33.0687</v>
+        <v>29.064</v>
       </c>
     </row>
     <row r="178">
@@ -10435,10 +10435,10 @@
         <v>1.56</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2339</v>
+        <v>1.1725</v>
       </c>
       <c r="J178" t="n">
-        <v>25.9119</v>
+        <v>24.6225</v>
       </c>
     </row>
     <row r="179">
@@ -10475,10 +10475,10 @@
         <v>1.42</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9172</v>
+        <v>0.9971</v>
       </c>
       <c r="J179" t="n">
-        <v>19.2612</v>
+        <v>20.9391</v>
       </c>
     </row>
     <row r="180">
@@ -10515,10 +10515,10 @@
         <v>1.31</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6615</v>
+        <v>0.7734</v>
       </c>
       <c r="J180" t="n">
-        <v>13.8915</v>
+        <v>16.2414</v>
       </c>
     </row>
     <row r="181">
@@ -10555,10 +10555,10 @@
         <v>1.1</v>
       </c>
       <c r="I181" t="n">
-        <v>0.1563</v>
+        <v>0.2511</v>
       </c>
       <c r="J181" t="n">
-        <v>3.2823</v>
+        <v>5.2731</v>
       </c>
     </row>
     <row r="182">
@@ -10595,10 +10595,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4343</v>
+        <v>1.2774</v>
       </c>
       <c r="J182" t="n">
-        <v>35.8575</v>
+        <v>31.935</v>
       </c>
     </row>
     <row r="183">
@@ -10635,10 +10635,10 @@
         <v>1.19</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5622</v>
+        <v>0.5501</v>
       </c>
       <c r="J183" t="n">
-        <v>14.055</v>
+        <v>13.7525</v>
       </c>
     </row>
     <row r="184">
@@ -10675,10 +10675,10 @@
         <v>1.19</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5622</v>
+        <v>0.5501</v>
       </c>
       <c r="J184" t="n">
-        <v>14.055</v>
+        <v>13.7525</v>
       </c>
     </row>
     <row r="185">
@@ -10715,10 +10715,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3952</v>
+        <v>-0.3257</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.880000000000001</v>
+        <v>-8.1425</v>
       </c>
     </row>
     <row r="186">
@@ -10755,10 +10755,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.828</v>
+        <v>-0.7845</v>
       </c>
       <c r="J186" t="n">
-        <v>-20.7</v>
+        <v>-19.6125</v>
       </c>
     </row>
     <row r="187">
@@ -10795,10 +10795,10 @@
         <v>1.19</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3712</v>
+        <v>0.4222</v>
       </c>
       <c r="J187" t="n">
-        <v>9.279999999999999</v>
+        <v>10.555</v>
       </c>
     </row>
     <row r="188">
@@ -10835,10 +10835,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3416</v>
+        <v>0.3848</v>
       </c>
       <c r="J188" t="n">
-        <v>8.539999999999999</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -10875,10 +10875,10 @@
         <v>1.13</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2798</v>
+        <v>0.3079</v>
       </c>
       <c r="J189" t="n">
-        <v>6.995</v>
+        <v>7.6975</v>
       </c>
     </row>
     <row r="190">
@@ -10915,10 +10915,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.226</v>
+        <v>-0.1336</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.65</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="191">
@@ -10955,10 +10955,10 @@
         <v>0.58</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6691</v>
+        <v>-0.4468</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.7275</v>
+        <v>-11.17</v>
       </c>
     </row>
     <row r="192">
@@ -10995,10 +10995,10 @@
         <v>0.9</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>-1.7842</v>
+        <v>-2.0196</v>
       </c>
     </row>
     <row r="193">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2955</v>
+        <v>-0.2335</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.501</v>
+        <v>-5.137</v>
       </c>
     </row>
     <row r="194">
@@ -11075,10 +11075,10 @@
         <v>0.74</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3459</v>
+        <v>-0.2627</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.6098</v>
+        <v>-5.7794</v>
       </c>
     </row>
     <row r="195">
@@ -11115,10 +11115,10 @@
         <v>0.59</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5955</v>
+        <v>-0.4009</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.101</v>
+        <v>-8.819800000000001</v>
       </c>
     </row>
     <row r="196">
@@ -11155,10 +11155,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6231</v>
+        <v>-0.4196</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.7082</v>
+        <v>-9.231199999999999</v>
       </c>
     </row>
     <row r="197">
@@ -11195,10 +11195,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8922</v>
+        <v>1.5994</v>
       </c>
       <c r="J197" t="n">
-        <v>41.6284</v>
+        <v>35.1868</v>
       </c>
     </row>
     <row r="198">
@@ -11235,10 +11235,10 @@
         <v>1.93</v>
       </c>
       <c r="I198" t="n">
-        <v>1.8777</v>
+        <v>1.5882</v>
       </c>
       <c r="J198" t="n">
-        <v>41.3094</v>
+        <v>34.9404</v>
       </c>
     </row>
     <row r="199">
@@ -11275,10 +11275,10 @@
         <v>1.37</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7694</v>
+        <v>0.894</v>
       </c>
       <c r="J199" t="n">
-        <v>16.9268</v>
+        <v>19.668</v>
       </c>
     </row>
     <row r="200">
@@ -11315,10 +11315,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.194</v>
+        <v>0.2945</v>
       </c>
       <c r="J200" t="n">
-        <v>4.268</v>
+        <v>6.479</v>
       </c>
     </row>
     <row r="201">
@@ -11355,10 +11355,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.0582</v>
+        <v>0.1508</v>
       </c>
       <c r="J201" t="n">
-        <v>1.2804</v>
+        <v>3.3176</v>
       </c>
     </row>
     <row r="202">
@@ -11395,10 +11395,10 @@
         <v>1.57</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3244</v>
+        <v>1.2122</v>
       </c>
       <c r="J202" t="n">
-        <v>34.4344</v>
+        <v>31.5172</v>
       </c>
     </row>
     <row r="203">
@@ -11435,10 +11435,10 @@
         <v>1.4</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9769</v>
+        <v>0.9873</v>
       </c>
       <c r="J203" t="n">
-        <v>25.3994</v>
+        <v>25.6698</v>
       </c>
     </row>
     <row r="204">
@@ -11475,10 +11475,10 @@
         <v>1.35</v>
       </c>
       <c r="I204" t="n">
-        <v>0.865</v>
+        <v>0.8871</v>
       </c>
       <c r="J204" t="n">
-        <v>22.49</v>
+        <v>23.0646</v>
       </c>
     </row>
     <row r="205">
@@ -11515,10 +11515,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0228</v>
+        <v>0.1012</v>
       </c>
       <c r="J205" t="n">
-        <v>0.5928</v>
+        <v>2.6312</v>
       </c>
     </row>
     <row r="206">
@@ -11555,10 +11555,10 @@
         <v>1.01</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0902</v>
+        <v>-0.0118</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.3452</v>
+        <v>-0.3068</v>
       </c>
     </row>
     <row r="207">
@@ -11595,10 +11595,10 @@
         <v>1.15</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3626</v>
+        <v>0.3991</v>
       </c>
       <c r="J207" t="n">
-        <v>9.4276</v>
+        <v>10.3766</v>
       </c>
     </row>
     <row r="208">
@@ -11635,10 +11635,10 @@
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2703</v>
+        <v>-0.1818</v>
       </c>
       <c r="J208" t="n">
-        <v>-7.0278</v>
+        <v>-4.7268</v>
       </c>
     </row>
     <row r="209">
@@ -11675,10 +11675,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3226</v>
+        <v>-0.2115</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.387600000000001</v>
+        <v>-5.499</v>
       </c>
     </row>
     <row r="210">
@@ -11715,10 +11715,10 @@
         <v>0.74</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4307</v>
+        <v>-0.28</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.1982</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="211">
@@ -11755,10 +11755,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4307</v>
+        <v>-0.28</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.1982</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="212">
@@ -11795,10 +11795,10 @@
         <v>0.93</v>
       </c>
       <c r="I212" t="n">
-        <v>0.0242</v>
+        <v>-0.0169</v>
       </c>
       <c r="J212" t="n">
-        <v>0.4598</v>
+        <v>-0.3211</v>
       </c>
     </row>
     <row r="213">
@@ -11835,10 +11835,10 @@
         <v>0.67</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.3958</v>
+        <v>-0.3115</v>
       </c>
       <c r="J213" t="n">
-        <v>-7.5202</v>
+        <v>-5.9185</v>
       </c>
     </row>
     <row r="214">
@@ -11875,10 +11875,10 @@
         <v>0.61</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.5072</v>
+        <v>-0.3665</v>
       </c>
       <c r="J214" t="n">
-        <v>-9.636799999999999</v>
+        <v>-6.9635</v>
       </c>
     </row>
     <row r="215">
@@ -11915,10 +11915,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6103</v>
+        <v>-0.4205</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.5957</v>
+        <v>-7.9895</v>
       </c>
     </row>
     <row r="216">
@@ -11955,10 +11955,10 @@
         <v>0.3</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.917</v>
+        <v>-12.4982</v>
       </c>
     </row>
     <row r="217">
@@ -11995,10 +11995,10 @@
         <v>2.17</v>
       </c>
       <c r="I217" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J217" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="218">
@@ -12035,10 +12035,10 @@
         <v>1.67</v>
       </c>
       <c r="I218" t="n">
-        <v>1.397</v>
+        <v>1.2853</v>
       </c>
       <c r="J218" t="n">
-        <v>26.543</v>
+        <v>24.4207</v>
       </c>
     </row>
     <row r="219">
@@ -12075,10 +12075,10 @@
         <v>1.4</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8132</v>
+        <v>0.9462</v>
       </c>
       <c r="J219" t="n">
-        <v>15.4508</v>
+        <v>17.9778</v>
       </c>
     </row>
     <row r="220">
@@ -12115,10 +12115,10 @@
         <v>1.26</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5124</v>
+        <v>0.6362</v>
       </c>
       <c r="J220" t="n">
-        <v>9.7356</v>
+        <v>12.0878</v>
       </c>
     </row>
     <row r="221">
@@ -12155,10 +12155,10 @@
         <v>1.19</v>
       </c>
       <c r="I221" t="n">
-        <v>0.3531</v>
+        <v>0.4668</v>
       </c>
       <c r="J221" t="n">
-        <v>6.7089</v>
+        <v>8.869199999999999</v>
       </c>
     </row>
     <row r="222">
@@ -12195,10 +12195,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.571</v>
+        <v>0.6877</v>
       </c>
       <c r="J222" t="n">
-        <v>15.417</v>
+        <v>18.5679</v>
       </c>
     </row>
     <row r="223">
@@ -12235,10 +12235,10 @@
         <v>1.32</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5329</v>
+        <v>0.6369</v>
       </c>
       <c r="J223" t="n">
-        <v>14.3883</v>
+        <v>17.1963</v>
       </c>
     </row>
     <row r="224">
@@ -12275,10 +12275,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1363</v>
+        <v>0.1544</v>
       </c>
       <c r="J224" t="n">
-        <v>3.6801</v>
+        <v>4.1688</v>
       </c>
     </row>
     <row r="225">
@@ -12315,10 +12315,10 @@
         <v>0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1875</v>
+        <v>-0.1043</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.0625</v>
+        <v>-2.8161</v>
       </c>
     </row>
     <row r="226">
@@ -12355,10 +12355,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7221</v>
+        <v>-0.4873</v>
       </c>
       <c r="J226" t="n">
-        <v>-19.4967</v>
+        <v>-13.1571</v>
       </c>
     </row>
     <row r="227">
@@ -12395,10 +12395,10 @@
         <v>1.68</v>
       </c>
       <c r="I227" t="n">
-        <v>1.5968</v>
+        <v>1.3877</v>
       </c>
       <c r="J227" t="n">
-        <v>43.1136</v>
+        <v>37.4679</v>
       </c>
     </row>
     <row r="228">
@@ -12435,10 +12435,10 @@
         <v>1.27</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7557</v>
+        <v>0.7413</v>
       </c>
       <c r="J228" t="n">
-        <v>20.4039</v>
+        <v>20.0151</v>
       </c>
     </row>
     <row r="229">
@@ -12475,10 +12475,10 @@
         <v>1.11</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3018</v>
+        <v>0.3436</v>
       </c>
       <c r="J229" t="n">
-        <v>8.1486</v>
+        <v>9.277200000000001</v>
       </c>
     </row>
     <row r="230">
@@ -12515,10 +12515,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.339</v>
+        <v>-0.2672</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.153</v>
+        <v>-7.2144</v>
       </c>
     </row>
     <row r="231">
@@ -12555,10 +12555,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.9426</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>-25.4502</v>
+        <v>-24.5916</v>
       </c>
     </row>
     <row r="232">
@@ -12595,10 +12595,10 @@
         <v>1.99</v>
       </c>
       <c r="I232" t="n">
-        <v>2.0064</v>
+        <v>1.714</v>
       </c>
       <c r="J232" t="n">
-        <v>46.1472</v>
+        <v>39.422</v>
       </c>
     </row>
     <row r="233">
@@ -12635,10 +12635,10 @@
         <v>1.32</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7914</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="J233" t="n">
-        <v>18.2022</v>
+        <v>18.8623</v>
       </c>
     </row>
     <row r="234">
@@ -12675,10 +12675,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2027</v>
+        <v>0.2842</v>
       </c>
       <c r="J234" t="n">
-        <v>4.6621</v>
+        <v>6.5366</v>
       </c>
     </row>
     <row r="235">
@@ -12715,10 +12715,10 @@
         <v>1.03</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.013</v>
+        <v>0.0655</v>
       </c>
       <c r="J235" t="n">
-        <v>-0.299</v>
+        <v>1.5065</v>
       </c>
     </row>
     <row r="236">
@@ -12755,10 +12755,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3519</v>
+        <v>-0.2694</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.0937</v>
+        <v>-6.1962</v>
       </c>
     </row>
     <row r="237">
@@ -12795,10 +12795,10 @@
         <v>1.12</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3056</v>
+        <v>0.3262</v>
       </c>
       <c r="J237" t="n">
-        <v>7.0288</v>
+        <v>7.5026</v>
       </c>
     </row>
     <row r="238">
@@ -12835,10 +12835,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2894</v>
+        <v>0.3053</v>
       </c>
       <c r="J238" t="n">
-        <v>6.6562</v>
+        <v>7.0219</v>
       </c>
     </row>
     <row r="239">
@@ -12875,10 +12875,10 @@
         <v>0.98</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0003</v>
+        <v>-0.0233</v>
       </c>
       <c r="J239" t="n">
-        <v>0.0069</v>
+        <v>-0.5359</v>
       </c>
     </row>
     <row r="240">
@@ -12915,10 +12915,10 @@
         <v>0.78</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.38</v>
+        <v>-0.2444</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.74</v>
+        <v>-5.6212</v>
       </c>
     </row>
     <row r="241">
@@ -12955,10 +12955,10 @@
         <v>0.42</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8416</v>
+        <v>-0.5795</v>
       </c>
       <c r="J241" t="n">
-        <v>-19.3568</v>
+        <v>-13.3285</v>
       </c>
     </row>
     <row r="242">
@@ -12995,10 +12995,10 @@
         <v>0.83</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.2172</v>
+        <v>-0.1791</v>
       </c>
       <c r="J242" t="n">
-        <v>-4.7784</v>
+        <v>-3.9402</v>
       </c>
     </row>
     <row r="243">
@@ -13035,10 +13035,10 @@
         <v>0.79</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2842</v>
+        <v>-0.2198</v>
       </c>
       <c r="J243" t="n">
-        <v>-6.2524</v>
+        <v>-4.8356</v>
       </c>
     </row>
     <row r="244">
@@ -13075,10 +13075,10 @@
         <v>0.78</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3014</v>
+        <v>-0.2296</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.6308</v>
+        <v>-5.0512</v>
       </c>
     </row>
     <row r="245">
@@ -13115,10 +13115,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.338</v>
+        <v>-0.2485</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.436</v>
+        <v>-5.467</v>
       </c>
     </row>
     <row r="246">
@@ -13155,10 +13155,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5942</v>
+        <v>-0.3975</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.0724</v>
+        <v>-8.744999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -13195,10 +13195,10 @@
         <v>2.12</v>
       </c>
       <c r="I247" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J247" t="n">
-        <v>45.3046</v>
+        <v>40.3436</v>
       </c>
     </row>
     <row r="248">
@@ -13235,10 +13235,10 @@
         <v>1.45</v>
       </c>
       <c r="I248" t="n">
-        <v>1.0499</v>
+        <v>1.0507</v>
       </c>
       <c r="J248" t="n">
-        <v>23.0978</v>
+        <v>23.1154</v>
       </c>
     </row>
     <row r="249">
@@ -13275,10 +13275,10 @@
         <v>1.3</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6812</v>
+        <v>0.7672</v>
       </c>
       <c r="J249" t="n">
-        <v>14.9864</v>
+        <v>16.8784</v>
       </c>
     </row>
     <row r="250">
@@ -13315,10 +13315,10 @@
         <v>1.15</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3136</v>
+        <v>0.406</v>
       </c>
       <c r="J250" t="n">
-        <v>6.8992</v>
+        <v>8.932</v>
       </c>
     </row>
     <row r="251">
@@ -13355,10 +13355,10 @@
         <v>0.68</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.0219</v>
+        <v>-1.0002</v>
       </c>
       <c r="J251" t="n">
-        <v>-22.4818</v>
+        <v>-22.0044</v>
       </c>
     </row>
     <row r="252">
@@ -13395,10 +13395,10 @@
         <v>1.5</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1423</v>
+        <v>1.1092</v>
       </c>
       <c r="J252" t="n">
-        <v>27.4152</v>
+        <v>26.6208</v>
       </c>
     </row>
     <row r="253">
@@ -13435,10 +13435,10 @@
         <v>1.44</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0153</v>
+        <v>1.0336</v>
       </c>
       <c r="J253" t="n">
-        <v>24.3672</v>
+        <v>24.8064</v>
       </c>
     </row>
     <row r="254">
@@ -13475,10 +13475,10 @@
         <v>1.4</v>
       </c>
       <c r="I254" t="n">
-        <v>0.925</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="J254" t="n">
-        <v>22.2</v>
+        <v>23.2872</v>
       </c>
     </row>
     <row r="255">
@@ -13515,10 +13515,10 @@
         <v>1.3</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6675</v>
+        <v>0.7629</v>
       </c>
       <c r="J255" t="n">
-        <v>16.02</v>
+        <v>18.3096</v>
       </c>
     </row>
     <row r="256">
@@ -13555,10 +13555,10 @@
         <v>1.18</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3804</v>
+        <v>0.4778</v>
       </c>
       <c r="J256" t="n">
-        <v>9.1296</v>
+        <v>11.4672</v>
       </c>
     </row>
     <row r="257">
@@ -13595,10 +13595,10 @@
         <v>1.01</v>
       </c>
       <c r="I257" t="n">
-        <v>0.1467</v>
+        <v>0.1165</v>
       </c>
       <c r="J257" t="n">
-        <v>3.5208</v>
+        <v>2.796</v>
       </c>
     </row>
     <row r="258">
@@ -13635,10 +13635,10 @@
         <v>0.93</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0488</v>
+        <v>-0.0667</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.1712</v>
+        <v>-1.6008</v>
       </c>
     </row>
     <row r="259">
@@ -13675,10 +13675,10 @@
         <v>0.76</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3478</v>
+        <v>-0.2491</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.347200000000001</v>
+        <v>-5.9784</v>
       </c>
     </row>
     <row r="260">
@@ -13715,10 +13715,10 @@
         <v>0.64</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5415</v>
+        <v>-0.3613</v>
       </c>
       <c r="J260" t="n">
-        <v>-12.996</v>
+        <v>-8.671200000000001</v>
       </c>
     </row>
     <row r="261">
@@ -13755,10 +13755,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7759</v>
+        <v>-0.5289</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.6216</v>
+        <v>-12.6936</v>
       </c>
     </row>
     <row r="262">
@@ -13795,10 +13795,10 @@
         <v>1.83</v>
       </c>
       <c r="I262" t="n">
-        <v>1.7303</v>
+        <v>1.4857</v>
       </c>
       <c r="J262" t="n">
-        <v>36.3363</v>
+        <v>31.1997</v>
       </c>
     </row>
     <row r="263">
@@ -13835,10 +13835,10 @@
         <v>1.5</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1049</v>
+        <v>1.0997</v>
       </c>
       <c r="J263" t="n">
-        <v>23.2029</v>
+        <v>23.0937</v>
       </c>
     </row>
     <row r="264">
@@ -13875,10 +13875,10 @@
         <v>1.38</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8147</v>
+        <v>0.9236</v>
       </c>
       <c r="J264" t="n">
-        <v>17.1087</v>
+        <v>19.3956</v>
       </c>
     </row>
     <row r="265">
@@ -13915,10 +13915,10 @@
         <v>1.31</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6574</v>
+        <v>0.7714</v>
       </c>
       <c r="J265" t="n">
-        <v>13.8054</v>
+        <v>16.1994</v>
       </c>
     </row>
     <row r="266">
@@ -13955,10 +13955,10 @@
         <v>1.16</v>
       </c>
       <c r="I266" t="n">
-        <v>0.308</v>
+        <v>0.4112</v>
       </c>
       <c r="J266" t="n">
-        <v>6.468</v>
+        <v>8.635199999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13995,10 +13995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I267" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0596</v>
       </c>
       <c r="J267" t="n">
-        <v>1.7241</v>
+        <v>1.2516</v>
       </c>
     </row>
     <row r="268">
@@ -14035,10 +14035,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.5329</v>
+        <v>-0.4013</v>
       </c>
       <c r="J268" t="n">
-        <v>-11.1909</v>
+        <v>-8.427300000000001</v>
       </c>
     </row>
     <row r="269">
@@ -14075,10 +14075,10 @@
         <v>0.5</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.6509</v>
+        <v>-0.4543</v>
       </c>
       <c r="J269" t="n">
-        <v>-13.6689</v>
+        <v>-9.5403</v>
       </c>
     </row>
     <row r="270">
@@ -14115,10 +14115,10 @@
         <v>0.49</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.6667</v>
+        <v>-0.4635</v>
       </c>
       <c r="J270" t="n">
-        <v>-14.0007</v>
+        <v>-9.733499999999999</v>
       </c>
     </row>
     <row r="271">
@@ -14155,10 +14155,10 @@
         <v>0.24</v>
       </c>
       <c r="I271" t="n">
-        <v>-1.0048</v>
+        <v>-0.7065</v>
       </c>
       <c r="J271" t="n">
-        <v>-21.1008</v>
+        <v>-14.8365</v>
       </c>
     </row>
     <row r="272">
@@ -14195,10 +14195,10 @@
         <v>1.16</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3222</v>
+        <v>0.3623</v>
       </c>
       <c r="J272" t="n">
-        <v>14.8212</v>
+        <v>16.6658</v>
       </c>
     </row>
     <row r="273">
@@ -14235,10 +14235,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3069</v>
+        <v>0.3433</v>
       </c>
       <c r="J273" t="n">
-        <v>14.1174</v>
+        <v>15.7918</v>
       </c>
     </row>
     <row r="274">
@@ -14275,10 +14275,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1327</v>
+        <v>0.1381</v>
       </c>
       <c r="J274" t="n">
-        <v>6.1042</v>
+        <v>6.3526</v>
       </c>
     </row>
     <row r="275">
@@ -14315,10 +14315,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0359</v>
+        <v>0.037</v>
       </c>
       <c r="J275" t="n">
-        <v>1.6514</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="276">
@@ -14355,10 +14355,10 @@
         <v>0.66</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5726</v>
+        <v>-0.3745</v>
       </c>
       <c r="J276" t="n">
-        <v>-26.3396</v>
+        <v>-17.227</v>
       </c>
     </row>
     <row r="277">
@@ -14395,10 +14395,10 @@
         <v>1.36</v>
       </c>
       <c r="I277" t="n">
-        <v>0.98</v>
+        <v>0.962</v>
       </c>
       <c r="J277" t="n">
-        <v>45.08</v>
+        <v>44.252</v>
       </c>
     </row>
     <row r="278">
@@ -14435,10 +14435,10 @@
         <v>1.25</v>
       </c>
       <c r="I278" t="n">
-        <v>0.7286</v>
+        <v>0.7053</v>
       </c>
       <c r="J278" t="n">
-        <v>33.5156</v>
+        <v>32.4438</v>
       </c>
     </row>
     <row r="279">
@@ -14475,10 +14475,10 @@
         <v>1.01</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.022</v>
+        <v>0.0308</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.012</v>
+        <v>1.4168</v>
       </c>
     </row>
     <row r="280">
@@ -14515,10 +14515,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1415</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.509</v>
+        <v>-3.6202</v>
       </c>
     </row>
     <row r="281">
@@ -14555,10 +14555,10 @@
         <v>0.91</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4153</v>
+        <v>-0.3491</v>
       </c>
       <c r="J281" t="n">
-        <v>-19.1038</v>
+        <v>-16.0586</v>
       </c>
     </row>
     <row r="282">
@@ -14595,10 +14595,10 @@
         <v>1.87</v>
       </c>
       <c r="I282" t="n">
-        <v>1.8012</v>
+        <v>1.5322</v>
       </c>
       <c r="J282" t="n">
-        <v>36.024</v>
+        <v>30.644</v>
       </c>
     </row>
     <row r="283">
@@ -14635,10 +14635,10 @@
         <v>1.82</v>
       </c>
       <c r="I283" t="n">
-        <v>1.7145</v>
+        <v>1.4751</v>
       </c>
       <c r="J283" t="n">
-        <v>34.29</v>
+        <v>29.502</v>
       </c>
     </row>
     <row r="284">
@@ -14675,10 +14675,10 @@
         <v>1.53</v>
       </c>
       <c r="I284" t="n">
-        <v>1.17</v>
+        <v>1.1359</v>
       </c>
       <c r="J284" t="n">
-        <v>23.4</v>
+        <v>22.718</v>
       </c>
     </row>
     <row r="285">
@@ -14715,10 +14715,10 @@
         <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.189</v>
+        <v>-0.1015</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.78</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="286">
@@ -14755,10 +14755,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4185</v>
+        <v>-0.3347</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.369999999999999</v>
+        <v>-6.694</v>
       </c>
     </row>
     <row r="287">
@@ -14795,10 +14795,10 @@
         <v>1.01</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1723</v>
+        <v>0.1495</v>
       </c>
       <c r="J287" t="n">
-        <v>3.446</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="288">
@@ -14835,10 +14835,10 @@
         <v>0.9</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.089</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.526</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="289">
@@ -14875,10 +14875,10 @@
         <v>0.73</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3564</v>
+        <v>-0.2707</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.128</v>
+        <v>-5.414</v>
       </c>
     </row>
     <row r="290">
@@ -14915,10 +14915,10 @@
         <v>0.49</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.726</v>
+        <v>-0.4927</v>
       </c>
       <c r="J290" t="n">
-        <v>-14.52</v>
+        <v>-9.853999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -14955,10 +14955,10 @@
         <v>0.39</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.8506</v>
+        <v>-0.586</v>
       </c>
       <c r="J291" t="n">
-        <v>-17.012</v>
+        <v>-11.72</v>
       </c>
     </row>
     <row r="292">
@@ -14995,10 +14995,10 @@
         <v>1.46</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1727</v>
+        <v>1.1056</v>
       </c>
       <c r="J292" t="n">
-        <v>48.0807</v>
+        <v>45.3296</v>
       </c>
     </row>
     <row r="293">
@@ -15035,10 +15035,10 @@
         <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1522</v>
+        <v>1.0924</v>
       </c>
       <c r="J293" t="n">
-        <v>47.2402</v>
+        <v>44.7884</v>
       </c>
     </row>
     <row r="294">
@@ -15075,10 +15075,10 @@
         <v>1.05</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1127</v>
+        <v>0.1676</v>
       </c>
       <c r="J294" t="n">
-        <v>4.6207</v>
+        <v>6.8716</v>
       </c>
     </row>
     <row r="295">
@@ -15115,10 +15115,10 @@
         <v>0.89</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.484</v>
+        <v>-0.4163</v>
       </c>
       <c r="J295" t="n">
-        <v>-19.844</v>
+        <v>-17.0683</v>
       </c>
     </row>
     <row r="296">
@@ -15155,10 +15155,10 @@
         <v>0.84</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.5544</v>
       </c>
       <c r="J296" t="n">
-        <v>-25.2314</v>
+        <v>-22.7304</v>
       </c>
     </row>
     <row r="297">
@@ -15195,10 +15195,10 @@
         <v>1.31</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5193</v>
+        <v>0.6192</v>
       </c>
       <c r="J297" t="n">
-        <v>21.2913</v>
+        <v>25.3872</v>
       </c>
     </row>
     <row r="298">
@@ -15235,10 +15235,10 @@
         <v>1.17</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3245</v>
+        <v>0.3713</v>
       </c>
       <c r="J298" t="n">
-        <v>13.3045</v>
+        <v>15.2233</v>
       </c>
     </row>
     <row r="299">
@@ -15275,10 +15275,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1696</v>
+        <v>-0.0925</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.9536</v>
+        <v>-3.7925</v>
       </c>
     </row>
     <row r="300">
@@ -15315,10 +15315,10 @@
         <v>0.93</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.188</v>
+        <v>-0.1045</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.708</v>
+        <v>-4.2845</v>
       </c>
     </row>
     <row r="301">
@@ -15355,10 +15355,10 @@
         <v>0.86</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3042</v>
+        <v>-0.1822</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.4722</v>
+        <v>-7.4702</v>
       </c>
     </row>
     <row r="302">
@@ -15395,10 +15395,10 @@
         <v>1.23</v>
       </c>
       <c r="I302" t="n">
-        <v>0.7259</v>
+        <v>0.6864</v>
       </c>
       <c r="J302" t="n">
-        <v>21.0511</v>
+        <v>19.9056</v>
       </c>
     </row>
     <row r="303">
@@ -15435,10 +15435,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5213</v>
+        <v>0.4784</v>
       </c>
       <c r="J303" t="n">
-        <v>15.1177</v>
+        <v>13.8736</v>
       </c>
     </row>
     <row r="304">
@@ -15475,10 +15475,10 @@
         <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0318</v>
+        <v>-0.0047</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.9222</v>
+        <v>-0.1363</v>
       </c>
     </row>
     <row r="305">
@@ -15515,10 +15515,10 @@
         <v>0.97</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1798</v>
+        <v>-0.1364</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.2142</v>
+        <v>-3.9556</v>
       </c>
     </row>
     <row r="306">
@@ -15555,10 +15555,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7266</v>
+        <v>-0.6806</v>
       </c>
       <c r="J306" t="n">
-        <v>-21.0714</v>
+        <v>-19.7374</v>
       </c>
     </row>
     <row r="307">
@@ -15595,10 +15595,10 @@
         <v>1.54</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7896</v>
+        <v>0.9813</v>
       </c>
       <c r="J307" t="n">
-        <v>22.8984</v>
+        <v>28.4577</v>
       </c>
     </row>
     <row r="308">
@@ -15635,10 +15635,10 @@
         <v>1.06</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1213</v>
+        <v>0.1521</v>
       </c>
       <c r="J308" t="n">
-        <v>3.5177</v>
+        <v>4.4109</v>
       </c>
     </row>
     <row r="309">
@@ -15675,10 +15675,10 @@
         <v>0.96</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1362</v>
+        <v>-0.0693</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.9498</v>
+        <v>-2.0097</v>
       </c>
     </row>
     <row r="310">
@@ -15715,10 +15715,10 @@
         <v>0.92</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2109</v>
+        <v>-0.1181</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.1161</v>
+        <v>-3.4249</v>
       </c>
     </row>
     <row r="311">
@@ -15755,10 +15755,10 @@
         <v>0.82</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3679</v>
+        <v>-0.2256</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.6691</v>
+        <v>-6.5424</v>
       </c>
     </row>
     <row r="312">
@@ -15795,10 +15795,10 @@
         <v>1.45</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0945</v>
+        <v>1.0661</v>
       </c>
       <c r="J312" t="n">
-        <v>38.3075</v>
+        <v>37.3135</v>
       </c>
     </row>
     <row r="313">
@@ -15835,10 +15835,10 @@
         <v>1.4</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9885</v>
+        <v>0.9923</v>
       </c>
       <c r="J313" t="n">
-        <v>34.5975</v>
+        <v>34.7305</v>
       </c>
     </row>
     <row r="314">
@@ -15875,10 +15875,10 @@
         <v>1.3</v>
       </c>
       <c r="I314" t="n">
-        <v>0.7599</v>
+        <v>0.7808</v>
       </c>
       <c r="J314" t="n">
-        <v>26.5965</v>
+        <v>27.328</v>
       </c>
     </row>
     <row r="315">
@@ -15915,10 +15915,10 @@
         <v>1.15</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3497</v>
+        <v>0.4258</v>
       </c>
       <c r="J315" t="n">
-        <v>12.2395</v>
+        <v>14.903</v>
       </c>
     </row>
     <row r="316">
@@ -15955,10 +15955,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3121</v>
+        <v>-0.2298</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.9235</v>
+        <v>-8.042999999999999</v>
       </c>
     </row>
     <row r="317">
@@ -15995,10 +15995,10 @@
         <v>0.99</v>
       </c>
       <c r="I317" t="n">
-        <v>0.024</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J317" t="n">
-        <v>0.84</v>
+        <v>-0.2765</v>
       </c>
     </row>
     <row r="318">
@@ -16035,10 +16035,10 @@
         <v>0.99</v>
       </c>
       <c r="I318" t="n">
-        <v>0.024</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J318" t="n">
-        <v>0.84</v>
+        <v>-0.2765</v>
       </c>
     </row>
     <row r="319">
@@ -16075,10 +16075,10 @@
         <v>0.93</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1067</v>
+        <v>-0.0895</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.7345</v>
+        <v>-3.1325</v>
       </c>
     </row>
     <row r="320">
@@ -16115,10 +16115,10 @@
         <v>0.78</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3814</v>
+        <v>-0.2449</v>
       </c>
       <c r="J320" t="n">
-        <v>-13.349</v>
+        <v>-8.5715</v>
       </c>
     </row>
     <row r="321">
@@ -16155,10 +16155,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4399</v>
+        <v>-0.2839</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.3965</v>
+        <v>-9.936500000000001</v>
       </c>
     </row>
     <row r="322">
@@ -16195,10 +16195,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2704</v>
+        <v>0.2868</v>
       </c>
       <c r="J322" t="n">
-        <v>6.76</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="323">
@@ -16235,10 +16235,10 @@
         <v>1.01</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0743</v>
+        <v>0.0513</v>
       </c>
       <c r="J323" t="n">
-        <v>1.8575</v>
+        <v>1.2825</v>
       </c>
     </row>
     <row r="324">
@@ -16275,10 +16275,10 @@
         <v>0.89</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2199</v>
+        <v>-0.1378</v>
       </c>
       <c r="J324" t="n">
-        <v>-5.4975</v>
+        <v>-3.445</v>
       </c>
     </row>
     <row r="325">
@@ -16315,10 +16315,10 @@
         <v>0.86</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2717</v>
+        <v>-0.1696</v>
       </c>
       <c r="J325" t="n">
-        <v>-6.7925</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="326">
@@ -16355,10 +16355,10 @@
         <v>0.79</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3807</v>
+        <v>-0.2408</v>
       </c>
       <c r="J326" t="n">
-        <v>-9.5175</v>
+        <v>-6.02</v>
       </c>
     </row>
     <row r="327">
@@ -16395,10 +16395,10 @@
         <v>1.66</v>
       </c>
       <c r="I327" t="n">
-        <v>1.4987</v>
+        <v>1.3247</v>
       </c>
       <c r="J327" t="n">
-        <v>37.4675</v>
+        <v>33.1175</v>
       </c>
     </row>
     <row r="328">
@@ -16435,10 +16435,10 @@
         <v>1.39</v>
       </c>
       <c r="I328" t="n">
-        <v>0.9594</v>
+        <v>0.9711</v>
       </c>
       <c r="J328" t="n">
-        <v>23.985</v>
+        <v>24.2775</v>
       </c>
     </row>
     <row r="329">
@@ -16475,10 +16475,10 @@
         <v>1.32</v>
       </c>
       <c r="I329" t="n">
-        <v>0.7993</v>
+        <v>0.8226</v>
       </c>
       <c r="J329" t="n">
-        <v>19.9825</v>
+        <v>20.565</v>
       </c>
     </row>
     <row r="330">
@@ -16515,10 +16515,10 @@
         <v>1.03</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.0091</v>
+        <v>0.0683</v>
       </c>
       <c r="J330" t="n">
-        <v>-0.2275</v>
+        <v>1.7075</v>
       </c>
     </row>
     <row r="331">
@@ -16555,10 +16555,10 @@
         <v>0.93</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4096</v>
+        <v>-0.33</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.24</v>
+        <v>-8.25</v>
       </c>
     </row>
     <row r="332">
@@ -16595,10 +16595,10 @@
         <v>1.35</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9559</v>
+        <v>0.9396</v>
       </c>
       <c r="J332" t="n">
-        <v>34.4124</v>
+        <v>33.8256</v>
       </c>
     </row>
     <row r="333">
@@ -16635,10 +16635,10 @@
         <v>1.29</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8208</v>
+        <v>0.8002</v>
       </c>
       <c r="J333" t="n">
-        <v>29.5488</v>
+        <v>28.8072</v>
       </c>
     </row>
     <row r="334">
@@ -16675,10 +16675,10 @@
         <v>1.04</v>
       </c>
       <c r="I334" t="n">
-        <v>0.095</v>
+        <v>0.142</v>
       </c>
       <c r="J334" t="n">
-        <v>3.42</v>
+        <v>5.112</v>
       </c>
     </row>
     <row r="335">
@@ -16715,10 +16715,10 @@
         <v>1.01</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0241</v>
+        <v>0.0298</v>
       </c>
       <c r="J335" t="n">
-        <v>-0.8676</v>
+        <v>1.0728</v>
       </c>
     </row>
     <row r="336">
@@ -16755,10 +16755,10 @@
         <v>0.85</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5802</v>
+        <v>-0.5194</v>
       </c>
       <c r="J336" t="n">
-        <v>-20.8872</v>
+        <v>-18.6984</v>
       </c>
     </row>
     <row r="337">
@@ -16795,10 +16795,10 @@
         <v>1.6</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8562</v>
+        <v>1.049</v>
       </c>
       <c r="J337" t="n">
-        <v>30.8232</v>
+        <v>37.764</v>
       </c>
     </row>
     <row r="338">
@@ -16835,10 +16835,10 @@
         <v>1.1</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2032</v>
+        <v>0.2336</v>
       </c>
       <c r="J338" t="n">
-        <v>7.3152</v>
+        <v>8.409599999999999</v>
       </c>
     </row>
     <row r="339">
@@ -16875,10 +16875,10 @@
         <v>1.04</v>
       </c>
       <c r="I339" t="n">
-        <v>0.0743</v>
+        <v>0.1079</v>
       </c>
       <c r="J339" t="n">
-        <v>2.6748</v>
+        <v>3.8844</v>
       </c>
     </row>
     <row r="340">
@@ -16915,10 +16915,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3679</v>
+        <v>-0.2256</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.2444</v>
+        <v>-8.121600000000001</v>
       </c>
     </row>
     <row r="341">
@@ -16955,10 +16955,10 @@
         <v>0.74</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4783</v>
+        <v>-0.3046</v>
       </c>
       <c r="J341" t="n">
-        <v>-17.2188</v>
+        <v>-10.9656</v>
       </c>
     </row>
     <row r="342">
@@ -16995,10 +16995,10 @@
         <v>1.12</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3692</v>
+        <v>0.4095</v>
       </c>
       <c r="J342" t="n">
-        <v>7.0148</v>
+        <v>7.7805</v>
       </c>
     </row>
     <row r="343">
@@ -17035,10 +17035,10 @@
         <v>0.74</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.3579</v>
+        <v>-0.2647</v>
       </c>
       <c r="J343" t="n">
-        <v>-6.8001</v>
+        <v>-5.0293</v>
       </c>
     </row>
     <row r="344">
@@ -17075,10 +17075,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.4543</v>
+        <v>-0.31</v>
       </c>
       <c r="J344" t="n">
-        <v>-8.6317</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="345">
@@ -17115,10 +17115,10 @@
         <v>0.63</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.5448</v>
+        <v>-0.366</v>
       </c>
       <c r="J345" t="n">
-        <v>-10.3512</v>
+        <v>-6.954</v>
       </c>
     </row>
     <row r="346">
@@ -17155,10 +17155,10 @@
         <v>0.47</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.7575</v>
+        <v>-0.5154</v>
       </c>
       <c r="J346" t="n">
-        <v>-14.3925</v>
+        <v>-9.7926</v>
       </c>
     </row>
     <row r="347">
@@ -17195,10 +17195,10 @@
         <v>1.61</v>
       </c>
       <c r="I347" t="n">
-        <v>1.3475</v>
+        <v>1.2374</v>
       </c>
       <c r="J347" t="n">
-        <v>25.6025</v>
+        <v>23.5106</v>
       </c>
     </row>
     <row r="348">
@@ -17235,10 +17235,10 @@
         <v>1.57</v>
       </c>
       <c r="I348" t="n">
-        <v>1.2697</v>
+        <v>1.1896</v>
       </c>
       <c r="J348" t="n">
-        <v>24.1243</v>
+        <v>22.6024</v>
       </c>
     </row>
     <row r="349">
@@ -17275,10 +17275,10 @@
         <v>1.48</v>
       </c>
       <c r="I349" t="n">
-        <v>1.0862</v>
+        <v>1.0809</v>
       </c>
       <c r="J349" t="n">
-        <v>20.6378</v>
+        <v>20.5371</v>
       </c>
     </row>
     <row r="350">
@@ -17315,10 +17315,10 @@
         <v>1.3</v>
       </c>
       <c r="I350" t="n">
-        <v>0.6536</v>
+        <v>0.7575</v>
       </c>
       <c r="J350" t="n">
-        <v>12.4184</v>
+        <v>14.3925</v>
       </c>
     </row>
     <row r="351">
@@ -17355,10 +17355,10 @@
         <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.1798</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J351" t="n">
-        <v>-3.4162</v>
+        <v>-1.7708</v>
       </c>
     </row>
     <row r="352">
@@ -17395,10 +17395,10 @@
         <v>1.41</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6737</v>
+        <v>0.8266</v>
       </c>
       <c r="J352" t="n">
-        <v>20.211</v>
+        <v>24.798</v>
       </c>
     </row>
     <row r="353">
@@ -17435,10 +17435,10 @@
         <v>1.06</v>
       </c>
       <c r="I353" t="n">
-        <v>0.1742</v>
+        <v>0.1729</v>
       </c>
       <c r="J353" t="n">
-        <v>5.226</v>
+        <v>5.187</v>
       </c>
     </row>
     <row r="354">
@@ -17475,10 +17475,10 @@
         <v>0.91</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1932</v>
+        <v>-0.1181</v>
       </c>
       <c r="J354" t="n">
-        <v>-5.796</v>
+        <v>-3.543</v>
       </c>
     </row>
     <row r="355">
@@ -17515,10 +17515,10 @@
         <v>0.73</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.4711</v>
+        <v>-0.3022</v>
       </c>
       <c r="J355" t="n">
-        <v>-14.133</v>
+        <v>-9.066000000000001</v>
       </c>
     </row>
     <row r="356">
@@ -17555,10 +17555,10 @@
         <v>0.66</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5635</v>
+        <v>-0.3686</v>
       </c>
       <c r="J356" t="n">
-        <v>-16.905</v>
+        <v>-11.058</v>
       </c>
     </row>
     <row r="357">
@@ -17595,10 +17595,10 @@
         <v>1.5</v>
       </c>
       <c r="I357" t="n">
-        <v>1.2292</v>
+        <v>1.145</v>
       </c>
       <c r="J357" t="n">
-        <v>36.876</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="358">
@@ -17635,10 +17635,10 @@
         <v>1.33</v>
       </c>
       <c r="I358" t="n">
-        <v>0.8691</v>
+        <v>0.8665</v>
       </c>
       <c r="J358" t="n">
-        <v>26.073</v>
+        <v>25.995</v>
       </c>
     </row>
     <row r="359">
@@ -17675,10 +17675,10 @@
         <v>1.18</v>
       </c>
       <c r="I359" t="n">
-        <v>0.4763</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J359" t="n">
-        <v>14.289</v>
+        <v>15.438</v>
       </c>
     </row>
     <row r="360">
@@ -17715,10 +17715,10 @@
         <v>1.03</v>
       </c>
       <c r="I360" t="n">
-        <v>0.0206</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J360" t="n">
-        <v>0.618</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="361">
@@ -17755,10 +17755,10 @@
         <v>0.89</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4994</v>
+        <v>-0.4287</v>
       </c>
       <c r="J361" t="n">
-        <v>-14.982</v>
+        <v>-12.861</v>
       </c>
     </row>
     <row r="362">
@@ -17795,10 +17795,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.4492</v>
+        <v>1.2915</v>
       </c>
       <c r="J362" t="n">
-        <v>33.3316</v>
+        <v>29.7045</v>
       </c>
     </row>
     <row r="363">
@@ -17835,10 +17835,10 @@
         <v>1.55</v>
       </c>
       <c r="I363" t="n">
-        <v>1.2959</v>
+        <v>1.1924</v>
       </c>
       <c r="J363" t="n">
-        <v>29.8057</v>
+        <v>27.4252</v>
       </c>
     </row>
     <row r="364">
@@ -17875,10 +17875,10 @@
         <v>1.39</v>
       </c>
       <c r="I364" t="n">
-        <v>0.9668</v>
+        <v>0.9744</v>
       </c>
       <c r="J364" t="n">
-        <v>22.2364</v>
+        <v>22.4112</v>
       </c>
     </row>
     <row r="365">
@@ -17915,10 +17915,10 @@
         <v>0.91</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4631</v>
+        <v>-0.3869</v>
       </c>
       <c r="J365" t="n">
-        <v>-10.6513</v>
+        <v>-8.8987</v>
       </c>
     </row>
     <row r="366">
@@ -17955,10 +17955,10 @@
         <v>0.78</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.7883</v>
+        <v>-0.7381</v>
       </c>
       <c r="J366" t="n">
-        <v>-18.1309</v>
+        <v>-16.9763</v>
       </c>
     </row>
     <row r="367">
@@ -17995,10 +17995,10 @@
         <v>0.99</v>
       </c>
       <c r="I367" t="n">
-        <v>0.0604</v>
+        <v>0.0166</v>
       </c>
       <c r="J367" t="n">
-        <v>1.3892</v>
+        <v>0.3818</v>
       </c>
     </row>
     <row r="368">
@@ -18035,10 +18035,10 @@
         <v>0.96</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0083</v>
+        <v>-0.0366</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.1909</v>
+        <v>-0.8418</v>
       </c>
     </row>
     <row r="369">
@@ -18075,10 +18075,10 @@
         <v>0.95</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.0284</v>
+        <v>-0.05</v>
       </c>
       <c r="J369" t="n">
-        <v>-0.6532</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="370">
@@ -18115,10 +18115,10 @@
         <v>0.58</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.6338</v>
+        <v>-0.4234</v>
       </c>
       <c r="J370" t="n">
-        <v>-14.5774</v>
+        <v>-9.738200000000001</v>
       </c>
     </row>
     <row r="371">
@@ -18155,10 +18155,10 @@
         <v>0.52</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.7099</v>
+        <v>-0.479</v>
       </c>
       <c r="J371" t="n">
-        <v>-16.3277</v>
+        <v>-11.017</v>
       </c>
     </row>
     <row r="372">
@@ -18195,10 +18195,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5661</v>
+        <v>0.6768</v>
       </c>
       <c r="J372" t="n">
-        <v>15.2847</v>
+        <v>18.2736</v>
       </c>
     </row>
     <row r="373">
@@ -18235,10 +18235,10 @@
         <v>1.12</v>
       </c>
       <c r="I373" t="n">
-        <v>0.283</v>
+        <v>0.3038</v>
       </c>
       <c r="J373" t="n">
-        <v>7.641</v>
+        <v>8.2026</v>
       </c>
     </row>
     <row r="374">
@@ -18275,10 +18275,10 @@
         <v>0.88</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.2417</v>
+        <v>-0.1496</v>
       </c>
       <c r="J374" t="n">
-        <v>-6.5259</v>
+        <v>-4.0392</v>
       </c>
     </row>
     <row r="375">
@@ -18315,10 +18315,10 @@
         <v>0.88</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.2417</v>
+        <v>-0.1496</v>
       </c>
       <c r="J375" t="n">
-        <v>-6.5259</v>
+        <v>-4.0392</v>
       </c>
     </row>
     <row r="376">
@@ -18355,10 +18355,10 @@
         <v>0.51</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.7451</v>
+        <v>-0.5048</v>
       </c>
       <c r="J376" t="n">
-        <v>-20.1177</v>
+        <v>-13.6296</v>
       </c>
     </row>
     <row r="377">
@@ -18395,10 +18395,10 @@
         <v>1.28</v>
       </c>
       <c r="I377" t="n">
-        <v>0.7805</v>
+        <v>0.7657</v>
       </c>
       <c r="J377" t="n">
-        <v>21.0735</v>
+        <v>20.6739</v>
       </c>
     </row>
     <row r="378">
@@ -18435,10 +18435,10 @@
         <v>1.19</v>
       </c>
       <c r="I378" t="n">
-        <v>0.5553</v>
+        <v>0.5476</v>
       </c>
       <c r="J378" t="n">
-        <v>14.9931</v>
+        <v>14.7852</v>
       </c>
     </row>
     <row r="379">
@@ -18475,10 +18475,10 @@
         <v>1.13</v>
       </c>
       <c r="I379" t="n">
-        <v>0.3671</v>
+        <v>0.3969</v>
       </c>
       <c r="J379" t="n">
-        <v>9.9117</v>
+        <v>10.7163</v>
       </c>
     </row>
     <row r="380">
@@ -18515,10 +18515,10 @@
         <v>1.07</v>
       </c>
       <c r="I380" t="n">
-        <v>0.1783</v>
+        <v>0.2298</v>
       </c>
       <c r="J380" t="n">
-        <v>4.8141</v>
+        <v>6.2046</v>
       </c>
     </row>
     <row r="381">
@@ -18555,10 +18555,10 @@
         <v>1.02</v>
       </c>
       <c r="I381" t="n">
-        <v>0.0039</v>
+        <v>0.063</v>
       </c>
       <c r="J381" t="n">
-        <v>0.1053</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="382">
@@ -18595,10 +18595,10 @@
         <v>1.63</v>
       </c>
       <c r="I382" t="n">
-        <v>1.4062</v>
+        <v>1.27</v>
       </c>
       <c r="J382" t="n">
-        <v>30.9364</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="383">
@@ -18635,10 +18635,10 @@
         <v>1.55</v>
       </c>
       <c r="I383" t="n">
-        <v>1.2517</v>
+        <v>1.1732</v>
       </c>
       <c r="J383" t="n">
-        <v>27.5374</v>
+        <v>25.8104</v>
       </c>
     </row>
     <row r="384">
@@ -18675,10 +18675,10 @@
         <v>1.3</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6776</v>
+        <v>0.7662</v>
       </c>
       <c r="J384" t="n">
-        <v>14.9072</v>
+        <v>16.8564</v>
       </c>
     </row>
     <row r="385">
@@ -18715,10 +18715,10 @@
         <v>1.16</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3369</v>
+        <v>0.4307</v>
       </c>
       <c r="J385" t="n">
-        <v>7.4118</v>
+        <v>9.4754</v>
       </c>
     </row>
     <row r="386">
@@ -18755,10 +18755,10 @@
         <v>1.09</v>
       </c>
       <c r="I386" t="n">
-        <v>0.1516</v>
+        <v>0.2399</v>
       </c>
       <c r="J386" t="n">
-        <v>3.3352</v>
+        <v>5.2778</v>
       </c>
     </row>
     <row r="387">
@@ -18795,10 +18795,10 @@
         <v>1.21</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5064</v>
+        <v>0.6032</v>
       </c>
       <c r="J387" t="n">
-        <v>11.1408</v>
+        <v>13.2704</v>
       </c>
     </row>
     <row r="388">
@@ -18835,10 +18835,10 @@
         <v>0.76</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3194</v>
+        <v>-0.2453</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.0268</v>
+        <v>-5.3966</v>
       </c>
     </row>
     <row r="389">
@@ -18875,10 +18875,10 @@
         <v>0.7</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.4355</v>
+        <v>-0.3002</v>
       </c>
       <c r="J389" t="n">
-        <v>-9.581</v>
+        <v>-6.6044</v>
       </c>
     </row>
     <row r="390">
@@ -18915,10 +18915,10 @@
         <v>0.51</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.7058</v>
+        <v>-0.4775</v>
       </c>
       <c r="J390" t="n">
-        <v>-15.5276</v>
+        <v>-10.505</v>
       </c>
     </row>
     <row r="391">
@@ -18955,10 +18955,10 @@
         <v>0.45</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.7815</v>
+        <v>-0.5334</v>
       </c>
       <c r="J391" t="n">
-        <v>-17.193</v>
+        <v>-11.7348</v>
       </c>
     </row>
     <row r="392">
@@ -18995,10 +18995,10 @@
         <v>1.52</v>
       </c>
       <c r="I392" t="n">
-        <v>1.2396</v>
+        <v>1.1561</v>
       </c>
       <c r="J392" t="n">
-        <v>27.2712</v>
+        <v>25.4342</v>
       </c>
     </row>
     <row r="393">
@@ -19035,10 +19035,10 @@
         <v>1.4</v>
       </c>
       <c r="I393" t="n">
-        <v>0.9917</v>
+        <v>0.9937</v>
       </c>
       <c r="J393" t="n">
-        <v>21.8174</v>
+        <v>21.8614</v>
       </c>
     </row>
     <row r="394">
@@ -19075,10 +19075,10 @@
         <v>1.3</v>
       </c>
       <c r="I394" t="n">
-        <v>0.7638</v>
+        <v>0.7821</v>
       </c>
       <c r="J394" t="n">
-        <v>16.8036</v>
+        <v>17.2062</v>
       </c>
     </row>
     <row r="395">
@@ -19115,10 +19115,10 @@
         <v>1.23</v>
       </c>
       <c r="I395" t="n">
-        <v>0.5664</v>
+        <v>0.6239</v>
       </c>
       <c r="J395" t="n">
-        <v>12.4608</v>
+        <v>13.7258</v>
       </c>
     </row>
     <row r="396">
@@ -19155,10 +19155,10 @@
         <v>0.78</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.787</v>
+        <v>-0.7368</v>
       </c>
       <c r="J396" t="n">
-        <v>-17.314</v>
+        <v>-16.2096</v>
       </c>
     </row>
     <row r="397">
@@ -19195,10 +19195,10 @@
         <v>1.19</v>
       </c>
       <c r="I397" t="n">
-        <v>0.438</v>
+        <v>0.5004</v>
       </c>
       <c r="J397" t="n">
-        <v>9.635999999999999</v>
+        <v>11.0088</v>
       </c>
     </row>
     <row r="398">
@@ -19235,10 +19235,10 @@
         <v>0.75</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.4009</v>
+        <v>-0.265</v>
       </c>
       <c r="J398" t="n">
-        <v>-8.819800000000001</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="399">
@@ -19275,10 +19275,10 @@
         <v>0.72</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.4462</v>
+        <v>-0.2937</v>
       </c>
       <c r="J399" t="n">
-        <v>-9.8164</v>
+        <v>-6.4614</v>
       </c>
     </row>
     <row r="400">
@@ -19315,10 +19315,10 @@
         <v>0.72</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4462</v>
+        <v>-0.2937</v>
       </c>
       <c r="J400" t="n">
-        <v>-9.8164</v>
+        <v>-6.4614</v>
       </c>
     </row>
     <row r="401">
@@ -19355,10 +19355,10 @@
         <v>0.7</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.4753</v>
+        <v>-0.3128</v>
       </c>
       <c r="J401" t="n">
-        <v>-10.4566</v>
+        <v>-6.8816</v>
       </c>
     </row>
     <row r="402">
@@ -19395,10 +19395,10 @@
         <v>1.53</v>
       </c>
       <c r="I402" t="n">
-        <v>1.3119</v>
+        <v>1.1964</v>
       </c>
       <c r="J402" t="n">
-        <v>36.7332</v>
+        <v>33.4992</v>
       </c>
     </row>
     <row r="403">
@@ -19435,10 +19435,10 @@
         <v>1.22</v>
       </c>
       <c r="I403" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6208</v>
       </c>
       <c r="J403" t="n">
-        <v>17.7128</v>
+        <v>17.3824</v>
       </c>
     </row>
     <row r="404">
@@ -19475,10 +19475,10 @@
         <v>1.02</v>
       </c>
       <c r="I404" t="n">
-        <v>0.003</v>
+        <v>0.0625</v>
       </c>
       <c r="J404" t="n">
-        <v>0.08400000000000001</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="405">
@@ -19515,10 +19515,10 @@
         <v>1</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.099</v>
+        <v>-0.0333</v>
       </c>
       <c r="J405" t="n">
-        <v>-2.772</v>
+        <v>-0.9324</v>
       </c>
     </row>
     <row r="406">
@@ -19555,10 +19555,10 @@
         <v>0.93</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3698</v>
+        <v>-0.2984</v>
       </c>
       <c r="J406" t="n">
-        <v>-10.3544</v>
+        <v>-8.3552</v>
       </c>
     </row>
     <row r="407">
@@ -19595,10 +19595,10 @@
         <v>1.38</v>
       </c>
       <c r="I407" t="n">
-        <v>0.6115</v>
+        <v>0.7418</v>
       </c>
       <c r="J407" t="n">
-        <v>17.122</v>
+        <v>20.7704</v>
       </c>
     </row>
     <row r="408">
@@ -19635,10 +19635,10 @@
         <v>1.23</v>
       </c>
       <c r="I408" t="n">
-        <v>0.4158</v>
+        <v>0.4836</v>
       </c>
       <c r="J408" t="n">
-        <v>11.6424</v>
+        <v>13.5408</v>
       </c>
     </row>
     <row r="409">
@@ -19675,10 +19675,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1658</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J409" t="n">
-        <v>-4.6424</v>
+        <v>-2.5564</v>
       </c>
     </row>
     <row r="410">
@@ -19715,10 +19715,10 @@
         <v>0.87</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2856</v>
+        <v>-0.1703</v>
       </c>
       <c r="J410" t="n">
-        <v>-7.9968</v>
+        <v>-4.7684</v>
       </c>
     </row>
     <row r="411">
@@ -19755,10 +19755,10 @@
         <v>0.73</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4863</v>
+        <v>-0.311</v>
       </c>
       <c r="J411" t="n">
-        <v>-13.6164</v>
+        <v>-8.708</v>
       </c>
     </row>
     <row r="412">
@@ -19795,10 +19795,10 @@
         <v>1.73</v>
       </c>
       <c r="I412" t="n">
-        <v>0.9792</v>
+        <v>1.1533</v>
       </c>
       <c r="J412" t="n">
-        <v>28.3968</v>
+        <v>33.4457</v>
       </c>
     </row>
     <row r="413">
@@ -19835,10 +19835,10 @@
         <v>1.22</v>
       </c>
       <c r="I413" t="n">
-        <v>0.3743</v>
+        <v>0.4448</v>
       </c>
       <c r="J413" t="n">
-        <v>10.8547</v>
+        <v>12.8992</v>
       </c>
     </row>
     <row r="414">
@@ -19875,10 +19875,10 @@
         <v>1.1</v>
       </c>
       <c r="I414" t="n">
-        <v>0.1701</v>
+        <v>0.2273</v>
       </c>
       <c r="J414" t="n">
-        <v>4.9329</v>
+        <v>6.5917</v>
       </c>
     </row>
     <row r="415">
@@ -19915,10 +19915,10 @@
         <v>0.79</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.4194</v>
+        <v>-0.261</v>
       </c>
       <c r="J415" t="n">
-        <v>-12.1626</v>
+        <v>-7.569</v>
       </c>
     </row>
     <row r="416">
@@ -19955,10 +19955,10 @@
         <v>0.71</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.525</v>
+        <v>-0.3383</v>
       </c>
       <c r="J416" t="n">
-        <v>-15.225</v>
+        <v>-9.810700000000001</v>
       </c>
     </row>
     <row r="417">
@@ -19995,10 +19995,10 @@
         <v>1.31</v>
       </c>
       <c r="I417" t="n">
-        <v>0.8878</v>
+        <v>0.8636</v>
       </c>
       <c r="J417" t="n">
-        <v>25.7462</v>
+        <v>25.0444</v>
       </c>
     </row>
     <row r="418">
@@ -20035,10 +20035,10 @@
         <v>1.28</v>
       </c>
       <c r="I418" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.7913</v>
       </c>
       <c r="J418" t="n">
-        <v>23.7539</v>
+        <v>22.9477</v>
       </c>
     </row>
     <row r="419">
@@ -20075,10 +20075,10 @@
         <v>1.1</v>
       </c>
       <c r="I419" t="n">
-        <v>0.3453</v>
+        <v>0.3284</v>
       </c>
       <c r="J419" t="n">
-        <v>10.0137</v>
+        <v>9.5236</v>
       </c>
     </row>
     <row r="420">
@@ -20115,10 +20115,10 @@
         <v>0.93</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3409</v>
+        <v>-0.2794</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.886100000000001</v>
+        <v>-8.102600000000001</v>
       </c>
     </row>
     <row r="421">
@@ -20155,10 +20155,10 @@
         <v>0.73</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.858</v>
+        <v>-0.8192</v>
       </c>
       <c r="J421" t="n">
-        <v>-24.882</v>
+        <v>-23.7568</v>
       </c>
     </row>
     <row r="422">
@@ -20195,10 +20195,10 @@
         <v>1.28</v>
       </c>
       <c r="I422" t="n">
-        <v>0.7609</v>
+        <v>0.755</v>
       </c>
       <c r="J422" t="n">
-        <v>19.0225</v>
+        <v>18.875</v>
       </c>
     </row>
     <row r="423">
@@ -20235,10 +20235,10 @@
         <v>1.23</v>
       </c>
       <c r="I423" t="n">
-        <v>0.6374</v>
+        <v>0.6367</v>
       </c>
       <c r="J423" t="n">
-        <v>15.935</v>
+        <v>15.9175</v>
       </c>
     </row>
     <row r="424">
@@ -20275,10 +20275,10 @@
         <v>1.15</v>
       </c>
       <c r="I424" t="n">
-        <v>0.3978</v>
+        <v>0.4425</v>
       </c>
       <c r="J424" t="n">
-        <v>9.945</v>
+        <v>11.0625</v>
       </c>
     </row>
     <row r="425">
@@ -20315,10 +20315,10 @@
         <v>1.12</v>
       </c>
       <c r="I425" t="n">
-        <v>0.3098</v>
+        <v>0.364</v>
       </c>
       <c r="J425" t="n">
-        <v>7.745</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="426">
@@ -20355,10 +20355,10 @@
         <v>1.08</v>
       </c>
       <c r="I426" t="n">
-        <v>0.1908</v>
+        <v>0.2515</v>
       </c>
       <c r="J426" t="n">
-        <v>4.77</v>
+        <v>6.2875</v>
       </c>
     </row>
     <row r="427">
@@ -20395,10 +20395,10 @@
         <v>1.36</v>
       </c>
       <c r="I427" t="n">
-        <v>0.621</v>
+        <v>0.7528</v>
       </c>
       <c r="J427" t="n">
-        <v>15.525</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="428">
@@ -20435,10 +20435,10 @@
         <v>0.99</v>
       </c>
       <c r="I428" t="n">
-        <v>0.0047</v>
+        <v>-0.0142</v>
       </c>
       <c r="J428" t="n">
-        <v>0.1175</v>
+        <v>-0.355</v>
       </c>
     </row>
     <row r="429">
@@ -20475,10 +20475,10 @@
         <v>0.78</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.3948</v>
+        <v>-0.2505</v>
       </c>
       <c r="J429" t="n">
-        <v>-9.869999999999999</v>
+        <v>-6.2625</v>
       </c>
     </row>
     <row r="430">
@@ -20515,10 +20515,10 @@
         <v>0.77</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4092</v>
+        <v>-0.2603</v>
       </c>
       <c r="J430" t="n">
-        <v>-10.23</v>
+        <v>-6.5075</v>
       </c>
     </row>
     <row r="431">
@@ -20555,10 +20555,10 @@
         <v>0.75</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.4377</v>
+        <v>-0.2799</v>
       </c>
       <c r="J431" t="n">
-        <v>-10.9425</v>
+        <v>-6.9975</v>
       </c>
     </row>
     <row r="432">
@@ -20595,10 +20595,10 @@
         <v>1.42</v>
       </c>
       <c r="I432" t="n">
-        <v>0.6575</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="J432" t="n">
-        <v>27.615</v>
+        <v>33.8058</v>
       </c>
     </row>
     <row r="433">
@@ -20635,10 +20635,10 @@
         <v>1.09</v>
       </c>
       <c r="I433" t="n">
-        <v>0.1949</v>
+        <v>0.2176</v>
       </c>
       <c r="J433" t="n">
-        <v>8.1858</v>
+        <v>9.139200000000001</v>
       </c>
     </row>
     <row r="434">
@@ -20675,10 +20675,10 @@
         <v>1.06</v>
       </c>
       <c r="I434" t="n">
-        <v>0.1374</v>
+        <v>0.1548</v>
       </c>
       <c r="J434" t="n">
-        <v>5.7708</v>
+        <v>6.5016</v>
       </c>
     </row>
     <row r="435">
@@ -20715,10 +20715,10 @@
         <v>1.01</v>
       </c>
       <c r="I435" t="n">
-        <v>0.012</v>
+        <v>0.0331</v>
       </c>
       <c r="J435" t="n">
-        <v>0.504</v>
+        <v>1.3902</v>
       </c>
     </row>
     <row r="436">
@@ -20755,10 +20755,10 @@
         <v>0.61</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.639</v>
+        <v>-0.4239</v>
       </c>
       <c r="J436" t="n">
-        <v>-26.838</v>
+        <v>-17.8038</v>
       </c>
     </row>
     <row r="437">
@@ -20795,10 +20795,10 @@
         <v>1.38</v>
       </c>
       <c r="I437" t="n">
-        <v>1.0384</v>
+        <v>1.0098</v>
       </c>
       <c r="J437" t="n">
-        <v>43.6128</v>
+        <v>42.4116</v>
       </c>
     </row>
     <row r="438">
@@ -20835,10 +20835,10 @@
         <v>1.17</v>
       </c>
       <c r="I438" t="n">
-        <v>0.5431</v>
+        <v>0.5142</v>
       </c>
       <c r="J438" t="n">
-        <v>22.8102</v>
+        <v>21.5964</v>
       </c>
     </row>
     <row r="439">
@@ -20875,10 +20875,10 @@
         <v>1.16</v>
       </c>
       <c r="I439" t="n">
-        <v>0.5161</v>
+        <v>0.4882</v>
       </c>
       <c r="J439" t="n">
-        <v>21.6762</v>
+        <v>20.5044</v>
       </c>
     </row>
     <row r="440">
@@ -20915,10 +20915,10 @@
         <v>1.03</v>
       </c>
       <c r="I440" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1152</v>
       </c>
       <c r="J440" t="n">
-        <v>3.2886</v>
+        <v>4.8384</v>
       </c>
     </row>
     <row r="441">
@@ -20955,10 +20955,10 @@
         <v>0.64</v>
       </c>
       <c r="I441" t="n">
-        <v>-1.0572</v>
+        <v>-1.0398</v>
       </c>
       <c r="J441" t="n">
-        <v>-44.4024</v>
+        <v>-43.6716</v>
       </c>
     </row>
     <row r="442">
@@ -20995,10 +20995,10 @@
         <v>1.32</v>
       </c>
       <c r="I442" t="n">
-        <v>0.8783</v>
+        <v>0.8635</v>
       </c>
       <c r="J442" t="n">
-        <v>23.7141</v>
+        <v>23.3145</v>
       </c>
     </row>
     <row r="443">
@@ -21035,10 +21035,10 @@
         <v>1.22</v>
       </c>
       <c r="I443" t="n">
-        <v>0.6402</v>
+        <v>0.6242</v>
       </c>
       <c r="J443" t="n">
-        <v>17.2854</v>
+        <v>16.8534</v>
       </c>
     </row>
     <row r="444">
@@ -21075,10 +21075,10 @@
         <v>1.14</v>
       </c>
       <c r="I444" t="n">
-        <v>0.4188</v>
+        <v>0.4236</v>
       </c>
       <c r="J444" t="n">
-        <v>11.3076</v>
+        <v>11.4372</v>
       </c>
     </row>
     <row r="445">
@@ -21115,10 +21115,10 @@
         <v>1.07</v>
       </c>
       <c r="I445" t="n">
-        <v>0.1843</v>
+        <v>0.2321</v>
       </c>
       <c r="J445" t="n">
-        <v>4.9761</v>
+        <v>6.2667</v>
       </c>
     </row>
     <row r="446">
@@ -21155,10 +21155,10 @@
         <v>0.89</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.4806</v>
+        <v>-0.4136</v>
       </c>
       <c r="J446" t="n">
-        <v>-12.9762</v>
+        <v>-11.1672</v>
       </c>
     </row>
     <row r="447">
@@ -21195,10 +21195,10 @@
         <v>1.16</v>
       </c>
       <c r="I447" t="n">
-        <v>0.328</v>
+        <v>0.367</v>
       </c>
       <c r="J447" t="n">
-        <v>8.856</v>
+        <v>9.909000000000001</v>
       </c>
     </row>
     <row r="448">
@@ -21235,10 +21235,10 @@
         <v>1.02</v>
       </c>
       <c r="I448" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="J448" t="n">
-        <v>1.9818</v>
+        <v>1.8279</v>
       </c>
     </row>
     <row r="449">
@@ -21275,10 +21275,10 @@
         <v>1.02</v>
       </c>
       <c r="I449" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="J449" t="n">
-        <v>1.9818</v>
+        <v>1.8279</v>
       </c>
     </row>
     <row r="450">
@@ -21315,10 +21315,10 @@
         <v>0.96</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.1099</v>
+        <v>-0.0623</v>
       </c>
       <c r="J450" t="n">
-        <v>-2.9673</v>
+        <v>-1.6821</v>
       </c>
     </row>
     <row r="451">
@@ -21355,10 +21355,10 @@
         <v>0.79</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.3956</v>
+        <v>-0.2478</v>
       </c>
       <c r="J451" t="n">
-        <v>-10.6812</v>
+        <v>-6.6906</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2956/event_2956_evp_summary.xlsx
+++ b/database/event/2956/event_2956_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4663</v>
+        <v>7.4409</v>
       </c>
       <c r="C2" t="n">
-        <v>3.298</v>
+        <v>3.2868</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7326</v>
+        <v>2.763</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4663</v>
+        <v>7.4409</v>
       </c>
       <c r="F2" t="n">
-        <v>4.195</v>
+        <v>4.1314</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2713</v>
+        <v>3.3095</v>
       </c>
       <c r="H2" t="n">
-        <v>9.2941</v>
+        <v>8.736800000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8325</v>
+        <v>4.7178</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2713</v>
+        <v>3.3095</v>
       </c>
       <c r="K2" t="n">
         <v>124</v>
@@ -529,7 +529,7 @@
         <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1038</v>
+        <v>8.0273</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2423</v>
+        <v>6.3002</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7573</v>
+        <v>2.7829</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1801</v>
+        <v>2.2438</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2423</v>
+        <v>6.3002</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7628</v>
+        <v>3.7323</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4795</v>
+        <v>2.5679</v>
       </c>
       <c r="H3" t="n">
-        <v>7.7714</v>
+        <v>7.4201</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0408</v>
+        <v>4.0068</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4795</v>
+        <v>2.5679</v>
       </c>
       <c r="K3" t="n">
         <v>124</v>
@@ -575,7 +575,7 @@
         <v>199</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5203</v>
+        <v>6.5747</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4437</v>
+        <v>5.4273</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4046</v>
+        <v>2.3973</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8195</v>
+        <v>1.8464</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4437</v>
+        <v>5.4273</v>
       </c>
       <c r="F4" t="n">
-        <v>2.804</v>
+        <v>2.7207</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6397</v>
+        <v>2.7066</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3933</v>
+        <v>4.0825</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2843</v>
+        <v>2.2045</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6397</v>
+        <v>2.7066</v>
       </c>
       <c r="K4" t="n">
         <v>118</v>
@@ -621,7 +621,7 @@
         <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>4.923999999999999</v>
+        <v>4.911099999999999</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3571</v>
+        <v>5.3766</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3663</v>
+        <v>2.3749</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7804</v>
+        <v>1.8233</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3571</v>
+        <v>5.3766</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9703</v>
+        <v>2.8876</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3868</v>
+        <v>2.489</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9791</v>
+        <v>4.633</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5889</v>
+        <v>2.5018</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3868</v>
+        <v>2.489</v>
       </c>
       <c r="K5" t="n">
         <v>118</v>
@@ -667,7 +667,7 @@
         <v>169</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9757</v>
+        <v>4.9908</v>
       </c>
       <c r="N5" t="n">
         <v>287</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9195</v>
+        <v>5.0205</v>
       </c>
       <c r="C6" t="n">
-        <v>2.173</v>
+        <v>2.2176</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5829</v>
+        <v>1.6612</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9195</v>
+        <v>5.0205</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4083</v>
+        <v>2.331</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5112</v>
+        <v>2.6895</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9992</v>
+        <v>2.7965</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5594</v>
+        <v>1.5101</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5112</v>
+        <v>2.6895</v>
       </c>
       <c r="K6" t="n">
         <v>118</v>
@@ -713,7 +713,7 @@
         <v>169</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0706</v>
+        <v>4.1996</v>
       </c>
       <c r="N6" t="n">
         <v>287</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6593</v>
+        <v>4.9532</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0581</v>
+        <v>2.1879</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4654</v>
+        <v>1.6306</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6593</v>
+        <v>4.9532</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0683</v>
+        <v>2.0644</v>
       </c>
       <c r="G7" t="n">
-        <v>2.591</v>
+        <v>2.8888</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0683</v>
+        <v>2.0644</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1534</v>
+        <v>2.1176</v>
       </c>
       <c r="J7" t="n">
-        <v>2.591</v>
+        <v>2.8888</v>
       </c>
       <c r="K7" t="n">
         <v>162</v>
@@ -759,7 +759,7 @@
         <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>4.744400000000001</v>
+        <v>5.006399999999999</v>
       </c>
       <c r="N7" t="n">
         <v>284</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4908</v>
+        <v>4.4592</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9837</v>
+        <v>1.9697</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3894</v>
+        <v>1.4057</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4908</v>
+        <v>4.4592</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9542</v>
+        <v>2.5454</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5366</v>
+        <v>1.9138</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1272</v>
+        <v>3.5039</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2558</v>
+        <v>1.8921</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5366</v>
+        <v>1.9138</v>
       </c>
       <c r="K8" t="n">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7924</v>
+        <v>3.8059</v>
       </c>
       <c r="N8" t="n">
-        <v>284</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4851</v>
+        <v>4.286</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9812</v>
+        <v>1.8932</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3868</v>
+        <v>1.3269</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4851</v>
+        <v>4.286</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5956</v>
+        <v>2.6284</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8895</v>
+        <v>1.6576</v>
       </c>
       <c r="H9" t="n">
-        <v>3.659</v>
+        <v>3.0279</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9025</v>
+        <v>3.1059</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8895</v>
+        <v>1.6576</v>
       </c>
       <c r="K9" t="n">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="L9" t="n">
-        <v>199</v>
+        <v>122</v>
       </c>
       <c r="M9" t="n">
-        <v>3.792</v>
+        <v>4.763500000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>323</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1048</v>
+        <v>4.099</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8132</v>
+        <v>1.8106</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2151</v>
+        <v>1.2417</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1048</v>
+        <v>4.099</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6774</v>
+        <v>2.5887</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4274</v>
+        <v>1.5103</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9473</v>
+        <v>3.6469</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0524</v>
+        <v>1.9693</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4274</v>
+        <v>1.5103</v>
       </c>
       <c r="K10" t="n">
         <v>118</v>
@@ -897,7 +897,7 @@
         <v>169</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4798</v>
+        <v>3.4796</v>
       </c>
       <c r="N10" t="n">
         <v>287</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0971</v>
+        <v>3.9471</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8098</v>
+        <v>1.7435</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2116</v>
+        <v>1.1726</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0971</v>
+        <v>3.9471</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9053</v>
+        <v>2.6545</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1918</v>
+        <v>1.2926</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0198</v>
+        <v>3.0849</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0198</v>
+        <v>3.0849</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1918</v>
+        <v>1.2926</v>
       </c>
       <c r="K11" t="n">
         <v>143</v>
@@ -943,7 +943,7 @@
         <v>89</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2116</v>
+        <v>4.3775</v>
       </c>
       <c r="N11" t="n">
         <v>232</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2678</v>
+        <v>3.3372</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4434</v>
+        <v>1.4741</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.895</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2678</v>
+        <v>3.3372</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2678</v>
+        <v>1.3379</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.9993</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8158</v>
+        <v>1.3379</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8158</v>
+        <v>1.3724</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.9993</v>
       </c>
       <c r="K12" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8158</v>
+        <v>3.3717</v>
       </c>
       <c r="N12" t="n">
-        <v>137</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2278</v>
+        <v>3.0891</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4258</v>
+        <v>1.3645</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8192</v>
+        <v>0.782</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2278</v>
+        <v>3.0891</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4125</v>
+        <v>1.9972</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8153</v>
+        <v>1.0919</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4125</v>
+        <v>1.9972</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4706</v>
+        <v>2.0487</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8153</v>
+        <v>1.0919</v>
       </c>
       <c r="K13" t="n">
         <v>114</v>
@@ -1035,7 +1035,7 @@
         <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2859</v>
+        <v>3.1406</v>
       </c>
       <c r="N13" t="n">
         <v>249</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.945</v>
+        <v>3.0474</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3009</v>
+        <v>1.3461</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6915</v>
+        <v>0.763</v>
       </c>
       <c r="E14" t="n">
-        <v>2.945</v>
+        <v>3.0474</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9789</v>
+        <v>1.685</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9661</v>
+        <v>1.3624</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9789</v>
+        <v>1.685</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0603</v>
+        <v>1.7284</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9661</v>
+        <v>1.3624</v>
       </c>
       <c r="K14" t="n">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="L14" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0264</v>
+        <v>3.0908</v>
       </c>
       <c r="N14" t="n">
-        <v>249</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9321</v>
+        <v>2.9666</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2952</v>
+        <v>1.3104</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6857</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9321</v>
+        <v>2.9666</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9321</v>
+        <v>2.9666</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0787</v>
+        <v>3.7681</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0787</v>
+        <v>3.7681</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0787</v>
+        <v>3.7681</v>
       </c>
       <c r="N15" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9098</v>
+        <v>2.579</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2853</v>
+        <v>1.1392</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6756</v>
+        <v>0.5498</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9098</v>
+        <v>2.579</v>
       </c>
       <c r="F16" t="n">
-        <v>1.712</v>
+        <v>2.579</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1978</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.712</v>
+        <v>2.9197</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7824</v>
+        <v>2.9197</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1978</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="L16" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9802</v>
+        <v>2.9197</v>
       </c>
       <c r="N16" t="n">
-        <v>284</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8899</v>
+        <v>2.5445</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2765</v>
+        <v>1.124</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6666</v>
+        <v>0.5341</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8899</v>
+        <v>2.5445</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8899</v>
+        <v>2.5445</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.986</v>
+        <v>2.8442</v>
       </c>
       <c r="I17" t="n">
-        <v>2.986</v>
+        <v>2.8442</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.986</v>
+        <v>2.8442</v>
       </c>
       <c r="N17" t="n">
         <v>151</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.781</v>
+        <v>2.4737</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2284</v>
+        <v>1.0927</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6175</v>
+        <v>0.5019</v>
       </c>
       <c r="E18" t="n">
-        <v>2.781</v>
+        <v>2.4737</v>
       </c>
       <c r="F18" t="n">
-        <v>2.781</v>
+        <v>3.0002</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.5265</v>
       </c>
       <c r="H18" t="n">
-        <v>2.781</v>
+        <v>5.0045</v>
       </c>
       <c r="I18" t="n">
-        <v>2.781</v>
+        <v>2.7024</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.5265</v>
       </c>
       <c r="K18" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M18" t="n">
-        <v>2.781</v>
+        <v>2.1759</v>
       </c>
       <c r="N18" t="n">
-        <v>148</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4462</v>
+        <v>2.4503</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0805</v>
+        <v>1.0823</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4663</v>
+        <v>0.4912</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4462</v>
+        <v>2.4503</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0573</v>
+        <v>2.4503</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6111</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2858</v>
+        <v>2.6381</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7484</v>
+        <v>2.6381</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6111</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="L19" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1373</v>
+        <v>2.6381</v>
       </c>
       <c r="N19" t="n">
-        <v>323</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2531</v>
+        <v>2.2292</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9952</v>
+        <v>0.9847</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3791</v>
+        <v>0.3906</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2531</v>
+        <v>2.2292</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2531</v>
+        <v>2.2292</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2531</v>
+        <v>2.2292</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3458</v>
+        <v>2.2866</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.3458</v>
+        <v>2.2866</v>
       </c>
       <c r="N20" t="n">
         <v>144</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2165</v>
+        <v>2.1155</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9791</v>
+        <v>0.9345</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3626</v>
+        <v>0.3388</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2165</v>
+        <v>2.1155</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2757</v>
+        <v>2.1155</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0592</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2757</v>
+        <v>2.1155</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2757</v>
+        <v>2.1155</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0592</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L21" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.2165</v>
+        <v>2.1155</v>
       </c>
       <c r="N21" t="n">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1722</v>
+        <v>2.0947</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9595</v>
+        <v>0.9253</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3426</v>
+        <v>0.3293</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1722</v>
+        <v>2.0947</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1722</v>
+        <v>2.1672</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.0725</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1722</v>
+        <v>2.1672</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1722</v>
+        <v>2.1672</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.0725</v>
       </c>
       <c r="K22" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1722</v>
+        <v>2.0947</v>
       </c>
       <c r="N22" t="n">
-        <v>148</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.963</v>
+        <v>2.061</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8671</v>
+        <v>0.9104</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2482</v>
+        <v>0.314</v>
       </c>
       <c r="E23" t="n">
-        <v>1.963</v>
+        <v>2.061</v>
       </c>
       <c r="F23" t="n">
-        <v>1.963</v>
+        <v>2.061</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.963</v>
+        <v>2.061</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0437</v>
+        <v>2.1141</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0437</v>
+        <v>2.1141</v>
       </c>
       <c r="N23" t="n">
         <v>144</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9571</v>
+        <v>1.9219</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8645</v>
+        <v>0.8489</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2455</v>
+        <v>0.2507</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9571</v>
+        <v>1.9219</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9571</v>
+        <v>1.9219</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9571</v>
+        <v>1.9219</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9571</v>
+        <v>1.9219</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9571</v>
+        <v>1.9219</v>
       </c>
       <c r="N24" t="n">
         <v>148</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8778</v>
+        <v>1.8586</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8295</v>
+        <v>0.821</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2097</v>
+        <v>0.2219</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8778</v>
+        <v>1.8586</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7915</v>
+        <v>1.7353</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0863</v>
+        <v>0.1233</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7915</v>
+        <v>1.7353</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8652</v>
+        <v>1.78</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0863</v>
+        <v>0.1233</v>
       </c>
       <c r="K25" t="n">
         <v>114</v>
@@ -1587,7 +1587,7 @@
         <v>135</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9515</v>
+        <v>1.9033</v>
       </c>
       <c r="N25" t="n">
         <v>249</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7727</v>
+        <v>1.7015</v>
       </c>
       <c r="C26" t="n">
-        <v>0.783</v>
+        <v>0.7516</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1623</v>
+        <v>0.1504</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7727</v>
+        <v>1.7015</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9627</v>
+        <v>1.8154</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.19</v>
+        <v>-0.1139</v>
       </c>
       <c r="H26" t="n">
-        <v>1.9627</v>
+        <v>1.8154</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0205</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.19</v>
+        <v>-0.1139</v>
       </c>
       <c r="K26" t="n">
         <v>118</v>
@@ -1633,7 +1633,7 @@
         <v>169</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8305</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>287</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6973</v>
+        <v>1.6218</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7497</v>
+        <v>0.7164</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1282</v>
+        <v>0.1141</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6973</v>
+        <v>1.6218</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6973</v>
+        <v>1.6218</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6973</v>
+        <v>1.6218</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6973</v>
+        <v>1.6636</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6973</v>
+        <v>1.6636</v>
       </c>
       <c r="N27" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6921</v>
+        <v>1.6066</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7474</v>
+        <v>0.7097</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1259</v>
+        <v>0.1072</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6921</v>
+        <v>1.6066</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6921</v>
+        <v>1.6066</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6921</v>
+        <v>1.6066</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7617</v>
+        <v>1.6066</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7617</v>
+        <v>1.6066</v>
       </c>
       <c r="N28" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6444</v>
+        <v>1.5925</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7264</v>
+        <v>0.7034</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1044</v>
+        <v>0.1007</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6444</v>
+        <v>1.5925</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7415</v>
+        <v>1.661</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7415</v>
+        <v>1.661</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8131</v>
+        <v>1.7038</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>120</v>
@@ -1771,7 +1771,7 @@
         <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>1.716</v>
+        <v>1.6353</v>
       </c>
       <c r="N29" t="n">
         <v>166</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3924</v>
+        <v>1.3618</v>
       </c>
       <c r="C30" t="n">
-        <v>0.615</v>
+        <v>0.6015</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0094</v>
+        <v>-0.0043</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3924</v>
+        <v>1.3618</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2145</v>
+        <v>1.1436</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1779</v>
+        <v>0.2182</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2145</v>
+        <v>1.1436</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2645</v>
+        <v>1.1731</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1779</v>
+        <v>0.2182</v>
       </c>
       <c r="K30" t="n">
         <v>114</v>
@@ -1817,7 +1817,7 @@
         <v>135</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4424</v>
+        <v>1.3913</v>
       </c>
       <c r="N30" t="n">
         <v>249</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3329</v>
+        <v>1.2207</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5888</v>
+        <v>0.5392</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0363</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3329</v>
+        <v>1.2207</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6422</v>
+        <v>0.395</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3093</v>
+        <v>0.8257</v>
       </c>
       <c r="H31" t="n">
-        <v>1.6422</v>
+        <v>0.395</v>
       </c>
       <c r="I31" t="n">
-        <v>1.7097</v>
+        <v>0.4052</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3093</v>
+        <v>0.8257</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4004</v>
+        <v>1.2309</v>
       </c>
       <c r="N31" t="n">
-        <v>166</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1718</v>
+        <v>1.212</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5354</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.109</v>
+        <v>-0.0725</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1718</v>
+        <v>1.212</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1718</v>
+        <v>1.5308</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.3188</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1718</v>
+        <v>1.5308</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1718</v>
+        <v>1.5702</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.3188</v>
       </c>
       <c r="K32" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1718</v>
+        <v>1.2514</v>
       </c>
       <c r="N32" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1449</v>
+        <v>1.1775</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5057</v>
+        <v>0.5201</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1211</v>
+        <v>-0.0882</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1449</v>
+        <v>1.1775</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1449</v>
+        <v>1.1775</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1449</v>
+        <v>1.1775</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1449</v>
+        <v>1.1775</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1449</v>
+        <v>1.1775</v>
       </c>
       <c r="N33" t="n">
         <v>137</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1047</v>
+        <v>1.0871</v>
       </c>
       <c r="C34" t="n">
-        <v>0.488</v>
+        <v>0.4802</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1393</v>
+        <v>-0.1293</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1047</v>
+        <v>1.0871</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3547</v>
+        <v>1.0871</v>
       </c>
       <c r="G34" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3547</v>
+        <v>1.0871</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3693</v>
+        <v>1.0871</v>
       </c>
       <c r="J34" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="L34" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1193</v>
+        <v>1.0871</v>
       </c>
       <c r="N34" t="n">
-        <v>284</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0261</v>
+        <v>0.9061</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4532</v>
+        <v>0.4002</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1748</v>
+        <v>-0.2117</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0261</v>
+        <v>0.9061</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4232</v>
+        <v>1.3229</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3971</v>
+        <v>-0.4168</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4232</v>
+        <v>1.3229</v>
       </c>
       <c r="I35" t="n">
-        <v>1.4232</v>
+        <v>1.3229</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3971</v>
+        <v>-0.4168</v>
       </c>
       <c r="K35" t="n">
         <v>143</v>
@@ -2047,7 +2047,7 @@
         <v>89</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0261</v>
+        <v>0.9060999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>232</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7403</v>
+        <v>0.7075</v>
       </c>
       <c r="C36" t="n">
-        <v>0.327</v>
+        <v>0.3125</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3038</v>
+        <v>-0.3021</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7403</v>
+        <v>0.7075</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7403</v>
+        <v>0.7075</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7403</v>
+        <v>0.7075</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7403</v>
+        <v>0.7075</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7403</v>
+        <v>0.7075</v>
       </c>
       <c r="N36" t="n">
         <v>137</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.702</v>
+        <v>0.6589</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3101</v>
+        <v>0.291</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3211</v>
+        <v>-0.3243</v>
       </c>
       <c r="E37" t="n">
-        <v>0.702</v>
+        <v>0.6589</v>
       </c>
       <c r="F37" t="n">
-        <v>0.702</v>
+        <v>0.6589</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.702</v>
+        <v>0.6589</v>
       </c>
       <c r="I37" t="n">
-        <v>0.702</v>
+        <v>0.6589</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.702</v>
+        <v>0.6589</v>
       </c>
       <c r="N37" t="n">
         <v>151</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6031</v>
+        <v>0.5443</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2664</v>
+        <v>0.2404</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3657</v>
+        <v>-0.3764</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6031</v>
+        <v>0.5443</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6031</v>
+        <v>0.5443</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6031</v>
+        <v>0.5443</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6031</v>
+        <v>0.5443</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6031</v>
+        <v>0.5443</v>
       </c>
       <c r="N38" t="n">
         <v>137</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2442</v>
+        <v>0.2105</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3884</v>
+        <v>-0.4073</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="N39" t="n">
         <v>143</v>
@@ -2240,185 +2240,185 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tsogoo</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4698</v>
+        <v>0.3628</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2075</v>
+        <v>0.1603</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4259</v>
+        <v>-0.459</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4698</v>
+        <v>0.3628</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4698</v>
+        <v>0.3628</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4698</v>
+        <v>0.3628</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4698</v>
+        <v>0.3628</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4698</v>
+        <v>0.3628</v>
       </c>
       <c r="N40" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>Tsogoo</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.391</v>
+        <v>0.3575</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1727</v>
+        <v>0.1579</v>
       </c>
       <c r="D41" t="n">
         <v>-0.4615</v>
       </c>
       <c r="E41" t="n">
-        <v>0.391</v>
+        <v>0.3575</v>
       </c>
       <c r="F41" t="n">
-        <v>0.391</v>
+        <v>0.3575</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.391</v>
+        <v>0.3575</v>
       </c>
       <c r="I41" t="n">
-        <v>0.391</v>
+        <v>0.3575</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.391</v>
+        <v>0.3575</v>
       </c>
       <c r="N41" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2994</v>
+        <v>0.2716</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1323</v>
+        <v>0.12</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5029</v>
+        <v>-0.5006</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2994</v>
+        <v>0.2716</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5213</v>
+        <v>0.2716</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2219</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5213</v>
+        <v>0.2716</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5427</v>
+        <v>0.2786</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2219</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L42" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3208</v>
+        <v>0.2786</v>
       </c>
       <c r="N42" t="n">
-        <v>166</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2802</v>
+        <v>0.2625</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1238</v>
+        <v>0.116</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5115</v>
+        <v>-0.5047</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2802</v>
+        <v>0.2625</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2802</v>
+        <v>0.4951</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.2326</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2802</v>
+        <v>0.4951</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2917</v>
+        <v>0.5079</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.2326</v>
       </c>
       <c r="K43" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2917</v>
+        <v>0.2753</v>
       </c>
       <c r="N43" t="n">
-        <v>117</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44">
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2701</v>
+        <v>0.2188</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1193</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5161</v>
+        <v>-0.5246</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2701</v>
+        <v>0.2188</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5901</v>
+        <v>0.555</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.32</v>
+        <v>-0.3362</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5901</v>
+        <v>0.555</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5901</v>
+        <v>0.555</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.32</v>
+        <v>-0.3362</v>
       </c>
       <c r="K44" t="n">
         <v>143</v>
@@ -2461,7 +2461,7 @@
         <v>89</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2701</v>
+        <v>0.2188000000000001</v>
       </c>
       <c r="N44" t="n">
         <v>232</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0786</v>
+        <v>0.0023</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0347</v>
+        <v>0.001</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6025</v>
+        <v>-0.6232</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0786</v>
+        <v>0.0023</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0786</v>
+        <v>0.0023</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0786</v>
+        <v>0.0023</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0786</v>
+        <v>0.0023</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0786</v>
+        <v>0.0023</v>
       </c>
       <c r="N45" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0083</v>
+        <v>-0.0071</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0037</v>
+        <v>-0.0031</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6343</v>
+        <v>-0.6274</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0083</v>
+        <v>-0.0071</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0083</v>
+        <v>-0.0071</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0083</v>
+        <v>-0.0071</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0083</v>
+        <v>-0.0071</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0083</v>
+        <v>-0.0071</v>
       </c>
       <c r="N46" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.002</v>
+        <v>-0.0116</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0009</v>
+        <v>-0.0051</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6371</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>0.002</v>
+        <v>-0.0116</v>
       </c>
       <c r="F47" t="n">
-        <v>0.002</v>
+        <v>-0.0116</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.002</v>
+        <v>-0.0116</v>
       </c>
       <c r="I47" t="n">
-        <v>0.002</v>
+        <v>-0.0116</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.002</v>
+        <v>-0.0116</v>
       </c>
       <c r="N47" t="n">
         <v>143</v>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2016</v>
+        <v>-0.2238</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0891</v>
+        <v>-0.0989</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.729</v>
+        <v>-0.7261</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2016</v>
+        <v>-0.2238</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0648</v>
+        <v>0.0572</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.2664</v>
+        <v>-0.281</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0648</v>
+        <v>0.0572</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0648</v>
+        <v>0.0572</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2664</v>
+        <v>-0.281</v>
       </c>
       <c r="K48" t="n">
         <v>143</v>
@@ -2645,7 +2645,7 @@
         <v>89</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2016</v>
+        <v>-0.2238</v>
       </c>
       <c r="N48" t="n">
         <v>232</v>
@@ -2654,231 +2654,231 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zilkenberg</t>
+          <t>zonic</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.2371</v>
+        <v>-0.2614</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1047</v>
+        <v>-0.1155</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7451</v>
+        <v>-0.7432</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.2371</v>
+        <v>-0.2614</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2371</v>
+        <v>-0.2614</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2371</v>
+        <v>-0.2614</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2371</v>
+        <v>-0.2614</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.2371</v>
+        <v>-0.2614</v>
       </c>
       <c r="N49" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machinegun</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.2432</v>
+        <v>-0.3104</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1074</v>
+        <v>-0.1371</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7478</v>
+        <v>-0.7655</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2432</v>
+        <v>-0.3104</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.2432</v>
+        <v>0.0169</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.3273</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.2432</v>
+        <v>0.0169</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2432</v>
+        <v>0.0173</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.3273</v>
       </c>
       <c r="K50" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.2432</v>
+        <v>-0.31</v>
       </c>
       <c r="N50" t="n">
-        <v>118</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>zonic</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2478</v>
+        <v>-0.3214</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1095</v>
+        <v>-0.142</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7499</v>
+        <v>-0.7705</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2478</v>
+        <v>-0.3214</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2478</v>
+        <v>-0.3214</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2478</v>
+        <v>-0.3214</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2478</v>
+        <v>-0.3214</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2478</v>
+        <v>-0.3214</v>
       </c>
       <c r="N51" t="n">
-        <v>27</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>Machinegun</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2574</v>
+        <v>-0.355</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1137</v>
+        <v>-0.1568</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7542</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2574</v>
+        <v>-0.355</v>
       </c>
       <c r="F52" t="n">
-        <v>0.061</v>
+        <v>-0.355</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.3184</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.061</v>
+        <v>-0.355</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0635</v>
+        <v>-0.355</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.3184</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2549</v>
+        <v>-0.355</v>
       </c>
       <c r="N52" t="n">
-        <v>166</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>Zilkenberg</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3298</v>
+        <v>-0.3617</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1457</v>
+        <v>-0.1598</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7869</v>
+        <v>-0.7889</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3298</v>
+        <v>-0.3617</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3298</v>
+        <v>-0.3617</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3298</v>
+        <v>-0.3617</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3298</v>
+        <v>-0.3617</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3298</v>
+        <v>-0.3617</v>
       </c>
       <c r="N53" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.4398</v>
+        <v>-0.3845</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1943</v>
+        <v>-0.1698</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8366</v>
+        <v>-0.7992</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4398</v>
+        <v>-0.3845</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4398</v>
+        <v>-0.3845</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.4398</v>
+        <v>-0.3845</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4579</v>
+        <v>-0.3944</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.4579</v>
+        <v>-0.3944</v>
       </c>
       <c r="N54" t="n">
         <v>144</v>
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4892</v>
+        <v>-0.5463</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2161</v>
+        <v>-0.2413</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8589</v>
+        <v>-0.8729</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4892</v>
+        <v>-0.5463</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2772</v>
+        <v>0.252</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.7664</v>
+        <v>-0.7983</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2772</v>
+        <v>0.252</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2886</v>
+        <v>0.2585</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.7664</v>
+        <v>-0.7983</v>
       </c>
       <c r="K55" t="n">
         <v>120</v>
@@ -2967,7 +2967,7 @@
         <v>46</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.4777999999999999</v>
+        <v>-0.5398000000000001</v>
       </c>
       <c r="N55" t="n">
         <v>166</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6378</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2861</v>
+        <v>-0.2817</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9304</v>
+        <v>-0.9145</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6378</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6378</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6378</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6378</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6378</v>
       </c>
       <c r="N56" t="n">
         <v>151</v>
@@ -3022,93 +3022,93 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.7662</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3384</v>
+        <v>-0.3124</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9839</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.7662</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.7662</v>
+        <v>-1.1277</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.4205</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.7662</v>
+        <v>-1.1277</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.7662</v>
+        <v>-1.1568</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.4205</v>
       </c>
       <c r="K57" t="n">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.7662</v>
+        <v>-0.7363000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>143</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.8101</v>
+        <v>-0.8062</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3578</v>
+        <v>-0.3561</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.0037</v>
+        <v>-0.9912</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.8101</v>
+        <v>-0.8062</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.1758</v>
+        <v>-0.8062</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3657</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.1758</v>
+        <v>-0.8062</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.2242</v>
+        <v>-0.8062</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3657</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="L58" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.8584999999999999</v>
+        <v>-0.8062</v>
       </c>
       <c r="N58" t="n">
-        <v>249</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59">
@@ -3118,31 +3118,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1655</v>
+        <v>-0.9747</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5148</v>
+        <v>-0.4305</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1642</v>
+        <v>-1.0679</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.1655</v>
+        <v>-0.9747</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.3621</v>
+        <v>-1.305</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1966</v>
+        <v>0.3303</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.3621</v>
+        <v>-1.305</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.4181</v>
+        <v>-1.3386</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1966</v>
+        <v>0.3303</v>
       </c>
       <c r="K59" t="n">
         <v>162</v>
@@ -3151,7 +3151,7 @@
         <v>122</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.2215</v>
+        <v>-1.0083</v>
       </c>
       <c r="N59" t="n">
         <v>284</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.7229</v>
+        <v>-1.7977</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.761</v>
+        <v>-0.7941</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4158</v>
+        <v>-1.4426</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.7229</v>
+        <v>-1.7977</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.7229</v>
+        <v>-1.7977</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.7229</v>
+        <v>-1.7977</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.7229</v>
+        <v>-1.7977</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.7229</v>
+        <v>-1.7977</v>
       </c>
       <c r="N60" t="n">
         <v>118</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.8596</v>
+        <v>-1.908</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.8214</v>
+        <v>-0.8428</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4775</v>
+        <v>-1.4928</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.8596</v>
+        <v>-1.908</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.8596</v>
+        <v>-1.908</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.8596</v>
+        <v>-1.908</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.8596</v>
+        <v>-1.908</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.8596</v>
+        <v>-1.908</v>
       </c>
       <c r="N61" t="n">
         <v>118</v>
@@ -3256,31 +3256,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-2.3483</v>
+        <v>-2.0233</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.0373</v>
+        <v>-0.8937</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.6982</v>
+        <v>-1.5453</v>
       </c>
       <c r="E62" t="n">
-        <v>-2.3483</v>
+        <v>-2.0233</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.7265</v>
+        <v>-1.5056</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.6218</v>
+        <v>-0.5177</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.7265</v>
+        <v>-1.5056</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.6218</v>
+        <v>-0.5177</v>
       </c>
       <c r="K62" t="n">
         <v>124</v>
@@ -3289,7 +3289,7 @@
         <v>199</v>
       </c>
       <c r="M62" t="n">
-        <v>-1.5195</v>
+        <v>-1.3307</v>
       </c>
       <c r="N62" t="n">
         <v>323</v>
@@ -3395,10 +3395,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1474</v>
+        <v>1.15</v>
       </c>
       <c r="J2" t="n">
-        <v>29.8324</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="3">
@@ -3435,10 +3435,10 @@
         <v>1.47</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0965</v>
+        <v>1.076</v>
       </c>
       <c r="J3" t="n">
-        <v>28.509</v>
+        <v>27.976</v>
       </c>
     </row>
     <row r="4">
@@ -3475,10 +3475,10 @@
         <v>1.27</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7177</v>
+        <v>0.6874</v>
       </c>
       <c r="J4" t="n">
-        <v>18.6602</v>
+        <v>17.8724</v>
       </c>
     </row>
     <row r="5">
@@ -3515,10 +3515,10 @@
         <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4568</v>
+        <v>0.4528</v>
       </c>
       <c r="J5" t="n">
-        <v>11.8768</v>
+        <v>11.7728</v>
       </c>
     </row>
     <row r="6">
@@ -3555,10 +3555,10 @@
         <v>0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8575</v>
+        <v>-0.7853</v>
       </c>
       <c r="J6" t="n">
-        <v>-22.295</v>
+        <v>-20.4178</v>
       </c>
     </row>
     <row r="7">
@@ -3595,10 +3595,10 @@
         <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2725</v>
+        <v>0.2667</v>
       </c>
       <c r="J7" t="n">
-        <v>7.085</v>
+        <v>6.9342</v>
       </c>
     </row>
     <row r="8">
@@ -3635,10 +3635,10 @@
         <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1523</v>
+        <v>-0.169</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.9598</v>
+        <v>-4.394</v>
       </c>
     </row>
     <row r="9">
@@ -3675,10 +3675,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1623</v>
+        <v>-0.1793</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.2198</v>
+        <v>-4.6618</v>
       </c>
     </row>
     <row r="10">
@@ -3715,10 +3715,10 @@
         <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1919</v>
+        <v>-0.2093</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.9894</v>
+        <v>-5.4418</v>
       </c>
     </row>
     <row r="11">
@@ -3755,10 +3755,10 @@
         <v>0.64</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3753</v>
+        <v>-0.3885</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.7578</v>
+        <v>-10.101</v>
       </c>
     </row>
     <row r="12">
@@ -3795,10 +3795,10 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2002</v>
+        <v>0.1948</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6046</v>
+        <v>4.4804</v>
       </c>
     </row>
     <row r="13">
@@ -3835,10 +3835,10 @@
         <v>0.91</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0969</v>
+        <v>-0.1153</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2287</v>
+        <v>-2.6519</v>
       </c>
     </row>
     <row r="14">
@@ -3875,10 +3875,10 @@
         <v>0.72</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2896</v>
+        <v>-0.3076</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.6608</v>
+        <v>-7.0748</v>
       </c>
     </row>
     <row r="15">
@@ -3915,10 +3915,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3463</v>
+        <v>-0.3625</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.9649</v>
+        <v>-8.3375</v>
       </c>
     </row>
     <row r="16">
@@ -3955,10 +3955,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4307</v>
+        <v>-0.4429</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.9061</v>
+        <v>-10.1867</v>
       </c>
     </row>
     <row r="17">
@@ -3995,10 +3995,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7974</v>
+        <v>0.7873</v>
       </c>
       <c r="J17" t="n">
-        <v>18.3402</v>
+        <v>18.1079</v>
       </c>
     </row>
     <row r="18">
@@ -4035,10 +4035,10 @@
         <v>1.64</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7659</v>
+        <v>0.7582</v>
       </c>
       <c r="J18" t="n">
-        <v>17.6157</v>
+        <v>17.4386</v>
       </c>
     </row>
     <row r="19">
@@ -4075,10 +4075,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2289</v>
+        <v>0.2478</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2647</v>
+        <v>5.6994</v>
       </c>
     </row>
     <row r="20">
@@ -4115,10 +4115,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1758</v>
+        <v>0.195</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0434</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="21">
@@ -4155,10 +4155,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4585</v>
+        <v>-0.4618</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.5455</v>
+        <v>-10.6214</v>
       </c>
     </row>
     <row r="22">
@@ -4195,10 +4195,10 @@
         <v>1.53</v>
       </c>
       <c r="I22" t="n">
-        <v>1.186</v>
+        <v>1.2025</v>
       </c>
       <c r="J22" t="n">
-        <v>30.836</v>
+        <v>31.265</v>
       </c>
     </row>
     <row r="23">
@@ -4235,10 +4235,10 @@
         <v>1.39</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9947</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>25.8622</v>
+        <v>24.362</v>
       </c>
     </row>
     <row r="24">
@@ -4275,10 +4275,10 @@
         <v>1.22</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6118</v>
+        <v>0.5908</v>
       </c>
       <c r="J24" t="n">
-        <v>15.9068</v>
+        <v>15.3608</v>
       </c>
     </row>
     <row r="25">
@@ -4315,10 +4315,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4545</v>
+        <v>-0.4281</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.817</v>
+        <v>-11.1306</v>
       </c>
     </row>
     <row r="26">
@@ -4355,10 +4355,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.51</v>
+        <v>-0.4785</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.26</v>
+        <v>-12.441</v>
       </c>
     </row>
     <row r="27">
@@ -4395,10 +4395,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1914</v>
+        <v>0.1916</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9764</v>
+        <v>4.9816</v>
       </c>
     </row>
     <row r="28">
@@ -4435,10 +4435,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0532</v>
+        <v>-0.0649</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.3832</v>
+        <v>-1.6874</v>
       </c>
     </row>
     <row r="29">
@@ -4475,10 +4475,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0532</v>
+        <v>-0.0649</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.3832</v>
+        <v>-1.6874</v>
       </c>
     </row>
     <row r="30">
@@ -4515,10 +4515,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2361</v>
+        <v>-0.2522</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.1386</v>
+        <v>-6.5572</v>
       </c>
     </row>
     <row r="31">
@@ -4555,10 +4555,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3234</v>
+        <v>-0.3376</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.4084</v>
+        <v>-8.7776</v>
       </c>
     </row>
     <row r="32">
@@ -4595,10 +4595,10 @@
         <v>0.93</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.055</v>
+        <v>-0.0766</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.21</v>
+        <v>-1.6852</v>
       </c>
     </row>
     <row r="33">
@@ -4635,10 +4635,10 @@
         <v>0.78</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2239</v>
+        <v>-0.245</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.9258</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="34">
@@ -4675,10 +4675,10 @@
         <v>0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2534</v>
+        <v>-0.274</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.5748</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="35">
@@ -4715,10 +4715,10 @@
         <v>0.66</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3358</v>
+        <v>-0.3543</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.3876</v>
+        <v>-7.7946</v>
       </c>
     </row>
     <row r="36">
@@ -4755,10 +4755,10 @@
         <v>0.46</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5226</v>
+        <v>-0.5309</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.4972</v>
+        <v>-11.6798</v>
       </c>
     </row>
     <row r="37">
@@ -4795,10 +4795,10 @@
         <v>1.99</v>
       </c>
       <c r="I37" t="n">
-        <v>1.044</v>
+        <v>1.0479</v>
       </c>
       <c r="J37" t="n">
-        <v>22.968</v>
+        <v>23.0538</v>
       </c>
     </row>
     <row r="38">
@@ -4835,10 +4835,10 @@
         <v>1.63</v>
       </c>
       <c r="I38" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="J38" t="n">
-        <v>15.884</v>
+        <v>15.906</v>
       </c>
     </row>
     <row r="39">
@@ -4875,10 +4875,10 @@
         <v>1.32</v>
       </c>
       <c r="I39" t="n">
-        <v>0.401</v>
+        <v>0.4194</v>
       </c>
       <c r="J39" t="n">
-        <v>8.821999999999999</v>
+        <v>9.226800000000001</v>
       </c>
     </row>
     <row r="40">
@@ -4915,10 +4915,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.098</v>
+        <v>0.1217</v>
       </c>
       <c r="J40" t="n">
-        <v>2.156</v>
+        <v>2.6774</v>
       </c>
     </row>
     <row r="41">
@@ -4955,10 +4955,10 @@
         <v>1.07</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0829</v>
+        <v>0.1062</v>
       </c>
       <c r="J41" t="n">
-        <v>1.8238</v>
+        <v>2.3364</v>
       </c>
     </row>
     <row r="42">
@@ -4995,10 +4995,10 @@
         <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5051</v>
+        <v>0.486</v>
       </c>
       <c r="J42" t="n">
-        <v>13.1326</v>
+        <v>12.636</v>
       </c>
     </row>
     <row r="43">
@@ -5035,10 +5035,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1906</v>
+        <v>0.1957</v>
       </c>
       <c r="J43" t="n">
-        <v>4.9556</v>
+        <v>5.0882</v>
       </c>
     </row>
     <row r="44">
@@ -5075,10 +5075,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1247</v>
+        <v>0.1318</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2422</v>
+        <v>3.4268</v>
       </c>
     </row>
     <row r="45">
@@ -5115,10 +5115,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0493</v>
+        <v>0.056</v>
       </c>
       <c r="J45" t="n">
-        <v>1.2818</v>
+        <v>1.456</v>
       </c>
     </row>
     <row r="46">
@@ -5155,10 +5155,10 @@
         <v>0.88</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4133</v>
+        <v>-0.3993</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.7458</v>
+        <v>-10.3818</v>
       </c>
     </row>
     <row r="47">
@@ -5195,10 +5195,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5855</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>15.223</v>
+        <v>14.8486</v>
       </c>
     </row>
     <row r="48">
@@ -5235,10 +5235,10 @@
         <v>1.15</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3344</v>
+        <v>0.3385</v>
       </c>
       <c r="J48" t="n">
-        <v>8.6944</v>
+        <v>8.801</v>
       </c>
     </row>
     <row r="49">
@@ -5275,10 +5275,10 @@
         <v>1.13</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2962</v>
+        <v>0.3024</v>
       </c>
       <c r="J49" t="n">
-        <v>7.7012</v>
+        <v>7.8624</v>
       </c>
     </row>
     <row r="50">
@@ -5315,10 +5315,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1606</v>
+        <v>-0.1728</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.1756</v>
+        <v>-4.4928</v>
       </c>
     </row>
     <row r="51">
@@ -5355,10 +5355,10 @@
         <v>0.75</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2928</v>
+        <v>-0.3045</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.6128</v>
+        <v>-7.917</v>
       </c>
     </row>
     <row r="52">
@@ -5395,10 +5395,10 @@
         <v>1.25</v>
       </c>
       <c r="I52" t="n">
-        <v>0.541</v>
+        <v>0.5992</v>
       </c>
       <c r="J52" t="n">
-        <v>12.984</v>
+        <v>14.3808</v>
       </c>
     </row>
     <row r="53">
@@ -5435,10 +5435,10 @@
         <v>1.23</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5129</v>
+        <v>0.5679</v>
       </c>
       <c r="J53" t="n">
-        <v>12.3096</v>
+        <v>13.6296</v>
       </c>
     </row>
     <row r="54">
@@ -5475,10 +5475,10 @@
         <v>1.21</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4846</v>
+        <v>0.5361</v>
       </c>
       <c r="J54" t="n">
-        <v>11.6304</v>
+        <v>12.8664</v>
       </c>
     </row>
     <row r="55">
@@ -5515,10 +5515,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4274</v>
+        <v>0.4712</v>
       </c>
       <c r="J55" t="n">
-        <v>10.2576</v>
+        <v>11.3088</v>
       </c>
     </row>
     <row r="56">
@@ -5555,10 +5555,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1366</v>
+        <v>-0.1292</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.2784</v>
+        <v>-3.1008</v>
       </c>
     </row>
     <row r="57">
@@ -5595,10 +5595,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3887</v>
+        <v>0.4169</v>
       </c>
       <c r="J57" t="n">
-        <v>9.328799999999999</v>
+        <v>10.0056</v>
       </c>
     </row>
     <row r="58">
@@ -5635,10 +5635,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3264</v>
+        <v>0.3261</v>
       </c>
       <c r="J58" t="n">
-        <v>7.8336</v>
+        <v>7.8264</v>
       </c>
     </row>
     <row r="59">
@@ -5675,10 +5675,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2203</v>
+        <v>-0.2357</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.2872</v>
+        <v>-5.6568</v>
       </c>
     </row>
     <row r="60">
@@ -5715,10 +5715,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2203</v>
+        <v>-0.2357</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.2872</v>
+        <v>-5.6568</v>
       </c>
     </row>
     <row r="61">
@@ -5755,10 +5755,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.6368</v>
+        <v>-7.9608</v>
       </c>
     </row>
     <row r="62">
@@ -5795,10 +5795,10 @@
         <v>1.7</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0804</v>
+        <v>1.19</v>
       </c>
       <c r="J62" t="n">
-        <v>23.7688</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="63">
@@ -5835,10 +5835,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6896</v>
+        <v>0.7691</v>
       </c>
       <c r="J63" t="n">
-        <v>15.1712</v>
+        <v>16.9202</v>
       </c>
     </row>
     <row r="64">
@@ -5875,10 +5875,10 @@
         <v>1.34</v>
       </c>
       <c r="I64" t="n">
-        <v>0.64</v>
+        <v>0.7143</v>
       </c>
       <c r="J64" t="n">
-        <v>14.08</v>
+        <v>15.7146</v>
       </c>
     </row>
     <row r="65">
@@ -5915,10 +5915,10 @@
         <v>1.2</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4507</v>
+        <v>0.5032</v>
       </c>
       <c r="J65" t="n">
-        <v>9.9154</v>
+        <v>11.0704</v>
       </c>
     </row>
     <row r="66">
@@ -5955,10 +5955,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.269</v>
+        <v>0.2869</v>
       </c>
       <c r="J66" t="n">
-        <v>5.918</v>
+        <v>6.3118</v>
       </c>
     </row>
     <row r="67">
@@ -5995,10 +5995,10 @@
         <v>1.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4112</v>
+        <v>0.4389</v>
       </c>
       <c r="J67" t="n">
-        <v>9.0464</v>
+        <v>9.655799999999999</v>
       </c>
     </row>
     <row r="68">
@@ -6035,10 +6035,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0517</v>
+        <v>-0.0675</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.1374</v>
+        <v>-1.485</v>
       </c>
     </row>
     <row r="69">
@@ -6075,10 +6075,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2161</v>
+        <v>-0.2347</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.7542</v>
+        <v>-5.1634</v>
       </c>
     </row>
     <row r="70">
@@ -6115,10 +6115,10 @@
         <v>0.59</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4152</v>
+        <v>-0.4277</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.134399999999999</v>
+        <v>-9.4094</v>
       </c>
     </row>
     <row r="71">
@@ -6155,10 +6155,10 @@
         <v>0.53</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4708</v>
+        <v>-0.4804</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.3576</v>
+        <v>-10.5688</v>
       </c>
     </row>
     <row r="72">
@@ -6195,10 +6195,10 @@
         <v>1.07</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2312</v>
+        <v>0.2263</v>
       </c>
       <c r="J72" t="n">
-        <v>5.78</v>
+        <v>5.6575</v>
       </c>
     </row>
     <row r="73">
@@ -6235,10 +6235,10 @@
         <v>0.98</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0178</v>
+        <v>-0.0288</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.445</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="74">
@@ -6275,10 +6275,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.141</v>
+        <v>-0.1577</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.525</v>
+        <v>-3.9425</v>
       </c>
     </row>
     <row r="75">
@@ -6315,10 +6315,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.201</v>
+        <v>-0.2186</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.025</v>
+        <v>-5.465</v>
       </c>
     </row>
     <row r="76">
@@ -6355,10 +6355,10 @@
         <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5037</v>
+        <v>-0.5105</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.5925</v>
+        <v>-12.7625</v>
       </c>
     </row>
     <row r="77">
@@ -6395,10 +6395,10 @@
         <v>1.63</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0123</v>
+        <v>1.1147</v>
       </c>
       <c r="J77" t="n">
-        <v>25.3075</v>
+        <v>27.8675</v>
       </c>
     </row>
     <row r="78">
@@ -6435,10 +6435,10 @@
         <v>1.52</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8763</v>
+        <v>0.9694</v>
       </c>
       <c r="J78" t="n">
-        <v>21.9075</v>
+        <v>24.235</v>
       </c>
     </row>
     <row r="79">
@@ -6475,10 +6475,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.488</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>12.2</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="80">
@@ -6515,10 +6515,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1663</v>
+        <v>0.1872</v>
       </c>
       <c r="J80" t="n">
-        <v>4.1575</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="81">
@@ -6555,10 +6555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3006</v>
+        <v>-0.2804</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.515</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="82">
@@ -6595,10 +6595,10 @@
         <v>2.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8779</v>
+        <v>1.0093</v>
       </c>
       <c r="J82" t="n">
-        <v>21.0696</v>
+        <v>24.2232</v>
       </c>
     </row>
     <row r="83">
@@ -6635,10 +6635,10 @@
         <v>1.6</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5476</v>
+        <v>0.6308</v>
       </c>
       <c r="J83" t="n">
-        <v>13.1424</v>
+        <v>15.1392</v>
       </c>
     </row>
     <row r="84">
@@ -6675,10 +6675,10 @@
         <v>1.38</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4135</v>
+        <v>0.472</v>
       </c>
       <c r="J84" t="n">
-        <v>9.923999999999999</v>
+        <v>11.328</v>
       </c>
     </row>
     <row r="85">
@@ -6715,10 +6715,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0866</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.076</v>
+        <v>-2.0784</v>
       </c>
     </row>
     <row r="86">
@@ -6755,10 +6755,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2748</v>
+        <v>-0.2806</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.5952</v>
+        <v>-6.7344</v>
       </c>
     </row>
     <row r="87">
@@ -6795,10 +6795,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4835</v>
+        <v>0.5283</v>
       </c>
       <c r="J87" t="n">
-        <v>11.604</v>
+        <v>12.6792</v>
       </c>
     </row>
     <row r="88">
@@ -6835,10 +6835,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0857</v>
+        <v>-0.1037</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.0568</v>
+        <v>-2.4888</v>
       </c>
     </row>
     <row r="89">
@@ -6875,10 +6875,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2052</v>
+        <v>-0.2241</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.9248</v>
+        <v>-5.3784</v>
       </c>
     </row>
     <row r="90">
@@ -6915,10 +6915,10 @@
         <v>0.51</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4869</v>
+        <v>-0.4958</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.6856</v>
+        <v>-11.8992</v>
       </c>
     </row>
     <row r="91">
@@ -6955,10 +6955,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5969</v>
+        <v>-0.5987</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.3256</v>
+        <v>-14.3688</v>
       </c>
     </row>
     <row r="92">
@@ -6995,10 +6995,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3972</v>
+        <v>0.4233</v>
       </c>
       <c r="J92" t="n">
-        <v>10.7244</v>
+        <v>11.4291</v>
       </c>
     </row>
     <row r="93">
@@ -7035,10 +7035,10 @@
         <v>0.85</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1716</v>
+        <v>-0.1889</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.6332</v>
+        <v>-5.1003</v>
       </c>
     </row>
     <row r="94">
@@ -7075,10 +7075,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2012</v>
+        <v>-0.2187</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.4324</v>
+        <v>-5.9049</v>
       </c>
     </row>
     <row r="95">
@@ -7115,10 +7115,10 @@
         <v>0.72</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2987</v>
+        <v>-0.3147</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.0649</v>
+        <v>-8.4969</v>
       </c>
     </row>
     <row r="96">
@@ -7155,10 +7155,10 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3178</v>
+        <v>-0.3332</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.5806</v>
+        <v>-8.9964</v>
       </c>
     </row>
     <row r="97">
@@ -7195,10 +7195,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7752</v>
+        <v>0.8576</v>
       </c>
       <c r="J97" t="n">
-        <v>20.9304</v>
+        <v>23.1552</v>
       </c>
     </row>
     <row r="98">
@@ -7235,10 +7235,10 @@
         <v>1.34</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7287</v>
       </c>
       <c r="J98" t="n">
-        <v>17.7336</v>
+        <v>19.6749</v>
       </c>
     </row>
     <row r="99">
@@ -7275,10 +7275,10 @@
         <v>1.31</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6166</v>
+        <v>0.6845</v>
       </c>
       <c r="J99" t="n">
-        <v>16.6482</v>
+        <v>18.4815</v>
       </c>
     </row>
     <row r="100">
@@ -7315,10 +7315,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1061</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.8647</v>
+        <v>-2.5704</v>
       </c>
     </row>
     <row r="101">
@@ -7355,10 +7355,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1472</v>
+        <v>-0.1366</v>
       </c>
       <c r="J101" t="n">
-        <v>-3.9744</v>
+        <v>-3.6882</v>
       </c>
     </row>
     <row r="102">
@@ -7395,10 +7395,10 @@
         <v>1.09</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1721</v>
+        <v>0.1817</v>
       </c>
       <c r="J102" t="n">
-        <v>6.0235</v>
+        <v>6.3595</v>
       </c>
     </row>
     <row r="103">
@@ -7435,10 +7435,10 @@
         <v>1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0882</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>3.087</v>
+        <v>3.402</v>
       </c>
     </row>
     <row r="104">
@@ -7475,10 +7475,10 @@
         <v>0.99</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0208</v>
+        <v>-0.0254</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.728</v>
+        <v>-0.889</v>
       </c>
     </row>
     <row r="105">
@@ -7515,10 +7515,10 @@
         <v>0.97</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0504</v>
+        <v>-0.0585</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.764</v>
+        <v>-2.0475</v>
       </c>
     </row>
     <row r="106">
@@ -7555,10 +7555,10 @@
         <v>0.93</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1005</v>
+        <v>-0.1118</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.5175</v>
+        <v>-3.913</v>
       </c>
     </row>
     <row r="107">
@@ -7595,10 +7595,10 @@
         <v>1.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4557</v>
+        <v>0.5153</v>
       </c>
       <c r="J107" t="n">
-        <v>15.9495</v>
+        <v>18.0355</v>
       </c>
     </row>
     <row r="108">
@@ -7635,10 +7635,10 @@
         <v>1.07</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1223</v>
+        <v>0.1361</v>
       </c>
       <c r="J108" t="n">
-        <v>4.2805</v>
+        <v>4.7635</v>
       </c>
     </row>
     <row r="109">
@@ -7675,10 +7675,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.04</v>
+        <v>0.0493</v>
       </c>
       <c r="J109" t="n">
-        <v>1.4</v>
+        <v>1.7255</v>
       </c>
     </row>
     <row r="110">
@@ -7715,10 +7715,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0271</v>
+        <v>-0.0302</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.9485</v>
+        <v>-1.057</v>
       </c>
     </row>
     <row r="111">
@@ -7755,10 +7755,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1641</v>
+        <v>-0.1755</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.7435</v>
+        <v>-6.1425</v>
       </c>
     </row>
     <row r="112">
@@ -7795,10 +7795,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.9066</v>
       </c>
       <c r="J112" t="n">
-        <v>22.1157</v>
+        <v>24.4782</v>
       </c>
     </row>
     <row r="113">
@@ -7835,10 +7835,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.664</v>
+        <v>0.738</v>
       </c>
       <c r="J113" t="n">
-        <v>17.928</v>
+        <v>19.926</v>
       </c>
     </row>
     <row r="114">
@@ -7875,10 +7875,10 @@
         <v>1.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4629</v>
+        <v>0.5137</v>
       </c>
       <c r="J114" t="n">
-        <v>12.4983</v>
+        <v>13.8699</v>
       </c>
     </row>
     <row r="115">
@@ -7915,10 +7915,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3735</v>
+        <v>0.4027</v>
       </c>
       <c r="J115" t="n">
-        <v>10.0845</v>
+        <v>10.8729</v>
       </c>
     </row>
     <row r="116">
@@ -7955,10 +7955,10 @@
         <v>1.07</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2038</v>
+        <v>0.2209</v>
       </c>
       <c r="J116" t="n">
-        <v>5.5026</v>
+        <v>5.9643</v>
       </c>
     </row>
     <row r="117">
@@ -7995,10 +7995,10 @@
         <v>1.22</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4317</v>
+        <v>0.4733</v>
       </c>
       <c r="J117" t="n">
-        <v>11.6559</v>
+        <v>12.7791</v>
       </c>
     </row>
     <row r="118">
@@ -8035,10 +8035,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0508</v>
+        <v>0.0527</v>
       </c>
       <c r="J118" t="n">
-        <v>1.3716</v>
+        <v>1.4229</v>
       </c>
     </row>
     <row r="119">
@@ -8075,10 +8075,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0448</v>
+        <v>-0.0542</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.2096</v>
+        <v>-1.4634</v>
       </c>
     </row>
     <row r="120">
@@ -8115,10 +8115,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.251</v>
+        <v>-0.2659</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.777</v>
+        <v>-7.1793</v>
       </c>
     </row>
     <row r="121">
@@ -8155,10 +8155,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.338</v>
+        <v>-0.3508</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.125999999999999</v>
+        <v>-9.4716</v>
       </c>
     </row>
     <row r="122">
@@ -8195,10 +8195,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8722</v>
+        <v>0.9609</v>
       </c>
       <c r="J122" t="n">
-        <v>23.5494</v>
+        <v>25.9443</v>
       </c>
     </row>
     <row r="123">
@@ -8235,10 +8235,10 @@
         <v>1.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.7771</v>
       </c>
       <c r="J123" t="n">
-        <v>18.9567</v>
+        <v>20.9817</v>
       </c>
     </row>
     <row r="124">
@@ -8275,10 +8275,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3662</v>
+        <v>0.3885</v>
       </c>
       <c r="J124" t="n">
-        <v>9.8874</v>
+        <v>10.4895</v>
       </c>
     </row>
     <row r="125">
@@ -8315,10 +8315,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1567</v>
+        <v>0.1726</v>
       </c>
       <c r="J125" t="n">
-        <v>4.2309</v>
+        <v>4.6602</v>
       </c>
     </row>
     <row r="126">
@@ -8355,10 +8355,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5115</v>
+        <v>-0.4795</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.8105</v>
+        <v>-12.9465</v>
       </c>
     </row>
     <row r="127">
@@ -8395,10 +8395,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3044</v>
+        <v>0.304</v>
       </c>
       <c r="J127" t="n">
-        <v>8.2188</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="128">
@@ -8435,10 +8435,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.105</v>
+        <v>0.1095</v>
       </c>
       <c r="J128" t="n">
-        <v>2.835</v>
+        <v>2.9565</v>
       </c>
     </row>
     <row r="129">
@@ -8475,10 +8475,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0829</v>
+        <v>-0.095</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.2383</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="130">
@@ -8515,10 +8515,10 @@
         <v>0.84</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1913</v>
+        <v>-0.2064</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.1651</v>
+        <v>-5.5728</v>
       </c>
     </row>
     <row r="131">
@@ -8555,10 +8555,10 @@
         <v>0.77</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2616</v>
+        <v>-0.2761</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.0632</v>
+        <v>-7.4547</v>
       </c>
     </row>
     <row r="132">
@@ -8595,10 +8595,10 @@
         <v>2.39</v>
       </c>
       <c r="I132" t="n">
-        <v>1.7594</v>
+        <v>1.9126</v>
       </c>
       <c r="J132" t="n">
-        <v>31.6692</v>
+        <v>34.4268</v>
       </c>
     </row>
     <row r="133">
@@ -8635,10 +8635,10 @@
         <v>1.96</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3079</v>
+        <v>1.4419</v>
       </c>
       <c r="J133" t="n">
-        <v>23.5422</v>
+        <v>25.9542</v>
       </c>
     </row>
     <row r="134">
@@ -8675,10 +8675,10 @@
         <v>1.54</v>
       </c>
       <c r="I134" t="n">
-        <v>0.8481</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>15.2658</v>
+        <v>17.1018</v>
       </c>
     </row>
     <row r="135">
@@ -8715,10 +8715,10 @@
         <v>1.49</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7885</v>
+        <v>0.8855</v>
       </c>
       <c r="J135" t="n">
-        <v>14.193</v>
+        <v>15.939</v>
       </c>
     </row>
     <row r="136">
@@ -8755,10 +8755,10 @@
         <v>1.18</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3788</v>
+        <v>0.4286</v>
       </c>
       <c r="J136" t="n">
-        <v>6.8184</v>
+        <v>7.7148</v>
       </c>
     </row>
     <row r="137">
@@ -8795,10 +8795,10 @@
         <v>0.48</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.4543</v>
+        <v>-0.475</v>
       </c>
       <c r="J137" t="n">
-        <v>-8.1774</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="138">
@@ -8835,10 +8835,10 @@
         <v>0.47</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.4637</v>
+        <v>-0.4837</v>
       </c>
       <c r="J138" t="n">
-        <v>-8.3466</v>
+        <v>-8.7066</v>
       </c>
     </row>
     <row r="139">
@@ -8875,10 +8875,10 @@
         <v>0.46</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4728</v>
+        <v>-0.4922</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.510400000000001</v>
+        <v>-8.8596</v>
       </c>
     </row>
     <row r="140">
@@ -8915,10 +8915,10 @@
         <v>0.43</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4988</v>
+        <v>-0.5165</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.978400000000001</v>
+        <v>-9.297000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8955,10 +8955,10 @@
         <v>0.41</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5175</v>
+        <v>-0.5337</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.315</v>
+        <v>-9.6066</v>
       </c>
     </row>
     <row r="142">
@@ -8995,10 +8995,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5452</v>
+        <v>0.5995</v>
       </c>
       <c r="J142" t="n">
-        <v>15.2656</v>
+        <v>16.786</v>
       </c>
     </row>
     <row r="143">
@@ -9035,10 +9035,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2999</v>
+        <v>0.3015</v>
       </c>
       <c r="J143" t="n">
-        <v>8.3972</v>
+        <v>8.442</v>
       </c>
     </row>
     <row r="144">
@@ -9075,10 +9075,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2432</v>
+        <v>0.2481</v>
       </c>
       <c r="J144" t="n">
-        <v>6.8096</v>
+        <v>6.9468</v>
       </c>
     </row>
     <row r="145">
@@ -9115,10 +9115,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1113</v>
+        <v>-0.1116</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.1164</v>
+        <v>-3.1248</v>
       </c>
     </row>
     <row r="146">
@@ -9155,10 +9155,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1113</v>
+        <v>-0.1116</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.1164</v>
+        <v>-3.1248</v>
       </c>
     </row>
     <row r="147">
@@ -9195,10 +9195,10 @@
         <v>1.23</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4204</v>
+        <v>0.4652</v>
       </c>
       <c r="J147" t="n">
-        <v>11.7712</v>
+        <v>13.0256</v>
       </c>
     </row>
     <row r="148">
@@ -9235,10 +9235,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2769</v>
+        <v>0.2839</v>
       </c>
       <c r="J148" t="n">
-        <v>7.7532</v>
+        <v>7.9492</v>
       </c>
     </row>
     <row r="149">
@@ -9275,10 +9275,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1544</v>
+        <v>0.1649</v>
       </c>
       <c r="J149" t="n">
-        <v>4.3232</v>
+        <v>4.6172</v>
       </c>
     </row>
     <row r="150">
@@ -9315,10 +9315,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1544</v>
+        <v>0.1649</v>
       </c>
       <c r="J150" t="n">
-        <v>4.3232</v>
+        <v>4.6172</v>
       </c>
     </row>
     <row r="151">
@@ -9355,10 +9355,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3121</v>
+        <v>-0.3233</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.738799999999999</v>
+        <v>-9.0524</v>
       </c>
     </row>
     <row r="152">
@@ -9395,10 +9395,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>28.716</v>
+        <v>27.264</v>
       </c>
     </row>
     <row r="153">
@@ -9435,10 +9435,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3502</v>
+        <v>0.354</v>
       </c>
       <c r="J153" t="n">
-        <v>10.506</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="154">
@@ -9475,10 +9475,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0408</v>
+        <v>-0.0464</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.224</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="155">
@@ -9515,10 +9515,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2449</v>
+        <v>-0.257</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.347</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="156">
@@ -9555,10 +9555,10 @@
         <v>0.8</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2449</v>
+        <v>-0.257</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.347</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="157">
@@ -9595,10 +9595,10 @@
         <v>1.38</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9979</v>
+        <v>0.9353</v>
       </c>
       <c r="J157" t="n">
-        <v>29.937</v>
+        <v>28.059</v>
       </c>
     </row>
     <row r="158">
@@ -9635,10 +9635,10 @@
         <v>1.2</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5588</v>
       </c>
       <c r="J158" t="n">
-        <v>17.403</v>
+        <v>16.764</v>
       </c>
     </row>
     <row r="159">
@@ -9675,10 +9675,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2058</v>
+        <v>0.2146</v>
       </c>
       <c r="J159" t="n">
-        <v>6.174</v>
+        <v>6.438</v>
       </c>
     </row>
     <row r="160">
@@ -9715,10 +9715,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1935</v>
+        <v>-0.189</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.805</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="161">
@@ -9755,10 +9755,10 @@
         <v>0.95</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2269</v>
+        <v>-0.2208</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.807</v>
+        <v>-6.624</v>
       </c>
     </row>
     <row r="162">
@@ -9795,10 +9795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J162" t="n">
-        <v>-1.7375</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="163">
@@ -9835,10 +9835,10 @@
         <v>0.89</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.128</v>
+        <v>-0.1451</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.2</v>
+        <v>-3.6275</v>
       </c>
     </row>
     <row r="164">
@@ -9875,10 +9875,10 @@
         <v>0.85</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1703</v>
+        <v>-0.1879</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.2575</v>
+        <v>-4.6975</v>
       </c>
     </row>
     <row r="165">
@@ -9915,10 +9915,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.248</v>
+        <v>-0.2656</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.2</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="166">
@@ -9955,10 +9955,10 @@
         <v>0.72</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2962</v>
+        <v>-0.3128</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.405</v>
+        <v>-7.82</v>
       </c>
     </row>
     <row r="167">
@@ -9995,10 +9995,10 @@
         <v>1.56</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1972</v>
+        <v>1.1678</v>
       </c>
       <c r="J167" t="n">
-        <v>29.93</v>
+        <v>29.195</v>
       </c>
     </row>
     <row r="168">
@@ -10035,10 +10035,10 @@
         <v>1.42</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0176</v>
+        <v>0.9668</v>
       </c>
       <c r="J168" t="n">
-        <v>25.44</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="169">
@@ -10075,10 +10075,10 @@
         <v>1.37</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9271</v>
+        <v>0.875</v>
       </c>
       <c r="J169" t="n">
-        <v>23.1775</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="170">
@@ -10115,10 +10115,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1943</v>
+        <v>0.2143</v>
       </c>
       <c r="J170" t="n">
-        <v>4.8575</v>
+        <v>5.3575</v>
       </c>
     </row>
     <row r="171">
@@ -10155,10 +10155,10 @@
         <v>1.01</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0146</v>
+        <v>0.0116</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.365</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="172">
@@ -10195,10 +10195,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2891</v>
+        <v>0.2521</v>
       </c>
       <c r="J172" t="n">
-        <v>6.0711</v>
+        <v>5.2941</v>
       </c>
     </row>
     <row r="173">
@@ -10235,10 +10235,10 @@
         <v>0.73</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2579</v>
+        <v>-0.2814</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.4159</v>
+        <v>-5.9094</v>
       </c>
     </row>
     <row r="174">
@@ -10275,10 +10275,10 @@
         <v>0.58</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3974</v>
+        <v>-0.4153</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.3454</v>
+        <v>-8.721299999999999</v>
       </c>
     </row>
     <row r="175">
@@ -10315,10 +10315,10 @@
         <v>0.49</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4815</v>
+        <v>-0.4945</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.1115</v>
+        <v>-10.3845</v>
       </c>
     </row>
     <row r="176">
@@ -10355,10 +10355,10 @@
         <v>0.35</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.614</v>
+        <v>-0.6172</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.894</v>
+        <v>-12.9612</v>
       </c>
     </row>
     <row r="177">
@@ -10395,10 +10395,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.384</v>
+        <v>1.372</v>
       </c>
       <c r="J177" t="n">
-        <v>29.064</v>
+        <v>28.812</v>
       </c>
     </row>
     <row r="178">
@@ -10435,10 +10435,10 @@
         <v>1.56</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1725</v>
+        <v>1.1461</v>
       </c>
       <c r="J178" t="n">
-        <v>24.6225</v>
+        <v>24.0681</v>
       </c>
     </row>
     <row r="179">
@@ -10475,10 +10475,10 @@
         <v>1.42</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9971</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>20.9391</v>
+        <v>19.9311</v>
       </c>
     </row>
     <row r="180">
@@ -10515,10 +10515,10 @@
         <v>1.31</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7734</v>
+        <v>0.7436</v>
       </c>
       <c r="J180" t="n">
-        <v>16.2414</v>
+        <v>15.6156</v>
       </c>
     </row>
     <row r="181">
@@ -10555,10 +10555,10 @@
         <v>1.1</v>
       </c>
       <c r="I181" t="n">
-        <v>0.2511</v>
+        <v>0.2744</v>
       </c>
       <c r="J181" t="n">
-        <v>5.2731</v>
+        <v>5.7624</v>
       </c>
     </row>
     <row r="182">
@@ -10595,10 +10595,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2774</v>
+        <v>1.2456</v>
       </c>
       <c r="J182" t="n">
-        <v>31.935</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="183">
@@ -10635,10 +10635,10 @@
         <v>1.19</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5501</v>
+        <v>0.533</v>
       </c>
       <c r="J183" t="n">
-        <v>13.7525</v>
+        <v>13.325</v>
       </c>
     </row>
     <row r="184">
@@ -10675,10 +10675,10 @@
         <v>1.19</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5501</v>
+        <v>0.533</v>
       </c>
       <c r="J184" t="n">
-        <v>13.7525</v>
+        <v>13.325</v>
       </c>
     </row>
     <row r="185">
@@ -10715,10 +10715,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3257</v>
+        <v>-0.3124</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.1425</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="186">
@@ -10755,10 +10755,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7845</v>
+        <v>-0.7252</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.6125</v>
+        <v>-18.13</v>
       </c>
     </row>
     <row r="187">
@@ -10795,10 +10795,10 @@
         <v>1.19</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4222</v>
+        <v>0.418</v>
       </c>
       <c r="J187" t="n">
-        <v>10.555</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="188">
@@ -10835,10 +10835,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3848</v>
+        <v>0.3831</v>
       </c>
       <c r="J188" t="n">
-        <v>9.619999999999999</v>
+        <v>9.577500000000001</v>
       </c>
     </row>
     <row r="189">
@@ -10875,10 +10875,10 @@
         <v>1.13</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3079</v>
+        <v>0.3108</v>
       </c>
       <c r="J189" t="n">
-        <v>7.6975</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="190">
@@ -10915,10 +10915,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1336</v>
+        <v>-0.1464</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.34</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="191">
@@ -10955,10 +10955,10 @@
         <v>0.58</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4468</v>
+        <v>-0.4541</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.17</v>
+        <v>-11.3525</v>
       </c>
     </row>
     <row r="192">
@@ -10995,10 +10995,10 @@
         <v>0.9</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.1141</v>
       </c>
       <c r="J192" t="n">
-        <v>-2.0196</v>
+        <v>-2.5102</v>
       </c>
     </row>
     <row r="193">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2335</v>
+        <v>-0.2546</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.137</v>
+        <v>-5.6012</v>
       </c>
     </row>
     <row r="194">
@@ -11075,10 +11075,10 @@
         <v>0.74</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2627</v>
+        <v>-0.2831</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.7794</v>
+        <v>-6.2282</v>
       </c>
     </row>
     <row r="195">
@@ -11115,10 +11115,10 @@
         <v>0.59</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4009</v>
+        <v>-0.4165</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.819800000000001</v>
+        <v>-9.163</v>
       </c>
     </row>
     <row r="196">
@@ -11155,10 +11155,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4196</v>
+        <v>-0.4342</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.231199999999999</v>
+        <v>-9.5524</v>
       </c>
     </row>
     <row r="197">
@@ -11195,10 +11195,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.5994</v>
+        <v>1.6011</v>
       </c>
       <c r="J197" t="n">
-        <v>35.1868</v>
+        <v>35.2242</v>
       </c>
     </row>
     <row r="198">
@@ -11235,10 +11235,10 @@
         <v>1.93</v>
       </c>
       <c r="I198" t="n">
-        <v>1.5882</v>
+        <v>1.5893</v>
       </c>
       <c r="J198" t="n">
-        <v>34.9404</v>
+        <v>34.9646</v>
       </c>
     </row>
     <row r="199">
@@ -11275,10 +11275,10 @@
         <v>1.37</v>
       </c>
       <c r="I199" t="n">
-        <v>0.894</v>
+        <v>0.8517</v>
       </c>
       <c r="J199" t="n">
-        <v>19.668</v>
+        <v>18.7374</v>
       </c>
     </row>
     <row r="200">
@@ -11315,10 +11315,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2945</v>
+        <v>0.317</v>
       </c>
       <c r="J200" t="n">
-        <v>6.479</v>
+        <v>6.974</v>
       </c>
     </row>
     <row r="201">
@@ -11355,10 +11355,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1508</v>
+        <v>0.1838</v>
       </c>
       <c r="J201" t="n">
-        <v>3.3176</v>
+        <v>4.0436</v>
       </c>
     </row>
     <row r="202">
@@ -11395,10 +11395,10 @@
         <v>1.57</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2122</v>
+        <v>1.1833</v>
       </c>
       <c r="J202" t="n">
-        <v>31.5172</v>
+        <v>30.7658</v>
       </c>
     </row>
     <row r="203">
@@ -11435,10 +11435,10 @@
         <v>1.4</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9873</v>
+        <v>0.9334</v>
       </c>
       <c r="J203" t="n">
-        <v>25.6698</v>
+        <v>24.2684</v>
       </c>
     </row>
     <row r="204">
@@ -11475,10 +11475,10 @@
         <v>1.35</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8871</v>
+        <v>0.8387</v>
       </c>
       <c r="J204" t="n">
-        <v>23.0646</v>
+        <v>21.8062</v>
       </c>
     </row>
     <row r="205">
@@ -11515,10 +11515,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1012</v>
+        <v>0.1252</v>
       </c>
       <c r="J205" t="n">
-        <v>2.6312</v>
+        <v>3.2552</v>
       </c>
     </row>
     <row r="206">
@@ -11555,10 +11555,10 @@
         <v>1.01</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0118</v>
+        <v>0.0136</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.3068</v>
+        <v>0.3536</v>
       </c>
     </row>
     <row r="207">
@@ -11595,10 +11595,10 @@
         <v>1.15</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3991</v>
+        <v>0.3859</v>
       </c>
       <c r="J207" t="n">
-        <v>10.3766</v>
+        <v>10.0334</v>
       </c>
     </row>
     <row r="208">
@@ -11635,10 +11635,10 @@
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1818</v>
+        <v>-0.1991</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.7268</v>
+        <v>-5.1766</v>
       </c>
     </row>
     <row r="209">
@@ -11675,10 +11675,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2115</v>
+        <v>-0.2289</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.499</v>
+        <v>-5.9514</v>
       </c>
     </row>
     <row r="210">
@@ -11715,10 +11715,10 @@
         <v>0.74</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.28</v>
+        <v>-0.2963</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.28</v>
+        <v>-7.7038</v>
       </c>
     </row>
     <row r="211">
@@ -11755,10 +11755,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.28</v>
+        <v>-0.2963</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.28</v>
+        <v>-7.7038</v>
       </c>
     </row>
     <row r="212">
@@ -11795,10 +11795,10 @@
         <v>0.93</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0169</v>
+        <v>-0.0465</v>
       </c>
       <c r="J212" t="n">
-        <v>-0.3211</v>
+        <v>-0.8835</v>
       </c>
     </row>
     <row r="213">
@@ -11835,10 +11835,10 @@
         <v>0.67</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.3115</v>
+        <v>-0.3339</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.9185</v>
+        <v>-6.3441</v>
       </c>
     </row>
     <row r="214">
@@ -11875,10 +11875,10 @@
         <v>0.61</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3665</v>
+        <v>-0.3866</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.9635</v>
+        <v>-7.3454</v>
       </c>
     </row>
     <row r="215">
@@ -11915,10 +11915,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4205</v>
+        <v>-0.438</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.9895</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -11955,10 +11955,10 @@
         <v>0.3</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.6579</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.4982</v>
+        <v>-12.5001</v>
       </c>
     </row>
     <row r="217">
@@ -11995,10 +11995,10 @@
         <v>2.17</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8338</v>
+        <v>1.8544</v>
       </c>
       <c r="J217" t="n">
-        <v>34.8422</v>
+        <v>35.2336</v>
       </c>
     </row>
     <row r="218">
@@ -12035,10 +12035,10 @@
         <v>1.67</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2853</v>
+        <v>1.2703</v>
       </c>
       <c r="J218" t="n">
-        <v>24.4207</v>
+        <v>24.1357</v>
       </c>
     </row>
     <row r="219">
@@ -12075,10 +12075,10 @@
         <v>1.4</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9462</v>
+        <v>0.9012</v>
       </c>
       <c r="J219" t="n">
-        <v>17.9778</v>
+        <v>17.1228</v>
       </c>
     </row>
     <row r="220">
@@ -12115,10 +12115,10 @@
         <v>1.26</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6362</v>
+        <v>0.6266</v>
       </c>
       <c r="J220" t="n">
-        <v>12.0878</v>
+        <v>11.9054</v>
       </c>
     </row>
     <row r="221">
@@ -12155,10 +12155,10 @@
         <v>1.19</v>
       </c>
       <c r="I221" t="n">
-        <v>0.4668</v>
+        <v>0.4754</v>
       </c>
       <c r="J221" t="n">
-        <v>8.869199999999999</v>
+        <v>9.0326</v>
       </c>
     </row>
     <row r="222">
@@ -12195,10 +12195,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6877</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>18.5679</v>
+        <v>17.9226</v>
       </c>
     </row>
     <row r="223">
@@ -12235,10 +12235,10 @@
         <v>1.32</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6369</v>
+        <v>0.6178</v>
       </c>
       <c r="J223" t="n">
-        <v>17.1963</v>
+        <v>16.6806</v>
       </c>
     </row>
     <row r="224">
@@ -12275,10 +12275,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1544</v>
+        <v>0.1649</v>
       </c>
       <c r="J224" t="n">
-        <v>4.1688</v>
+        <v>4.4523</v>
       </c>
     </row>
     <row r="225">
@@ -12315,10 +12315,10 @@
         <v>0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1043</v>
+        <v>-0.1148</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.8161</v>
+        <v>-3.0996</v>
       </c>
     </row>
     <row r="226">
@@ -12355,10 +12355,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4873</v>
+        <v>-0.492</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.1571</v>
+        <v>-13.284</v>
       </c>
     </row>
     <row r="227">
@@ -12395,10 +12395,10 @@
         <v>1.68</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3877</v>
+        <v>1.3628</v>
       </c>
       <c r="J227" t="n">
-        <v>37.4679</v>
+        <v>36.7956</v>
       </c>
     </row>
     <row r="228">
@@ -12435,10 +12435,10 @@
         <v>1.27</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7413</v>
+        <v>0.7036</v>
       </c>
       <c r="J228" t="n">
-        <v>20.0151</v>
+        <v>18.9972</v>
       </c>
     </row>
     <row r="229">
@@ -12475,10 +12475,10 @@
         <v>1.11</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3436</v>
+        <v>0.345</v>
       </c>
       <c r="J229" t="n">
-        <v>9.277200000000001</v>
+        <v>9.315</v>
       </c>
     </row>
     <row r="230">
@@ -12515,10 +12515,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2672</v>
+        <v>-0.2569</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.2144</v>
+        <v>-6.9363</v>
       </c>
     </row>
     <row r="231">
@@ -12555,10 +12555,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>-24.5916</v>
+        <v>-22.5504</v>
       </c>
     </row>
     <row r="232">
@@ -12595,10 +12595,10 @@
         <v>1.99</v>
       </c>
       <c r="I232" t="n">
-        <v>1.714</v>
+        <v>1.7118</v>
       </c>
       <c r="J232" t="n">
-        <v>39.422</v>
+        <v>39.3714</v>
       </c>
     </row>
     <row r="233">
@@ -12635,10 +12635,10 @@
         <v>1.32</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.7799</v>
       </c>
       <c r="J233" t="n">
-        <v>18.8623</v>
+        <v>17.9377</v>
       </c>
     </row>
     <row r="234">
@@ -12675,10 +12675,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2842</v>
+        <v>0.2975</v>
       </c>
       <c r="J234" t="n">
-        <v>6.5366</v>
+        <v>6.8425</v>
       </c>
     </row>
     <row r="235">
@@ -12715,10 +12715,10 @@
         <v>1.03</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0655</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>1.5065</v>
+        <v>2.0907</v>
       </c>
     </row>
     <row r="236">
@@ -12755,10 +12755,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2694</v>
+        <v>-0.2506</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.1962</v>
+        <v>-5.7638</v>
       </c>
     </row>
     <row r="237">
@@ -12795,10 +12795,10 @@
         <v>1.12</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3262</v>
+        <v>0.3199</v>
       </c>
       <c r="J237" t="n">
-        <v>7.5026</v>
+        <v>7.3577</v>
       </c>
     </row>
     <row r="238">
@@ -12835,10 +12835,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3053</v>
+        <v>0.3002</v>
       </c>
       <c r="J238" t="n">
-        <v>7.0219</v>
+        <v>6.9046</v>
       </c>
     </row>
     <row r="239">
@@ -12875,10 +12875,10 @@
         <v>0.98</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0233</v>
+        <v>-0.033</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.5359</v>
+        <v>-0.759</v>
       </c>
     </row>
     <row r="240">
@@ -12915,10 +12915,10 @@
         <v>0.78</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2444</v>
+        <v>-0.2608</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.6212</v>
+        <v>-5.9984</v>
       </c>
     </row>
     <row r="241">
@@ -12955,10 +12955,10 @@
         <v>0.42</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5795</v>
+        <v>-0.5812</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.3285</v>
+        <v>-13.3676</v>
       </c>
     </row>
     <row r="242">
@@ -12995,10 +12995,10 @@
         <v>0.83</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1791</v>
+        <v>-0.1995</v>
       </c>
       <c r="J242" t="n">
-        <v>-3.9402</v>
+        <v>-4.389</v>
       </c>
     </row>
     <row r="243">
@@ -13035,10 +13035,10 @@
         <v>0.79</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2198</v>
+        <v>-0.2398</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.8356</v>
+        <v>-5.2756</v>
       </c>
     </row>
     <row r="244">
@@ -13075,10 +13075,10 @@
         <v>0.78</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2296</v>
+        <v>-0.2494</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.0512</v>
+        <v>-5.4868</v>
       </c>
     </row>
     <row r="245">
@@ -13115,10 +13115,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2485</v>
+        <v>-0.2681</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.467</v>
+        <v>-5.8982</v>
       </c>
     </row>
     <row r="246">
@@ -13155,10 +13155,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3975</v>
+        <v>-0.4123</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.744999999999999</v>
+        <v>-9.070600000000001</v>
       </c>
     </row>
     <row r="247">
@@ -13195,10 +13195,10 @@
         <v>2.12</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8338</v>
+        <v>1.8478</v>
       </c>
       <c r="J247" t="n">
-        <v>40.3436</v>
+        <v>40.6516</v>
       </c>
     </row>
     <row r="248">
@@ -13235,10 +13235,10 @@
         <v>1.45</v>
       </c>
       <c r="I248" t="n">
-        <v>1.0507</v>
+        <v>1.0073</v>
       </c>
       <c r="J248" t="n">
-        <v>23.1154</v>
+        <v>22.1606</v>
       </c>
     </row>
     <row r="249">
@@ -13275,10 +13275,10 @@
         <v>1.3</v>
       </c>
       <c r="I249" t="n">
-        <v>0.7672</v>
+        <v>0.735</v>
       </c>
       <c r="J249" t="n">
-        <v>16.8784</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="250">
@@ -13315,10 +13315,10 @@
         <v>1.15</v>
       </c>
       <c r="I250" t="n">
-        <v>0.406</v>
+        <v>0.4121</v>
       </c>
       <c r="J250" t="n">
-        <v>8.932</v>
+        <v>9.0662</v>
       </c>
     </row>
     <row r="251">
@@ -13355,10 +13355,10 @@
         <v>0.68</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.0002</v>
+        <v>-0.9063</v>
       </c>
       <c r="J251" t="n">
-        <v>-22.0044</v>
+        <v>-19.9386</v>
       </c>
     </row>
     <row r="252">
@@ -13395,10 +13395,10 @@
         <v>1.5</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1092</v>
+        <v>1.0758</v>
       </c>
       <c r="J252" t="n">
-        <v>26.6208</v>
+        <v>25.8192</v>
       </c>
     </row>
     <row r="253">
@@ -13435,10 +13435,10 @@
         <v>1.44</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0336</v>
+        <v>0.9881</v>
       </c>
       <c r="J253" t="n">
-        <v>24.8064</v>
+        <v>23.7144</v>
       </c>
     </row>
     <row r="254">
@@ -13475,10 +13475,10 @@
         <v>1.4</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9197</v>
       </c>
       <c r="J254" t="n">
-        <v>23.2872</v>
+        <v>22.0728</v>
       </c>
     </row>
     <row r="255">
@@ -13515,10 +13515,10 @@
         <v>1.3</v>
       </c>
       <c r="I255" t="n">
-        <v>0.7629</v>
+        <v>0.7321</v>
       </c>
       <c r="J255" t="n">
-        <v>18.3096</v>
+        <v>17.5704</v>
       </c>
     </row>
     <row r="256">
@@ -13555,10 +13555,10 @@
         <v>1.18</v>
       </c>
       <c r="I256" t="n">
-        <v>0.4778</v>
+        <v>0.4781</v>
       </c>
       <c r="J256" t="n">
-        <v>11.4672</v>
+        <v>11.4744</v>
       </c>
     </row>
     <row r="257">
@@ -13595,10 +13595,10 @@
         <v>1.01</v>
       </c>
       <c r="I257" t="n">
-        <v>0.1165</v>
+        <v>0.1008</v>
       </c>
       <c r="J257" t="n">
-        <v>2.796</v>
+        <v>2.4192</v>
       </c>
     </row>
     <row r="258">
@@ -13635,10 +13635,10 @@
         <v>0.93</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0667</v>
+        <v>-0.0858</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.6008</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="259">
@@ -13675,10 +13675,10 @@
         <v>0.76</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2491</v>
+        <v>-0.2686</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.9784</v>
+        <v>-6.4464</v>
       </c>
     </row>
     <row r="260">
@@ -13715,10 +13715,10 @@
         <v>0.64</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3613</v>
+        <v>-0.3775</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.671200000000001</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="261">
@@ -13755,10 +13755,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5289</v>
+        <v>-0.5359</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.6936</v>
+        <v>-12.8616</v>
       </c>
     </row>
     <row r="262">
@@ -13795,10 +13795,10 @@
         <v>1.83</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4857</v>
+        <v>1.4798</v>
       </c>
       <c r="J262" t="n">
-        <v>31.1997</v>
+        <v>31.0758</v>
       </c>
     </row>
     <row r="263">
@@ -13835,10 +13835,10 @@
         <v>1.5</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0997</v>
+        <v>1.0674</v>
       </c>
       <c r="J263" t="n">
-        <v>23.0937</v>
+        <v>22.4154</v>
       </c>
     </row>
     <row r="264">
@@ -13875,10 +13875,10 @@
         <v>1.38</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9236</v>
+        <v>0.8767</v>
       </c>
       <c r="J264" t="n">
-        <v>19.3956</v>
+        <v>18.4107</v>
       </c>
     </row>
     <row r="265">
@@ -13915,10 +13915,10 @@
         <v>1.31</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7714</v>
+        <v>0.7423</v>
       </c>
       <c r="J265" t="n">
-        <v>16.1994</v>
+        <v>15.5883</v>
       </c>
     </row>
     <row r="266">
@@ -13955,10 +13955,10 @@
         <v>1.16</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4112</v>
+        <v>0.4211</v>
       </c>
       <c r="J266" t="n">
-        <v>8.635199999999999</v>
+        <v>8.8431</v>
       </c>
     </row>
     <row r="267">
@@ -13995,10 +13995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I267" t="n">
-        <v>0.0596</v>
+        <v>-0.0042</v>
       </c>
       <c r="J267" t="n">
-        <v>1.2516</v>
+        <v>-0.0882</v>
       </c>
     </row>
     <row r="268">
@@ -14035,10 +14035,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.4013</v>
+        <v>-0.4217</v>
       </c>
       <c r="J268" t="n">
-        <v>-8.427300000000001</v>
+        <v>-8.855700000000001</v>
       </c>
     </row>
     <row r="269">
@@ -14075,10 +14075,10 @@
         <v>0.5</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4543</v>
+        <v>-0.4718</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.5403</v>
+        <v>-9.9078</v>
       </c>
     </row>
     <row r="270">
@@ -14115,10 +14115,10 @@
         <v>0.49</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4635</v>
+        <v>-0.4805</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.733499999999999</v>
+        <v>-10.0905</v>
       </c>
     </row>
     <row r="271">
@@ -14155,10 +14155,10 @@
         <v>0.24</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7065</v>
+        <v>-0.7034</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.8365</v>
+        <v>-14.7714</v>
       </c>
     </row>
     <row r="272">
@@ -14195,10 +14195,10 @@
         <v>1.16</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3623</v>
+        <v>0.3628</v>
       </c>
       <c r="J272" t="n">
-        <v>16.6658</v>
+        <v>16.6888</v>
       </c>
     </row>
     <row r="273">
@@ -14235,10 +14235,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3433</v>
+        <v>0.3449</v>
       </c>
       <c r="J273" t="n">
-        <v>15.7918</v>
+        <v>15.8654</v>
       </c>
     </row>
     <row r="274">
@@ -14275,10 +14275,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1381</v>
+        <v>0.147</v>
       </c>
       <c r="J274" t="n">
-        <v>6.3526</v>
+        <v>6.762</v>
       </c>
     </row>
     <row r="275">
@@ -14315,10 +14315,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.037</v>
+        <v>0.0428</v>
       </c>
       <c r="J275" t="n">
-        <v>1.702</v>
+        <v>1.9688</v>
       </c>
     </row>
     <row r="276">
@@ -14355,10 +14355,10 @@
         <v>0.66</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3745</v>
+        <v>-0.3846</v>
       </c>
       <c r="J276" t="n">
-        <v>-17.227</v>
+        <v>-17.6916</v>
       </c>
     </row>
     <row r="277">
@@ -14395,10 +14395,10 @@
         <v>1.36</v>
       </c>
       <c r="I277" t="n">
-        <v>0.962</v>
+        <v>0.8979</v>
       </c>
       <c r="J277" t="n">
-        <v>44.252</v>
+        <v>41.3034</v>
       </c>
     </row>
     <row r="278">
@@ -14435,10 +14435,10 @@
         <v>1.25</v>
       </c>
       <c r="I278" t="n">
-        <v>0.7053</v>
+        <v>0.6696</v>
       </c>
       <c r="J278" t="n">
-        <v>32.4438</v>
+        <v>30.8016</v>
       </c>
     </row>
     <row r="279">
@@ -14475,10 +14475,10 @@
         <v>1.01</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0308</v>
+        <v>0.0433</v>
       </c>
       <c r="J279" t="n">
-        <v>1.4168</v>
+        <v>1.9918</v>
       </c>
     </row>
     <row r="280">
@@ -14515,10 +14515,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J280" t="n">
-        <v>-3.6202</v>
+        <v>-3.5006</v>
       </c>
     </row>
     <row r="281">
@@ -14555,10 +14555,10 @@
         <v>0.91</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3491</v>
+        <v>-0.3355</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.0586</v>
+        <v>-15.433</v>
       </c>
     </row>
     <row r="282">
@@ -14595,10 +14595,10 @@
         <v>1.87</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5322</v>
+        <v>1.5286</v>
       </c>
       <c r="J282" t="n">
-        <v>30.644</v>
+        <v>30.572</v>
       </c>
     </row>
     <row r="283">
@@ -14635,10 +14635,10 @@
         <v>1.82</v>
       </c>
       <c r="I283" t="n">
-        <v>1.4751</v>
+        <v>1.4684</v>
       </c>
       <c r="J283" t="n">
-        <v>29.502</v>
+        <v>29.368</v>
       </c>
     </row>
     <row r="284">
@@ -14675,10 +14675,10 @@
         <v>1.53</v>
       </c>
       <c r="I284" t="n">
-        <v>1.1359</v>
+        <v>1.1068</v>
       </c>
       <c r="J284" t="n">
-        <v>22.718</v>
+        <v>22.136</v>
       </c>
     </row>
     <row r="285">
@@ -14715,10 +14715,10 @@
         <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1015</v>
+        <v>-0.0707</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.03</v>
+        <v>-1.414</v>
       </c>
     </row>
     <row r="286">
@@ -14755,10 +14755,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3347</v>
+        <v>-0.3043</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.694</v>
+        <v>-6.086</v>
       </c>
     </row>
     <row r="287">
@@ -14795,10 +14795,10 @@
         <v>1.01</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1495</v>
+        <v>0.1252</v>
       </c>
       <c r="J287" t="n">
-        <v>2.99</v>
+        <v>2.504</v>
       </c>
     </row>
     <row r="288">
@@ -14835,10 +14835,10 @@
         <v>0.9</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.089</v>
+        <v>-0.1119</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.78</v>
+        <v>-2.238</v>
       </c>
     </row>
     <row r="289">
@@ -14875,10 +14875,10 @@
         <v>0.73</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2707</v>
+        <v>-0.2912</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.414</v>
+        <v>-5.824</v>
       </c>
     </row>
     <row r="290">
@@ -14915,10 +14915,10 @@
         <v>0.49</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4927</v>
+        <v>-0.5033</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.853999999999999</v>
+        <v>-10.066</v>
       </c>
     </row>
     <row r="291">
@@ -14955,10 +14955,10 @@
         <v>0.39</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.586</v>
+        <v>-0.5901</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.72</v>
+        <v>-11.802</v>
       </c>
     </row>
     <row r="292">
@@ -14995,10 +14995,10 @@
         <v>1.46</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1056</v>
+        <v>1.0622</v>
       </c>
       <c r="J292" t="n">
-        <v>45.3296</v>
+        <v>43.5502</v>
       </c>
     </row>
     <row r="293">
@@ -15035,10 +15035,10 @@
         <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0924</v>
+        <v>1.0473</v>
       </c>
       <c r="J293" t="n">
-        <v>44.7884</v>
+        <v>42.9393</v>
       </c>
     </row>
     <row r="294">
@@ -15075,10 +15075,10 @@
         <v>1.05</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1676</v>
+        <v>0.1801</v>
       </c>
       <c r="J294" t="n">
-        <v>6.8716</v>
+        <v>7.3841</v>
       </c>
     </row>
     <row r="295">
@@ -15115,10 +15115,10 @@
         <v>0.89</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4163</v>
+        <v>-0.3953</v>
       </c>
       <c r="J295" t="n">
-        <v>-17.0683</v>
+        <v>-16.2073</v>
       </c>
     </row>
     <row r="296">
@@ -15155,10 +15155,10 @@
         <v>0.84</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5544</v>
+        <v>-0.5204</v>
       </c>
       <c r="J296" t="n">
-        <v>-22.7304</v>
+        <v>-21.3364</v>
       </c>
     </row>
     <row r="297">
@@ -15195,10 +15195,10 @@
         <v>1.31</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6192</v>
+        <v>0.6019</v>
       </c>
       <c r="J297" t="n">
-        <v>25.3872</v>
+        <v>24.6779</v>
       </c>
     </row>
     <row r="298">
@@ -15235,10 +15235,10 @@
         <v>1.17</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3713</v>
+        <v>0.3733</v>
       </c>
       <c r="J298" t="n">
-        <v>15.2233</v>
+        <v>15.3053</v>
       </c>
     </row>
     <row r="299">
@@ -15275,10 +15275,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0925</v>
+        <v>-0.1024</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.7925</v>
+        <v>-4.1984</v>
       </c>
     </row>
     <row r="300">
@@ -15315,10 +15315,10 @@
         <v>0.93</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1045</v>
+        <v>-0.115</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.2845</v>
+        <v>-4.715</v>
       </c>
     </row>
     <row r="301">
@@ -15355,10 +15355,10 @@
         <v>0.86</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1822</v>
+        <v>-0.1946</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.4702</v>
+        <v>-7.9786</v>
       </c>
     </row>
     <row r="302">
@@ -15395,10 +15395,10 @@
         <v>1.23</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6864</v>
+        <v>0.6473</v>
       </c>
       <c r="J302" t="n">
-        <v>19.9056</v>
+        <v>18.7717</v>
       </c>
     </row>
     <row r="303">
@@ -15435,10 +15435,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4784</v>
+        <v>0.4619</v>
       </c>
       <c r="J303" t="n">
-        <v>13.8736</v>
+        <v>13.3951</v>
       </c>
     </row>
     <row r="304">
@@ -15475,10 +15475,10 @@
         <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0047</v>
+        <v>-0.0032</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.1363</v>
+        <v>-0.09279999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -15515,10 +15515,10 @@
         <v>0.97</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1364</v>
+        <v>-0.1398</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.9556</v>
+        <v>-4.0542</v>
       </c>
     </row>
     <row r="306">
@@ -15555,10 +15555,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6806</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="J306" t="n">
-        <v>-19.7374</v>
+        <v>-18.5194</v>
       </c>
     </row>
     <row r="307">
@@ -15595,10 +15595,10 @@
         <v>1.54</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9813</v>
+        <v>0.9338</v>
       </c>
       <c r="J307" t="n">
-        <v>28.4577</v>
+        <v>27.0802</v>
       </c>
     </row>
     <row r="308">
@@ -15635,10 +15635,10 @@
         <v>1.06</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1521</v>
+        <v>0.1633</v>
       </c>
       <c r="J308" t="n">
-        <v>4.4109</v>
+        <v>4.7357</v>
       </c>
     </row>
     <row r="309">
@@ -15675,10 +15675,10 @@
         <v>0.96</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0693</v>
+        <v>-0.0772</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.0097</v>
+        <v>-2.2388</v>
       </c>
     </row>
     <row r="310">
@@ -15715,10 +15715,10 @@
         <v>0.92</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1181</v>
+        <v>-0.1287</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.4249</v>
+        <v>-3.7323</v>
       </c>
     </row>
     <row r="311">
@@ -15755,10 +15755,10 @@
         <v>0.82</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2256</v>
+        <v>-0.2377</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.5424</v>
+        <v>-6.8933</v>
       </c>
     </row>
     <row r="312">
@@ -15795,10 +15795,10 @@
         <v>1.45</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0661</v>
+        <v>1.0221</v>
       </c>
       <c r="J312" t="n">
-        <v>37.3135</v>
+        <v>35.7735</v>
       </c>
     </row>
     <row r="313">
@@ -15835,10 +15835,10 @@
         <v>1.4</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9923</v>
+        <v>0.9376</v>
       </c>
       <c r="J313" t="n">
-        <v>34.7305</v>
+        <v>32.816</v>
       </c>
     </row>
     <row r="314">
@@ -15875,10 +15875,10 @@
         <v>1.3</v>
       </c>
       <c r="I314" t="n">
-        <v>0.7808</v>
+        <v>0.7442</v>
       </c>
       <c r="J314" t="n">
-        <v>27.328</v>
+        <v>26.047</v>
       </c>
     </row>
     <row r="315">
@@ -15955,10 +15955,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2298</v>
+        <v>-0.2143</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.042999999999999</v>
+        <v>-7.5005</v>
       </c>
     </row>
     <row r="317">
@@ -15995,10 +15995,10 @@
         <v>0.99</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0155</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.2765</v>
+        <v>-0.5425</v>
       </c>
     </row>
     <row r="318">
@@ -16035,10 +16035,10 @@
         <v>0.99</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0155</v>
       </c>
       <c r="J318" t="n">
-        <v>-0.2765</v>
+        <v>-0.5425</v>
       </c>
     </row>
     <row r="319">
@@ -16075,10 +16075,10 @@
         <v>0.93</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0895</v>
+        <v>-0.1035</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.1325</v>
+        <v>-3.6225</v>
       </c>
     </row>
     <row r="320">
@@ -16115,10 +16115,10 @@
         <v>0.78</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2449</v>
+        <v>-0.2612</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.5715</v>
+        <v>-9.141999999999999</v>
       </c>
     </row>
     <row r="321">
@@ -16155,10 +16155,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2839</v>
+        <v>-0.2994</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.936500000000001</v>
+        <v>-10.479</v>
       </c>
     </row>
     <row r="322">
@@ -16195,10 +16195,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2868</v>
+        <v>0.2866</v>
       </c>
       <c r="J322" t="n">
-        <v>7.17</v>
+        <v>7.165</v>
       </c>
     </row>
     <row r="323">
@@ -16235,10 +16235,10 @@
         <v>1.01</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0513</v>
+        <v>0.0531</v>
       </c>
       <c r="J323" t="n">
-        <v>1.2825</v>
+        <v>1.3275</v>
       </c>
     </row>
     <row r="324">
@@ -16275,10 +16275,10 @@
         <v>0.89</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1378</v>
+        <v>-0.1525</v>
       </c>
       <c r="J324" t="n">
-        <v>-3.445</v>
+        <v>-3.8125</v>
       </c>
     </row>
     <row r="325">
@@ -16315,10 +16315,10 @@
         <v>0.86</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1696</v>
+        <v>-0.1848</v>
       </c>
       <c r="J325" t="n">
-        <v>-4.24</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="326">
@@ -16355,10 +16355,10 @@
         <v>0.79</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2408</v>
+        <v>-0.2559</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.02</v>
+        <v>-6.3975</v>
       </c>
     </row>
     <row r="327">
@@ -16395,10 +16395,10 @@
         <v>1.66</v>
       </c>
       <c r="I327" t="n">
-        <v>1.3247</v>
+        <v>1.3027</v>
       </c>
       <c r="J327" t="n">
-        <v>33.1175</v>
+        <v>32.5675</v>
       </c>
     </row>
     <row r="328">
@@ -16435,10 +16435,10 @@
         <v>1.39</v>
       </c>
       <c r="I328" t="n">
-        <v>0.9711</v>
+        <v>0.9164</v>
       </c>
       <c r="J328" t="n">
-        <v>24.2775</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="329">
@@ -16475,10 +16475,10 @@
         <v>1.32</v>
       </c>
       <c r="I329" t="n">
-        <v>0.8226</v>
+        <v>0.7816</v>
       </c>
       <c r="J329" t="n">
-        <v>20.565</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="330">
@@ -16515,10 +16515,10 @@
         <v>1.03</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0683</v>
+        <v>0.0929</v>
       </c>
       <c r="J330" t="n">
-        <v>1.7075</v>
+        <v>2.3225</v>
       </c>
     </row>
     <row r="331">
@@ -16555,10 +16555,10 @@
         <v>0.93</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.33</v>
+        <v>-0.3084</v>
       </c>
       <c r="J331" t="n">
-        <v>-8.25</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="332">
@@ -16595,10 +16595,10 @@
         <v>1.35</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9396</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="J332" t="n">
-        <v>33.8256</v>
+        <v>31.554</v>
       </c>
     </row>
     <row r="333">
@@ -16635,10 +16635,10 @@
         <v>1.29</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8002</v>
+        <v>0.7533</v>
       </c>
       <c r="J333" t="n">
-        <v>28.8072</v>
+        <v>27.1188</v>
       </c>
     </row>
     <row r="334">
@@ -16675,10 +16675,10 @@
         <v>1.04</v>
       </c>
       <c r="I334" t="n">
-        <v>0.142</v>
+        <v>0.1536</v>
       </c>
       <c r="J334" t="n">
-        <v>5.112</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="335">
@@ -16715,10 +16715,10 @@
         <v>1.01</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0298</v>
+        <v>0.0426</v>
       </c>
       <c r="J335" t="n">
-        <v>1.0728</v>
+        <v>1.5336</v>
       </c>
     </row>
     <row r="336">
@@ -16755,10 +16755,10 @@
         <v>0.85</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5194</v>
+        <v>-0.4905</v>
       </c>
       <c r="J336" t="n">
-        <v>-18.6984</v>
+        <v>-17.658</v>
       </c>
     </row>
     <row r="337">
@@ -16795,10 +16795,10 @@
         <v>1.6</v>
       </c>
       <c r="I337" t="n">
-        <v>1.049</v>
+        <v>1.0097</v>
       </c>
       <c r="J337" t="n">
-        <v>37.764</v>
+        <v>36.3492</v>
       </c>
     </row>
     <row r="338">
@@ -16835,10 +16835,10 @@
         <v>1.1</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2336</v>
+        <v>0.2433</v>
       </c>
       <c r="J338" t="n">
-        <v>8.409599999999999</v>
+        <v>8.758800000000001</v>
       </c>
     </row>
     <row r="339">
@@ -16875,10 +16875,10 @@
         <v>1.04</v>
       </c>
       <c r="I339" t="n">
-        <v>0.1079</v>
+        <v>0.1189</v>
       </c>
       <c r="J339" t="n">
-        <v>3.8844</v>
+        <v>4.2804</v>
       </c>
     </row>
     <row r="340">
@@ -16915,10 +16915,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2256</v>
+        <v>-0.2377</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.121600000000001</v>
+        <v>-8.5572</v>
       </c>
     </row>
     <row r="341">
@@ -16955,10 +16955,10 @@
         <v>0.74</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3046</v>
+        <v>-0.3156</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.9656</v>
+        <v>-11.3616</v>
       </c>
     </row>
     <row r="342">
@@ -16995,10 +16995,10 @@
         <v>1.12</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4095</v>
+        <v>0.3815</v>
       </c>
       <c r="J342" t="n">
-        <v>7.7805</v>
+        <v>7.2485</v>
       </c>
     </row>
     <row r="343">
@@ -17035,10 +17035,10 @@
         <v>0.74</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.2647</v>
+        <v>-0.2846</v>
       </c>
       <c r="J343" t="n">
-        <v>-5.0293</v>
+        <v>-5.4074</v>
       </c>
     </row>
     <row r="344">
@@ -17075,10 +17075,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.31</v>
+        <v>-0.329</v>
       </c>
       <c r="J344" t="n">
-        <v>-5.89</v>
+        <v>-6.251</v>
       </c>
     </row>
     <row r="345">
@@ -17115,10 +17115,10 @@
         <v>0.63</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.366</v>
+        <v>-0.3828</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.954</v>
+        <v>-7.2732</v>
       </c>
     </row>
     <row r="346">
@@ -17155,10 +17155,10 @@
         <v>0.47</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5154</v>
+        <v>-0.5239</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.7926</v>
+        <v>-9.9541</v>
       </c>
     </row>
     <row r="347">
@@ -17195,10 +17195,10 @@
         <v>1.61</v>
       </c>
       <c r="I347" t="n">
-        <v>1.2374</v>
+        <v>1.2147</v>
       </c>
       <c r="J347" t="n">
-        <v>23.5106</v>
+        <v>23.0793</v>
       </c>
     </row>
     <row r="348">
@@ -17235,10 +17235,10 @@
         <v>1.57</v>
       </c>
       <c r="I348" t="n">
-        <v>1.1896</v>
+        <v>1.1635</v>
       </c>
       <c r="J348" t="n">
-        <v>22.6024</v>
+        <v>22.1065</v>
       </c>
     </row>
     <row r="349">
@@ -17275,10 +17275,10 @@
         <v>1.48</v>
       </c>
       <c r="I349" t="n">
-        <v>1.0809</v>
+        <v>1.0448</v>
       </c>
       <c r="J349" t="n">
-        <v>20.5371</v>
+        <v>19.8512</v>
       </c>
     </row>
     <row r="350">
@@ -17315,10 +17315,10 @@
         <v>1.3</v>
       </c>
       <c r="I350" t="n">
-        <v>0.7575</v>
+        <v>0.7284</v>
       </c>
       <c r="J350" t="n">
-        <v>14.3925</v>
+        <v>13.8396</v>
       </c>
     </row>
     <row r="351">
@@ -17355,10 +17355,10 @@
         <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0648</v>
       </c>
       <c r="J351" t="n">
-        <v>-1.7708</v>
+        <v>-1.2312</v>
       </c>
     </row>
     <row r="352">
@@ -17395,10 +17395,10 @@
         <v>1.41</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8266</v>
+        <v>0.7825</v>
       </c>
       <c r="J352" t="n">
-        <v>24.798</v>
+        <v>23.475</v>
       </c>
     </row>
     <row r="353">
@@ -17435,10 +17435,10 @@
         <v>1.06</v>
       </c>
       <c r="I353" t="n">
-        <v>0.1729</v>
+        <v>0.1782</v>
       </c>
       <c r="J353" t="n">
-        <v>5.187</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="354">
@@ -17475,10 +17475,10 @@
         <v>0.91</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1181</v>
+        <v>-0.1316</v>
       </c>
       <c r="J354" t="n">
-        <v>-3.543</v>
+        <v>-3.948</v>
       </c>
     </row>
     <row r="355">
@@ -17515,10 +17515,10 @@
         <v>0.73</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3022</v>
+        <v>-0.3156</v>
       </c>
       <c r="J355" t="n">
-        <v>-9.066000000000001</v>
+        <v>-9.468</v>
       </c>
     </row>
     <row r="356">
@@ -17555,10 +17555,10 @@
         <v>0.66</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3686</v>
+        <v>-0.3799</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.058</v>
+        <v>-11.397</v>
       </c>
     </row>
     <row r="357">
@@ -17595,10 +17595,10 @@
         <v>1.5</v>
       </c>
       <c r="I357" t="n">
-        <v>1.145</v>
+        <v>1.1073</v>
       </c>
       <c r="J357" t="n">
-        <v>34.35</v>
+        <v>33.219</v>
       </c>
     </row>
     <row r="358">
@@ -17635,10 +17635,10 @@
         <v>1.33</v>
       </c>
       <c r="I358" t="n">
-        <v>0.8665</v>
+        <v>0.8162</v>
       </c>
       <c r="J358" t="n">
-        <v>25.995</v>
+        <v>24.486</v>
       </c>
     </row>
     <row r="359">
@@ -17675,10 +17675,10 @@
         <v>1.18</v>
       </c>
       <c r="I359" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5034</v>
       </c>
       <c r="J359" t="n">
-        <v>15.438</v>
+        <v>15.102</v>
       </c>
     </row>
     <row r="360">
@@ -17715,10 +17715,10 @@
         <v>1.03</v>
       </c>
       <c r="I360" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1066</v>
       </c>
       <c r="J360" t="n">
-        <v>2.64</v>
+        <v>3.198</v>
       </c>
     </row>
     <row r="361">
@@ -17755,10 +17755,10 @@
         <v>0.89</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4287</v>
+        <v>-0.404</v>
       </c>
       <c r="J361" t="n">
-        <v>-12.861</v>
+        <v>-12.12</v>
       </c>
     </row>
     <row r="362">
@@ -17795,10 +17795,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2915</v>
+        <v>1.2669</v>
       </c>
       <c r="J362" t="n">
-        <v>29.7045</v>
+        <v>29.1387</v>
       </c>
     </row>
     <row r="363">
@@ -17835,10 +17835,10 @@
         <v>1.55</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1924</v>
+        <v>1.1611</v>
       </c>
       <c r="J363" t="n">
-        <v>27.4252</v>
+        <v>26.7053</v>
       </c>
     </row>
     <row r="364">
@@ -17875,10 +17875,10 @@
         <v>1.39</v>
       </c>
       <c r="I364" t="n">
-        <v>0.9744</v>
+        <v>0.9191</v>
       </c>
       <c r="J364" t="n">
-        <v>22.4112</v>
+        <v>21.1393</v>
       </c>
     </row>
     <row r="365">
@@ -17915,10 +17915,10 @@
         <v>0.91</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3869</v>
+        <v>-0.3621</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.8987</v>
+        <v>-8.3283</v>
       </c>
     </row>
     <row r="366">
@@ -17955,10 +17955,10 @@
         <v>0.78</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.7381</v>
+        <v>-0.6791</v>
       </c>
       <c r="J366" t="n">
-        <v>-16.9763</v>
+        <v>-15.6193</v>
       </c>
     </row>
     <row r="367">
@@ -17995,10 +17995,10 @@
         <v>0.99</v>
       </c>
       <c r="I367" t="n">
-        <v>0.0166</v>
+        <v>-0.0023</v>
       </c>
       <c r="J367" t="n">
-        <v>0.3818</v>
+        <v>-0.0529</v>
       </c>
     </row>
     <row r="368">
@@ -18035,10 +18035,10 @@
         <v>0.96</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0366</v>
+        <v>-0.052</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.8418</v>
+        <v>-1.196</v>
       </c>
     </row>
     <row r="369">
@@ -18075,10 +18075,10 @@
         <v>0.95</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.05</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J369" t="n">
-        <v>-1.15</v>
+        <v>-1.5226</v>
       </c>
     </row>
     <row r="370">
@@ -18115,10 +18115,10 @@
         <v>0.58</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4234</v>
+        <v>-0.4356</v>
       </c>
       <c r="J370" t="n">
-        <v>-9.738200000000001</v>
+        <v>-10.0188</v>
       </c>
     </row>
     <row r="371">
@@ -18155,10 +18155,10 @@
         <v>0.52</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.479</v>
+        <v>-0.4882</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.017</v>
+        <v>-11.2286</v>
       </c>
     </row>
     <row r="372">
@@ -18195,10 +18195,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.6768</v>
+        <v>0.6473</v>
       </c>
       <c r="J372" t="n">
-        <v>18.2736</v>
+        <v>17.4771</v>
       </c>
     </row>
     <row r="373">
@@ -18235,10 +18235,10 @@
         <v>1.12</v>
       </c>
       <c r="I373" t="n">
-        <v>0.3038</v>
+        <v>0.3035</v>
       </c>
       <c r="J373" t="n">
-        <v>8.2026</v>
+        <v>8.1945</v>
       </c>
     </row>
     <row r="374">
@@ -18275,10 +18275,10 @@
         <v>0.88</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1496</v>
+        <v>-0.1642</v>
       </c>
       <c r="J374" t="n">
-        <v>-4.0392</v>
+        <v>-4.4334</v>
       </c>
     </row>
     <row r="375">
@@ -18315,10 +18315,10 @@
         <v>0.88</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1496</v>
+        <v>-0.1642</v>
       </c>
       <c r="J375" t="n">
-        <v>-4.0392</v>
+        <v>-4.4334</v>
       </c>
     </row>
     <row r="376">
@@ -18355,10 +18355,10 @@
         <v>0.51</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5048</v>
+        <v>-0.51</v>
       </c>
       <c r="J376" t="n">
-        <v>-13.6296</v>
+        <v>-13.77</v>
       </c>
     </row>
     <row r="377">
@@ -18395,10 +18395,10 @@
         <v>1.28</v>
       </c>
       <c r="I377" t="n">
-        <v>0.7657</v>
+        <v>0.725</v>
       </c>
       <c r="J377" t="n">
-        <v>20.6739</v>
+        <v>19.575</v>
       </c>
     </row>
     <row r="378">
@@ -18435,10 +18435,10 @@
         <v>1.19</v>
       </c>
       <c r="I378" t="n">
-        <v>0.5476</v>
+        <v>0.5313</v>
       </c>
       <c r="J378" t="n">
-        <v>14.7852</v>
+        <v>14.3451</v>
       </c>
     </row>
     <row r="379">
@@ -18475,10 +18475,10 @@
         <v>1.13</v>
       </c>
       <c r="I379" t="n">
-        <v>0.3969</v>
+        <v>0.3941</v>
       </c>
       <c r="J379" t="n">
-        <v>10.7163</v>
+        <v>10.6407</v>
       </c>
     </row>
     <row r="380">
@@ -18515,10 +18515,10 @@
         <v>1.07</v>
       </c>
       <c r="I380" t="n">
-        <v>0.2298</v>
+        <v>0.2389</v>
       </c>
       <c r="J380" t="n">
-        <v>6.2046</v>
+        <v>6.4503</v>
       </c>
     </row>
     <row r="381">
@@ -18555,10 +18555,10 @@
         <v>1.02</v>
       </c>
       <c r="I381" t="n">
-        <v>0.063</v>
+        <v>0.0785</v>
       </c>
       <c r="J381" t="n">
-        <v>1.701</v>
+        <v>2.1195</v>
       </c>
     </row>
     <row r="382">
@@ -18595,10 +18595,10 @@
         <v>1.63</v>
       </c>
       <c r="I382" t="n">
-        <v>1.27</v>
+        <v>1.2479</v>
       </c>
       <c r="J382" t="n">
-        <v>27.94</v>
+        <v>27.4538</v>
       </c>
     </row>
     <row r="383">
@@ -18635,10 +18635,10 @@
         <v>1.55</v>
       </c>
       <c r="I383" t="n">
-        <v>1.1732</v>
+        <v>1.1443</v>
       </c>
       <c r="J383" t="n">
-        <v>25.8104</v>
+        <v>25.1746</v>
       </c>
     </row>
     <row r="384">
@@ -18675,10 +18675,10 @@
         <v>1.3</v>
       </c>
       <c r="I384" t="n">
-        <v>0.7662</v>
+        <v>0.7343</v>
       </c>
       <c r="J384" t="n">
-        <v>16.8564</v>
+        <v>16.1546</v>
       </c>
     </row>
     <row r="385">
@@ -18715,10 +18715,10 @@
         <v>1.16</v>
       </c>
       <c r="I385" t="n">
-        <v>0.4307</v>
+        <v>0.4347</v>
       </c>
       <c r="J385" t="n">
-        <v>9.4754</v>
+        <v>9.5634</v>
       </c>
     </row>
     <row r="386">
@@ -18755,10 +18755,10 @@
         <v>1.09</v>
       </c>
       <c r="I386" t="n">
-        <v>0.2399</v>
+        <v>0.26</v>
       </c>
       <c r="J386" t="n">
-        <v>5.2778</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="387">
@@ -18795,10 +18795,10 @@
         <v>1.21</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6032</v>
+        <v>0.5588</v>
       </c>
       <c r="J387" t="n">
-        <v>13.2704</v>
+        <v>12.2936</v>
       </c>
     </row>
     <row r="388">
@@ -18835,10 +18835,10 @@
         <v>0.76</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.2453</v>
+        <v>-0.2657</v>
       </c>
       <c r="J388" t="n">
-        <v>-5.3966</v>
+        <v>-5.8454</v>
       </c>
     </row>
     <row r="389">
@@ -18875,10 +18875,10 @@
         <v>0.7</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.3002</v>
+        <v>-0.3196</v>
       </c>
       <c r="J389" t="n">
-        <v>-6.6044</v>
+        <v>-7.0312</v>
       </c>
     </row>
     <row r="390">
@@ -18915,10 +18915,10 @@
         <v>0.51</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4775</v>
+        <v>-0.4885</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.505</v>
+        <v>-10.747</v>
       </c>
     </row>
     <row r="391">
@@ -18955,10 +18955,10 @@
         <v>0.45</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5334</v>
+        <v>-0.5407</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.7348</v>
+        <v>-11.8954</v>
       </c>
     </row>
     <row r="392">
@@ -18995,10 +18995,10 @@
         <v>1.52</v>
       </c>
       <c r="I392" t="n">
-        <v>1.1561</v>
+        <v>1.122</v>
       </c>
       <c r="J392" t="n">
-        <v>25.4342</v>
+        <v>24.684</v>
       </c>
     </row>
     <row r="393">
@@ -19035,10 +19035,10 @@
         <v>1.4</v>
       </c>
       <c r="I393" t="n">
-        <v>0.9937</v>
+        <v>0.9388</v>
       </c>
       <c r="J393" t="n">
-        <v>21.8614</v>
+        <v>20.6536</v>
       </c>
     </row>
     <row r="394">
@@ -19075,10 +19075,10 @@
         <v>1.3</v>
       </c>
       <c r="I394" t="n">
-        <v>0.7821</v>
+        <v>0.7451</v>
       </c>
       <c r="J394" t="n">
-        <v>17.2062</v>
+        <v>16.3922</v>
       </c>
     </row>
     <row r="395">
@@ -19115,10 +19115,10 @@
         <v>1.23</v>
       </c>
       <c r="I395" t="n">
-        <v>0.6239</v>
+        <v>0.6041</v>
       </c>
       <c r="J395" t="n">
-        <v>13.7258</v>
+        <v>13.2902</v>
       </c>
     </row>
     <row r="396">
@@ -19155,10 +19155,10 @@
         <v>0.78</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.7368</v>
+        <v>-0.6782</v>
       </c>
       <c r="J396" t="n">
-        <v>-16.2096</v>
+        <v>-14.9204</v>
       </c>
     </row>
     <row r="397">
@@ -19195,10 +19195,10 @@
         <v>1.19</v>
       </c>
       <c r="I397" t="n">
-        <v>0.5004</v>
+        <v>0.4756</v>
       </c>
       <c r="J397" t="n">
-        <v>11.0088</v>
+        <v>10.4632</v>
       </c>
     </row>
     <row r="398">
@@ -19235,10 +19235,10 @@
         <v>0.75</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.265</v>
+        <v>-0.2828</v>
       </c>
       <c r="J398" t="n">
-        <v>-5.83</v>
+        <v>-6.2216</v>
       </c>
     </row>
     <row r="399">
@@ -19275,10 +19275,10 @@
         <v>0.72</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.2937</v>
+        <v>-0.3108</v>
       </c>
       <c r="J399" t="n">
-        <v>-6.4614</v>
+        <v>-6.8376</v>
       </c>
     </row>
     <row r="400">
@@ -19315,10 +19315,10 @@
         <v>0.72</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.2937</v>
+        <v>-0.3108</v>
       </c>
       <c r="J400" t="n">
-        <v>-6.4614</v>
+        <v>-6.8376</v>
       </c>
     </row>
     <row r="401">
@@ -19355,10 +19355,10 @@
         <v>0.7</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3128</v>
+        <v>-0.3293</v>
       </c>
       <c r="J401" t="n">
-        <v>-6.8816</v>
+        <v>-7.2446</v>
       </c>
     </row>
     <row r="402">
@@ -19395,10 +19395,10 @@
         <v>1.53</v>
       </c>
       <c r="I402" t="n">
-        <v>1.1964</v>
+        <v>1.1599</v>
       </c>
       <c r="J402" t="n">
-        <v>33.4992</v>
+        <v>32.4772</v>
       </c>
     </row>
     <row r="403">
@@ -19435,10 +19435,10 @@
         <v>1.22</v>
       </c>
       <c r="I403" t="n">
-        <v>0.6208</v>
+        <v>0.5969</v>
       </c>
       <c r="J403" t="n">
-        <v>17.3824</v>
+        <v>16.7132</v>
       </c>
     </row>
     <row r="404">
@@ -19475,10 +19475,10 @@
         <v>1.02</v>
       </c>
       <c r="I404" t="n">
-        <v>0.0625</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J404" t="n">
-        <v>1.75</v>
+        <v>2.1896</v>
       </c>
     </row>
     <row r="405">
@@ -19515,10 +19515,10 @@
         <v>1</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.0333</v>
+        <v>-0.0229</v>
       </c>
       <c r="J405" t="n">
-        <v>-0.9324</v>
+        <v>-0.6412</v>
       </c>
     </row>
     <row r="406">
@@ -19555,10 +19555,10 @@
         <v>0.93</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2984</v>
+        <v>-0.2863</v>
       </c>
       <c r="J406" t="n">
-        <v>-8.3552</v>
+        <v>-8.016400000000001</v>
       </c>
     </row>
     <row r="407">
@@ -19595,10 +19595,10 @@
         <v>1.38</v>
       </c>
       <c r="I407" t="n">
-        <v>0.7418</v>
+        <v>0.7119</v>
       </c>
       <c r="J407" t="n">
-        <v>20.7704</v>
+        <v>19.9332</v>
       </c>
     </row>
     <row r="408">
@@ -19635,10 +19635,10 @@
         <v>1.23</v>
       </c>
       <c r="I408" t="n">
-        <v>0.4836</v>
+        <v>0.4771</v>
       </c>
       <c r="J408" t="n">
-        <v>13.5408</v>
+        <v>13.3588</v>
       </c>
     </row>
     <row r="409">
@@ -19675,10 +19675,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1014</v>
       </c>
       <c r="J409" t="n">
-        <v>-2.5564</v>
+        <v>-2.8392</v>
       </c>
     </row>
     <row r="410">
@@ -19715,10 +19715,10 @@
         <v>0.87</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1703</v>
+        <v>-0.1828</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.7684</v>
+        <v>-5.1184</v>
       </c>
     </row>
     <row r="411">
@@ -19755,10 +19755,10 @@
         <v>0.73</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.311</v>
+        <v>-0.3225</v>
       </c>
       <c r="J411" t="n">
-        <v>-8.708</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="412">
@@ -19795,10 +19795,10 @@
         <v>1.73</v>
       </c>
       <c r="I412" t="n">
-        <v>1.1533</v>
+        <v>1.131</v>
       </c>
       <c r="J412" t="n">
-        <v>33.4457</v>
+        <v>32.799</v>
       </c>
     </row>
     <row r="413">
@@ -19835,10 +19835,10 @@
         <v>1.22</v>
       </c>
       <c r="I413" t="n">
-        <v>0.4448</v>
+        <v>0.4453</v>
       </c>
       <c r="J413" t="n">
-        <v>12.8992</v>
+        <v>12.9137</v>
       </c>
     </row>
     <row r="414">
@@ -19875,10 +19875,10 @@
         <v>1.1</v>
       </c>
       <c r="I414" t="n">
-        <v>0.2273</v>
+        <v>0.2388</v>
       </c>
       <c r="J414" t="n">
-        <v>6.5917</v>
+        <v>6.9252</v>
       </c>
     </row>
     <row r="415">
@@ -19915,10 +19915,10 @@
         <v>0.79</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.261</v>
+        <v>-0.2717</v>
       </c>
       <c r="J415" t="n">
-        <v>-7.569</v>
+        <v>-7.8793</v>
       </c>
     </row>
     <row r="416">
@@ -19955,10 +19955,10 @@
         <v>0.71</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3383</v>
+        <v>-0.3475</v>
       </c>
       <c r="J416" t="n">
-        <v>-9.810700000000001</v>
+        <v>-10.0775</v>
       </c>
     </row>
     <row r="417">
@@ -19995,10 +19995,10 @@
         <v>1.31</v>
       </c>
       <c r="I417" t="n">
-        <v>0.8636</v>
+        <v>0.806</v>
       </c>
       <c r="J417" t="n">
-        <v>25.0444</v>
+        <v>23.374</v>
       </c>
     </row>
     <row r="418">
@@ -20035,10 +20035,10 @@
         <v>1.28</v>
       </c>
       <c r="I418" t="n">
-        <v>0.7913</v>
+        <v>0.7429</v>
       </c>
       <c r="J418" t="n">
-        <v>22.9477</v>
+        <v>21.5441</v>
       </c>
     </row>
     <row r="419">
@@ -20075,10 +20075,10 @@
         <v>1.1</v>
       </c>
       <c r="I419" t="n">
-        <v>0.3284</v>
+        <v>0.3279</v>
       </c>
       <c r="J419" t="n">
-        <v>9.5236</v>
+        <v>9.5091</v>
       </c>
     </row>
     <row r="420">
@@ -20115,10 +20115,10 @@
         <v>0.93</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.2794</v>
+        <v>-0.273</v>
       </c>
       <c r="J420" t="n">
-        <v>-8.102600000000001</v>
+        <v>-7.917</v>
       </c>
     </row>
     <row r="421">
@@ -20155,10 +20155,10 @@
         <v>0.73</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.8192</v>
+        <v>-0.7582</v>
       </c>
       <c r="J421" t="n">
-        <v>-23.7568</v>
+        <v>-21.9878</v>
       </c>
     </row>
     <row r="422">
@@ -20195,10 +20195,10 @@
         <v>1.28</v>
       </c>
       <c r="I422" t="n">
-        <v>0.755</v>
+        <v>0.7176</v>
       </c>
       <c r="J422" t="n">
-        <v>18.875</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="423">
@@ -20235,10 +20235,10 @@
         <v>1.23</v>
       </c>
       <c r="I423" t="n">
-        <v>0.6367</v>
+        <v>0.6128</v>
       </c>
       <c r="J423" t="n">
-        <v>15.9175</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="424">
@@ -20275,10 +20275,10 @@
         <v>1.15</v>
       </c>
       <c r="I424" t="n">
-        <v>0.4425</v>
+        <v>0.4373</v>
       </c>
       <c r="J424" t="n">
-        <v>11.0625</v>
+        <v>10.9325</v>
       </c>
     </row>
     <row r="425">
@@ -20315,10 +20315,10 @@
         <v>1.12</v>
       </c>
       <c r="I425" t="n">
-        <v>0.364</v>
+        <v>0.3654</v>
       </c>
       <c r="J425" t="n">
-        <v>9.1</v>
+        <v>9.135</v>
       </c>
     </row>
     <row r="426">
@@ -20355,10 +20355,10 @@
         <v>1.08</v>
       </c>
       <c r="I426" t="n">
-        <v>0.2515</v>
+        <v>0.2613</v>
       </c>
       <c r="J426" t="n">
-        <v>6.2875</v>
+        <v>6.5325</v>
       </c>
     </row>
     <row r="427">
@@ -20395,10 +20395,10 @@
         <v>1.36</v>
       </c>
       <c r="I427" t="n">
-        <v>0.7528</v>
+        <v>0.7147</v>
       </c>
       <c r="J427" t="n">
-        <v>18.82</v>
+        <v>17.8675</v>
       </c>
     </row>
     <row r="428">
@@ -20435,10 +20435,10 @@
         <v>0.99</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.0142</v>
+        <v>-0.0204</v>
       </c>
       <c r="J428" t="n">
-        <v>-0.355</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="429">
@@ -20475,10 +20475,10 @@
         <v>0.78</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2505</v>
+        <v>-0.2655</v>
       </c>
       <c r="J429" t="n">
-        <v>-6.2625</v>
+        <v>-6.6375</v>
       </c>
     </row>
     <row r="430">
@@ -20515,10 +20515,10 @@
         <v>0.77</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.2603</v>
+        <v>-0.2752</v>
       </c>
       <c r="J430" t="n">
-        <v>-6.5075</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="431">
@@ -20555,10 +20555,10 @@
         <v>0.75</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.2799</v>
+        <v>-0.2944</v>
       </c>
       <c r="J431" t="n">
-        <v>-6.9975</v>
+        <v>-7.36</v>
       </c>
     </row>
     <row r="432">
@@ -20595,10 +20595,10 @@
         <v>1.42</v>
       </c>
       <c r="I432" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.7691</v>
       </c>
       <c r="J432" t="n">
-        <v>33.8058</v>
+        <v>32.3022</v>
       </c>
     </row>
     <row r="433">
@@ -20635,10 +20635,10 @@
         <v>1.09</v>
       </c>
       <c r="I433" t="n">
-        <v>0.2176</v>
+        <v>0.2267</v>
       </c>
       <c r="J433" t="n">
-        <v>9.139200000000001</v>
+        <v>9.5214</v>
       </c>
     </row>
     <row r="434">
@@ -20675,10 +20675,10 @@
         <v>1.06</v>
       </c>
       <c r="I434" t="n">
-        <v>0.1548</v>
+        <v>0.1651</v>
       </c>
       <c r="J434" t="n">
-        <v>6.5016</v>
+        <v>6.9342</v>
       </c>
     </row>
     <row r="435">
@@ -20715,10 +20715,10 @@
         <v>1.01</v>
       </c>
       <c r="I435" t="n">
-        <v>0.0331</v>
+        <v>0.0401</v>
       </c>
       <c r="J435" t="n">
-        <v>1.3902</v>
+        <v>1.6842</v>
       </c>
     </row>
     <row r="436">
@@ -20755,10 +20755,10 @@
         <v>0.61</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.4239</v>
+        <v>-0.4315</v>
       </c>
       <c r="J436" t="n">
-        <v>-17.8038</v>
+        <v>-18.123</v>
       </c>
     </row>
     <row r="437">
@@ -20795,10 +20795,10 @@
         <v>1.38</v>
       </c>
       <c r="I437" t="n">
-        <v>1.0098</v>
+        <v>0.946</v>
       </c>
       <c r="J437" t="n">
-        <v>42.4116</v>
+        <v>39.732</v>
       </c>
     </row>
     <row r="438">
@@ -20835,10 +20835,10 @@
         <v>1.17</v>
       </c>
       <c r="I438" t="n">
-        <v>0.5142</v>
+        <v>0.4976</v>
       </c>
       <c r="J438" t="n">
-        <v>21.5964</v>
+        <v>20.8992</v>
       </c>
     </row>
     <row r="439">
@@ -20875,10 +20875,10 @@
         <v>1.16</v>
       </c>
       <c r="I439" t="n">
-        <v>0.4882</v>
+        <v>0.4742</v>
       </c>
       <c r="J439" t="n">
-        <v>20.5044</v>
+        <v>19.9164</v>
       </c>
     </row>
     <row r="440">
@@ -20915,10 +20915,10 @@
         <v>1.03</v>
       </c>
       <c r="I440" t="n">
-        <v>0.1152</v>
+        <v>0.1254</v>
       </c>
       <c r="J440" t="n">
-        <v>4.8384</v>
+        <v>5.2668</v>
       </c>
     </row>
     <row r="441">
@@ -20955,10 +20955,10 @@
         <v>0.64</v>
       </c>
       <c r="I441" t="n">
-        <v>-1.0398</v>
+        <v>-0.9495</v>
       </c>
       <c r="J441" t="n">
-        <v>-43.6716</v>
+        <v>-39.879</v>
       </c>
     </row>
     <row r="442">
@@ -20995,10 +20995,10 @@
         <v>1.32</v>
       </c>
       <c r="I442" t="n">
-        <v>0.8635</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J442" t="n">
-        <v>23.3145</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="443">
@@ -21035,10 +21035,10 @@
         <v>1.22</v>
       </c>
       <c r="I443" t="n">
-        <v>0.6242</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="J443" t="n">
-        <v>16.8534</v>
+        <v>16.1811</v>
       </c>
     </row>
     <row r="444">
@@ -21075,10 +21075,10 @@
         <v>1.14</v>
       </c>
       <c r="I444" t="n">
-        <v>0.4236</v>
+        <v>0.4184</v>
       </c>
       <c r="J444" t="n">
-        <v>11.4372</v>
+        <v>11.2968</v>
       </c>
     </row>
     <row r="445">
@@ -21115,10 +21115,10 @@
         <v>1.07</v>
       </c>
       <c r="I445" t="n">
-        <v>0.2321</v>
+        <v>0.2405</v>
       </c>
       <c r="J445" t="n">
-        <v>6.2667</v>
+        <v>6.4935</v>
       </c>
     </row>
     <row r="446">
@@ -21155,10 +21155,10 @@
         <v>0.89</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.4136</v>
+        <v>-0.3934</v>
       </c>
       <c r="J446" t="n">
-        <v>-11.1672</v>
+        <v>-10.6218</v>
       </c>
     </row>
     <row r="447">
@@ -21195,10 +21195,10 @@
         <v>1.16</v>
       </c>
       <c r="I447" t="n">
-        <v>0.367</v>
+        <v>0.3663</v>
       </c>
       <c r="J447" t="n">
-        <v>9.909000000000001</v>
+        <v>9.8901</v>
       </c>
     </row>
     <row r="448">
@@ -21235,10 +21235,10 @@
         <v>1.02</v>
       </c>
       <c r="I448" t="n">
-        <v>0.0677</v>
+        <v>0.0746</v>
       </c>
       <c r="J448" t="n">
-        <v>1.8279</v>
+        <v>2.0142</v>
       </c>
     </row>
     <row r="449">
@@ -21275,10 +21275,10 @@
         <v>1.02</v>
       </c>
       <c r="I449" t="n">
-        <v>0.0677</v>
+        <v>0.0746</v>
       </c>
       <c r="J449" t="n">
-        <v>1.8279</v>
+        <v>2.0142</v>
       </c>
     </row>
     <row r="450">
@@ -21315,10 +21315,10 @@
         <v>0.96</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.0623</v>
+        <v>-0.0718</v>
       </c>
       <c r="J450" t="n">
-        <v>-1.6821</v>
+        <v>-1.9386</v>
       </c>
     </row>
     <row r="451">
@@ -21355,10 +21355,10 @@
         <v>0.79</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.2478</v>
+        <v>-0.2614</v>
       </c>
       <c r="J451" t="n">
-        <v>-6.6906</v>
+        <v>-7.0578</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2956/event_2956_evp_summary.xlsx
+++ b/database/event/2956/event_2956_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4409</v>
+        <v>7.2341</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2868</v>
+        <v>3.1954</v>
       </c>
       <c r="D2" t="n">
-        <v>2.763</v>
+        <v>2.6897</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4409</v>
+        <v>7.2341</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1314</v>
+        <v>3.9493</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3095</v>
+        <v>3.2848</v>
       </c>
       <c r="H2" t="n">
-        <v>8.736800000000001</v>
+        <v>8.384600000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7178</v>
+        <v>4.7077</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3095</v>
+        <v>3.2848</v>
       </c>
       <c r="K2" t="n">
         <v>124</v>
@@ -529,7 +529,7 @@
         <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>8.0273</v>
+        <v>7.9925</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3002</v>
+        <v>6.2157</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7829</v>
+        <v>2.7456</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2438</v>
+        <v>2.2258</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3002</v>
+        <v>6.2157</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7323</v>
+        <v>3.6262</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5679</v>
+        <v>2.5895</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4201</v>
+        <v>7.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0068</v>
+        <v>4.0267</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5679</v>
+        <v>2.5895</v>
       </c>
       <c r="K3" t="n">
         <v>124</v>
@@ -575,7 +575,7 @@
         <v>199</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5747</v>
+        <v>6.6162</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4273</v>
+        <v>5.2961</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3973</v>
+        <v>2.3394</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8464</v>
+        <v>1.8068</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4273</v>
+        <v>5.2961</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7207</v>
+        <v>2.7881</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7066</v>
+        <v>2.508</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0825</v>
+        <v>4.025</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2045</v>
+        <v>2.2599</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7066</v>
+        <v>2.508</v>
       </c>
       <c r="K4" t="n">
         <v>118</v>
@@ -621,7 +621,7 @@
         <v>169</v>
       </c>
       <c r="M4" t="n">
-        <v>4.911099999999999</v>
+        <v>4.7679</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3766</v>
+        <v>5.2197</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3749</v>
+        <v>2.3056</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8233</v>
+        <v>1.772</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3766</v>
+        <v>5.2197</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8876</v>
+        <v>2.8813</v>
       </c>
       <c r="G5" t="n">
-        <v>2.489</v>
+        <v>2.3384</v>
       </c>
       <c r="H5" t="n">
-        <v>4.633</v>
+        <v>4.3751</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5018</v>
+        <v>2.4565</v>
       </c>
       <c r="J5" t="n">
-        <v>2.489</v>
+        <v>2.3384</v>
       </c>
       <c r="K5" t="n">
         <v>118</v>
@@ -667,7 +667,7 @@
         <v>169</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9908</v>
+        <v>4.7949</v>
       </c>
       <c r="N5" t="n">
         <v>287</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0205</v>
+        <v>4.9599</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2176</v>
+        <v>2.1909</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6612</v>
+        <v>1.6537</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0205</v>
+        <v>4.9599</v>
       </c>
       <c r="F6" t="n">
-        <v>2.331</v>
+        <v>2.4787</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6895</v>
+        <v>2.4812</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7965</v>
+        <v>2.8636</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5101</v>
+        <v>1.6078</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6895</v>
+        <v>2.4812</v>
       </c>
       <c r="K6" t="n">
         <v>118</v>
@@ -713,7 +713,7 @@
         <v>169</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1996</v>
+        <v>4.089</v>
       </c>
       <c r="N6" t="n">
         <v>287</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9532</v>
+        <v>4.7369</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1879</v>
+        <v>2.0924</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6306</v>
+        <v>1.5521</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9532</v>
+        <v>4.7369</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0644</v>
+        <v>1.9749</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8888</v>
+        <v>2.762</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0644</v>
+        <v>1.9749</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1176</v>
+        <v>2.0277</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8888</v>
+        <v>2.762</v>
       </c>
       <c r="K7" t="n">
         <v>162</v>
@@ -759,7 +759,7 @@
         <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>5.006399999999999</v>
+        <v>4.7897</v>
       </c>
       <c r="N7" t="n">
         <v>284</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4592</v>
+        <v>4.3916</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9697</v>
+        <v>1.9398</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4057</v>
+        <v>1.3948</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4592</v>
+        <v>4.3916</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5454</v>
+        <v>2.5471</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9138</v>
+        <v>1.8445</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5039</v>
+        <v>3.1204</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8921</v>
+        <v>1.752</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9138</v>
+        <v>1.8445</v>
       </c>
       <c r="K8" t="n">
         <v>124</v>
@@ -805,7 +805,7 @@
         <v>199</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8059</v>
+        <v>3.5965</v>
       </c>
       <c r="N8" t="n">
         <v>323</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.286</v>
+        <v>4.2704</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8932</v>
+        <v>1.8863</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3269</v>
+        <v>1.3396</v>
       </c>
       <c r="E9" t="n">
-        <v>4.286</v>
+        <v>4.2704</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6284</v>
+        <v>2.534</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6576</v>
+        <v>1.7365</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0279</v>
+        <v>2.857</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1059</v>
+        <v>2.9333</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6576</v>
+        <v>1.7365</v>
       </c>
       <c r="K9" t="n">
         <v>162</v>
@@ -851,7 +851,7 @@
         <v>122</v>
       </c>
       <c r="M9" t="n">
-        <v>4.763500000000001</v>
+        <v>4.6698</v>
       </c>
       <c r="N9" t="n">
         <v>284</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.099</v>
+        <v>4.0705</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8106</v>
+        <v>1.798</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2417</v>
+        <v>1.2485</v>
       </c>
       <c r="E10" t="n">
-        <v>4.099</v>
+        <v>4.0705</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5887</v>
+        <v>2.6366</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5103</v>
+        <v>1.4339</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6469</v>
+        <v>3.4563</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9693</v>
+        <v>1.9406</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5103</v>
+        <v>1.4339</v>
       </c>
       <c r="K10" t="n">
         <v>118</v>
@@ -897,7 +897,7 @@
         <v>169</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4796</v>
+        <v>3.3745</v>
       </c>
       <c r="N10" t="n">
         <v>287</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9471</v>
+        <v>3.78</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7435</v>
+        <v>1.6697</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1726</v>
+        <v>1.1162</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9471</v>
+        <v>3.78</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6545</v>
+        <v>2.6338</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2926</v>
+        <v>1.1462</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0849</v>
+        <v>3.0858</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0849</v>
+        <v>3.0858</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2926</v>
+        <v>1.1462</v>
       </c>
       <c r="K11" t="n">
         <v>143</v>
@@ -943,7 +943,7 @@
         <v>89</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3775</v>
+        <v>4.232</v>
       </c>
       <c r="N11" t="n">
         <v>232</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3372</v>
+        <v>3.2089</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4741</v>
+        <v>1.4174</v>
       </c>
       <c r="D12" t="n">
-        <v>0.895</v>
+        <v>0.856</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3372</v>
+        <v>3.2089</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3379</v>
+        <v>1.2786</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9993</v>
+        <v>1.9303</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3379</v>
+        <v>1.2786</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3724</v>
+        <v>1.3128</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9993</v>
+        <v>1.9303</v>
       </c>
       <c r="K12" t="n">
         <v>114</v>
@@ -989,7 +989,7 @@
         <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3717</v>
+        <v>3.2431</v>
       </c>
       <c r="N12" t="n">
         <v>249</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0891</v>
+        <v>3.1034</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3645</v>
+        <v>1.3708</v>
       </c>
       <c r="D13" t="n">
-        <v>0.782</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0891</v>
+        <v>3.1034</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9972</v>
+        <v>2.0004</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0919</v>
+        <v>1.103</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9972</v>
+        <v>2.0004</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0487</v>
+        <v>2.0539</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0919</v>
+        <v>1.103</v>
       </c>
       <c r="K13" t="n">
         <v>114</v>
@@ -1035,7 +1035,7 @@
         <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1406</v>
+        <v>3.1569</v>
       </c>
       <c r="N13" t="n">
         <v>249</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0474</v>
+        <v>2.9427</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3461</v>
+        <v>1.2998</v>
       </c>
       <c r="D14" t="n">
-        <v>0.763</v>
+        <v>0.7348</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0474</v>
+        <v>2.9427</v>
       </c>
       <c r="F14" t="n">
-        <v>1.685</v>
+        <v>1.6248</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3624</v>
+        <v>1.3179</v>
       </c>
       <c r="H14" t="n">
-        <v>1.685</v>
+        <v>1.6248</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7284</v>
+        <v>1.6682</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3624</v>
+        <v>1.3179</v>
       </c>
       <c r="K14" t="n">
         <v>162</v>
@@ -1081,7 +1081,7 @@
         <v>122</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0908</v>
+        <v>2.9861</v>
       </c>
       <c r="N14" t="n">
         <v>284</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9666</v>
+        <v>2.9226</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3104</v>
+        <v>1.291</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7256</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9666</v>
+        <v>2.9226</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9666</v>
+        <v>2.9226</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7681</v>
+        <v>3.7476</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7681</v>
+        <v>3.7476</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7681</v>
+        <v>3.7476</v>
       </c>
       <c r="N15" t="n">
         <v>137</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.579</v>
+        <v>2.5287</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1392</v>
+        <v>1.117</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5498</v>
+        <v>0.5462</v>
       </c>
       <c r="E16" t="n">
-        <v>2.579</v>
+        <v>2.5287</v>
       </c>
       <c r="F16" t="n">
-        <v>2.579</v>
+        <v>2.5287</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9197</v>
+        <v>2.8449</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9197</v>
+        <v>2.8449</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9197</v>
+        <v>2.8449</v>
       </c>
       <c r="N16" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5445</v>
+        <v>2.4972</v>
       </c>
       <c r="C17" t="n">
-        <v>1.124</v>
+        <v>1.1031</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5341</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5445</v>
+        <v>2.4972</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5445</v>
+        <v>2.4972</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8442</v>
+        <v>2.7726</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8442</v>
+        <v>2.7726</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8442</v>
+        <v>2.7726</v>
       </c>
       <c r="N17" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4737</v>
+        <v>2.4866</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0927</v>
+        <v>1.0984</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5019</v>
+        <v>0.527</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4737</v>
+        <v>2.4866</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0002</v>
+        <v>2.9776</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5265</v>
+        <v>-0.491</v>
       </c>
       <c r="H18" t="n">
-        <v>5.0045</v>
+        <v>4.7365</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7024</v>
+        <v>2.6594</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5265</v>
+        <v>-0.491</v>
       </c>
       <c r="K18" t="n">
         <v>124</v>
@@ -1265,7 +1265,7 @@
         <v>199</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1759</v>
+        <v>2.1684</v>
       </c>
       <c r="N18" t="n">
         <v>323</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4503</v>
+        <v>2.4352</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0823</v>
+        <v>1.0757</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4912</v>
+        <v>0.5036</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4503</v>
+        <v>2.4352</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4503</v>
+        <v>2.4352</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6381</v>
+        <v>2.6307</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6381</v>
+        <v>2.6307</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6381</v>
+        <v>2.6307</v>
       </c>
       <c r="N19" t="n">
         <v>148</v>
@@ -1320,32 +1320,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2292</v>
+        <v>2.1455</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9847</v>
+        <v>0.9477</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3906</v>
+        <v>0.3716</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2292</v>
+        <v>2.1455</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2292</v>
+        <v>2.1455</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2292</v>
+        <v>2.1455</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2866</v>
+        <v>2.2028</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2866</v>
+        <v>2.2028</v>
       </c>
       <c r="N20" t="n">
         <v>144</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1155</v>
+        <v>2.0752</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9345</v>
+        <v>0.9167</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3388</v>
+        <v>0.3396</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1155</v>
+        <v>2.0752</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1155</v>
+        <v>2.0752</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1155</v>
+        <v>2.0752</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1155</v>
+        <v>2.1307</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1155</v>
+        <v>2.1307</v>
       </c>
       <c r="N21" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0947</v>
+        <v>2.0562</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9253</v>
+        <v>0.9083</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3293</v>
+        <v>0.3309</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0947</v>
+        <v>2.0562</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1672</v>
+        <v>2.122</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0725</v>
+        <v>-0.0658</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1672</v>
+        <v>2.122</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1672</v>
+        <v>2.122</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0725</v>
+        <v>-0.0658</v>
       </c>
       <c r="K22" t="n">
         <v>143</v>
@@ -1449,7 +1449,7 @@
         <v>89</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0947</v>
+        <v>2.0562</v>
       </c>
       <c r="N22" t="n">
         <v>232</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.061</v>
+        <v>1.9434</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9104</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.314</v>
+        <v>0.2795</v>
       </c>
       <c r="E23" t="n">
-        <v>2.061</v>
+        <v>1.9434</v>
       </c>
       <c r="F23" t="n">
-        <v>2.061</v>
+        <v>1.9434</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.061</v>
+        <v>1.9434</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1141</v>
+        <v>1.9434</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.1141</v>
+        <v>1.9434</v>
       </c>
       <c r="N23" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9219</v>
+        <v>1.8222</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8489</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2507</v>
+        <v>0.2243</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9219</v>
+        <v>1.8222</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9219</v>
+        <v>1.8222</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9219</v>
+        <v>1.8222</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9219</v>
+        <v>1.8222</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9219</v>
+        <v>1.8222</v>
       </c>
       <c r="N24" t="n">
         <v>148</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8586</v>
+        <v>1.7821</v>
       </c>
       <c r="C25" t="n">
-        <v>0.821</v>
+        <v>0.7872</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2219</v>
+        <v>0.206</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8586</v>
+        <v>1.7821</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7353</v>
+        <v>1.6802</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1233</v>
+        <v>0.1019</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7353</v>
+        <v>1.6802</v>
       </c>
       <c r="I25" t="n">
-        <v>1.78</v>
+        <v>1.7251</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1233</v>
+        <v>0.1019</v>
       </c>
       <c r="K25" t="n">
         <v>114</v>
@@ -1587,7 +1587,7 @@
         <v>135</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9033</v>
+        <v>1.827</v>
       </c>
       <c r="N25" t="n">
         <v>249</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7015</v>
+        <v>1.5621</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7516</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1504</v>
+        <v>0.1058</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7015</v>
+        <v>1.5621</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8154</v>
+        <v>1.5621</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1139</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8154</v>
+        <v>1.5621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9802999999999999</v>
+        <v>1.5621</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1139</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="L26" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8663999999999999</v>
+        <v>1.5621</v>
       </c>
       <c r="N26" t="n">
-        <v>287</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6218</v>
+        <v>1.5476</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7164</v>
+        <v>0.6836</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1141</v>
+        <v>0.0992</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6218</v>
+        <v>1.5476</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6218</v>
+        <v>1.5476</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6218</v>
+        <v>1.5476</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6636</v>
+        <v>1.5889</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6636</v>
+        <v>1.5889</v>
       </c>
       <c r="N27" t="n">
         <v>144</v>
@@ -1688,185 +1688,185 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6066</v>
+        <v>1.5449</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7097</v>
+        <v>0.6824</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1072</v>
+        <v>0.098</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6066</v>
+        <v>1.5449</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6066</v>
+        <v>1.6665</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.1216</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6066</v>
+        <v>1.6665</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6066</v>
+        <v>1.711</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.1216</v>
       </c>
       <c r="K28" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6066</v>
+        <v>1.5894</v>
       </c>
       <c r="N28" t="n">
-        <v>137</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5925</v>
+        <v>1.4497</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7034</v>
+        <v>0.6404</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1007</v>
+        <v>0.0546</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5925</v>
+        <v>1.4497</v>
       </c>
       <c r="F29" t="n">
-        <v>1.661</v>
+        <v>1.606</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1563</v>
       </c>
       <c r="H29" t="n">
-        <v>1.661</v>
+        <v>1.606</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7038</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1563</v>
       </c>
       <c r="K29" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L29" t="n">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6353</v>
+        <v>0.7454</v>
       </c>
       <c r="N29" t="n">
-        <v>166</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3618</v>
+        <v>1.2571</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6015</v>
+        <v>0.5553</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0043</v>
+        <v>-0.0331</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3618</v>
+        <v>1.2571</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1436</v>
+        <v>1.2571</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2182</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1436</v>
+        <v>1.2571</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1731</v>
+        <v>1.2571</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2182</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="L30" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3913</v>
+        <v>1.2571</v>
       </c>
       <c r="N30" t="n">
-        <v>249</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2207</v>
+        <v>1.2283</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5392</v>
+        <v>0.5426</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0462</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2207</v>
+        <v>1.2283</v>
       </c>
       <c r="F31" t="n">
-        <v>0.395</v>
+        <v>1.0997</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8257</v>
+        <v>0.1286</v>
       </c>
       <c r="H31" t="n">
-        <v>0.395</v>
+        <v>1.0997</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4052</v>
+        <v>1.1291</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8257</v>
+        <v>0.1286</v>
       </c>
       <c r="K31" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="L31" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2309</v>
+        <v>1.2577</v>
       </c>
       <c r="N31" t="n">
-        <v>284</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.212</v>
+        <v>1.1461</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5354</v>
+        <v>0.5063</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0725</v>
+        <v>-0.0837</v>
       </c>
       <c r="E32" t="n">
-        <v>1.212</v>
+        <v>1.1461</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5308</v>
+        <v>1.5026</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.3188</v>
+        <v>-0.3565</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5308</v>
+        <v>1.5026</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5702</v>
+        <v>1.5428</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3188</v>
+        <v>-0.3565</v>
       </c>
       <c r="K32" t="n">
         <v>120</v>
@@ -1909,7 +1909,7 @@
         <v>46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2514</v>
+        <v>1.1863</v>
       </c>
       <c r="N32" t="n">
         <v>166</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1775</v>
+        <v>1.0596</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5201</v>
+        <v>0.468</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0882</v>
+        <v>-0.1231</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1775</v>
+        <v>1.0596</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1775</v>
+        <v>0.3202</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1775</v>
+        <v>0.3202</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1775</v>
+        <v>0.3287</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1775</v>
+        <v>1.0681</v>
       </c>
       <c r="N33" t="n">
-        <v>137</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0871</v>
+        <v>1.0167</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4802</v>
+        <v>0.4491</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1293</v>
+        <v>-0.1426</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0871</v>
+        <v>1.0167</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0871</v>
+        <v>1.0167</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0871</v>
+        <v>1.0167</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0871</v>
+        <v>1.0167</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0871</v>
+        <v>1.0167</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9061</v>
+        <v>0.9277</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4002</v>
+        <v>0.4098</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2117</v>
+        <v>-0.1832</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9061</v>
+        <v>0.9277</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3229</v>
+        <v>1.3379</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4168</v>
+        <v>-0.4102</v>
       </c>
       <c r="H35" t="n">
-        <v>1.3229</v>
+        <v>1.3379</v>
       </c>
       <c r="I35" t="n">
-        <v>1.3229</v>
+        <v>1.3379</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4168</v>
+        <v>-0.4102</v>
       </c>
       <c r="K35" t="n">
         <v>143</v>
@@ -2047,7 +2047,7 @@
         <v>89</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9060999999999999</v>
+        <v>0.9277000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>232</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7075</v>
+        <v>0.6731</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3125</v>
+        <v>0.2973</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3021</v>
+        <v>-0.2992</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7075</v>
+        <v>0.6731</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7075</v>
+        <v>0.6731</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7075</v>
+        <v>0.6731</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7075</v>
+        <v>0.6731</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7075</v>
+        <v>0.6731</v>
       </c>
       <c r="N36" t="n">
         <v>137</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6589</v>
+        <v>0.6082</v>
       </c>
       <c r="C37" t="n">
-        <v>0.291</v>
+        <v>0.2687</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3243</v>
+        <v>-0.3287</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6589</v>
+        <v>0.6082</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6589</v>
+        <v>0.6082</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6589</v>
+        <v>0.6082</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6589</v>
+        <v>0.6082</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6589</v>
+        <v>0.6082</v>
       </c>
       <c r="N37" t="n">
         <v>151</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5443</v>
+        <v>0.545</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2404</v>
+        <v>0.2407</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3764</v>
+        <v>-0.3575</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5443</v>
+        <v>0.545</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5443</v>
+        <v>0.545</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5443</v>
+        <v>0.545</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5443</v>
+        <v>0.545</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5443</v>
+        <v>0.545</v>
       </c>
       <c r="N38" t="n">
         <v>137</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4765</v>
+        <v>0.4519</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2105</v>
+        <v>0.1996</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4073</v>
+        <v>-0.3999</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4765</v>
+        <v>0.4519</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4765</v>
+        <v>0.4519</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4765</v>
+        <v>0.4519</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4765</v>
+        <v>0.4519</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4765</v>
+        <v>0.4519</v>
       </c>
       <c r="N39" t="n">
         <v>143</v>
@@ -2240,231 +2240,231 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3628</v>
+        <v>0.2799</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1603</v>
+        <v>0.1236</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.459</v>
+        <v>-0.4783</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3628</v>
+        <v>0.2799</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3628</v>
+        <v>0.5643</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.2844</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3628</v>
+        <v>0.5643</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3628</v>
+        <v>0.5794</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.2844</v>
       </c>
       <c r="K40" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3628</v>
+        <v>0.295</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tsogoo</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3575</v>
+        <v>0.2781</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1579</v>
+        <v>0.1228</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4615</v>
+        <v>-0.4791</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3575</v>
+        <v>0.2781</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3575</v>
+        <v>0.2781</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3575</v>
+        <v>0.2781</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3575</v>
+        <v>0.2781</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3575</v>
+        <v>0.2781</v>
       </c>
       <c r="N41" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Tsogoo</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2716</v>
+        <v>0.2758</v>
       </c>
       <c r="C42" t="n">
-        <v>0.12</v>
+        <v>0.1218</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5006</v>
+        <v>-0.4801</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2716</v>
+        <v>0.2758</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2716</v>
+        <v>0.2758</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2716</v>
+        <v>0.2758</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2786</v>
+        <v>0.2758</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2786</v>
+        <v>0.2758</v>
       </c>
       <c r="N42" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2625</v>
+        <v>0.2648</v>
       </c>
       <c r="C43" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5047</v>
+        <v>-0.4852</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2625</v>
+        <v>0.2648</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4951</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.2326</v>
+        <v>-0.3295</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4951</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5079</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2326</v>
+        <v>-0.3295</v>
       </c>
       <c r="K43" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="L43" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2753</v>
+        <v>0.2648</v>
       </c>
       <c r="N43" t="n">
-        <v>166</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2188</v>
+        <v>0.2606</v>
       </c>
       <c r="C44" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1151</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5246</v>
+        <v>-0.4871</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2188</v>
+        <v>0.2606</v>
       </c>
       <c r="F44" t="n">
-        <v>0.555</v>
+        <v>0.2606</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.3362</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.555</v>
+        <v>0.2606</v>
       </c>
       <c r="I44" t="n">
-        <v>0.555</v>
+        <v>0.2676</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3362</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="L44" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2188000000000001</v>
+        <v>0.2676</v>
       </c>
       <c r="N44" t="n">
-        <v>232</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0023</v>
+        <v>0.0378</v>
       </c>
       <c r="C45" t="n">
-        <v>0.001</v>
+        <v>0.0167</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6232</v>
+        <v>-0.5886</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0023</v>
+        <v>0.0378</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0023</v>
+        <v>0.0378</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0023</v>
+        <v>0.0378</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0023</v>
+        <v>0.0378</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0023</v>
+        <v>0.0378</v>
       </c>
       <c r="N45" t="n">
         <v>151</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0071</v>
+        <v>-0.0122</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0031</v>
+        <v>-0.0054</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6274</v>
+        <v>-0.6113</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0071</v>
+        <v>-0.0122</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0071</v>
+        <v>-0.0122</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0071</v>
+        <v>-0.0122</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0071</v>
+        <v>-0.0122</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0071</v>
+        <v>-0.0122</v>
       </c>
       <c r="N46" t="n">
         <v>143</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0116</v>
+        <v>-0.0881</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0051</v>
+        <v>-0.0389</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.6459</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0116</v>
+        <v>-0.0881</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0116</v>
+        <v>-0.0881</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0116</v>
+        <v>-0.0881</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0116</v>
+        <v>-0.0881</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0116</v>
+        <v>-0.0881</v>
       </c>
       <c r="N47" t="n">
         <v>143</v>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2238</v>
+        <v>-0.201</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0989</v>
+        <v>-0.0888</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7261</v>
+        <v>-0.6974</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2238</v>
+        <v>-0.201</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0572</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.281</v>
+        <v>-0.2662</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0572</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0572</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.281</v>
+        <v>-0.2662</v>
       </c>
       <c r="K48" t="n">
         <v>143</v>
@@ -2645,7 +2645,7 @@
         <v>89</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2238</v>
+        <v>-0.201</v>
       </c>
       <c r="N48" t="n">
         <v>232</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1155</v>
+        <v>-0.1068</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7432</v>
+        <v>-0.7159</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="N49" t="n">
         <v>27</v>
@@ -2700,93 +2700,93 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>Zilkenberg</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.3104</v>
+        <v>-0.3198</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1371</v>
+        <v>-0.1413</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7655</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.3104</v>
+        <v>-0.3198</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0169</v>
+        <v>-0.3198</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.3273</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0169</v>
+        <v>-0.3198</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0173</v>
+        <v>-0.3198</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.3273</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L50" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.31</v>
+        <v>-0.3198</v>
       </c>
       <c r="N50" t="n">
-        <v>166</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3214</v>
+        <v>-0.3517</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.142</v>
+        <v>-0.1554</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7705</v>
+        <v>-0.766</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3214</v>
+        <v>-0.3517</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3214</v>
+        <v>0.0135</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.3652</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3214</v>
+        <v>0.0135</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3214</v>
+        <v>0.0139</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.3652</v>
       </c>
       <c r="K51" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3214</v>
+        <v>-0.3513</v>
       </c>
       <c r="N51" t="n">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.355</v>
+        <v>-0.3554</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1568</v>
+        <v>-0.157</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.7677</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.355</v>
+        <v>-0.3554</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.355</v>
+        <v>-0.3554</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.355</v>
+        <v>-0.3554</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.355</v>
+        <v>-0.3554</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.355</v>
+        <v>-0.3554</v>
       </c>
       <c r="N52" t="n">
         <v>118</v>
@@ -2838,47 +2838,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Zilkenberg</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3617</v>
+        <v>-0.3783</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1598</v>
+        <v>-0.1671</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7889</v>
+        <v>-0.7781</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3617</v>
+        <v>-0.3783</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3617</v>
+        <v>-0.3783</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3617</v>
+        <v>-0.3783</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3617</v>
+        <v>-0.3783</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3617</v>
+        <v>-0.3783</v>
       </c>
       <c r="N53" t="n">
-        <v>118</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3845</v>
+        <v>-0.4342</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1698</v>
+        <v>-0.1918</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7992</v>
+        <v>-0.8036</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3845</v>
+        <v>-0.4342</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3845</v>
+        <v>-0.4342</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3845</v>
+        <v>-0.4342</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3944</v>
+        <v>-0.4458</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3944</v>
+        <v>-0.4458</v>
       </c>
       <c r="N54" t="n">
         <v>144</v>
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.5463</v>
+        <v>-0.4936</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2413</v>
+        <v>-0.218</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8729</v>
+        <v>-0.8306</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5463</v>
+        <v>-0.4936</v>
       </c>
       <c r="F55" t="n">
-        <v>0.252</v>
+        <v>0.2906</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.7983</v>
+        <v>-0.7842</v>
       </c>
       <c r="H55" t="n">
-        <v>0.252</v>
+        <v>0.2906</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2585</v>
+        <v>0.2984</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.7983</v>
+        <v>-0.7842</v>
       </c>
       <c r="K55" t="n">
         <v>120</v>
@@ -2967,7 +2967,7 @@
         <v>46</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.5398000000000001</v>
+        <v>-0.4858</v>
       </c>
       <c r="N55" t="n">
         <v>166</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.6378</v>
+        <v>-0.5725</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2817</v>
+        <v>-0.2529</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9145</v>
+        <v>-0.8666</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.6378</v>
+        <v>-0.5725</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.6378</v>
+        <v>-0.5725</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.6378</v>
+        <v>-0.5725</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6378</v>
+        <v>-0.5725</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.6378</v>
+        <v>-0.5725</v>
       </c>
       <c r="N56" t="n">
         <v>151</v>
@@ -3026,31 +3026,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.7342</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3124</v>
+        <v>-0.3243</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.9403</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.7342</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.1277</v>
+        <v>-1.1235</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4205</v>
+        <v>0.3893</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.1277</v>
+        <v>-1.1235</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.1568</v>
+        <v>-1.1535</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4205</v>
+        <v>0.3893</v>
       </c>
       <c r="K57" t="n">
         <v>114</v>
@@ -3059,7 +3059,7 @@
         <v>135</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.7363000000000001</v>
+        <v>-0.7642</v>
       </c>
       <c r="N57" t="n">
         <v>249</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.8062</v>
+        <v>-0.7672</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3561</v>
+        <v>-0.3389</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.9912</v>
+        <v>-0.9553</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.8062</v>
+        <v>-0.7672</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.8062</v>
+        <v>-0.7672</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.8062</v>
+        <v>-0.7672</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.8062</v>
+        <v>-0.7672</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.8062</v>
+        <v>-0.7672</v>
       </c>
       <c r="N58" t="n">
         <v>143</v>
@@ -3118,31 +3118,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.9747</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4305</v>
+        <v>-0.4237</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.0679</v>
+        <v>-1.0427</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.9747</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.305</v>
+        <v>-1.3307</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3303</v>
+        <v>0.3715</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.305</v>
+        <v>-1.3307</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.3386</v>
+        <v>-1.3663</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3303</v>
+        <v>0.3715</v>
       </c>
       <c r="K59" t="n">
         <v>162</v>
@@ -3151,7 +3151,7 @@
         <v>122</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.0083</v>
+        <v>-0.9948000000000001</v>
       </c>
       <c r="N59" t="n">
         <v>284</v>
@@ -3160,78 +3160,78 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ncl</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.7977</v>
+        <v>-1.7309</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.7941</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.4426</v>
+        <v>-1.3943</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.7977</v>
+        <v>-1.7309</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.7977</v>
+        <v>-1.2337</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-0.4972</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.7977</v>
+        <v>-1.2337</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.7977</v>
+        <v>-0.6927</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-0.4972</v>
       </c>
       <c r="K60" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.7977</v>
+        <v>-1.1899</v>
       </c>
       <c r="N60" t="n">
-        <v>118</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>maaRaa</t>
+          <t>ncl</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.908</v>
+        <v>-1.74</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.8428</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4928</v>
+        <v>-1.3984</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.908</v>
+        <v>-1.74</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.908</v>
+        <v>-1.74</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.908</v>
+        <v>-1.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.908</v>
+        <v>-1.74</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-1.908</v>
+        <v>-1.74</v>
       </c>
       <c r="N61" t="n">
         <v>118</v>
@@ -3252,47 +3252,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>maaRaa</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-2.0233</v>
+        <v>-1.8903</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.8937</v>
+        <v>-0.835</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.5453</v>
+        <v>-1.4669</v>
       </c>
       <c r="E62" t="n">
-        <v>-2.0233</v>
+        <v>-1.8903</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.5056</v>
+        <v>-1.8903</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.5177</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.5056</v>
+        <v>-1.8903</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-1.8903</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.5177</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L62" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-1.3307</v>
+        <v>-1.8903</v>
       </c>
       <c r="N62" t="n">
-        <v>323</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -3395,10 +3395,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>1.15</v>
+        <v>1.1588</v>
       </c>
       <c r="J2" t="n">
-        <v>29.9</v>
+        <v>30.1288</v>
       </c>
     </row>
     <row r="3">
@@ -3435,10 +3435,10 @@
         <v>1.47</v>
       </c>
       <c r="I3" t="n">
-        <v>1.076</v>
+        <v>1.0762</v>
       </c>
       <c r="J3" t="n">
-        <v>27.976</v>
+        <v>27.9812</v>
       </c>
     </row>
     <row r="4">
@@ -3475,10 +3475,10 @@
         <v>1.27</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6874</v>
+        <v>0.6585</v>
       </c>
       <c r="J4" t="n">
-        <v>17.8724</v>
+        <v>17.121</v>
       </c>
     </row>
     <row r="5">
@@ -3515,10 +3515,10 @@
         <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4528</v>
+        <v>0.4193</v>
       </c>
       <c r="J5" t="n">
-        <v>11.7728</v>
+        <v>10.9018</v>
       </c>
     </row>
     <row r="6">
@@ -3555,10 +3555,10 @@
         <v>0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7853</v>
+        <v>-0.7644</v>
       </c>
       <c r="J6" t="n">
-        <v>-20.4178</v>
+        <v>-19.8744</v>
       </c>
     </row>
     <row r="7">
@@ -3595,10 +3595,10 @@
         <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2667</v>
+        <v>0.2207</v>
       </c>
       <c r="J7" t="n">
-        <v>6.9342</v>
+        <v>5.7382</v>
       </c>
     </row>
     <row r="8">
@@ -3635,10 +3635,10 @@
         <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.169</v>
+        <v>-0.1513</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.394</v>
+        <v>-3.9338</v>
       </c>
     </row>
     <row r="9">
@@ -3675,10 +3675,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1793</v>
+        <v>-0.1612</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.6618</v>
+        <v>-4.1912</v>
       </c>
     </row>
     <row r="10">
@@ -3715,10 +3715,10 @@
         <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2093</v>
+        <v>-0.1904</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.4418</v>
+        <v>-4.9504</v>
       </c>
     </row>
     <row r="11">
@@ -3755,10 +3755,10 @@
         <v>0.64</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3885</v>
+        <v>-0.3761</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.101</v>
+        <v>-9.778600000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3795,10 +3795,10 @@
         <v>1.07</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1948</v>
+        <v>0.1837</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4804</v>
+        <v>4.2251</v>
       </c>
     </row>
     <row r="13">
@@ -3835,10 +3835,10 @@
         <v>0.91</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1153</v>
+        <v>-0.1007</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.6519</v>
+        <v>-2.3161</v>
       </c>
     </row>
     <row r="14">
@@ -3875,10 +3875,10 @@
         <v>0.72</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3076</v>
+        <v>-0.2911</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.0748</v>
+        <v>-6.6953</v>
       </c>
     </row>
     <row r="15">
@@ -3915,10 +3915,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3625</v>
+        <v>-0.3483</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.3375</v>
+        <v>-8.010899999999999</v>
       </c>
     </row>
     <row r="16">
@@ -3955,10 +3955,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4429</v>
+        <v>-0.4353</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.1867</v>
+        <v>-10.0119</v>
       </c>
     </row>
     <row r="17">
@@ -3995,10 +3995,10 @@
         <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7873</v>
+        <v>0.7161</v>
       </c>
       <c r="J17" t="n">
-        <v>18.1079</v>
+        <v>16.4703</v>
       </c>
     </row>
     <row r="18">
@@ -4035,10 +4035,10 @@
         <v>1.64</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7582</v>
+        <v>0.6865</v>
       </c>
       <c r="J18" t="n">
-        <v>17.4386</v>
+        <v>15.7895</v>
       </c>
     </row>
     <row r="19">
@@ -4075,10 +4075,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2478</v>
+        <v>0.2019</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6994</v>
+        <v>4.6437</v>
       </c>
     </row>
     <row r="20">
@@ -4115,10 +4115,10 @@
         <v>1.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.195</v>
+        <v>0.1557</v>
       </c>
       <c r="J20" t="n">
-        <v>4.485</v>
+        <v>3.5811</v>
       </c>
     </row>
     <row r="21">
@@ -4155,10 +4155,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4618</v>
+        <v>-0.4616</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.6214</v>
+        <v>-10.6168</v>
       </c>
     </row>
     <row r="22">
@@ -4195,10 +4195,10 @@
         <v>1.53</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2025</v>
+        <v>1.2182</v>
       </c>
       <c r="J22" t="n">
-        <v>31.265</v>
+        <v>31.6732</v>
       </c>
     </row>
     <row r="23">
@@ -4235,10 +4235,10 @@
         <v>1.39</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9226</v>
       </c>
       <c r="J23" t="n">
-        <v>24.362</v>
+        <v>23.9876</v>
       </c>
     </row>
     <row r="24">
@@ -4275,10 +4275,10 @@
         <v>1.22</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5908</v>
+        <v>0.5561</v>
       </c>
       <c r="J24" t="n">
-        <v>15.3608</v>
+        <v>14.4586</v>
       </c>
     </row>
     <row r="25">
@@ -4315,10 +4315,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4281</v>
+        <v>-0.3867</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.1306</v>
+        <v>-10.0542</v>
       </c>
     </row>
     <row r="26">
@@ -4355,10 +4355,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4785</v>
+        <v>-0.4379</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.441</v>
+        <v>-11.3854</v>
       </c>
     </row>
     <row r="27">
@@ -4395,10 +4395,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1916</v>
+        <v>0.1516</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9816</v>
+        <v>3.9416</v>
       </c>
     </row>
     <row r="28">
@@ -4435,10 +4435,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0649</v>
+        <v>-0.0534</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.6874</v>
+        <v>-1.3884</v>
       </c>
     </row>
     <row r="29">
@@ -4475,10 +4475,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0649</v>
+        <v>-0.0534</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.6874</v>
+        <v>-1.3884</v>
       </c>
     </row>
     <row r="30">
@@ -4515,10 +4515,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2522</v>
+        <v>-0.2327</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.5572</v>
+        <v>-6.0502</v>
       </c>
     </row>
     <row r="31">
@@ -4555,10 +4555,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3376</v>
+        <v>-0.3216</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.7776</v>
+        <v>-8.361599999999999</v>
       </c>
     </row>
     <row r="32">
@@ -4595,10 +4595,10 @@
         <v>0.93</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0766</v>
+        <v>-0.0617</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.6852</v>
+        <v>-1.3574</v>
       </c>
     </row>
     <row r="33">
@@ -4635,10 +4635,10 @@
         <v>0.78</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.245</v>
+        <v>-0.2301</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.39</v>
+        <v>-5.0622</v>
       </c>
     </row>
     <row r="34">
@@ -4675,10 +4675,10 @@
         <v>0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.274</v>
+        <v>-0.2593</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.028</v>
+        <v>-5.7046</v>
       </c>
     </row>
     <row r="35">
@@ -4715,10 +4715,10 @@
         <v>0.66</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3543</v>
+        <v>-0.3409</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.7946</v>
+        <v>-7.4998</v>
       </c>
     </row>
     <row r="36">
@@ -4755,10 +4755,10 @@
         <v>0.46</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5309</v>
+        <v>-0.5333</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.6798</v>
+        <v>-11.7326</v>
       </c>
     </row>
     <row r="37">
@@ -4795,10 +4795,10 @@
         <v>1.99</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0479</v>
+        <v>0.9845</v>
       </c>
       <c r="J37" t="n">
-        <v>23.0538</v>
+        <v>21.659</v>
       </c>
     </row>
     <row r="38">
@@ -4835,10 +4835,10 @@
         <v>1.63</v>
       </c>
       <c r="I38" t="n">
-        <v>0.723</v>
+        <v>0.6519</v>
       </c>
       <c r="J38" t="n">
-        <v>15.906</v>
+        <v>14.3418</v>
       </c>
     </row>
     <row r="39">
@@ -4875,10 +4875,10 @@
         <v>1.32</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4194</v>
+        <v>0.3611</v>
       </c>
       <c r="J39" t="n">
-        <v>9.226800000000001</v>
+        <v>7.9442</v>
       </c>
     </row>
     <row r="40">
@@ -4915,10 +4915,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1217</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>2.6774</v>
+        <v>2.0196</v>
       </c>
     </row>
     <row r="41">
@@ -4955,10 +4955,10 @@
         <v>1.07</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1062</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>2.3364</v>
+        <v>1.7314</v>
       </c>
     </row>
     <row r="42">
@@ -4995,10 +4995,10 @@
         <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.486</v>
+        <v>0.4439</v>
       </c>
       <c r="J42" t="n">
-        <v>12.636</v>
+        <v>11.5414</v>
       </c>
     </row>
     <row r="43">
@@ -5035,10 +5035,10 @@
         <v>1.05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1957</v>
+        <v>0.1628</v>
       </c>
       <c r="J43" t="n">
-        <v>5.0882</v>
+        <v>4.2328</v>
       </c>
     </row>
     <row r="44">
@@ -5075,10 +5075,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1318</v>
+        <v>0.1056</v>
       </c>
       <c r="J44" t="n">
-        <v>3.4268</v>
+        <v>2.7456</v>
       </c>
     </row>
     <row r="45">
@@ -5115,10 +5115,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.056</v>
+        <v>0.0416</v>
       </c>
       <c r="J45" t="n">
-        <v>1.456</v>
+        <v>1.0816</v>
       </c>
     </row>
     <row r="46">
@@ -5155,10 +5155,10 @@
         <v>0.88</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3993</v>
+        <v>-0.3562</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.3818</v>
+        <v>-9.261200000000001</v>
       </c>
     </row>
     <row r="47">
@@ -5195,10 +5195,10 @@
         <v>1.29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5114</v>
       </c>
       <c r="J47" t="n">
-        <v>14.8486</v>
+        <v>13.2964</v>
       </c>
     </row>
     <row r="48">
@@ -5235,10 +5235,10 @@
         <v>1.15</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3385</v>
+        <v>0.2858</v>
       </c>
       <c r="J48" t="n">
-        <v>8.801</v>
+        <v>7.4308</v>
       </c>
     </row>
     <row r="49">
@@ -5275,10 +5275,10 @@
         <v>1.13</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3024</v>
+        <v>0.2523</v>
       </c>
       <c r="J49" t="n">
-        <v>7.8624</v>
+        <v>6.5598</v>
       </c>
     </row>
     <row r="50">
@@ -5315,10 +5315,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1728</v>
+        <v>-0.1523</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.4928</v>
+        <v>-3.9598</v>
       </c>
     </row>
     <row r="51">
@@ -5355,10 +5355,10 @@
         <v>0.75</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3045</v>
+        <v>-0.2871</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.917</v>
+        <v>-7.4646</v>
       </c>
     </row>
     <row r="52">
@@ -5395,10 +5395,10 @@
         <v>1.25</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5992</v>
+        <v>0.5884</v>
       </c>
       <c r="J52" t="n">
-        <v>14.3808</v>
+        <v>14.1216</v>
       </c>
     </row>
     <row r="53">
@@ -5435,10 +5435,10 @@
         <v>1.23</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5679</v>
+        <v>0.5587</v>
       </c>
       <c r="J53" t="n">
-        <v>13.6296</v>
+        <v>13.4088</v>
       </c>
     </row>
     <row r="54">
@@ -5475,10 +5475,10 @@
         <v>1.21</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5361</v>
+        <v>0.5272</v>
       </c>
       <c r="J54" t="n">
-        <v>12.8664</v>
+        <v>12.6528</v>
       </c>
     </row>
     <row r="55">
@@ -5515,10 +5515,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4712</v>
+        <v>0.4465</v>
       </c>
       <c r="J55" t="n">
-        <v>11.3088</v>
+        <v>10.716</v>
       </c>
     </row>
     <row r="56">
@@ -5555,10 +5555,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1292</v>
+        <v>-0.1019</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.1008</v>
+        <v>-2.4456</v>
       </c>
     </row>
     <row r="57">
@@ -5595,10 +5595,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4169</v>
+        <v>0.3618</v>
       </c>
       <c r="J57" t="n">
-        <v>10.0056</v>
+        <v>8.683199999999999</v>
       </c>
     </row>
     <row r="58">
@@ -5635,10 +5635,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3261</v>
+        <v>0.274</v>
       </c>
       <c r="J58" t="n">
-        <v>7.8264</v>
+        <v>6.576</v>
       </c>
     </row>
     <row r="59">
@@ -5675,10 +5675,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2357</v>
+        <v>-0.2157</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.6568</v>
+        <v>-5.1768</v>
       </c>
     </row>
     <row r="60">
@@ -5715,10 +5715,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2357</v>
+        <v>-0.2157</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.6568</v>
+        <v>-5.1768</v>
       </c>
     </row>
     <row r="61">
@@ -5755,10 +5755,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.9608</v>
+        <v>-7.5696</v>
       </c>
     </row>
     <row r="62">
@@ -5795,10 +5795,10 @@
         <v>1.7</v>
       </c>
       <c r="I62" t="n">
-        <v>1.19</v>
+        <v>1.1856</v>
       </c>
       <c r="J62" t="n">
-        <v>26.18</v>
+        <v>26.0832</v>
       </c>
     </row>
     <row r="63">
@@ -5835,10 +5835,10 @@
         <v>1.38</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7691</v>
+        <v>0.7579</v>
       </c>
       <c r="J63" t="n">
-        <v>16.9202</v>
+        <v>16.6738</v>
       </c>
     </row>
     <row r="64">
@@ -5875,10 +5875,10 @@
         <v>1.34</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7143</v>
+        <v>0.7046</v>
       </c>
       <c r="J64" t="n">
-        <v>15.7146</v>
+        <v>15.5012</v>
       </c>
     </row>
     <row r="65">
@@ -5915,10 +5915,10 @@
         <v>1.2</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5032</v>
+        <v>0.4952</v>
       </c>
       <c r="J65" t="n">
-        <v>11.0704</v>
+        <v>10.8944</v>
       </c>
     </row>
     <row r="66">
@@ -5955,10 +5955,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2869</v>
+        <v>0.2553</v>
       </c>
       <c r="J66" t="n">
-        <v>6.3118</v>
+        <v>5.6166</v>
       </c>
     </row>
     <row r="67">
@@ -5995,10 +5995,10 @@
         <v>1.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4389</v>
+        <v>0.3931</v>
       </c>
       <c r="J67" t="n">
-        <v>9.655799999999999</v>
+        <v>8.648199999999999</v>
       </c>
     </row>
     <row r="68">
@@ -6035,10 +6035,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0675</v>
+        <v>-0.0556</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.485</v>
+        <v>-1.2232</v>
       </c>
     </row>
     <row r="69">
@@ -6075,10 +6075,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2347</v>
+        <v>-0.217</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.1634</v>
+        <v>-4.774</v>
       </c>
     </row>
     <row r="70">
@@ -6115,10 +6115,10 @@
         <v>0.59</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4277</v>
+        <v>-0.4187</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.4094</v>
+        <v>-9.211399999999999</v>
       </c>
     </row>
     <row r="71">
@@ -6155,10 +6155,10 @@
         <v>0.53</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4804</v>
+        <v>-0.4771</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.5688</v>
+        <v>-10.4962</v>
       </c>
     </row>
     <row r="72">
@@ -6195,10 +6195,10 @@
         <v>1.07</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2263</v>
+        <v>0.1841</v>
       </c>
       <c r="J72" t="n">
-        <v>5.6575</v>
+        <v>4.6025</v>
       </c>
     </row>
     <row r="73">
@@ -6235,10 +6235,10 @@
         <v>0.98</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0288</v>
+        <v>-0.0215</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.72</v>
+        <v>-0.5375</v>
       </c>
     </row>
     <row r="74">
@@ -6275,10 +6275,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1577</v>
+        <v>-0.1407</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.9425</v>
+        <v>-3.5175</v>
       </c>
     </row>
     <row r="75">
@@ -6315,10 +6315,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2186</v>
+        <v>-0.1998</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.465</v>
+        <v>-4.995</v>
       </c>
     </row>
     <row r="76">
@@ -6355,10 +6355,10 @@
         <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5105</v>
+        <v>-0.5117</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.7625</v>
+        <v>-12.7925</v>
       </c>
     </row>
     <row r="77">
@@ -6395,10 +6395,10 @@
         <v>1.63</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1147</v>
+        <v>1.1066</v>
       </c>
       <c r="J77" t="n">
-        <v>27.8675</v>
+        <v>27.665</v>
       </c>
     </row>
     <row r="78">
@@ -6435,10 +6435,10 @@
         <v>1.52</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9694</v>
+        <v>0.9562</v>
       </c>
       <c r="J78" t="n">
-        <v>24.235</v>
+        <v>23.905</v>
       </c>
     </row>
     <row r="79">
@@ -6475,10 +6475,10 @@
         <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5383</v>
       </c>
       <c r="J79" t="n">
-        <v>13.57</v>
+        <v>13.4575</v>
       </c>
     </row>
     <row r="80">
@@ -6515,10 +6515,10 @@
         <v>1.06</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1872</v>
+        <v>0.1595</v>
       </c>
       <c r="J80" t="n">
-        <v>4.68</v>
+        <v>3.9875</v>
       </c>
     </row>
     <row r="81">
@@ -6555,10 +6555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2804</v>
+        <v>-0.2436</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.01</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="82">
@@ -6595,10 +6595,10 @@
         <v>2.17</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0093</v>
+        <v>0.9512</v>
       </c>
       <c r="J82" t="n">
-        <v>24.2232</v>
+        <v>22.8288</v>
       </c>
     </row>
     <row r="83">
@@ -6635,10 +6635,10 @@
         <v>1.6</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6308</v>
+        <v>0.5913</v>
       </c>
       <c r="J83" t="n">
-        <v>15.1392</v>
+        <v>14.1912</v>
       </c>
     </row>
     <row r="84">
@@ -6675,10 +6675,10 @@
         <v>1.38</v>
       </c>
       <c r="I84" t="n">
-        <v>0.472</v>
+        <v>0.4206</v>
       </c>
       <c r="J84" t="n">
-        <v>11.328</v>
+        <v>10.0944</v>
       </c>
     </row>
     <row r="85">
@@ -6715,10 +6715,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0866</v>
+        <v>-0.0737</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.0784</v>
+        <v>-1.7688</v>
       </c>
     </row>
     <row r="86">
@@ -6755,10 +6755,10 @@
         <v>0.8</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2806</v>
+        <v>-0.2657</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.7344</v>
+        <v>-6.3768</v>
       </c>
     </row>
     <row r="87">
@@ -6795,10 +6795,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5283</v>
+        <v>0.5707</v>
       </c>
       <c r="J87" t="n">
-        <v>12.6792</v>
+        <v>13.6968</v>
       </c>
     </row>
     <row r="88">
@@ -6835,10 +6835,10 @@
         <v>0.92</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1037</v>
+        <v>-0.0896</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.4888</v>
+        <v>-2.1504</v>
       </c>
     </row>
     <row r="89">
@@ -6875,10 +6875,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2241</v>
+        <v>-0.2071</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.3784</v>
+        <v>-4.9704</v>
       </c>
     </row>
     <row r="90">
@@ -6915,10 +6915,10 @@
         <v>0.51</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4958</v>
+        <v>-0.4943</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.8992</v>
+        <v>-11.8632</v>
       </c>
     </row>
     <row r="91">
@@ -6955,10 +6955,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5987</v>
+        <v>-0.6126</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.3688</v>
+        <v>-14.7024</v>
       </c>
     </row>
     <row r="92">
@@ -6995,10 +6995,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4233</v>
+        <v>0.372</v>
       </c>
       <c r="J92" t="n">
-        <v>11.4291</v>
+        <v>10.044</v>
       </c>
     </row>
     <row r="93">
@@ -7035,10 +7035,10 @@
         <v>0.85</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1889</v>
+        <v>-0.1707</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.1003</v>
+        <v>-4.6089</v>
       </c>
     </row>
     <row r="94">
@@ -7075,10 +7075,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2187</v>
+        <v>-0.1999</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.9049</v>
+        <v>-5.3973</v>
       </c>
     </row>
     <row r="95">
@@ -7115,10 +7115,10 @@
         <v>0.72</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3147</v>
+        <v>-0.2975</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.4969</v>
+        <v>-8.032500000000001</v>
       </c>
     </row>
     <row r="96">
@@ -7155,10 +7155,10 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3332</v>
+        <v>-0.317</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.9964</v>
+        <v>-8.558999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -7195,10 +7195,10 @@
         <v>1.43</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8576</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>23.1552</v>
+        <v>22.7394</v>
       </c>
     </row>
     <row r="98">
@@ -7235,10 +7235,10 @@
         <v>1.34</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7287</v>
+        <v>0.7143</v>
       </c>
       <c r="J98" t="n">
-        <v>19.6749</v>
+        <v>19.2861</v>
       </c>
     </row>
     <row r="99">
@@ -7275,10 +7275,10 @@
         <v>1.31</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6845</v>
+        <v>0.6714</v>
       </c>
       <c r="J99" t="n">
-        <v>18.4815</v>
+        <v>18.1278</v>
       </c>
     </row>
     <row r="100">
@@ -7315,10 +7315,10 @@
         <v>0.99</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0743</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.5704</v>
+        <v>-2.0061</v>
       </c>
     </row>
     <row r="101">
@@ -7355,10 +7355,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1366</v>
+        <v>-0.1095</v>
       </c>
       <c r="J101" t="n">
-        <v>-3.6882</v>
+        <v>-2.9565</v>
       </c>
     </row>
     <row r="102">
@@ -7395,10 +7395,10 @@
         <v>1.09</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1817</v>
+        <v>0.1649</v>
       </c>
       <c r="J102" t="n">
-        <v>6.3595</v>
+        <v>5.7715</v>
       </c>
     </row>
     <row r="103">
@@ -7435,10 +7435,10 @@
         <v>1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0825</v>
       </c>
       <c r="J103" t="n">
-        <v>3.402</v>
+        <v>2.8875</v>
       </c>
     </row>
     <row r="104">
@@ -7475,10 +7475,10 @@
         <v>0.99</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0254</v>
+        <v>-0.0182</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.889</v>
+        <v>-0.637</v>
       </c>
     </row>
     <row r="105">
@@ -7515,10 +7515,10 @@
         <v>0.97</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0585</v>
+        <v>-0.0458</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.0475</v>
+        <v>-1.603</v>
       </c>
     </row>
     <row r="106">
@@ -7555,10 +7555,10 @@
         <v>0.93</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1118</v>
+        <v>-0.094</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.913</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="107">
@@ -7595,10 +7595,10 @@
         <v>1.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5153</v>
+        <v>0.4728</v>
       </c>
       <c r="J107" t="n">
-        <v>18.0355</v>
+        <v>16.548</v>
       </c>
     </row>
     <row r="108">
@@ -7635,10 +7635,10 @@
         <v>1.07</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1361</v>
+        <v>0.103</v>
       </c>
       <c r="J108" t="n">
-        <v>4.7635</v>
+        <v>3.605</v>
       </c>
     </row>
     <row r="109">
@@ -7675,10 +7675,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0493</v>
+        <v>0.0343</v>
       </c>
       <c r="J109" t="n">
-        <v>1.7255</v>
+        <v>1.2005</v>
       </c>
     </row>
     <row r="110">
@@ -7715,10 +7715,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0302</v>
+        <v>-0.0216</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.057</v>
+        <v>-0.756</v>
       </c>
     </row>
     <row r="111">
@@ -7755,10 +7755,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1755</v>
+        <v>-0.1551</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.1425</v>
+        <v>-5.4285</v>
       </c>
     </row>
     <row r="112">
@@ -7795,10 +7795,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9066</v>
+        <v>0.8921</v>
       </c>
       <c r="J112" t="n">
-        <v>24.4782</v>
+        <v>24.0867</v>
       </c>
     </row>
     <row r="113">
@@ -7835,10 +7835,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.738</v>
+        <v>0.7244</v>
       </c>
       <c r="J113" t="n">
-        <v>19.926</v>
+        <v>19.5588</v>
       </c>
     </row>
     <row r="114">
@@ -7875,10 +7875,10 @@
         <v>1.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5137</v>
+        <v>0.5053</v>
       </c>
       <c r="J114" t="n">
-        <v>13.8699</v>
+        <v>13.6431</v>
       </c>
     </row>
     <row r="115">
@@ -7915,10 +7915,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4027</v>
+        <v>0.3699</v>
       </c>
       <c r="J115" t="n">
-        <v>10.8729</v>
+        <v>9.987299999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7955,10 +7955,10 @@
         <v>1.07</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2209</v>
+        <v>0.1917</v>
       </c>
       <c r="J116" t="n">
-        <v>5.9643</v>
+        <v>5.1759</v>
       </c>
     </row>
     <row r="117">
@@ -7995,10 +7995,10 @@
         <v>1.22</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4733</v>
+        <v>0.4283</v>
       </c>
       <c r="J117" t="n">
-        <v>12.7791</v>
+        <v>11.5641</v>
       </c>
     </row>
     <row r="118">
@@ -8035,10 +8035,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0527</v>
+        <v>0.0355</v>
       </c>
       <c r="J118" t="n">
-        <v>1.4229</v>
+        <v>0.9585</v>
       </c>
     </row>
     <row r="119">
@@ -8075,10 +8075,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0542</v>
+        <v>-0.0435</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.4634</v>
+        <v>-1.1745</v>
       </c>
     </row>
     <row r="120">
@@ -8115,10 +8115,10 @@
         <v>0.78</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2659</v>
+        <v>-0.2464</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.1793</v>
+        <v>-6.6528</v>
       </c>
     </row>
     <row r="121">
@@ -8155,10 +8155,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3508</v>
+        <v>-0.3358</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.4716</v>
+        <v>-9.066599999999999</v>
       </c>
     </row>
     <row r="122">
@@ -8195,10 +8195,10 @@
         <v>1.5</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9609</v>
+        <v>0.9472</v>
       </c>
       <c r="J122" t="n">
-        <v>25.9443</v>
+        <v>25.5744</v>
       </c>
     </row>
     <row r="123">
@@ -8235,10 +8235,10 @@
         <v>1.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7771</v>
+        <v>0.7615</v>
       </c>
       <c r="J123" t="n">
-        <v>20.9817</v>
+        <v>20.5605</v>
       </c>
     </row>
     <row r="124">
@@ -8275,10 +8275,10 @@
         <v>1.13</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3885</v>
+        <v>0.3535</v>
       </c>
       <c r="J124" t="n">
-        <v>10.4895</v>
+        <v>9.544499999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8315,10 +8315,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1726</v>
+        <v>0.1462</v>
       </c>
       <c r="J125" t="n">
-        <v>4.6602</v>
+        <v>3.9474</v>
       </c>
     </row>
     <row r="126">
@@ -8355,10 +8355,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4795</v>
+        <v>-0.4391</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.9465</v>
+        <v>-11.8557</v>
       </c>
     </row>
     <row r="127">
@@ -8395,10 +8395,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.304</v>
+        <v>0.2531</v>
       </c>
       <c r="J127" t="n">
-        <v>8.208</v>
+        <v>6.8337</v>
       </c>
     </row>
     <row r="128">
@@ -8435,10 +8435,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1095</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>2.9565</v>
+        <v>2.1789</v>
       </c>
     </row>
     <row r="129">
@@ -8475,10 +8475,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.095</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.565</v>
+        <v>-2.1519</v>
       </c>
     </row>
     <row r="130">
@@ -8515,10 +8515,10 @@
         <v>0.84</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2064</v>
+        <v>-0.1861</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.5728</v>
+        <v>-5.0247</v>
       </c>
     </row>
     <row r="131">
@@ -8555,10 +8555,10 @@
         <v>0.77</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2761</v>
+        <v>-0.257</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.4547</v>
+        <v>-6.939</v>
       </c>
     </row>
     <row r="132">
@@ -8595,10 +8595,10 @@
         <v>2.39</v>
       </c>
       <c r="I132" t="n">
-        <v>1.9126</v>
+        <v>1.972</v>
       </c>
       <c r="J132" t="n">
-        <v>34.4268</v>
+        <v>35.496</v>
       </c>
     </row>
     <row r="133">
@@ -8635,10 +8635,10 @@
         <v>1.96</v>
       </c>
       <c r="I133" t="n">
-        <v>1.4419</v>
+        <v>1.457</v>
       </c>
       <c r="J133" t="n">
-        <v>25.9542</v>
+        <v>26.226</v>
       </c>
     </row>
     <row r="134">
@@ -8675,10 +8675,10 @@
         <v>1.54</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.9482</v>
       </c>
       <c r="J134" t="n">
-        <v>17.1018</v>
+        <v>17.0676</v>
       </c>
     </row>
     <row r="135">
@@ -8715,10 +8715,10 @@
         <v>1.49</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8855</v>
+        <v>0.8827</v>
       </c>
       <c r="J135" t="n">
-        <v>15.939</v>
+        <v>15.8886</v>
       </c>
     </row>
     <row r="136">
@@ -8755,10 +8755,10 @@
         <v>1.18</v>
       </c>
       <c r="I136" t="n">
-        <v>0.4286</v>
+        <v>0.396</v>
       </c>
       <c r="J136" t="n">
-        <v>7.7148</v>
+        <v>7.128</v>
       </c>
     </row>
     <row r="137">
@@ -8795,10 +8795,10 @@
         <v>0.48</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.475</v>
+        <v>-0.4771</v>
       </c>
       <c r="J137" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.5878</v>
       </c>
     </row>
     <row r="138">
@@ -8835,10 +8835,10 @@
         <v>0.47</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.4837</v>
+        <v>-0.4861</v>
       </c>
       <c r="J138" t="n">
-        <v>-8.7066</v>
+        <v>-8.7498</v>
       </c>
     </row>
     <row r="139">
@@ -8875,10 +8875,10 @@
         <v>0.46</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4922</v>
+        <v>-0.4948</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.8596</v>
+        <v>-8.9064</v>
       </c>
     </row>
     <row r="140">
@@ -8915,10 +8915,10 @@
         <v>0.43</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5165</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.297000000000001</v>
+        <v>-9.3546</v>
       </c>
     </row>
     <row r="141">
@@ -8955,10 +8955,10 @@
         <v>0.41</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5337</v>
+        <v>-0.5377</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.6066</v>
+        <v>-9.678599999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8995,10 +8995,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5995</v>
+        <v>0.5866</v>
       </c>
       <c r="J142" t="n">
-        <v>16.786</v>
+        <v>16.4248</v>
       </c>
     </row>
     <row r="143">
@@ -9035,10 +9035,10 @@
         <v>1.09</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3015</v>
+        <v>0.264</v>
       </c>
       <c r="J143" t="n">
-        <v>8.442</v>
+        <v>7.392</v>
       </c>
     </row>
     <row r="144">
@@ -9075,10 +9075,10 @@
         <v>1.07</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2481</v>
+        <v>0.2135</v>
       </c>
       <c r="J144" t="n">
-        <v>6.9468</v>
+        <v>5.978</v>
       </c>
     </row>
     <row r="145">
@@ -9115,10 +9115,10 @@
         <v>0.98</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1116</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.1248</v>
+        <v>-2.394</v>
       </c>
     </row>
     <row r="146">
@@ -9155,10 +9155,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1116</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.1248</v>
+        <v>-2.394</v>
       </c>
     </row>
     <row r="147">
@@ -9195,10 +9195,10 @@
         <v>1.23</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4652</v>
+        <v>0.4161</v>
       </c>
       <c r="J147" t="n">
-        <v>13.0256</v>
+        <v>11.6508</v>
       </c>
     </row>
     <row r="148">
@@ -9235,10 +9235,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2839</v>
+        <v>0.2353</v>
       </c>
       <c r="J148" t="n">
-        <v>7.9492</v>
+        <v>6.5884</v>
       </c>
     </row>
     <row r="149">
@@ -9275,10 +9275,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1649</v>
+        <v>0.1296</v>
       </c>
       <c r="J149" t="n">
-        <v>4.6172</v>
+        <v>3.6288</v>
       </c>
     </row>
     <row r="150">
@@ -9315,10 +9315,10 @@
         <v>1.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1649</v>
+        <v>0.1296</v>
       </c>
       <c r="J150" t="n">
-        <v>4.6172</v>
+        <v>3.6288</v>
       </c>
     </row>
     <row r="151">
@@ -9355,10 +9355,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3233</v>
+        <v>-0.3071</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.0524</v>
+        <v>-8.598800000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9395,10 +9395,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.8622</v>
       </c>
       <c r="J152" t="n">
-        <v>27.264</v>
+        <v>25.866</v>
       </c>
     </row>
     <row r="153">
@@ -9435,10 +9435,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.354</v>
+        <v>0.3006</v>
       </c>
       <c r="J153" t="n">
-        <v>10.62</v>
+        <v>9.018000000000001</v>
       </c>
     </row>
     <row r="154">
@@ -9475,10 +9475,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0464</v>
+        <v>-0.035</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.392</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="155">
@@ -9515,10 +9515,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.257</v>
+        <v>-0.2375</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.71</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="156">
@@ -9555,10 +9555,10 @@
         <v>0.8</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.257</v>
+        <v>-0.2375</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.71</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="157">
@@ -9595,10 +9595,10 @@
         <v>1.38</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9353</v>
+        <v>0.9214</v>
       </c>
       <c r="J157" t="n">
-        <v>28.059</v>
+        <v>27.642</v>
       </c>
     </row>
     <row r="158">
@@ -9635,10 +9635,10 @@
         <v>1.2</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5588</v>
+        <v>0.5205</v>
       </c>
       <c r="J158" t="n">
-        <v>16.764</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="159">
@@ -9675,10 +9675,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2146</v>
+        <v>0.184</v>
       </c>
       <c r="J159" t="n">
-        <v>6.438</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="160">
@@ -9715,10 +9715,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.189</v>
+        <v>-0.1544</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.67</v>
+        <v>-4.632</v>
       </c>
     </row>
     <row r="161">
@@ -9755,10 +9755,10 @@
         <v>0.95</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2208</v>
+        <v>-0.1838</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.624</v>
+        <v>-5.514</v>
       </c>
     </row>
     <row r="162">
@@ -9795,10 +9795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0848</v>
+        <v>-0.0718</v>
       </c>
       <c r="J162" t="n">
-        <v>-2.12</v>
+        <v>-1.795</v>
       </c>
     </row>
     <row r="163">
@@ -9835,10 +9835,10 @@
         <v>0.89</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1451</v>
+        <v>-0.1289</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.6275</v>
+        <v>-3.2225</v>
       </c>
     </row>
     <row r="164">
@@ -9875,10 +9875,10 @@
         <v>0.85</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1879</v>
+        <v>-0.1703</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.6975</v>
+        <v>-4.2575</v>
       </c>
     </row>
     <row r="165">
@@ -9915,10 +9915,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2656</v>
+        <v>-0.2472</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.64</v>
+        <v>-6.18</v>
       </c>
     </row>
     <row r="166">
@@ -9955,10 +9955,10 @@
         <v>0.72</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3128</v>
+        <v>-0.2957</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.82</v>
+        <v>-7.3925</v>
       </c>
     </row>
     <row r="167">
@@ -9995,10 +9995,10 @@
         <v>1.56</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1678</v>
+        <v>1.1816</v>
       </c>
       <c r="J167" t="n">
-        <v>29.195</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="168">
@@ -10035,10 +10035,10 @@
         <v>1.42</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9668</v>
+        <v>0.9605</v>
       </c>
       <c r="J168" t="n">
-        <v>24.17</v>
+        <v>24.0125</v>
       </c>
     </row>
     <row r="169">
@@ -10075,10 +10075,10 @@
         <v>1.37</v>
       </c>
       <c r="I169" t="n">
-        <v>0.875</v>
+        <v>0.8592</v>
       </c>
       <c r="J169" t="n">
-        <v>21.875</v>
+        <v>21.48</v>
       </c>
     </row>
     <row r="170">
@@ -10115,10 +10115,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2143</v>
+        <v>0.1852</v>
       </c>
       <c r="J170" t="n">
-        <v>5.3575</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="171">
@@ -10155,10 +10155,10 @@
         <v>1.01</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0116</v>
+        <v>0.0012</v>
       </c>
       <c r="J171" t="n">
-        <v>0.29</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="172">
@@ -10195,10 +10195,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2521</v>
+        <v>0.2375</v>
       </c>
       <c r="J172" t="n">
-        <v>5.2941</v>
+        <v>4.9875</v>
       </c>
     </row>
     <row r="173">
@@ -10235,10 +10235,10 @@
         <v>0.73</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2814</v>
+        <v>-0.2688</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.9094</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="174">
@@ -10275,10 +10275,10 @@
         <v>0.58</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4153</v>
+        <v>-0.4066</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.721299999999999</v>
+        <v>-8.538600000000001</v>
       </c>
     </row>
     <row r="175">
@@ -10315,10 +10315,10 @@
         <v>0.49</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4945</v>
+        <v>-0.492</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.3845</v>
+        <v>-10.332</v>
       </c>
     </row>
     <row r="176">
@@ -10355,10 +10355,10 @@
         <v>0.35</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6172</v>
+        <v>-0.632</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.9612</v>
+        <v>-13.272</v>
       </c>
     </row>
     <row r="177">
@@ -10395,10 +10395,10 @@
         <v>1.74</v>
       </c>
       <c r="I177" t="n">
-        <v>1.372</v>
+        <v>1.3954</v>
       </c>
       <c r="J177" t="n">
-        <v>28.812</v>
+        <v>29.3034</v>
       </c>
     </row>
     <row r="178">
@@ -10435,10 +10435,10 @@
         <v>1.56</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1461</v>
+        <v>1.162</v>
       </c>
       <c r="J178" t="n">
-        <v>24.0681</v>
+        <v>24.402</v>
       </c>
     </row>
     <row r="179">
@@ -10475,10 +10475,10 @@
         <v>1.42</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="J179" t="n">
-        <v>19.9311</v>
+        <v>19.887</v>
       </c>
     </row>
     <row r="180">
@@ -10515,10 +10515,10 @@
         <v>1.31</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7436</v>
+        <v>0.7265</v>
       </c>
       <c r="J180" t="n">
-        <v>15.6156</v>
+        <v>15.2565</v>
       </c>
     </row>
     <row r="181">
@@ -10555,10 +10555,10 @@
         <v>1.1</v>
       </c>
       <c r="I181" t="n">
-        <v>0.2744</v>
+        <v>0.2419</v>
       </c>
       <c r="J181" t="n">
-        <v>5.7624</v>
+        <v>5.0799</v>
       </c>
     </row>
     <row r="182">
@@ -10595,10 +10595,10 @@
         <v>1.59</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2456</v>
+        <v>1.2647</v>
       </c>
       <c r="J182" t="n">
-        <v>31.14</v>
+        <v>31.6175</v>
       </c>
     </row>
     <row r="183">
@@ -10635,10 +10635,10 @@
         <v>1.19</v>
       </c>
       <c r="I183" t="n">
-        <v>0.533</v>
+        <v>0.4949</v>
       </c>
       <c r="J183" t="n">
-        <v>13.325</v>
+        <v>12.3725</v>
       </c>
     </row>
     <row r="184">
@@ -10675,10 +10675,10 @@
         <v>1.19</v>
       </c>
       <c r="I184" t="n">
-        <v>0.533</v>
+        <v>0.4949</v>
       </c>
       <c r="J184" t="n">
-        <v>13.325</v>
+        <v>12.3725</v>
       </c>
     </row>
     <row r="185">
@@ -10715,10 +10715,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3124</v>
+        <v>-0.2712</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.81</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="186">
@@ -10755,10 +10755,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7252</v>
+        <v>-0.6964</v>
       </c>
       <c r="J186" t="n">
-        <v>-18.13</v>
+        <v>-17.41</v>
       </c>
     </row>
     <row r="187">
@@ -10795,10 +10795,10 @@
         <v>1.19</v>
       </c>
       <c r="I187" t="n">
-        <v>0.418</v>
+        <v>0.361</v>
       </c>
       <c r="J187" t="n">
-        <v>10.45</v>
+        <v>9.025</v>
       </c>
     </row>
     <row r="188">
@@ -10835,10 +10835,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3831</v>
+        <v>0.3275</v>
       </c>
       <c r="J188" t="n">
-        <v>9.577500000000001</v>
+        <v>8.1875</v>
       </c>
     </row>
     <row r="189">
@@ -10875,10 +10875,10 @@
         <v>1.13</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3108</v>
+        <v>0.2594</v>
       </c>
       <c r="J189" t="n">
-        <v>7.77</v>
+        <v>6.485</v>
       </c>
     </row>
     <row r="190">
@@ -10915,10 +10915,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1464</v>
+        <v>-0.1269</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.66</v>
+        <v>-3.1725</v>
       </c>
     </row>
     <row r="191">
@@ -10955,10 +10955,10 @@
         <v>0.58</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4541</v>
+        <v>-0.4498</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.3525</v>
+        <v>-11.245</v>
       </c>
     </row>
     <row r="192">
@@ -10995,10 +10995,10 @@
         <v>0.9</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1141</v>
+        <v>-0.0984</v>
       </c>
       <c r="J192" t="n">
-        <v>-2.5102</v>
+        <v>-2.1648</v>
       </c>
     </row>
     <row r="193">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2546</v>
+        <v>-0.2398</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.6012</v>
+        <v>-5.2756</v>
       </c>
     </row>
     <row r="194">
@@ -11075,10 +11075,10 @@
         <v>0.74</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2831</v>
+        <v>-0.2686</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.2282</v>
+        <v>-5.9092</v>
       </c>
     </row>
     <row r="195">
@@ -11115,10 +11115,10 @@
         <v>0.59</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4165</v>
+        <v>-0.4066</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.163</v>
+        <v>-8.9452</v>
       </c>
     </row>
     <row r="196">
@@ -11155,10 +11155,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4342</v>
+        <v>-0.4257</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.5524</v>
+        <v>-9.365399999999999</v>
       </c>
     </row>
     <row r="197">
@@ -11195,10 +11195,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6011</v>
+        <v>1.6401</v>
       </c>
       <c r="J197" t="n">
-        <v>35.2242</v>
+        <v>36.0822</v>
       </c>
     </row>
     <row r="198">
@@ -11235,10 +11235,10 @@
         <v>1.93</v>
       </c>
       <c r="I198" t="n">
-        <v>1.5893</v>
+        <v>1.6275</v>
       </c>
       <c r="J198" t="n">
-        <v>34.9646</v>
+        <v>35.805</v>
       </c>
     </row>
     <row r="199">
@@ -11275,10 +11275,10 @@
         <v>1.37</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8517</v>
+        <v>0.8437</v>
       </c>
       <c r="J199" t="n">
-        <v>18.7374</v>
+        <v>18.5614</v>
       </c>
     </row>
     <row r="200">
@@ -11315,10 +11315,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.317</v>
+        <v>0.2835</v>
       </c>
       <c r="J200" t="n">
-        <v>6.974</v>
+        <v>6.237</v>
       </c>
     </row>
     <row r="201">
@@ -11355,10 +11355,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1838</v>
+        <v>0.1518</v>
       </c>
       <c r="J201" t="n">
-        <v>4.0436</v>
+        <v>3.3396</v>
       </c>
     </row>
     <row r="202">
@@ -11395,10 +11395,10 @@
         <v>1.57</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1833</v>
+        <v>1.1976</v>
       </c>
       <c r="J202" t="n">
-        <v>30.7658</v>
+        <v>31.1376</v>
       </c>
     </row>
     <row r="203">
@@ -11435,10 +11435,10 @@
         <v>1.4</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9334</v>
+        <v>0.9222</v>
       </c>
       <c r="J203" t="n">
-        <v>24.2684</v>
+        <v>23.9772</v>
       </c>
     </row>
     <row r="204">
@@ -11475,10 +11475,10 @@
         <v>1.35</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8387</v>
+        <v>0.8198</v>
       </c>
       <c r="J204" t="n">
-        <v>21.8062</v>
+        <v>21.3148</v>
       </c>
     </row>
     <row r="205">
@@ -11515,10 +11515,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1252</v>
+        <v>0.1016</v>
       </c>
       <c r="J205" t="n">
-        <v>3.2552</v>
+        <v>2.6416</v>
       </c>
     </row>
     <row r="206">
@@ -11555,10 +11555,10 @@
         <v>1.01</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0136</v>
+        <v>0.0033</v>
       </c>
       <c r="J206" t="n">
-        <v>0.3536</v>
+        <v>0.0858</v>
       </c>
     </row>
     <row r="207">
@@ -11595,10 +11595,10 @@
         <v>1.15</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3859</v>
+        <v>0.3339</v>
       </c>
       <c r="J207" t="n">
-        <v>10.0334</v>
+        <v>8.6814</v>
       </c>
     </row>
     <row r="208">
@@ -11635,10 +11635,10 @@
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1991</v>
+        <v>-0.1806</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.1766</v>
+        <v>-4.6956</v>
       </c>
     </row>
     <row r="209">
@@ -11675,10 +11675,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2289</v>
+        <v>-0.2099</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.9514</v>
+        <v>-5.4574</v>
       </c>
     </row>
     <row r="210">
@@ -11715,10 +11715,10 @@
         <v>0.74</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2963</v>
+        <v>-0.2784</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.7038</v>
+        <v>-7.2384</v>
       </c>
     </row>
     <row r="211">
@@ -11755,10 +11755,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2963</v>
+        <v>-0.2784</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.7038</v>
+        <v>-7.2384</v>
       </c>
     </row>
     <row r="212">
@@ -11795,10 +11795,10 @@
         <v>0.93</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0465</v>
+        <v>-0.0235</v>
       </c>
       <c r="J212" t="n">
-        <v>-0.8835</v>
+        <v>-0.4465</v>
       </c>
     </row>
     <row r="213">
@@ -11835,10 +11835,10 @@
         <v>0.67</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.3339</v>
+        <v>-0.3238</v>
       </c>
       <c r="J213" t="n">
-        <v>-6.3441</v>
+        <v>-6.1522</v>
       </c>
     </row>
     <row r="214">
@@ -11875,10 +11875,10 @@
         <v>0.61</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3866</v>
+        <v>-0.3779</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.3454</v>
+        <v>-7.1801</v>
       </c>
     </row>
     <row r="215">
@@ -11915,10 +11915,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.438</v>
+        <v>-0.4312</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.321999999999999</v>
+        <v>-8.1928</v>
       </c>
     </row>
     <row r="216">
@@ -11955,10 +11955,10 @@
         <v>0.3</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6579</v>
+        <v>-0.6798</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.5001</v>
+        <v>-12.9162</v>
       </c>
     </row>
     <row r="217">
@@ -11995,10 +11995,10 @@
         <v>2.17</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8544</v>
+        <v>1.9174</v>
       </c>
       <c r="J217" t="n">
-        <v>35.2336</v>
+        <v>36.4306</v>
       </c>
     </row>
     <row r="218">
@@ -12035,10 +12035,10 @@
         <v>1.67</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2703</v>
+        <v>1.2919</v>
       </c>
       <c r="J218" t="n">
-        <v>24.1357</v>
+        <v>24.5461</v>
       </c>
     </row>
     <row r="219">
@@ -12075,10 +12075,10 @@
         <v>1.4</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9012</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>17.1228</v>
+        <v>17.0753</v>
       </c>
     </row>
     <row r="220">
@@ -12115,10 +12115,10 @@
         <v>1.26</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6266</v>
+        <v>0.604</v>
       </c>
       <c r="J220" t="n">
-        <v>11.9054</v>
+        <v>11.476</v>
       </c>
     </row>
     <row r="221">
@@ -12155,10 +12155,10 @@
         <v>1.19</v>
       </c>
       <c r="I221" t="n">
-        <v>0.4754</v>
+        <v>0.4452</v>
       </c>
       <c r="J221" t="n">
-        <v>9.0326</v>
+        <v>8.4588</v>
       </c>
     </row>
     <row r="222">
@@ -12195,10 +12195,10 @@
         <v>1.35</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6052</v>
       </c>
       <c r="J222" t="n">
-        <v>17.9226</v>
+        <v>16.3404</v>
       </c>
     </row>
     <row r="223">
@@ -12235,10 +12235,10 @@
         <v>1.32</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6178</v>
+        <v>0.5584</v>
       </c>
       <c r="J223" t="n">
-        <v>16.6806</v>
+        <v>15.0768</v>
       </c>
     </row>
     <row r="224">
@@ -12275,10 +12275,10 @@
         <v>1.06</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1649</v>
+        <v>0.1296</v>
       </c>
       <c r="J224" t="n">
-        <v>4.4523</v>
+        <v>3.4992</v>
       </c>
     </row>
     <row r="225">
@@ -12315,10 +12315,10 @@
         <v>0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1148</v>
+        <v>-0.0965</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.0996</v>
+        <v>-2.6055</v>
       </c>
     </row>
     <row r="226">
@@ -12355,10 +12355,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.492</v>
+        <v>-0.4931</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.284</v>
+        <v>-13.3137</v>
       </c>
     </row>
     <row r="227">
@@ -12395,10 +12395,10 @@
         <v>1.68</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3628</v>
+        <v>1.3897</v>
       </c>
       <c r="J227" t="n">
-        <v>36.7956</v>
+        <v>37.5219</v>
       </c>
     </row>
     <row r="228">
@@ -12435,10 +12435,10 @@
         <v>1.27</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7036</v>
+        <v>0.6717</v>
       </c>
       <c r="J228" t="n">
-        <v>18.9972</v>
+        <v>18.1359</v>
       </c>
     </row>
     <row r="229">
@@ -12475,10 +12475,10 @@
         <v>1.11</v>
       </c>
       <c r="I229" t="n">
-        <v>0.345</v>
+        <v>0.3092</v>
       </c>
       <c r="J229" t="n">
-        <v>9.315</v>
+        <v>8.3484</v>
       </c>
     </row>
     <row r="230">
@@ -12515,10 +12515,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2569</v>
+        <v>-0.2181</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.9363</v>
+        <v>-5.8887</v>
       </c>
     </row>
     <row r="231">
@@ -12555,10 +12555,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.8166</v>
       </c>
       <c r="J231" t="n">
-        <v>-22.5504</v>
+        <v>-22.0482</v>
       </c>
     </row>
     <row r="232">
@@ -12595,10 +12595,10 @@
         <v>1.99</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7118</v>
+        <v>1.7666</v>
       </c>
       <c r="J232" t="n">
-        <v>39.3714</v>
+        <v>40.6318</v>
       </c>
     </row>
     <row r="233">
@@ -12635,10 +12635,10 @@
         <v>1.32</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7799</v>
+        <v>0.7579</v>
       </c>
       <c r="J233" t="n">
-        <v>17.9377</v>
+        <v>17.4317</v>
       </c>
     </row>
     <row r="234">
@@ -12675,10 +12675,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2975</v>
+        <v>0.2659</v>
       </c>
       <c r="J234" t="n">
-        <v>6.8425</v>
+        <v>6.1157</v>
       </c>
     </row>
     <row r="235">
@@ -12715,10 +12715,10 @@
         <v>1.03</v>
       </c>
       <c r="I235" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="J235" t="n">
-        <v>2.0907</v>
+        <v>1.6146</v>
       </c>
     </row>
     <row r="236">
@@ -12755,10 +12755,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2506</v>
+        <v>-0.2154</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.7638</v>
+        <v>-4.9542</v>
       </c>
     </row>
     <row r="237">
@@ -12795,10 +12795,10 @@
         <v>1.12</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3199</v>
+        <v>0.2694</v>
       </c>
       <c r="J237" t="n">
-        <v>7.3577</v>
+        <v>6.1962</v>
       </c>
     </row>
     <row r="238">
@@ -12835,10 +12835,10 @@
         <v>1.11</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3002</v>
+        <v>0.2509</v>
       </c>
       <c r="J238" t="n">
-        <v>6.9046</v>
+        <v>5.7707</v>
       </c>
     </row>
     <row r="239">
@@ -12875,10 +12875,10 @@
         <v>0.98</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.033</v>
+        <v>-0.0256</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.759</v>
+        <v>-0.5888</v>
       </c>
     </row>
     <row r="240">
@@ -12915,10 +12915,10 @@
         <v>0.78</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2608</v>
+        <v>-0.2416</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.9984</v>
+        <v>-5.5568</v>
       </c>
     </row>
     <row r="241">
@@ -12955,10 +12955,10 @@
         <v>0.42</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5812</v>
+        <v>-0.5935</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.3676</v>
+        <v>-13.6505</v>
       </c>
     </row>
     <row r="242">
@@ -12995,10 +12995,10 @@
         <v>0.83</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1995</v>
+        <v>-0.1837</v>
       </c>
       <c r="J242" t="n">
-        <v>-4.389</v>
+        <v>-4.0414</v>
       </c>
     </row>
     <row r="243">
@@ -13035,10 +13035,10 @@
         <v>0.79</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2398</v>
+        <v>-0.2239</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.2756</v>
+        <v>-4.9258</v>
       </c>
     </row>
     <row r="244">
@@ -13075,10 +13075,10 @@
         <v>0.78</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2494</v>
+        <v>-0.2335</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.4868</v>
+        <v>-5.137</v>
       </c>
     </row>
     <row r="245">
@@ -13115,10 +13115,10 @@
         <v>0.76</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2681</v>
+        <v>-0.2522</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.8982</v>
+        <v>-5.5484</v>
       </c>
     </row>
     <row r="246">
@@ -13155,10 +13155,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4123</v>
+        <v>-0.4019</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.070600000000001</v>
+        <v>-8.841799999999999</v>
       </c>
     </row>
     <row r="247">
@@ -13195,10 +13195,10 @@
         <v>2.12</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8478</v>
+        <v>1.9162</v>
       </c>
       <c r="J247" t="n">
-        <v>40.6516</v>
+        <v>42.1564</v>
       </c>
     </row>
     <row r="248">
@@ -13235,10 +13235,10 @@
         <v>1.45</v>
       </c>
       <c r="I248" t="n">
-        <v>1.0073</v>
+        <v>1.0092</v>
       </c>
       <c r="J248" t="n">
-        <v>22.1606</v>
+        <v>22.2024</v>
       </c>
     </row>
     <row r="249">
@@ -13275,10 +13275,10 @@
         <v>1.3</v>
       </c>
       <c r="I249" t="n">
-        <v>0.735</v>
+        <v>0.714</v>
       </c>
       <c r="J249" t="n">
-        <v>16.17</v>
+        <v>15.708</v>
       </c>
     </row>
     <row r="250">
@@ -13315,10 +13315,10 @@
         <v>1.15</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4121</v>
+        <v>0.3805</v>
       </c>
       <c r="J250" t="n">
-        <v>9.0662</v>
+        <v>8.371</v>
       </c>
     </row>
     <row r="251">
@@ -13355,10 +13355,10 @@
         <v>0.68</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.9063</v>
+        <v>-0.9013</v>
       </c>
       <c r="J251" t="n">
-        <v>-19.9386</v>
+        <v>-19.8286</v>
       </c>
     </row>
     <row r="252">
@@ -13395,10 +13395,10 @@
         <v>1.5</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0758</v>
+        <v>1.0875</v>
       </c>
       <c r="J252" t="n">
-        <v>25.8192</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="253">
@@ -13435,10 +13435,10 @@
         <v>1.44</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9881</v>
+        <v>0.9882</v>
       </c>
       <c r="J253" t="n">
-        <v>23.7144</v>
+        <v>23.7168</v>
       </c>
     </row>
     <row r="254">
@@ -13475,10 +13475,10 @@
         <v>1.4</v>
       </c>
       <c r="I254" t="n">
-        <v>0.9197</v>
+        <v>0.9113</v>
       </c>
       <c r="J254" t="n">
-        <v>22.0728</v>
+        <v>21.8712</v>
       </c>
     </row>
     <row r="255">
@@ -13515,10 +13515,10 @@
         <v>1.3</v>
       </c>
       <c r="I255" t="n">
-        <v>0.7321</v>
+        <v>0.712</v>
       </c>
       <c r="J255" t="n">
-        <v>17.5704</v>
+        <v>17.088</v>
       </c>
     </row>
     <row r="256">
@@ -13555,10 +13555,10 @@
         <v>1.18</v>
       </c>
       <c r="I256" t="n">
-        <v>0.4781</v>
+        <v>0.448</v>
       </c>
       <c r="J256" t="n">
-        <v>11.4744</v>
+        <v>10.752</v>
       </c>
     </row>
     <row r="257">
@@ -13595,10 +13595,10 @@
         <v>1.01</v>
       </c>
       <c r="I257" t="n">
-        <v>0.1008</v>
+        <v>0.0832</v>
       </c>
       <c r="J257" t="n">
-        <v>2.4192</v>
+        <v>1.9968</v>
       </c>
     </row>
     <row r="258">
@@ -13635,10 +13635,10 @@
         <v>0.93</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0858</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.0592</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="259">
@@ -13675,10 +13675,10 @@
         <v>0.76</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2686</v>
+        <v>-0.2524</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.4464</v>
+        <v>-6.0576</v>
       </c>
     </row>
     <row r="260">
@@ -13715,10 +13715,10 @@
         <v>0.64</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3775</v>
+        <v>-0.3645</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.06</v>
+        <v>-8.747999999999999</v>
       </c>
     </row>
     <row r="261">
@@ -13755,10 +13755,10 @@
         <v>0.46</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5359</v>
+        <v>-0.5394</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.8616</v>
+        <v>-12.9456</v>
       </c>
     </row>
     <row r="262">
@@ -13795,10 +13795,10 @@
         <v>1.83</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4798</v>
+        <v>1.5098</v>
       </c>
       <c r="J262" t="n">
-        <v>31.0758</v>
+        <v>31.7058</v>
       </c>
     </row>
     <row r="263">
@@ -13835,10 +13835,10 @@
         <v>1.5</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0674</v>
+        <v>1.0807</v>
       </c>
       <c r="J263" t="n">
-        <v>22.4154</v>
+        <v>22.6947</v>
       </c>
     </row>
     <row r="264">
@@ -13875,10 +13875,10 @@
         <v>1.38</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8767</v>
+        <v>0.8685</v>
       </c>
       <c r="J264" t="n">
-        <v>18.4107</v>
+        <v>18.2385</v>
       </c>
     </row>
     <row r="265">
@@ -13915,10 +13915,10 @@
         <v>1.31</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7423</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="J265" t="n">
-        <v>15.5883</v>
+        <v>15.2313</v>
       </c>
     </row>
     <row r="266">
@@ -13955,10 +13955,10 @@
         <v>1.16</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4211</v>
+        <v>0.3898</v>
       </c>
       <c r="J266" t="n">
-        <v>8.8431</v>
+        <v>8.1858</v>
       </c>
     </row>
     <row r="267">
@@ -13995,10 +13995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0042</v>
+        <v>0.05</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.0882</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="268">
@@ -14035,10 +14035,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.4217</v>
+        <v>-0.4171</v>
       </c>
       <c r="J268" t="n">
-        <v>-8.855700000000001</v>
+        <v>-8.7591</v>
       </c>
     </row>
     <row r="269">
@@ -14075,10 +14075,10 @@
         <v>0.5</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4718</v>
+        <v>-0.4688</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.9078</v>
+        <v>-9.844799999999999</v>
       </c>
     </row>
     <row r="270">
@@ -14115,10 +14115,10 @@
         <v>0.49</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4805</v>
+        <v>-0.478</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.0905</v>
+        <v>-10.038</v>
       </c>
     </row>
     <row r="271">
@@ -14155,10 +14155,10 @@
         <v>0.24</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7034</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.7714</v>
+        <v>-15.4014</v>
       </c>
     </row>
     <row r="272">
@@ -14195,10 +14195,10 @@
         <v>1.16</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3628</v>
+        <v>0.3083</v>
       </c>
       <c r="J272" t="n">
-        <v>16.6888</v>
+        <v>14.1818</v>
       </c>
     </row>
     <row r="273">
@@ -14235,10 +14235,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3449</v>
+        <v>0.2914</v>
       </c>
       <c r="J273" t="n">
-        <v>15.8654</v>
+        <v>13.4044</v>
       </c>
     </row>
     <row r="274">
@@ -14275,10 +14275,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.147</v>
+        <v>0.1133</v>
       </c>
       <c r="J274" t="n">
-        <v>6.762</v>
+        <v>5.2118</v>
       </c>
     </row>
     <row r="275">
@@ -14315,10 +14315,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0428</v>
+        <v>0.0291</v>
       </c>
       <c r="J275" t="n">
-        <v>1.9688</v>
+        <v>1.3386</v>
       </c>
     </row>
     <row r="276">
@@ -14355,10 +14355,10 @@
         <v>0.66</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3846</v>
+        <v>-0.3729</v>
       </c>
       <c r="J276" t="n">
-        <v>-17.6916</v>
+        <v>-17.1534</v>
       </c>
     </row>
     <row r="277">
@@ -14395,10 +14395,10 @@
         <v>1.36</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8979</v>
+        <v>0.8796</v>
       </c>
       <c r="J277" t="n">
-        <v>41.3034</v>
+        <v>40.4616</v>
       </c>
     </row>
     <row r="278">
@@ -14435,10 +14435,10 @@
         <v>1.25</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6696</v>
+        <v>0.635</v>
       </c>
       <c r="J278" t="n">
-        <v>30.8016</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="279">
@@ -14475,10 +14475,10 @@
         <v>1.01</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0433</v>
+        <v>0.0323</v>
       </c>
       <c r="J279" t="n">
-        <v>1.9918</v>
+        <v>1.4858</v>
       </c>
     </row>
     <row r="280">
@@ -14515,10 +14515,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0761</v>
+        <v>-0.0558</v>
       </c>
       <c r="J280" t="n">
-        <v>-3.5006</v>
+        <v>-2.5668</v>
       </c>
     </row>
     <row r="281">
@@ -14555,10 +14555,10 @@
         <v>0.91</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3355</v>
+        <v>-0.2935</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.433</v>
+        <v>-13.501</v>
       </c>
     </row>
     <row r="282">
@@ -14595,10 +14595,10 @@
         <v>1.87</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5286</v>
+        <v>1.5621</v>
       </c>
       <c r="J282" t="n">
-        <v>30.572</v>
+        <v>31.242</v>
       </c>
     </row>
     <row r="283">
@@ -14635,10 +14635,10 @@
         <v>1.82</v>
       </c>
       <c r="I283" t="n">
-        <v>1.4684</v>
+        <v>1.4977</v>
       </c>
       <c r="J283" t="n">
-        <v>29.368</v>
+        <v>29.954</v>
       </c>
     </row>
     <row r="284">
@@ -14675,10 +14675,10 @@
         <v>1.53</v>
       </c>
       <c r="I284" t="n">
-        <v>1.1068</v>
+        <v>1.1224</v>
       </c>
       <c r="J284" t="n">
-        <v>22.136</v>
+        <v>22.448</v>
       </c>
     </row>
     <row r="285">
@@ -14715,10 +14715,10 @@
         <v>1</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0707</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J285" t="n">
-        <v>-1.414</v>
+        <v>-1.382</v>
       </c>
     </row>
     <row r="286">
@@ -14755,10 +14755,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3043</v>
+        <v>-0.272</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.086</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="287">
@@ -14795,10 +14795,10 @@
         <v>1.01</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1252</v>
+        <v>0.1117</v>
       </c>
       <c r="J287" t="n">
-        <v>2.504</v>
+        <v>2.234</v>
       </c>
     </row>
     <row r="288">
@@ -14835,10 +14835,10 @@
         <v>0.9</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1119</v>
+        <v>-0.0959</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.238</v>
+        <v>-1.918</v>
       </c>
     </row>
     <row r="289">
@@ -14875,10 +14875,10 @@
         <v>0.73</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2912</v>
+        <v>-0.2771</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.824</v>
+        <v>-5.542</v>
       </c>
     </row>
     <row r="290">
@@ -14915,10 +14915,10 @@
         <v>0.49</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.5033</v>
+        <v>-0.502</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.066</v>
+        <v>-10.04</v>
       </c>
     </row>
     <row r="291">
@@ -14955,10 +14955,10 @@
         <v>0.39</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5901</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.802</v>
+        <v>-12.026</v>
       </c>
     </row>
     <row r="292">
@@ -14995,10 +14995,10 @@
         <v>1.46</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0622</v>
+        <v>1.0696</v>
       </c>
       <c r="J292" t="n">
-        <v>43.5502</v>
+        <v>43.8536</v>
       </c>
     </row>
     <row r="293">
@@ -15035,10 +15035,10 @@
         <v>1.45</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0473</v>
+        <v>1.0524</v>
       </c>
       <c r="J293" t="n">
-        <v>42.9393</v>
+        <v>43.1484</v>
       </c>
     </row>
     <row r="294">
@@ -15075,10 +15075,10 @@
         <v>1.05</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1801</v>
+        <v>0.1527</v>
       </c>
       <c r="J294" t="n">
-        <v>7.3841</v>
+        <v>6.2607</v>
       </c>
     </row>
     <row r="295">
@@ -15115,10 +15115,10 @@
         <v>0.89</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3953</v>
+        <v>-0.353</v>
       </c>
       <c r="J295" t="n">
-        <v>-16.2073</v>
+        <v>-14.473</v>
       </c>
     </row>
     <row r="296">
@@ -15155,10 +15155,10 @@
         <v>0.84</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5204</v>
+        <v>-0.4802</v>
       </c>
       <c r="J296" t="n">
-        <v>-21.3364</v>
+        <v>-19.6882</v>
       </c>
     </row>
     <row r="297">
@@ -15195,10 +15195,10 @@
         <v>1.31</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6019</v>
+        <v>0.5423</v>
       </c>
       <c r="J297" t="n">
-        <v>24.6779</v>
+        <v>22.2343</v>
       </c>
     </row>
     <row r="298">
@@ -15235,10 +15235,10 @@
         <v>1.17</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3733</v>
+        <v>0.3185</v>
       </c>
       <c r="J298" t="n">
-        <v>15.3053</v>
+        <v>13.0585</v>
       </c>
     </row>
     <row r="299">
@@ -15275,10 +15275,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1024</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.1984</v>
+        <v>-3.485</v>
       </c>
     </row>
     <row r="300">
@@ -15315,10 +15315,10 @@
         <v>0.93</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.115</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.715</v>
+        <v>-3.9647</v>
       </c>
     </row>
     <row r="301">
@@ -15355,10 +15355,10 @@
         <v>0.86</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1946</v>
+        <v>-0.174</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.9786</v>
+        <v>-7.134</v>
       </c>
     </row>
     <row r="302">
@@ -15395,10 +15395,10 @@
         <v>1.23</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6473</v>
+        <v>0.6107</v>
       </c>
       <c r="J302" t="n">
-        <v>18.7717</v>
+        <v>17.7103</v>
       </c>
     </row>
     <row r="303">
@@ -15435,10 +15435,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4619</v>
+        <v>0.4195</v>
       </c>
       <c r="J303" t="n">
-        <v>13.3951</v>
+        <v>12.1655</v>
       </c>
     </row>
     <row r="304">
@@ -15475,10 +15475,10 @@
         <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0032</v>
+        <v>-0.0016</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0464</v>
       </c>
     </row>
     <row r="305">
@@ -15515,10 +15515,10 @@
         <v>0.97</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1398</v>
+        <v>-0.1106</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.0542</v>
+        <v>-3.2074</v>
       </c>
     </row>
     <row r="306">
@@ -15555,10 +15555,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.602</v>
       </c>
       <c r="J306" t="n">
-        <v>-18.5194</v>
+        <v>-17.458</v>
       </c>
     </row>
     <row r="307">
@@ -15595,10 +15595,10 @@
         <v>1.54</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9338</v>
+        <v>0.8893</v>
       </c>
       <c r="J307" t="n">
-        <v>27.0802</v>
+        <v>25.7897</v>
       </c>
     </row>
     <row r="308">
@@ -15635,10 +15635,10 @@
         <v>1.06</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1633</v>
+        <v>0.1289</v>
       </c>
       <c r="J308" t="n">
-        <v>4.7357</v>
+        <v>3.7381</v>
       </c>
     </row>
     <row r="309">
@@ -15675,10 +15675,10 @@
         <v>0.96</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0772</v>
+        <v>-0.0619</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.2388</v>
+        <v>-1.7951</v>
       </c>
     </row>
     <row r="310">
@@ -15715,10 +15715,10 @@
         <v>0.92</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1287</v>
+        <v>-0.1096</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.7323</v>
+        <v>-3.1784</v>
       </c>
     </row>
     <row r="311">
@@ -15755,10 +15755,10 @@
         <v>0.82</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2377</v>
+        <v>-0.2176</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.8933</v>
+        <v>-6.3104</v>
       </c>
     </row>
     <row r="312">
@@ -15795,10 +15795,10 @@
         <v>1.45</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0221</v>
+        <v>1.0237</v>
       </c>
       <c r="J312" t="n">
-        <v>35.7735</v>
+        <v>35.8295</v>
       </c>
     </row>
     <row r="313">
@@ -15835,10 +15835,10 @@
         <v>1.4</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9376</v>
+        <v>0.9262</v>
       </c>
       <c r="J313" t="n">
-        <v>32.816</v>
+        <v>32.417</v>
       </c>
     </row>
     <row r="314">
@@ -15875,10 +15875,10 @@
         <v>1.3</v>
       </c>
       <c r="I314" t="n">
-        <v>0.7442</v>
+        <v>0.719</v>
       </c>
       <c r="J314" t="n">
-        <v>26.047</v>
+        <v>25.165</v>
       </c>
     </row>
     <row r="315">
@@ -15915,10 +15915,10 @@
         <v>1.15</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4258</v>
+        <v>0.393</v>
       </c>
       <c r="J315" t="n">
-        <v>14.903</v>
+        <v>13.755</v>
       </c>
     </row>
     <row r="316">
@@ -15955,10 +15955,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2143</v>
+        <v>-0.1807</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.5005</v>
+        <v>-6.3245</v>
       </c>
     </row>
     <row r="317">
@@ -15995,10 +15995,10 @@
         <v>0.99</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.0155</v>
+        <v>-0.011</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.5425</v>
+        <v>-0.385</v>
       </c>
     </row>
     <row r="318">
@@ -16035,10 +16035,10 @@
         <v>0.99</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0155</v>
+        <v>-0.011</v>
       </c>
       <c r="J318" t="n">
-        <v>-0.5425</v>
+        <v>-0.385</v>
       </c>
     </row>
     <row r="319">
@@ -16075,10 +16075,10 @@
         <v>0.93</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1035</v>
+        <v>-0.0887</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.6225</v>
+        <v>-3.1045</v>
       </c>
     </row>
     <row r="320">
@@ -16115,10 +16115,10 @@
         <v>0.78</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2612</v>
+        <v>-0.2419</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.141999999999999</v>
+        <v>-8.4665</v>
       </c>
     </row>
     <row r="321">
@@ -16155,10 +16155,10 @@
         <v>0.74</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2994</v>
+        <v>-0.2814</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.479</v>
+        <v>-9.849</v>
       </c>
     </row>
     <row r="322">
@@ -16195,10 +16195,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2866</v>
+        <v>0.237</v>
       </c>
       <c r="J322" t="n">
-        <v>7.165</v>
+        <v>5.925</v>
       </c>
     </row>
     <row r="323">
@@ -16235,10 +16235,10 @@
         <v>1.01</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0531</v>
+        <v>0.0358</v>
       </c>
       <c r="J323" t="n">
-        <v>1.3275</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="324">
@@ -16275,10 +16275,10 @@
         <v>0.89</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1525</v>
+        <v>-0.1335</v>
       </c>
       <c r="J324" t="n">
-        <v>-3.8125</v>
+        <v>-3.3375</v>
       </c>
     </row>
     <row r="325">
@@ -16315,10 +16315,10 @@
         <v>0.86</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1848</v>
+        <v>-0.1649</v>
       </c>
       <c r="J325" t="n">
-        <v>-4.62</v>
+        <v>-4.1225</v>
       </c>
     </row>
     <row r="326">
@@ -16355,10 +16355,10 @@
         <v>0.79</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2559</v>
+        <v>-0.2362</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.3975</v>
+        <v>-5.905</v>
       </c>
     </row>
     <row r="327">
@@ -16395,10 +16395,10 @@
         <v>1.66</v>
       </c>
       <c r="I327" t="n">
-        <v>1.3027</v>
+        <v>1.3223</v>
       </c>
       <c r="J327" t="n">
-        <v>32.5675</v>
+        <v>33.0575</v>
       </c>
     </row>
     <row r="328">
@@ -16435,10 +16435,10 @@
         <v>1.39</v>
       </c>
       <c r="I328" t="n">
-        <v>0.9164</v>
+        <v>0.9031</v>
       </c>
       <c r="J328" t="n">
-        <v>22.91</v>
+        <v>22.5775</v>
       </c>
     </row>
     <row r="329">
@@ -16475,10 +16475,10 @@
         <v>1.32</v>
       </c>
       <c r="I329" t="n">
-        <v>0.7816</v>
+        <v>0.759</v>
       </c>
       <c r="J329" t="n">
-        <v>19.54</v>
+        <v>18.975</v>
       </c>
     </row>
     <row r="330">
@@ -16515,10 +16515,10 @@
         <v>1.03</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0929</v>
+        <v>0.0723</v>
       </c>
       <c r="J330" t="n">
-        <v>2.3225</v>
+        <v>1.8075</v>
       </c>
     </row>
     <row r="331">
@@ -16555,10 +16555,10 @@
         <v>0.93</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3084</v>
+        <v>-0.2703</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.71</v>
+        <v>-6.7575</v>
       </c>
     </row>
     <row r="332">
@@ -16595,10 +16595,10 @@
         <v>1.35</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8562</v>
       </c>
       <c r="J332" t="n">
-        <v>31.554</v>
+        <v>30.8232</v>
       </c>
     </row>
     <row r="333">
@@ -16635,10 +16635,10 @@
         <v>1.29</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7533</v>
+        <v>0.7235</v>
       </c>
       <c r="J333" t="n">
-        <v>27.1188</v>
+        <v>26.046</v>
       </c>
     </row>
     <row r="334">
@@ -16675,10 +16675,10 @@
         <v>1.04</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1536</v>
+        <v>0.1279</v>
       </c>
       <c r="J334" t="n">
-        <v>5.5296</v>
+        <v>4.6044</v>
       </c>
     </row>
     <row r="335">
@@ -16715,10 +16715,10 @@
         <v>1.01</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0426</v>
+        <v>0.0317</v>
       </c>
       <c r="J335" t="n">
-        <v>1.5336</v>
+        <v>1.1412</v>
       </c>
     </row>
     <row r="336">
@@ -16755,10 +16755,10 @@
         <v>0.85</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4905</v>
+        <v>-0.4489</v>
       </c>
       <c r="J336" t="n">
-        <v>-17.658</v>
+        <v>-16.1604</v>
       </c>
     </row>
     <row r="337">
@@ -16795,10 +16795,10 @@
         <v>1.6</v>
       </c>
       <c r="I337" t="n">
-        <v>1.0097</v>
+        <v>0.9788</v>
       </c>
       <c r="J337" t="n">
-        <v>36.3492</v>
+        <v>35.2368</v>
       </c>
     </row>
     <row r="338">
@@ -16835,10 +16835,10 @@
         <v>1.1</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2433</v>
+        <v>0.1991</v>
       </c>
       <c r="J338" t="n">
-        <v>8.758800000000001</v>
+        <v>7.1676</v>
       </c>
     </row>
     <row r="339">
@@ -16875,10 +16875,10 @@
         <v>1.04</v>
       </c>
       <c r="I339" t="n">
-        <v>0.1189</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J339" t="n">
-        <v>4.2804</v>
+        <v>3.2868</v>
       </c>
     </row>
     <row r="340">
@@ -16915,10 +16915,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2377</v>
+        <v>-0.2176</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.5572</v>
+        <v>-7.8336</v>
       </c>
     </row>
     <row r="341">
@@ -16955,10 +16955,10 @@
         <v>0.74</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3156</v>
+        <v>-0.2991</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.3616</v>
+        <v>-10.7676</v>
       </c>
     </row>
     <row r="342">
@@ -16995,10 +16995,10 @@
         <v>1.12</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3815</v>
+        <v>0.3426</v>
       </c>
       <c r="J342" t="n">
-        <v>7.2485</v>
+        <v>6.5094</v>
       </c>
     </row>
     <row r="343">
@@ -17035,10 +17035,10 @@
         <v>0.74</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.2846</v>
+        <v>-0.2695</v>
       </c>
       <c r="J343" t="n">
-        <v>-5.4074</v>
+        <v>-5.1205</v>
       </c>
     </row>
     <row r="344">
@@ -17075,10 +17075,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.329</v>
+        <v>-0.3144</v>
       </c>
       <c r="J344" t="n">
-        <v>-6.251</v>
+        <v>-5.9736</v>
       </c>
     </row>
     <row r="345">
@@ -17115,10 +17115,10 @@
         <v>0.63</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3828</v>
+        <v>-0.3705</v>
       </c>
       <c r="J345" t="n">
-        <v>-7.2732</v>
+        <v>-7.0395</v>
       </c>
     </row>
     <row r="346">
@@ -17155,10 +17155,10 @@
         <v>0.47</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5239</v>
+        <v>-0.5254</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.9541</v>
+        <v>-9.9826</v>
       </c>
     </row>
     <row r="347">
@@ -17195,10 +17195,10 @@
         <v>1.61</v>
       </c>
       <c r="I347" t="n">
-        <v>1.2147</v>
+        <v>1.2313</v>
       </c>
       <c r="J347" t="n">
-        <v>23.0793</v>
+        <v>23.3947</v>
       </c>
     </row>
     <row r="348">
@@ -17235,10 +17235,10 @@
         <v>1.57</v>
       </c>
       <c r="I348" t="n">
-        <v>1.1635</v>
+        <v>1.1788</v>
       </c>
       <c r="J348" t="n">
-        <v>22.1065</v>
+        <v>22.3972</v>
       </c>
     </row>
     <row r="349">
@@ -17275,10 +17275,10 @@
         <v>1.48</v>
       </c>
       <c r="I349" t="n">
-        <v>1.0448</v>
+        <v>1.0541</v>
       </c>
       <c r="J349" t="n">
-        <v>19.8512</v>
+        <v>20.0279</v>
       </c>
     </row>
     <row r="350">
@@ -17315,10 +17315,10 @@
         <v>1.3</v>
       </c>
       <c r="I350" t="n">
-        <v>0.7284</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="J350" t="n">
-        <v>13.8396</v>
+        <v>13.4748</v>
       </c>
     </row>
     <row r="351">
@@ -17355,10 +17355,10 @@
         <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.0648</v>
+        <v>-0.0622</v>
       </c>
       <c r="J351" t="n">
-        <v>-1.2312</v>
+        <v>-1.1818</v>
       </c>
     </row>
     <row r="352">
@@ -17395,10 +17395,10 @@
         <v>1.41</v>
       </c>
       <c r="I352" t="n">
-        <v>0.7825</v>
+        <v>0.7328</v>
       </c>
       <c r="J352" t="n">
-        <v>23.475</v>
+        <v>21.984</v>
       </c>
     </row>
     <row r="353">
@@ -17435,10 +17435,10 @@
         <v>1.06</v>
       </c>
       <c r="I353" t="n">
-        <v>0.1782</v>
+        <v>0.1393</v>
       </c>
       <c r="J353" t="n">
-        <v>5.346</v>
+        <v>4.179</v>
       </c>
     </row>
     <row r="354">
@@ -17475,10 +17475,10 @@
         <v>0.91</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1316</v>
+        <v>-0.1133</v>
       </c>
       <c r="J354" t="n">
-        <v>-3.948</v>
+        <v>-3.399</v>
       </c>
     </row>
     <row r="355">
@@ -17515,10 +17515,10 @@
         <v>0.73</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3156</v>
+        <v>-0.2983</v>
       </c>
       <c r="J355" t="n">
-        <v>-9.468</v>
+        <v>-8.949</v>
       </c>
     </row>
     <row r="356">
@@ -17555,10 +17555,10 @@
         <v>0.66</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3799</v>
+        <v>-0.3674</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.397</v>
+        <v>-11.022</v>
       </c>
     </row>
     <row r="357">
@@ -17595,10 +17595,10 @@
         <v>1.5</v>
       </c>
       <c r="I357" t="n">
-        <v>1.1073</v>
+        <v>1.1189</v>
       </c>
       <c r="J357" t="n">
-        <v>33.219</v>
+        <v>33.567</v>
       </c>
     </row>
     <row r="358">
@@ -17635,10 +17635,10 @@
         <v>1.33</v>
       </c>
       <c r="I358" t="n">
-        <v>0.8162</v>
+        <v>0.7924</v>
       </c>
       <c r="J358" t="n">
-        <v>24.486</v>
+        <v>23.772</v>
       </c>
     </row>
     <row r="359">
@@ -17675,10 +17675,10 @@
         <v>1.18</v>
       </c>
       <c r="I359" t="n">
-        <v>0.5034</v>
+        <v>0.4681</v>
       </c>
       <c r="J359" t="n">
-        <v>15.102</v>
+        <v>14.043</v>
       </c>
     </row>
     <row r="360">
@@ -17715,10 +17715,10 @@
         <v>1.03</v>
       </c>
       <c r="I360" t="n">
-        <v>0.1066</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J360" t="n">
-        <v>3.198</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="361">
@@ -17755,10 +17755,10 @@
         <v>0.89</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.404</v>
+        <v>-0.3627</v>
       </c>
       <c r="J361" t="n">
-        <v>-12.12</v>
+        <v>-10.881</v>
       </c>
     </row>
     <row r="362">
@@ -17795,10 +17795,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2669</v>
+        <v>1.2847</v>
       </c>
       <c r="J362" t="n">
-        <v>29.1387</v>
+        <v>29.5481</v>
       </c>
     </row>
     <row r="363">
@@ -17835,10 +17835,10 @@
         <v>1.55</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1611</v>
+        <v>1.1746</v>
       </c>
       <c r="J363" t="n">
-        <v>26.7053</v>
+        <v>27.0158</v>
       </c>
     </row>
     <row r="364">
@@ -17875,10 +17875,10 @@
         <v>1.39</v>
       </c>
       <c r="I364" t="n">
-        <v>0.9191</v>
+        <v>0.9055</v>
       </c>
       <c r="J364" t="n">
-        <v>21.1393</v>
+        <v>20.8265</v>
       </c>
     </row>
     <row r="365">
@@ -17915,10 +17915,10 @@
         <v>0.91</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3621</v>
+        <v>-0.3225</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.3283</v>
+        <v>-7.4175</v>
       </c>
     </row>
     <row r="366">
@@ -17955,10 +17955,10 @@
         <v>0.78</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.6791</v>
+        <v>-0.6503</v>
       </c>
       <c r="J366" t="n">
-        <v>-15.6193</v>
+        <v>-14.9569</v>
       </c>
     </row>
     <row r="367">
@@ -17995,10 +17995,10 @@
         <v>0.99</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.0023</v>
+        <v>0.0039</v>
       </c>
       <c r="J367" t="n">
-        <v>-0.0529</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="368">
@@ -18035,10 +18035,10 @@
         <v>0.96</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.052</v>
+        <v>-0.0412</v>
       </c>
       <c r="J368" t="n">
-        <v>-1.196</v>
+        <v>-0.9476</v>
       </c>
     </row>
     <row r="369">
@@ -18075,10 +18075,10 @@
         <v>0.95</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0543</v>
       </c>
       <c r="J369" t="n">
-        <v>-1.5226</v>
+        <v>-1.2489</v>
       </c>
     </row>
     <row r="370">
@@ -18115,10 +18115,10 @@
         <v>0.58</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4356</v>
+        <v>-0.4274</v>
       </c>
       <c r="J370" t="n">
-        <v>-10.0188</v>
+        <v>-9.8302</v>
       </c>
     </row>
     <row r="371">
@@ -18155,10 +18155,10 @@
         <v>0.52</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4882</v>
+        <v>-0.4859</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.2286</v>
+        <v>-11.1757</v>
       </c>
     </row>
     <row r="372">
@@ -18195,10 +18195,10 @@
         <v>1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>0.6473</v>
+        <v>0.5918</v>
       </c>
       <c r="J372" t="n">
-        <v>17.4771</v>
+        <v>15.9786</v>
       </c>
     </row>
     <row r="373">
@@ -18235,10 +18235,10 @@
         <v>1.12</v>
       </c>
       <c r="I373" t="n">
-        <v>0.3035</v>
+        <v>0.2527</v>
       </c>
       <c r="J373" t="n">
-        <v>8.1945</v>
+        <v>6.8229</v>
       </c>
     </row>
     <row r="374">
@@ -18275,10 +18275,10 @@
         <v>0.88</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1642</v>
+        <v>-0.1447</v>
       </c>
       <c r="J374" t="n">
-        <v>-4.4334</v>
+        <v>-3.9069</v>
       </c>
     </row>
     <row r="375">
@@ -18315,10 +18315,10 @@
         <v>0.88</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1642</v>
+        <v>-0.1447</v>
       </c>
       <c r="J375" t="n">
-        <v>-4.4334</v>
+        <v>-3.9069</v>
       </c>
     </row>
     <row r="376">
@@ -18355,10 +18355,10 @@
         <v>0.51</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.51</v>
+        <v>-0.5123</v>
       </c>
       <c r="J376" t="n">
-        <v>-13.77</v>
+        <v>-13.8321</v>
       </c>
     </row>
     <row r="377">
@@ -18395,10 +18395,10 @@
         <v>1.28</v>
       </c>
       <c r="I377" t="n">
-        <v>0.725</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J377" t="n">
-        <v>19.575</v>
+        <v>18.7407</v>
       </c>
     </row>
     <row r="378">
@@ -18435,10 +18435,10 @@
         <v>1.19</v>
       </c>
       <c r="I378" t="n">
-        <v>0.5313</v>
+        <v>0.4937</v>
       </c>
       <c r="J378" t="n">
-        <v>14.3451</v>
+        <v>13.3299</v>
       </c>
     </row>
     <row r="379">
@@ -18475,10 +18475,10 @@
         <v>1.13</v>
       </c>
       <c r="I379" t="n">
-        <v>0.3941</v>
+        <v>0.357</v>
       </c>
       <c r="J379" t="n">
-        <v>10.6407</v>
+        <v>9.638999999999999</v>
       </c>
     </row>
     <row r="380">
@@ -18515,10 +18515,10 @@
         <v>1.07</v>
       </c>
       <c r="I380" t="n">
-        <v>0.2389</v>
+        <v>0.2076</v>
       </c>
       <c r="J380" t="n">
-        <v>6.4503</v>
+        <v>5.6052</v>
       </c>
     </row>
     <row r="381">
@@ -18555,10 +18555,10 @@
         <v>1.02</v>
       </c>
       <c r="I381" t="n">
-        <v>0.0785</v>
+        <v>0.0617</v>
       </c>
       <c r="J381" t="n">
-        <v>2.1195</v>
+        <v>1.6659</v>
       </c>
     </row>
     <row r="382">
@@ -18595,10 +18595,10 @@
         <v>1.63</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2479</v>
+        <v>1.265</v>
       </c>
       <c r="J382" t="n">
-        <v>27.4538</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="383">
@@ -18635,10 +18635,10 @@
         <v>1.55</v>
       </c>
       <c r="I383" t="n">
-        <v>1.1443</v>
+        <v>1.1584</v>
       </c>
       <c r="J383" t="n">
-        <v>25.1746</v>
+        <v>25.4848</v>
       </c>
     </row>
     <row r="384">
@@ -18675,10 +18675,10 @@
         <v>1.3</v>
       </c>
       <c r="I384" t="n">
-        <v>0.7343</v>
+        <v>0.7135</v>
       </c>
       <c r="J384" t="n">
-        <v>16.1546</v>
+        <v>15.697</v>
       </c>
     </row>
     <row r="385">
@@ -18715,10 +18715,10 @@
         <v>1.16</v>
       </c>
       <c r="I385" t="n">
-        <v>0.4347</v>
+        <v>0.4035</v>
       </c>
       <c r="J385" t="n">
-        <v>9.5634</v>
+        <v>8.877000000000001</v>
       </c>
     </row>
     <row r="386">
@@ -18755,10 +18755,10 @@
         <v>1.09</v>
       </c>
       <c r="I386" t="n">
-        <v>0.26</v>
+        <v>0.2289</v>
       </c>
       <c r="J386" t="n">
-        <v>5.72</v>
+        <v>5.0358</v>
       </c>
     </row>
     <row r="387">
@@ -18795,10 +18795,10 @@
         <v>1.21</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5588</v>
+        <v>0.5239</v>
       </c>
       <c r="J387" t="n">
-        <v>12.2936</v>
+        <v>11.5258</v>
       </c>
     </row>
     <row r="388">
@@ -18835,10 +18835,10 @@
         <v>0.76</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.2657</v>
+        <v>-0.2506</v>
       </c>
       <c r="J388" t="n">
-        <v>-5.8454</v>
+        <v>-5.5132</v>
       </c>
     </row>
     <row r="389">
@@ -18875,10 +18875,10 @@
         <v>0.7</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.3196</v>
+        <v>-0.305</v>
       </c>
       <c r="J389" t="n">
-        <v>-7.0312</v>
+        <v>-6.71</v>
       </c>
     </row>
     <row r="390">
@@ -18915,10 +18915,10 @@
         <v>0.51</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4885</v>
+        <v>-0.4856</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.747</v>
+        <v>-10.6832</v>
       </c>
     </row>
     <row r="391">
@@ -18955,10 +18955,10 @@
         <v>0.45</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5407</v>
+        <v>-0.5446</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.8954</v>
+        <v>-11.9812</v>
       </c>
     </row>
     <row r="392">
@@ -18995,10 +18995,10 @@
         <v>1.52</v>
       </c>
       <c r="I392" t="n">
-        <v>1.122</v>
+        <v>1.1343</v>
       </c>
       <c r="J392" t="n">
-        <v>24.684</v>
+        <v>24.9546</v>
       </c>
     </row>
     <row r="393">
@@ -19035,10 +19035,10 @@
         <v>1.4</v>
       </c>
       <c r="I393" t="n">
-        <v>0.9388</v>
+        <v>0.9273</v>
       </c>
       <c r="J393" t="n">
-        <v>20.6536</v>
+        <v>20.4006</v>
       </c>
     </row>
     <row r="394">
@@ -19075,10 +19075,10 @@
         <v>1.3</v>
       </c>
       <c r="I394" t="n">
-        <v>0.7451</v>
+        <v>0.7197</v>
       </c>
       <c r="J394" t="n">
-        <v>16.3922</v>
+        <v>15.8334</v>
       </c>
     </row>
     <row r="395">
@@ -19115,10 +19115,10 @@
         <v>1.23</v>
       </c>
       <c r="I395" t="n">
-        <v>0.6041</v>
+        <v>0.5735</v>
       </c>
       <c r="J395" t="n">
-        <v>13.2902</v>
+        <v>12.617</v>
       </c>
     </row>
     <row r="396">
@@ -19155,10 +19155,10 @@
         <v>0.78</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.6782</v>
+        <v>-0.6491</v>
       </c>
       <c r="J396" t="n">
-        <v>-14.9204</v>
+        <v>-14.2802</v>
       </c>
     </row>
     <row r="397">
@@ -19195,10 +19195,10 @@
         <v>1.19</v>
       </c>
       <c r="I397" t="n">
-        <v>0.4756</v>
+        <v>0.4258</v>
       </c>
       <c r="J397" t="n">
-        <v>10.4632</v>
+        <v>9.367599999999999</v>
       </c>
     </row>
     <row r="398">
@@ -19235,10 +19235,10 @@
         <v>0.75</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.2828</v>
+        <v>-0.265</v>
       </c>
       <c r="J398" t="n">
-        <v>-6.2216</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="399">
@@ -19275,10 +19275,10 @@
         <v>0.72</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.3108</v>
+        <v>-0.2939</v>
       </c>
       <c r="J399" t="n">
-        <v>-6.8376</v>
+        <v>-6.4658</v>
       </c>
     </row>
     <row r="400">
@@ -19315,10 +19315,10 @@
         <v>0.72</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.3108</v>
+        <v>-0.2939</v>
       </c>
       <c r="J400" t="n">
-        <v>-6.8376</v>
+        <v>-6.4658</v>
       </c>
     </row>
     <row r="401">
@@ -19355,10 +19355,10 @@
         <v>0.7</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3293</v>
+        <v>-0.3131</v>
       </c>
       <c r="J401" t="n">
-        <v>-7.2446</v>
+        <v>-6.8882</v>
       </c>
     </row>
     <row r="402">
@@ -19395,10 +19395,10 @@
         <v>1.53</v>
       </c>
       <c r="I402" t="n">
-        <v>1.1599</v>
+        <v>1.1743</v>
       </c>
       <c r="J402" t="n">
-        <v>32.4772</v>
+        <v>32.8804</v>
       </c>
     </row>
     <row r="403">
@@ -19435,10 +19435,10 @@
         <v>1.22</v>
       </c>
       <c r="I403" t="n">
-        <v>0.5969</v>
+        <v>0.5608</v>
       </c>
       <c r="J403" t="n">
-        <v>16.7132</v>
+        <v>15.7024</v>
       </c>
     </row>
     <row r="404">
@@ -19475,10 +19475,10 @@
         <v>1.02</v>
       </c>
       <c r="I404" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="J404" t="n">
-        <v>2.1896</v>
+        <v>1.7192</v>
       </c>
     </row>
     <row r="405">
@@ -19515,10 +19515,10 @@
         <v>1</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.0229</v>
+        <v>-0.0176</v>
       </c>
       <c r="J405" t="n">
-        <v>-0.6412</v>
+        <v>-0.4928</v>
       </c>
     </row>
     <row r="406">
@@ -19555,10 +19555,10 @@
         <v>0.93</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2863</v>
+        <v>-0.2461</v>
       </c>
       <c r="J406" t="n">
-        <v>-8.016400000000001</v>
+        <v>-6.8908</v>
       </c>
     </row>
     <row r="407">
@@ -19595,10 +19595,10 @@
         <v>1.38</v>
       </c>
       <c r="I407" t="n">
-        <v>0.7119</v>
+        <v>0.6551</v>
       </c>
       <c r="J407" t="n">
-        <v>19.9332</v>
+        <v>18.3428</v>
       </c>
     </row>
     <row r="408">
@@ -19635,10 +19635,10 @@
         <v>1.23</v>
       </c>
       <c r="I408" t="n">
-        <v>0.4771</v>
+        <v>0.4183</v>
       </c>
       <c r="J408" t="n">
-        <v>13.3588</v>
+        <v>11.7124</v>
       </c>
     </row>
     <row r="409">
@@ -19675,10 +19675,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1014</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J409" t="n">
-        <v>-2.8392</v>
+        <v>-2.3548</v>
       </c>
     </row>
     <row r="410">
@@ -19715,10 +19715,10 @@
         <v>0.87</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1828</v>
+        <v>-0.1622</v>
       </c>
       <c r="J410" t="n">
-        <v>-5.1184</v>
+        <v>-4.5416</v>
       </c>
     </row>
     <row r="411">
@@ -19755,10 +19755,10 @@
         <v>0.73</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3225</v>
+        <v>-0.3061</v>
       </c>
       <c r="J411" t="n">
-        <v>-9.029999999999999</v>
+        <v>-8.5708</v>
       </c>
     </row>
     <row r="412">
@@ -19795,10 +19795,10 @@
         <v>1.73</v>
       </c>
       <c r="I412" t="n">
-        <v>1.131</v>
+        <v>1.1183</v>
       </c>
       <c r="J412" t="n">
-        <v>32.799</v>
+        <v>32.4307</v>
       </c>
     </row>
     <row r="413">
@@ -19835,10 +19835,10 @@
         <v>1.22</v>
       </c>
       <c r="I413" t="n">
-        <v>0.4453</v>
+        <v>0.3885</v>
       </c>
       <c r="J413" t="n">
-        <v>12.9137</v>
+        <v>11.2665</v>
       </c>
     </row>
     <row r="414">
@@ -19875,10 +19875,10 @@
         <v>1.1</v>
       </c>
       <c r="I414" t="n">
-        <v>0.2388</v>
+        <v>0.1969</v>
       </c>
       <c r="J414" t="n">
-        <v>6.9252</v>
+        <v>5.7101</v>
       </c>
     </row>
     <row r="415">
@@ -19915,10 +19915,10 @@
         <v>0.79</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.2717</v>
+        <v>-0.2532</v>
       </c>
       <c r="J415" t="n">
-        <v>-7.8793</v>
+        <v>-7.3428</v>
       </c>
     </row>
     <row r="416">
@@ -19955,10 +19955,10 @@
         <v>0.71</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.3475</v>
+        <v>-0.3338</v>
       </c>
       <c r="J416" t="n">
-        <v>-10.0775</v>
+        <v>-9.680199999999999</v>
       </c>
     </row>
     <row r="417">
@@ -19995,10 +19995,10 @@
         <v>1.31</v>
       </c>
       <c r="I417" t="n">
-        <v>0.806</v>
+        <v>0.7798</v>
       </c>
       <c r="J417" t="n">
-        <v>23.374</v>
+        <v>22.6142</v>
       </c>
     </row>
     <row r="418">
@@ -20035,10 +20035,10 @@
         <v>1.28</v>
       </c>
       <c r="I418" t="n">
-        <v>0.7429</v>
+        <v>0.712</v>
       </c>
       <c r="J418" t="n">
-        <v>21.5441</v>
+        <v>20.648</v>
       </c>
     </row>
     <row r="419">
@@ -20075,10 +20075,10 @@
         <v>1.1</v>
       </c>
       <c r="I419" t="n">
-        <v>0.3279</v>
+        <v>0.2891</v>
       </c>
       <c r="J419" t="n">
-        <v>9.5091</v>
+        <v>8.383900000000001</v>
       </c>
     </row>
     <row r="420">
@@ -20115,10 +20115,10 @@
         <v>0.93</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.273</v>
+        <v>-0.2329</v>
       </c>
       <c r="J420" t="n">
-        <v>-7.917</v>
+        <v>-6.7541</v>
       </c>
     </row>
     <row r="421">
@@ -20155,10 +20155,10 @@
         <v>0.73</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.7582</v>
+        <v>-0.7308</v>
       </c>
       <c r="J421" t="n">
-        <v>-21.9878</v>
+        <v>-21.1932</v>
       </c>
     </row>
     <row r="422">
@@ -20195,10 +20195,10 @@
         <v>1.28</v>
       </c>
       <c r="I422" t="n">
-        <v>0.7176</v>
+        <v>0.6875</v>
       </c>
       <c r="J422" t="n">
-        <v>17.94</v>
+        <v>17.1875</v>
       </c>
     </row>
     <row r="423">
@@ -20235,10 +20235,10 @@
         <v>1.23</v>
       </c>
       <c r="I423" t="n">
-        <v>0.6128</v>
+        <v>0.5785</v>
       </c>
       <c r="J423" t="n">
-        <v>15.32</v>
+        <v>14.4625</v>
       </c>
     </row>
     <row r="424">
@@ -20275,10 +20275,10 @@
         <v>1.15</v>
       </c>
       <c r="I424" t="n">
-        <v>0.4373</v>
+        <v>0.4014</v>
       </c>
       <c r="J424" t="n">
-        <v>10.9325</v>
+        <v>10.035</v>
       </c>
     </row>
     <row r="425">
@@ -20315,10 +20315,10 @@
         <v>1.12</v>
       </c>
       <c r="I425" t="n">
-        <v>0.3654</v>
+        <v>0.3305</v>
       </c>
       <c r="J425" t="n">
-        <v>9.135</v>
+        <v>8.262499999999999</v>
       </c>
     </row>
     <row r="426">
@@ -20355,10 +20355,10 @@
         <v>1.08</v>
       </c>
       <c r="I426" t="n">
-        <v>0.2613</v>
+        <v>0.2297</v>
       </c>
       <c r="J426" t="n">
-        <v>6.5325</v>
+        <v>5.7425</v>
       </c>
     </row>
     <row r="427">
@@ -20395,10 +20395,10 @@
         <v>1.36</v>
       </c>
       <c r="I427" t="n">
-        <v>0.7147</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="J427" t="n">
-        <v>17.8675</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="428">
@@ -20435,10 +20435,10 @@
         <v>0.99</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.0204</v>
+        <v>-0.0152</v>
       </c>
       <c r="J428" t="n">
-        <v>-0.51</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="429">
@@ -20475,10 +20475,10 @@
         <v>0.78</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2655</v>
+        <v>-0.246</v>
       </c>
       <c r="J429" t="n">
-        <v>-6.6375</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="430">
@@ -20515,10 +20515,10 @@
         <v>0.77</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.2752</v>
+        <v>-0.256</v>
       </c>
       <c r="J430" t="n">
-        <v>-6.88</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="431">
@@ -20555,10 +20555,10 @@
         <v>0.75</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.2944</v>
+        <v>-0.276</v>
       </c>
       <c r="J431" t="n">
-        <v>-7.36</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="432">
@@ -20595,10 +20595,10 @@
         <v>1.42</v>
       </c>
       <c r="I432" t="n">
-        <v>0.7691</v>
+        <v>0.7143</v>
       </c>
       <c r="J432" t="n">
-        <v>32.3022</v>
+        <v>30.0006</v>
       </c>
     </row>
     <row r="433">
@@ -20635,10 +20635,10 @@
         <v>1.09</v>
       </c>
       <c r="I433" t="n">
-        <v>0.2267</v>
+        <v>0.1837</v>
       </c>
       <c r="J433" t="n">
-        <v>9.5214</v>
+        <v>7.7154</v>
       </c>
     </row>
     <row r="434">
@@ -20675,10 +20675,10 @@
         <v>1.06</v>
       </c>
       <c r="I434" t="n">
-        <v>0.1651</v>
+        <v>0.1297</v>
       </c>
       <c r="J434" t="n">
-        <v>6.9342</v>
+        <v>5.4474</v>
       </c>
     </row>
     <row r="435">
@@ -20715,10 +20715,10 @@
         <v>1.01</v>
       </c>
       <c r="I435" t="n">
-        <v>0.0401</v>
+        <v>0.0279</v>
       </c>
       <c r="J435" t="n">
-        <v>1.6842</v>
+        <v>1.1718</v>
       </c>
     </row>
     <row r="436">
@@ -20755,10 +20755,10 @@
         <v>0.61</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.4315</v>
+        <v>-0.4251</v>
       </c>
       <c r="J436" t="n">
-        <v>-18.123</v>
+        <v>-17.8542</v>
       </c>
     </row>
     <row r="437">
@@ -20795,10 +20795,10 @@
         <v>1.38</v>
       </c>
       <c r="I437" t="n">
-        <v>0.946</v>
+        <v>0.9341</v>
       </c>
       <c r="J437" t="n">
-        <v>39.732</v>
+        <v>39.2322</v>
       </c>
     </row>
     <row r="438">
@@ -20835,10 +20835,10 @@
         <v>1.17</v>
       </c>
       <c r="I438" t="n">
-        <v>0.4976</v>
+        <v>0.457</v>
       </c>
       <c r="J438" t="n">
-        <v>20.8992</v>
+        <v>19.194</v>
       </c>
     </row>
     <row r="439">
@@ -20875,10 +20875,10 @@
         <v>1.16</v>
       </c>
       <c r="I439" t="n">
-        <v>0.4742</v>
+        <v>0.4334</v>
       </c>
       <c r="J439" t="n">
-        <v>19.9164</v>
+        <v>18.2028</v>
       </c>
     </row>
     <row r="440">
@@ -20915,10 +20915,10 @@
         <v>1.03</v>
       </c>
       <c r="I440" t="n">
-        <v>0.1254</v>
+        <v>0.102</v>
       </c>
       <c r="J440" t="n">
-        <v>5.2668</v>
+        <v>4.284</v>
       </c>
     </row>
     <row r="441">
@@ -20955,10 +20955,10 @@
         <v>0.64</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.9495</v>
+        <v>-0.9415</v>
       </c>
       <c r="J441" t="n">
-        <v>-39.879</v>
+        <v>-39.543</v>
       </c>
     </row>
     <row r="442">
@@ -20995,10 +20995,10 @@
         <v>1.32</v>
       </c>
       <c r="I442" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7844</v>
       </c>
       <c r="J442" t="n">
-        <v>21.87</v>
+        <v>21.1788</v>
       </c>
     </row>
     <row r="443">
@@ -21035,10 +21035,10 @@
         <v>1.22</v>
       </c>
       <c r="I443" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5627</v>
       </c>
       <c r="J443" t="n">
-        <v>16.1811</v>
+        <v>15.1929</v>
       </c>
     </row>
     <row r="444">
@@ -21075,10 +21075,10 @@
         <v>1.14</v>
       </c>
       <c r="I444" t="n">
-        <v>0.4184</v>
+        <v>0.3804</v>
       </c>
       <c r="J444" t="n">
-        <v>11.2968</v>
+        <v>10.2708</v>
       </c>
     </row>
     <row r="445">
@@ -21115,10 +21115,10 @@
         <v>1.07</v>
       </c>
       <c r="I445" t="n">
-        <v>0.2405</v>
+        <v>0.2088</v>
       </c>
       <c r="J445" t="n">
-        <v>6.4935</v>
+        <v>5.6376</v>
       </c>
     </row>
     <row r="446">
@@ -21155,10 +21155,10 @@
         <v>0.89</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.3934</v>
+        <v>-0.351</v>
       </c>
       <c r="J446" t="n">
-        <v>-10.6218</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="447">
@@ -21195,10 +21195,10 @@
         <v>1.16</v>
       </c>
       <c r="I447" t="n">
-        <v>0.3663</v>
+        <v>0.3115</v>
       </c>
       <c r="J447" t="n">
-        <v>9.8901</v>
+        <v>8.410500000000001</v>
       </c>
     </row>
     <row r="448">
@@ -21235,10 +21235,10 @@
         <v>1.02</v>
       </c>
       <c r="I448" t="n">
-        <v>0.0746</v>
+        <v>0.0531</v>
       </c>
       <c r="J448" t="n">
-        <v>2.0142</v>
+        <v>1.4337</v>
       </c>
     </row>
     <row r="449">
@@ -21275,10 +21275,10 @@
         <v>1.02</v>
       </c>
       <c r="I449" t="n">
-        <v>0.0746</v>
+        <v>0.0531</v>
       </c>
       <c r="J449" t="n">
-        <v>2.0142</v>
+        <v>1.4337</v>
       </c>
     </row>
     <row r="450">
@@ -21315,10 +21315,10 @@
         <v>0.96</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.0718</v>
+        <v>-0.0578</v>
       </c>
       <c r="J450" t="n">
-        <v>-1.9386</v>
+        <v>-1.5606</v>
       </c>
     </row>
     <row r="451">
@@ -21355,10 +21355,10 @@
         <v>0.79</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.2614</v>
+        <v>-0.2418</v>
       </c>
       <c r="J451" t="n">
-        <v>-7.0578</v>
+        <v>-6.5286</v>
       </c>
     </row>
   </sheetData>
